--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -31588,7 +31588,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-08-31T23:15:14+07:00</t>
+          <t>2026-09-17T09:37:41+07:00</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35625,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>2026-08-31T23:33:10+07:00</t>
+          <t>2026-09-17T09:43:14+07:00</t>
         </is>
       </c>
     </row>
@@ -38215,7 +38215,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>2026-08-31T23:42:53+07:00</t>
+          <t>2026-09-17T09:46:33+07:00</t>
         </is>
       </c>
     </row>
@@ -39669,7 +39669,7 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>2026-08-31T23:47:32+07:00</t>
+          <t>2026-09-17T09:48:13+07:00</t>
         </is>
       </c>
     </row>
@@ -40775,7 +40775,7 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>2026-08-31T23:53:52+07:00</t>
+          <t>2026-09-17T09:53:19+07:00</t>
         </is>
       </c>
     </row>
@@ -41583,7 +41583,7 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>2026-09-01T00:02:09+07:00</t>
+          <t>2026-09-17T09:59:43+07:00</t>
         </is>
       </c>
     </row>
@@ -41931,7 +41931,7 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>2026-09-01T00:02:19+07:00</t>
+          <t>2026-09-17T09:59:50+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30918,7 +30918,7 @@
         <v>4.068</v>
       </c>
       <c r="V4" t="n">
-        <v>8183.362999999996</v>
+        <v>8183.362999999999</v>
       </c>
       <c r="W4" t="n">
         <v>-7.633</v>
@@ -31007,7 +31007,7 @@
         <v>3.572</v>
       </c>
       <c r="V5" t="n">
-        <v>-2072.081999999995</v>
+        <v>-2072.081999999999</v>
       </c>
       <c r="W5" t="n">
         <v>-6.467</v>
@@ -31111,7 +31111,7 @@
         <v>4.395</v>
       </c>
       <c r="V6" t="n">
-        <v>-5551.592999999999</v>
+        <v>-5551.593000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0.38</v>
@@ -31408,7 +31408,7 @@
         <v>2.424</v>
       </c>
       <c r="V9" t="n">
-        <v>85041.65799999997</v>
+        <v>85041.658</v>
       </c>
       <c r="W9" t="n">
         <v>-9.567</v>
@@ -32303,12 +32303,98 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2856110.951</v>
+      </c>
+      <c r="F20" t="n">
+        <v>155906.31</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13945.584</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1976945.954</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2068679.098</v>
+      </c>
+      <c r="J20" t="n">
+        <v>104.64</v>
+      </c>
+      <c r="K20" t="n">
+        <v>419121.4939999999</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-197713.778</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-6.922</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-3.918</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-10.659</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2339610.113</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>861336.583</v>
+      </c>
+      <c r="R20" t="n">
+        <v>271.626</v>
+      </c>
+      <c r="S20" t="n">
+        <v>59.965</v>
+      </c>
+      <c r="T20" t="n">
+        <v>166.764</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-169700.807</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-17.588</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-11.033</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-5.942</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2718135.967</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2643816.65</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>102.811</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-936</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-6.712</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Nhap thu cong tu anh chup BCTC that (BID BCTC hop nhat GND Quy I 2025, OCR khong doc duoc)</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2026-08-31T16:51:48+07:00</t>
+          <t>2026-09-17T14:38:33+07:00</t>
         </is>
       </c>
     </row>
@@ -32624,7 +32710,7 @@
         <v>2.564</v>
       </c>
       <c r="V26" t="n">
-        <v>-2093.93</v>
+        <v>-2093.930000000001</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -33723,7 +33809,7 @@
         <v>584740.964</v>
       </c>
       <c r="L37" t="n">
-        <v>57219.16100000001</v>
+        <v>57219.161</v>
       </c>
       <c r="M37" t="n">
         <v>1.932</v>
@@ -34035,7 +34121,7 @@
         <v>2.439</v>
       </c>
       <c r="V40" t="n">
-        <v>-6843.675999999999</v>
+        <v>-6843.676</v>
       </c>
       <c r="W40" t="n">
         <v>-9.135999999999999</v>
@@ -34213,7 +34299,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="L42" t="n">
-        <v>2554.764000000001</v>
+        <v>2554.764</v>
       </c>
       <c r="M42" t="n">
         <v>0.946</v>
@@ -34710,7 +34796,7 @@
         <v>3.011</v>
       </c>
       <c r="V49" t="n">
-        <v>1097.082999999999</v>
+        <v>1097.083000000001</v>
       </c>
       <c r="W49" t="n">
         <v>3.244</v>
@@ -36365,7 +36451,7 @@
         <v>53049.641</v>
       </c>
       <c r="L68" t="n">
-        <v>-71627.23300000001</v>
+        <v>-71627.23299999999</v>
       </c>
       <c r="M68" t="n">
         <v>-22.759</v>
@@ -36707,7 +36793,7 @@
         <v>4.335</v>
       </c>
       <c r="V71" t="n">
-        <v>-36336.33499999999</v>
+        <v>-36336.335</v>
       </c>
       <c r="W71" t="n">
         <v>7.502</v>
@@ -36989,7 +37075,7 @@
         <v>3.04</v>
       </c>
       <c r="V74" t="n">
-        <v>1044.137999999999</v>
+        <v>1044.137999999998</v>
       </c>
       <c r="W74" t="n">
         <v>-0.302</v>
@@ -37093,7 +37179,7 @@
         <v>4.485</v>
       </c>
       <c r="V75" t="n">
-        <v>-7342.066000000003</v>
+        <v>-7342.066000000001</v>
       </c>
       <c r="W75" t="n">
         <v>1.12</v>
@@ -37880,7 +37966,7 @@
         <v>3.06</v>
       </c>
       <c r="V83" t="n">
-        <v>44447.072</v>
+        <v>44447.07199999999</v>
       </c>
       <c r="W83" t="n">
         <v>41.067</v>
@@ -38673,7 +38759,7 @@
         <v>6.429</v>
       </c>
       <c r="V95" t="n">
-        <v>-448.712</v>
+        <v>-448.7119999999998</v>
       </c>
       <c r="W95" t="n">
         <v>-8.398</v>
@@ -38955,7 +39041,7 @@
         <v>3.682</v>
       </c>
       <c r="V98" t="n">
-        <v>-8415.234000000002</v>
+        <v>-8415.234</v>
       </c>
       <c r="W98" t="n">
         <v>-5.98</v>
@@ -40770,12 +40856,98 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>859571.527</v>
+      </c>
+      <c r="F120" t="n">
+        <v>61476.611</v>
+      </c>
+      <c r="G120" t="n">
+        <v>6042.042</v>
+      </c>
+      <c r="H120" t="n">
+        <v>600788.965</v>
+      </c>
+      <c r="I120" t="n">
+        <v>604877.709</v>
+      </c>
+      <c r="J120" t="n">
+        <v>100.681</v>
+      </c>
+      <c r="K120" t="n">
+        <v>136075.405</v>
+      </c>
+      <c r="L120" t="n">
+        <v>-53926.931</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-6.274</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-10.42</v>
+      </c>
+      <c r="O120" t="n">
+        <v>-19.247</v>
+      </c>
+      <c r="P120" t="n">
+        <v>776960.677</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>281789.178</v>
+      </c>
+      <c r="R120" t="n">
+        <v>275.724</v>
+      </c>
+      <c r="S120" t="n">
+        <v>29.317</v>
+      </c>
+      <c r="T120" t="n">
+        <v>341.104</v>
+      </c>
+      <c r="U120" t="n">
+        <v>2.265</v>
+      </c>
+      <c r="V120" t="n">
+        <v>-38127.26599999999</v>
+      </c>
+      <c r="W120" t="n">
+        <v>1.911</v>
+      </c>
+      <c r="X120" t="n">
+        <v>27.897</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>-4.436</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>803932.3370000001</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>776334.534</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>103.555</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>659</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>10.907</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>1.072</v>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy I 2026, OCR khong doc duoc)</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>2026-09-17T09:53:19+07:00</t>
+          <t>2026-09-17T14:38:33+07:00</t>
         </is>
       </c>
     </row>
@@ -40792,12 +40964,98 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>892048.566</v>
+      </c>
+      <c r="F121" t="n">
+        <v>62807.249</v>
+      </c>
+      <c r="G121" t="n">
+        <v>6247.243</v>
+      </c>
+      <c r="H121" t="n">
+        <v>647939.224</v>
+      </c>
+      <c r="I121" t="n">
+        <v>608851.996</v>
+      </c>
+      <c r="J121" t="n">
+        <v>93.967</v>
+      </c>
+      <c r="K121" t="n">
+        <v>154058.217</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-32668.77299999999</v>
+      </c>
+      <c r="M121" t="n">
+        <v>-3.662</v>
+      </c>
+      <c r="N121" t="n">
+        <v>-5.884</v>
+      </c>
+      <c r="O121" t="n">
+        <v>-14.194</v>
+      </c>
+      <c r="P121" t="n">
+        <v>776523.792</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>280549.491</v>
+      </c>
+      <c r="R121" t="n">
+        <v>276.787</v>
+      </c>
+      <c r="S121" t="n">
+        <v>41.178</v>
+      </c>
+      <c r="T121" t="n">
+        <v>242.848</v>
+      </c>
+      <c r="U121" t="n">
+        <v>2.378</v>
+      </c>
+      <c r="V121" t="n">
+        <v>-7187.399999999994</v>
+      </c>
+      <c r="W121" t="n">
+        <v>2.313</v>
+      </c>
+      <c r="X121" t="n">
+        <v>29.993</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>-0.806</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>820020.6800000001</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>808189.617</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>101.464</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>923</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>14.775</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy II 2026, OCR khong doc duoc)</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>2026-09-01T10:10:24+07:00</t>
+          <t>2026-09-17T14:38:33+07:00</t>
         </is>
       </c>
     </row>
@@ -41166,7 +41424,7 @@
         <v>3.255</v>
       </c>
       <c r="V125" t="n">
-        <v>-95355.82799999998</v>
+        <v>-95355.82799999999</v>
       </c>
       <c r="W125" t="n">
         <v>-8.385</v>
@@ -41270,7 +41528,7 @@
         <v>3.105</v>
       </c>
       <c r="V126" t="n">
-        <v>31803.23300000001</v>
+        <v>31803.233</v>
       </c>
       <c r="W126" t="n">
         <v>4.369</v>
@@ -41374,7 +41632,7 @@
         <v>2.784</v>
       </c>
       <c r="V127" t="n">
-        <v>49624.19500000001</v>
+        <v>49624.19499999999</v>
       </c>
       <c r="W127" t="n">
         <v>9.231999999999999</v>
@@ -43376,7 +43634,7 @@
         <v>3.722</v>
       </c>
       <c r="V154" t="n">
-        <v>18205.90499999999</v>
+        <v>18205.905</v>
       </c>
       <c r="W154" t="n">
         <v>-11.997</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30918,7 +30918,7 @@
         <v>4.068</v>
       </c>
       <c r="V4" t="n">
-        <v>8183.362999999999</v>
+        <v>8183.362999999996</v>
       </c>
       <c r="W4" t="n">
         <v>-7.633</v>
@@ -31007,7 +31007,7 @@
         <v>3.572</v>
       </c>
       <c r="V5" t="n">
-        <v>-2072.081999999999</v>
+        <v>-2072.081999999995</v>
       </c>
       <c r="W5" t="n">
         <v>-6.467</v>
@@ -31111,7 +31111,7 @@
         <v>4.395</v>
       </c>
       <c r="V6" t="n">
-        <v>-5551.593000000001</v>
+        <v>-5551.592999999999</v>
       </c>
       <c r="W6" t="n">
         <v>0.38</v>
@@ -31408,7 +31408,7 @@
         <v>2.424</v>
       </c>
       <c r="V9" t="n">
-        <v>85041.658</v>
+        <v>85041.65799999997</v>
       </c>
       <c r="W9" t="n">
         <v>-9.567</v>
@@ -31561,12 +31561,103 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1025850.127</v>
+      </c>
+      <c r="F11" t="n">
+        <v>94519.719</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7093.272</v>
+      </c>
+      <c r="H11" t="n">
+        <v>585180.175</v>
+      </c>
+      <c r="I11" t="n">
+        <v>679152.623</v>
+      </c>
+      <c r="J11" t="n">
+        <v>116.059</v>
+      </c>
+      <c r="K11" t="n">
+        <v>175190.187</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-36148.089</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-3.524</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-3.551</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-3.553</v>
+      </c>
+      <c r="P11" t="n">
+        <v>39862.162</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>65.181</v>
+      </c>
+      <c r="R11" t="n">
+        <v>61156.107</v>
+      </c>
+      <c r="S11" t="n">
+        <v>206354.522</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.994</v>
+      </c>
+      <c r="V11" t="n">
+        <v>56064.00199999996</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-10.987</v>
+      </c>
+      <c r="X11" t="n">
+        <v>32.032</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.465</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>971913.916</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>906469.3540000001</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>107.22</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1290</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18.186</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-1/2026-03-07/no-name-1772854112.pdf</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2026-08-31T01:05:37+07:00</t>
+          <t>2026-09-17T14:57:20+07:00</t>
         </is>
       </c>
     </row>
@@ -32710,7 +32801,7 @@
         <v>2.564</v>
       </c>
       <c r="V26" t="n">
-        <v>-2093.930000000001</v>
+        <v>-2093.93</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -33809,7 +33900,7 @@
         <v>584740.964</v>
       </c>
       <c r="L37" t="n">
-        <v>57219.161</v>
+        <v>57219.16100000001</v>
       </c>
       <c r="M37" t="n">
         <v>1.932</v>
@@ -34121,7 +34212,7 @@
         <v>2.439</v>
       </c>
       <c r="V40" t="n">
-        <v>-6843.676</v>
+        <v>-6843.675999999999</v>
       </c>
       <c r="W40" t="n">
         <v>-9.135999999999999</v>
@@ -34299,7 +34390,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="L42" t="n">
-        <v>2554.764</v>
+        <v>2554.764000000001</v>
       </c>
       <c r="M42" t="n">
         <v>0.946</v>
@@ -34796,7 +34887,7 @@
         <v>3.011</v>
       </c>
       <c r="V49" t="n">
-        <v>1097.083000000001</v>
+        <v>1097.082999999999</v>
       </c>
       <c r="W49" t="n">
         <v>3.244</v>
@@ -36451,7 +36542,7 @@
         <v>53049.641</v>
       </c>
       <c r="L68" t="n">
-        <v>-71627.23299999999</v>
+        <v>-71627.23300000001</v>
       </c>
       <c r="M68" t="n">
         <v>-22.759</v>
@@ -36793,7 +36884,7 @@
         <v>4.335</v>
       </c>
       <c r="V71" t="n">
-        <v>-36336.335</v>
+        <v>-36336.33499999999</v>
       </c>
       <c r="W71" t="n">
         <v>7.502</v>
@@ -37075,7 +37166,7 @@
         <v>3.04</v>
       </c>
       <c r="V74" t="n">
-        <v>1044.137999999998</v>
+        <v>1044.137999999999</v>
       </c>
       <c r="W74" t="n">
         <v>-0.302</v>
@@ -37179,7 +37270,7 @@
         <v>4.485</v>
       </c>
       <c r="V75" t="n">
-        <v>-7342.066000000001</v>
+        <v>-7342.066000000003</v>
       </c>
       <c r="W75" t="n">
         <v>1.12</v>
@@ -37966,7 +38057,7 @@
         <v>3.06</v>
       </c>
       <c r="V83" t="n">
-        <v>44447.07199999999</v>
+        <v>44447.072</v>
       </c>
       <c r="W83" t="n">
         <v>41.067</v>
@@ -38759,7 +38850,7 @@
         <v>6.429</v>
       </c>
       <c r="V95" t="n">
-        <v>-448.7119999999998</v>
+        <v>-448.712</v>
       </c>
       <c r="W95" t="n">
         <v>-8.398</v>
@@ -39041,7 +39132,7 @@
         <v>3.682</v>
       </c>
       <c r="V98" t="n">
-        <v>-8415.234</v>
+        <v>-8415.234000000002</v>
       </c>
       <c r="W98" t="n">
         <v>-5.98</v>
@@ -41424,7 +41515,7 @@
         <v>3.255</v>
       </c>
       <c r="V125" t="n">
-        <v>-95355.82799999999</v>
+        <v>-95355.82799999998</v>
       </c>
       <c r="W125" t="n">
         <v>-8.385</v>
@@ -41528,7 +41619,7 @@
         <v>3.105</v>
       </c>
       <c r="V126" t="n">
-        <v>31803.233</v>
+        <v>31803.23300000001</v>
       </c>
       <c r="W126" t="n">
         <v>4.369</v>
@@ -41632,7 +41723,7 @@
         <v>2.784</v>
       </c>
       <c r="V127" t="n">
-        <v>49624.19499999999</v>
+        <v>49624.19500000001</v>
       </c>
       <c r="W127" t="n">
         <v>9.231999999999999</v>
@@ -43634,7 +43725,7 @@
         <v>3.722</v>
       </c>
       <c r="V154" t="n">
-        <v>18205.905</v>
+        <v>18205.90499999999</v>
       </c>
       <c r="W154" t="n">
         <v>-11.997</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -31674,12 +31674,94 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1030900.741</v>
+      </c>
+      <c r="F12" t="n">
+        <v>98751.052</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6989.162</v>
+      </c>
+      <c r="H12" t="n">
+        <v>569109.608</v>
+      </c>
+      <c r="I12" t="n">
+        <v>701211.785</v>
+      </c>
+      <c r="J12" t="n">
+        <v>123.212</v>
+      </c>
+      <c r="K12" t="n">
+        <v>156854.572</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-271.2610000000001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.026</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="P12" t="n">
+        <v>49924.416</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>51216.558</v>
+      </c>
+      <c r="R12" t="n">
+        <v>97.477</v>
+      </c>
+      <c r="S12" t="n">
+        <v>193.815</v>
+      </c>
+      <c r="T12" t="n">
+        <v>51.596</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.756</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260422_-_ACB_-_BCTC_Hop_nhat_Quy_1_nam_2026_1776932823.pdf</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2026-09-17T09:37:41+07:00</t>
+          <t>2026-09-17T15:01:42+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -32584,12 +32584,88 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2991644.165</v>
+      </c>
+      <c r="F21" t="n">
+        <v>162737.31</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14991.731</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2074787.517</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2141443.805</v>
+      </c>
+      <c r="J21" t="n">
+        <v>103.213</v>
+      </c>
+      <c r="K21" t="n">
+        <v>486478.838</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-677107.5850000001</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-25.843</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-8.513999999999999</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-22.633</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>569385.233</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1301394.451</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>43.752</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-4094</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-27.308</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-2.516</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BID_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025143111.pdf</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2026-08-31T11:50:13+07:00</t>
+          <t>2026-09-17T15:06:22+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -38462,7 +38462,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>2026-08-31T16:58:48+07:00</t>
+          <t>2026-09-17T15:23:31+07:00</t>
         </is>
       </c>
     </row>
@@ -39834,7 +39834,7 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>2026-08-31T17:00:11+07:00</t>
+          <t>2026-09-17T15:24:51+07:00</t>
         </is>
       </c>
     </row>
@@ -41930,12 +41930,103 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>388891.15</v>
+      </c>
+      <c r="F128" t="n">
+        <v>39491.596</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3383.618</v>
+      </c>
+      <c r="H128" t="n">
+        <v>233114.646</v>
+      </c>
+      <c r="I128" t="n">
+        <v>259070.461</v>
+      </c>
+      <c r="J128" t="n">
+        <v>111.134</v>
+      </c>
+      <c r="K128" t="n">
+        <v>53519.87700000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1173.397999999997</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="P128" t="n">
+        <v>29361.059</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>206.249</v>
+      </c>
+      <c r="R128" t="n">
+        <v>14235.734</v>
+      </c>
+      <c r="S128" t="n">
+        <v>19232.121</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U128" t="n">
+        <v>2.296</v>
+      </c>
+      <c r="V128" t="n">
+        <v>47597.061</v>
+      </c>
+      <c r="W128" t="n">
+        <v>12.611</v>
+      </c>
+      <c r="X128" t="n">
+        <v>12.468</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>12.239</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>62861.954</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>35233.365</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>178.416</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>461</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>13.624</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_Q1_2025_Hopnhat_23052025145349.pdf</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>2026-08-31T17:05:53+07:00</t>
+          <t>2026-09-17T15:27:28+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -38462,7 +38462,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>2026-09-17T15:23:31+07:00</t>
+          <t>2026-09-17T15:38:57+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30918,7 +30918,7 @@
         <v>4.068</v>
       </c>
       <c r="V4" t="n">
-        <v>8183.362999999996</v>
+        <v>8183.362999999999</v>
       </c>
       <c r="W4" t="n">
         <v>-7.633</v>
@@ -31007,7 +31007,7 @@
         <v>3.572</v>
       </c>
       <c r="V5" t="n">
-        <v>-2072.081999999995</v>
+        <v>-2072.081999999999</v>
       </c>
       <c r="W5" t="n">
         <v>-6.467</v>
@@ -31111,7 +31111,7 @@
         <v>4.395</v>
       </c>
       <c r="V6" t="n">
-        <v>-5551.592999999999</v>
+        <v>-5551.593000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0.38</v>
@@ -31408,7 +31408,7 @@
         <v>2.424</v>
       </c>
       <c r="V9" t="n">
-        <v>85041.65799999997</v>
+        <v>85041.658</v>
       </c>
       <c r="W9" t="n">
         <v>-9.567</v>
@@ -32959,7 +32959,7 @@
         <v>2.564</v>
       </c>
       <c r="V26" t="n">
-        <v>-2093.93</v>
+        <v>-2093.930000000001</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -34058,7 +34058,7 @@
         <v>584740.964</v>
       </c>
       <c r="L37" t="n">
-        <v>57219.16100000001</v>
+        <v>57219.161</v>
       </c>
       <c r="M37" t="n">
         <v>1.932</v>
@@ -34370,7 +34370,7 @@
         <v>2.439</v>
       </c>
       <c r="V40" t="n">
-        <v>-6843.675999999999</v>
+        <v>-6843.676</v>
       </c>
       <c r="W40" t="n">
         <v>-9.135999999999999</v>
@@ -34548,7 +34548,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="L42" t="n">
-        <v>2554.764000000001</v>
+        <v>2554.764</v>
       </c>
       <c r="M42" t="n">
         <v>0.946</v>
@@ -35045,7 +35045,7 @@
         <v>3.011</v>
       </c>
       <c r="V49" t="n">
-        <v>1097.082999999999</v>
+        <v>1097.083000000001</v>
       </c>
       <c r="W49" t="n">
         <v>3.244</v>
@@ -36700,7 +36700,7 @@
         <v>53049.641</v>
       </c>
       <c r="L68" t="n">
-        <v>-71627.23300000001</v>
+        <v>-71627.23299999999</v>
       </c>
       <c r="M68" t="n">
         <v>-22.759</v>
@@ -37042,7 +37042,7 @@
         <v>4.335</v>
       </c>
       <c r="V71" t="n">
-        <v>-36336.33499999999</v>
+        <v>-36336.335</v>
       </c>
       <c r="W71" t="n">
         <v>7.502</v>
@@ -37324,7 +37324,7 @@
         <v>3.04</v>
       </c>
       <c r="V74" t="n">
-        <v>1044.137999999999</v>
+        <v>1044.137999999998</v>
       </c>
       <c r="W74" t="n">
         <v>-0.302</v>
@@ -37428,7 +37428,7 @@
         <v>4.485</v>
       </c>
       <c r="V75" t="n">
-        <v>-7342.066000000003</v>
+        <v>-7342.066000000001</v>
       </c>
       <c r="W75" t="n">
         <v>1.12</v>
@@ -38215,7 +38215,7 @@
         <v>3.06</v>
       </c>
       <c r="V83" t="n">
-        <v>44447.072</v>
+        <v>44447.07199999999</v>
       </c>
       <c r="W83" t="n">
         <v>41.067</v>
@@ -38457,12 +38457,98 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>289066.935913466</v>
+      </c>
+      <c r="F86" t="n">
+        <v>32388.218496367</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2163.56288338</v>
+      </c>
+      <c r="H86" t="n">
+        <v>151153.873885092</v>
+      </c>
+      <c r="I86" t="n">
+        <v>172738.829352774</v>
+      </c>
+      <c r="J86" t="n">
+        <v>114.28</v>
+      </c>
+      <c r="K86" t="n">
+        <v>40416.050727173</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-40096.556</v>
+      </c>
+      <c r="M86" t="n">
+        <v>-13.871</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-19.78</v>
+      </c>
+      <c r="O86" t="n">
+        <v>-27.062</v>
+      </c>
+      <c r="P86" t="n">
+        <v>214942.078</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>154835.187</v>
+      </c>
+      <c r="R86" t="n">
+        <v>138.82</v>
+      </c>
+      <c r="S86" t="n">
+        <v>47.873</v>
+      </c>
+      <c r="T86" t="n">
+        <v>208.886</v>
+      </c>
+      <c r="U86" t="n">
+        <v>2.674</v>
+      </c>
+      <c r="V86" t="n">
+        <v>31866.49299999999</v>
+      </c>
+      <c r="W86" t="n">
+        <v>-11.425</v>
+      </c>
+      <c r="X86" t="n">
+        <v>-4.928</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>11.024</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>266228.092</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>247087.747</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>107.746</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>1.849</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>Nhap thu cong tu anh chup BCTC that (OCB thuyet minh BCTC hop nhat Quy 1 2025, OCR khong doc duoc - don vi VND thuc, da quy doi ve trieu dong)</t>
         </is>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>2026-09-17T15:38:57+07:00</t>
+          <t>2026-09-17T16:12:36+07:00</t>
         </is>
       </c>
     </row>
@@ -39008,7 +39094,7 @@
         <v>6.429</v>
       </c>
       <c r="V95" t="n">
-        <v>-448.712</v>
+        <v>-448.7119999999998</v>
       </c>
       <c r="W95" t="n">
         <v>-8.398</v>
@@ -39290,7 +39376,7 @@
         <v>3.682</v>
       </c>
       <c r="V98" t="n">
-        <v>-8415.234000000002</v>
+        <v>-8415.234</v>
       </c>
       <c r="W98" t="n">
         <v>-5.98</v>
@@ -41673,7 +41759,7 @@
         <v>3.255</v>
       </c>
       <c r="V125" t="n">
-        <v>-95355.82799999998</v>
+        <v>-95355.82799999999</v>
       </c>
       <c r="W125" t="n">
         <v>-8.385</v>
@@ -41777,7 +41863,7 @@
         <v>3.105</v>
       </c>
       <c r="V126" t="n">
-        <v>31803.23300000001</v>
+        <v>31803.233</v>
       </c>
       <c r="W126" t="n">
         <v>4.369</v>
@@ -41881,7 +41967,7 @@
         <v>2.784</v>
       </c>
       <c r="V127" t="n">
-        <v>49624.19500000001</v>
+        <v>49624.19499999999</v>
       </c>
       <c r="W127" t="n">
         <v>9.231999999999999</v>
@@ -41985,7 +42071,7 @@
         <v>2.296</v>
       </c>
       <c r="V128" t="n">
-        <v>47597.061</v>
+        <v>47597.06099999999</v>
       </c>
       <c r="W128" t="n">
         <v>12.611</v>
@@ -43974,7 +44060,7 @@
         <v>3.722</v>
       </c>
       <c r="V154" t="n">
-        <v>18205.90499999999</v>
+        <v>18205.905</v>
       </c>
       <c r="W154" t="n">
         <v>-11.997</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30918,7 +30918,7 @@
         <v>4.068</v>
       </c>
       <c r="V4" t="n">
-        <v>8183.362999999999</v>
+        <v>8183.362999999996</v>
       </c>
       <c r="W4" t="n">
         <v>-7.633</v>
@@ -31007,7 +31007,7 @@
         <v>3.572</v>
       </c>
       <c r="V5" t="n">
-        <v>-2072.081999999999</v>
+        <v>-2072.081999999995</v>
       </c>
       <c r="W5" t="n">
         <v>-6.467</v>
@@ -31111,7 +31111,7 @@
         <v>4.395</v>
       </c>
       <c r="V6" t="n">
-        <v>-5551.593000000001</v>
+        <v>-5551.592999999999</v>
       </c>
       <c r="W6" t="n">
         <v>0.38</v>
@@ -31408,7 +31408,7 @@
         <v>2.424</v>
       </c>
       <c r="V9" t="n">
-        <v>85041.658</v>
+        <v>85041.65799999997</v>
       </c>
       <c r="W9" t="n">
         <v>-9.567</v>
@@ -32959,7 +32959,7 @@
         <v>2.564</v>
       </c>
       <c r="V26" t="n">
-        <v>-2093.930000000001</v>
+        <v>-2093.93</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -34058,7 +34058,7 @@
         <v>584740.964</v>
       </c>
       <c r="L37" t="n">
-        <v>57219.161</v>
+        <v>57219.16100000001</v>
       </c>
       <c r="M37" t="n">
         <v>1.932</v>
@@ -34370,7 +34370,7 @@
         <v>2.439</v>
       </c>
       <c r="V40" t="n">
-        <v>-6843.676</v>
+        <v>-6843.675999999999</v>
       </c>
       <c r="W40" t="n">
         <v>-9.135999999999999</v>
@@ -34548,7 +34548,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="L42" t="n">
-        <v>2554.764</v>
+        <v>2554.764000000001</v>
       </c>
       <c r="M42" t="n">
         <v>0.946</v>
@@ -35045,7 +35045,7 @@
         <v>3.011</v>
       </c>
       <c r="V49" t="n">
-        <v>1097.083000000001</v>
+        <v>1097.082999999999</v>
       </c>
       <c r="W49" t="n">
         <v>3.244</v>
@@ -36700,7 +36700,7 @@
         <v>53049.641</v>
       </c>
       <c r="L68" t="n">
-        <v>-71627.23299999999</v>
+        <v>-71627.23300000001</v>
       </c>
       <c r="M68" t="n">
         <v>-22.759</v>
@@ -37042,7 +37042,7 @@
         <v>4.335</v>
       </c>
       <c r="V71" t="n">
-        <v>-36336.335</v>
+        <v>-36336.33499999999</v>
       </c>
       <c r="W71" t="n">
         <v>7.502</v>
@@ -37324,7 +37324,7 @@
         <v>3.04</v>
       </c>
       <c r="V74" t="n">
-        <v>1044.137999999998</v>
+        <v>1044.137999999999</v>
       </c>
       <c r="W74" t="n">
         <v>-0.302</v>
@@ -37428,7 +37428,7 @@
         <v>4.485</v>
       </c>
       <c r="V75" t="n">
-        <v>-7342.066000000001</v>
+        <v>-7342.066000000003</v>
       </c>
       <c r="W75" t="n">
         <v>1.12</v>
@@ -38215,7 +38215,7 @@
         <v>3.06</v>
       </c>
       <c r="V83" t="n">
-        <v>44447.07199999999</v>
+        <v>44447.072</v>
       </c>
       <c r="W83" t="n">
         <v>41.067</v>
@@ -39094,7 +39094,7 @@
         <v>6.429</v>
       </c>
       <c r="V95" t="n">
-        <v>-448.7119999999998</v>
+        <v>-448.712</v>
       </c>
       <c r="W95" t="n">
         <v>-8.398</v>
@@ -39376,7 +39376,7 @@
         <v>3.682</v>
       </c>
       <c r="V98" t="n">
-        <v>-8415.234</v>
+        <v>-8415.234000000002</v>
       </c>
       <c r="W98" t="n">
         <v>-5.98</v>
@@ -39920,7 +39920,7 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>2026-09-17T15:24:51+07:00</t>
+          <t>2026-09-17T16:19:39+07:00</t>
         </is>
       </c>
     </row>
@@ -41759,7 +41759,7 @@
         <v>3.255</v>
       </c>
       <c r="V125" t="n">
-        <v>-95355.82799999999</v>
+        <v>-95355.82799999998</v>
       </c>
       <c r="W125" t="n">
         <v>-8.385</v>
@@ -41863,7 +41863,7 @@
         <v>3.105</v>
       </c>
       <c r="V126" t="n">
-        <v>31803.233</v>
+        <v>31803.23300000001</v>
       </c>
       <c r="W126" t="n">
         <v>4.369</v>
@@ -41967,7 +41967,7 @@
         <v>2.784</v>
       </c>
       <c r="V127" t="n">
-        <v>49624.19499999999</v>
+        <v>49624.19500000001</v>
       </c>
       <c r="W127" t="n">
         <v>9.231999999999999</v>
@@ -42071,7 +42071,7 @@
         <v>2.296</v>
       </c>
       <c r="V128" t="n">
-        <v>47597.06099999999</v>
+        <v>47597.061</v>
       </c>
       <c r="W128" t="n">
         <v>12.611</v>
@@ -44060,7 +44060,7 @@
         <v>3.722</v>
       </c>
       <c r="V154" t="n">
-        <v>18205.905</v>
+        <v>18205.90499999999</v>
       </c>
       <c r="W154" t="n">
         <v>-11.997</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -34835,12 +34835,103 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>784096.287</v>
+      </c>
+      <c r="F45" t="n">
+        <v>64626.363</v>
+      </c>
+      <c r="G45" t="n">
+        <v>9819.157999999999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>478700.229</v>
+      </c>
+      <c r="I45" t="n">
+        <v>502451.955</v>
+      </c>
+      <c r="J45" t="n">
+        <v>104.962</v>
+      </c>
+      <c r="K45" t="n">
+        <v>145778.24</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1318.71</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="P45" t="n">
+        <v>348514.834</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>113472.208</v>
+      </c>
+      <c r="R45" t="n">
+        <v>307.137</v>
+      </c>
+      <c r="S45" t="n">
+        <v>156.953</v>
+      </c>
+      <c r="T45" t="n">
+        <v>63.713</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.045</v>
+      </c>
+      <c r="V45" t="n">
+        <v>172001.015</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.299</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>21.936</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1435902.857</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1263818.771</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>113.616</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>871</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/HDB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025151254.pdf</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>2026-08-31T12:01:17+07:00</t>
+          <t>2026-09-17T16:27:10+07:00</t>
         </is>
       </c>
     </row>
@@ -35822,12 +35913,103 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>513612.864</v>
+      </c>
+      <c r="F57" t="n">
+        <v>40699.872</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3735.854</v>
+      </c>
+      <c r="H57" t="n">
+        <v>313174.113</v>
+      </c>
+      <c r="I57" t="n">
+        <v>363890.539</v>
+      </c>
+      <c r="J57" t="n">
+        <v>116.194</v>
+      </c>
+      <c r="K57" t="n">
+        <v>82889.34299999999</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3650.622</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="O57" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="P57" t="n">
+        <v>853290.689</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>57642.309</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1480.32</v>
+      </c>
+      <c r="S57" t="n">
+        <v>76.93300000000001</v>
+      </c>
+      <c r="T57" t="n">
+        <v>129.983</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="V57" t="n">
+        <v>-30007.58</v>
+      </c>
+      <c r="W57" t="n">
+        <v>3.512</v>
+      </c>
+      <c r="X57" t="n">
+        <v>7.024</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>-5.842</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>495717.531</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>345939.057</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>143.296</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>-59</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>-1.579</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>-0.145</v>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/LPB_Baocaotaichinh_6T_2025_Soatxet_06102025090900.pdf</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>2026-08-31T12:07:34+07:00</t>
+          <t>2026-09-17T16:28:03+07:00</t>
         </is>
       </c>
     </row>
@@ -38570,7 +38752,7 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>2026-08-31T12:23:24+07:00</t>
+          <t>2026-09-17T16:31:33+07:00</t>
         </is>
       </c>
     </row>
@@ -42129,12 +42311,103 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>428589.979</v>
+      </c>
+      <c r="F129" t="n">
+        <v>38229.908</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3151.325</v>
+      </c>
+      <c r="H129" t="n">
+        <v>246844.312</v>
+      </c>
+      <c r="I129" t="n">
+        <v>281188.723</v>
+      </c>
+      <c r="J129" t="n">
+        <v>113.913</v>
+      </c>
+      <c r="K129" t="n">
+        <v>71542.25599999999</v>
+      </c>
+      <c r="L129" t="n">
+        <v>-68400.776</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-15.959</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-17.579</v>
+      </c>
+      <c r="O129" t="n">
+        <v>-17.575</v>
+      </c>
+      <c r="P129" t="n">
+        <v>322684.431</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>164687.777</v>
+      </c>
+      <c r="R129" t="n">
+        <v>195.937</v>
+      </c>
+      <c r="S129" t="n">
+        <v>64.307</v>
+      </c>
+      <c r="T129" t="n">
+        <v>155.504</v>
+      </c>
+      <c r="U129" t="n">
+        <v>2.898</v>
+      </c>
+      <c r="V129" t="n">
+        <v>-23865.841</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>4.669</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>-5.568</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>846378.6310000001</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>898757.455</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>94.172</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>82</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>2.602</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025102458.pdf</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>2026-08-31T12:42:52+07:00</t>
+          <t>2026-09-17T16:32:56+07:00</t>
         </is>
       </c>
     </row>
@@ -42462,12 +42735,88 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>133951.803544459</v>
+      </c>
+      <c r="F135" t="n">
+        <v>9420.642668476999</v>
+      </c>
+      <c r="G135" t="n">
+        <v>542.378510292</v>
+      </c>
+      <c r="H135" t="n">
+        <v>95784.767789663</v>
+      </c>
+      <c r="I135" t="n">
+        <v>86563.862420006</v>
+      </c>
+      <c r="J135" t="n">
+        <v>90.373</v>
+      </c>
+      <c r="K135" t="n">
+        <v>19972.595116502</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>2.085</v>
+      </c>
+      <c r="V135" t="n">
+        <v>-28908.298</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>-21.581</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>28914.298</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-126</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>-23.231</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>-1.337</v>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000007054673721340387ngn-hng-tmcp-vit-24072025-000000bo-co-ti-chnh-hp-nht-qu_1_0914.pdf</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>2026-08-31T12:46:28+07:00</t>
+          <t>2026-09-17T16:34:18+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30918,7 +30918,7 @@
         <v>4.068</v>
       </c>
       <c r="V4" t="n">
-        <v>8183.362999999996</v>
+        <v>8183.362999999999</v>
       </c>
       <c r="W4" t="n">
         <v>-7.633</v>
@@ -31007,7 +31007,7 @@
         <v>3.572</v>
       </c>
       <c r="V5" t="n">
-        <v>-2072.081999999995</v>
+        <v>-2072.081999999999</v>
       </c>
       <c r="W5" t="n">
         <v>-6.467</v>
@@ -31111,7 +31111,7 @@
         <v>4.395</v>
       </c>
       <c r="V6" t="n">
-        <v>-5551.592999999999</v>
+        <v>-5551.593000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0.38</v>
@@ -31408,7 +31408,7 @@
         <v>2.424</v>
       </c>
       <c r="V9" t="n">
-        <v>85041.65799999997</v>
+        <v>85041.658</v>
       </c>
       <c r="W9" t="n">
         <v>-9.567</v>
@@ -32959,7 +32959,7 @@
         <v>2.564</v>
       </c>
       <c r="V26" t="n">
-        <v>-2093.93</v>
+        <v>-2093.930000000001</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -34058,7 +34058,7 @@
         <v>584740.964</v>
       </c>
       <c r="L37" t="n">
-        <v>57219.16100000001</v>
+        <v>57219.161</v>
       </c>
       <c r="M37" t="n">
         <v>1.932</v>
@@ -34370,7 +34370,7 @@
         <v>2.439</v>
       </c>
       <c r="V40" t="n">
-        <v>-6843.675999999999</v>
+        <v>-6843.676</v>
       </c>
       <c r="W40" t="n">
         <v>-9.135999999999999</v>
@@ -34548,7 +34548,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="L42" t="n">
-        <v>2554.764000000001</v>
+        <v>2554.764</v>
       </c>
       <c r="M42" t="n">
         <v>0.946</v>
@@ -35136,7 +35136,7 @@
         <v>3.011</v>
       </c>
       <c r="V49" t="n">
-        <v>1097.082999999999</v>
+        <v>1097.083000000001</v>
       </c>
       <c r="W49" t="n">
         <v>3.244</v>
@@ -36882,7 +36882,7 @@
         <v>53049.641</v>
       </c>
       <c r="L68" t="n">
-        <v>-71627.23300000001</v>
+        <v>-71627.23299999999</v>
       </c>
       <c r="M68" t="n">
         <v>-22.759</v>
@@ -37224,7 +37224,7 @@
         <v>4.335</v>
       </c>
       <c r="V71" t="n">
-        <v>-36336.33499999999</v>
+        <v>-36336.335</v>
       </c>
       <c r="W71" t="n">
         <v>7.502</v>
@@ -37506,7 +37506,7 @@
         <v>3.04</v>
       </c>
       <c r="V74" t="n">
-        <v>1044.137999999999</v>
+        <v>1044.137999999998</v>
       </c>
       <c r="W74" t="n">
         <v>-0.302</v>
@@ -37610,7 +37610,7 @@
         <v>4.485</v>
       </c>
       <c r="V75" t="n">
-        <v>-7342.066000000003</v>
+        <v>-7342.066000000001</v>
       </c>
       <c r="W75" t="n">
         <v>1.12</v>
@@ -38397,7 +38397,7 @@
         <v>3.06</v>
       </c>
       <c r="V83" t="n">
-        <v>44447.072</v>
+        <v>44447.07199999999</v>
       </c>
       <c r="W83" t="n">
         <v>41.067</v>
@@ -38747,12 +38747,98 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>308899.421013687</v>
+      </c>
+      <c r="F87" t="n">
+        <v>33113.733211965</v>
+      </c>
+      <c r="G87" t="n">
+        <v>2179.122847119</v>
+      </c>
+      <c r="H87" t="n">
+        <v>153939.669388207</v>
+      </c>
+      <c r="I87" t="n">
+        <v>183717.021936619</v>
+      </c>
+      <c r="J87" t="n">
+        <v>119.344</v>
+      </c>
+      <c r="K87" t="n">
+        <v>52580.40211333201</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-54108.582</v>
+      </c>
+      <c r="M87" t="n">
+        <v>-17.517</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-21.187</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-22.834</v>
+      </c>
+      <c r="P87" t="n">
+        <v>224061.667</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>158073.753</v>
+      </c>
+      <c r="R87" t="n">
+        <v>141.745</v>
+      </c>
+      <c r="S87" t="n">
+        <v>53.67</v>
+      </c>
+      <c r="T87" t="n">
+        <v>186.325</v>
+      </c>
+      <c r="U87" t="n">
+        <v>3.416</v>
+      </c>
+      <c r="V87" t="n">
+        <v>36655.177</v>
+      </c>
+      <c r="W87" t="n">
+        <v>-14.516</v>
+      </c>
+      <c r="X87" t="n">
+        <v>-4.869</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>11.866</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>287379.692</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>270403.116</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>106.278</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>2.708</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>Nhap thu cong tu doc truc tiep BCTC that (OCB thuyet minh BCTC hop nhat Quy 2 2025, ban tieng Anh, don vi VND thuc da quy doi ve trieu dong, OCR khong doc duoc do bao cao tieng Anh)</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>2026-09-17T16:31:33+07:00</t>
+          <t>2026-09-17T16:58:29+07:00</t>
         </is>
       </c>
     </row>
@@ -39276,7 +39362,7 @@
         <v>6.429</v>
       </c>
       <c r="V95" t="n">
-        <v>-448.712</v>
+        <v>-448.7119999999998</v>
       </c>
       <c r="W95" t="n">
         <v>-8.398</v>
@@ -39558,7 +39644,7 @@
         <v>3.682</v>
       </c>
       <c r="V98" t="n">
-        <v>-8415.234000000002</v>
+        <v>-8415.234</v>
       </c>
       <c r="W98" t="n">
         <v>-5.98</v>
@@ -41941,7 +42027,7 @@
         <v>3.255</v>
       </c>
       <c r="V125" t="n">
-        <v>-95355.82799999998</v>
+        <v>-95355.82799999999</v>
       </c>
       <c r="W125" t="n">
         <v>-8.385</v>
@@ -42045,7 +42131,7 @@
         <v>3.105</v>
       </c>
       <c r="V126" t="n">
-        <v>31803.23300000001</v>
+        <v>31803.233</v>
       </c>
       <c r="W126" t="n">
         <v>4.369</v>
@@ -42149,7 +42235,7 @@
         <v>2.784</v>
       </c>
       <c r="V127" t="n">
-        <v>49624.19500000001</v>
+        <v>49624.19499999999</v>
       </c>
       <c r="W127" t="n">
         <v>9.231999999999999</v>
@@ -42253,7 +42339,7 @@
         <v>2.296</v>
       </c>
       <c r="V128" t="n">
-        <v>47597.061</v>
+        <v>47597.06099999999</v>
       </c>
       <c r="W128" t="n">
         <v>12.611</v>
@@ -44409,7 +44495,7 @@
         <v>3.722</v>
       </c>
       <c r="V154" t="n">
-        <v>18205.90499999999</v>
+        <v>18205.905</v>
       </c>
       <c r="W154" t="n">
         <v>-11.997</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30918,7 +30918,7 @@
         <v>4.068</v>
       </c>
       <c r="V4" t="n">
-        <v>8183.362999999999</v>
+        <v>8183.362999999996</v>
       </c>
       <c r="W4" t="n">
         <v>-7.633</v>
@@ -31007,7 +31007,7 @@
         <v>3.572</v>
       </c>
       <c r="V5" t="n">
-        <v>-2072.081999999999</v>
+        <v>-2072.081999999995</v>
       </c>
       <c r="W5" t="n">
         <v>-6.467</v>
@@ -31111,7 +31111,7 @@
         <v>4.395</v>
       </c>
       <c r="V6" t="n">
-        <v>-5551.593000000001</v>
+        <v>-5551.592999999999</v>
       </c>
       <c r="W6" t="n">
         <v>0.38</v>
@@ -31408,7 +31408,7 @@
         <v>2.424</v>
       </c>
       <c r="V9" t="n">
-        <v>85041.658</v>
+        <v>85041.65799999997</v>
       </c>
       <c r="W9" t="n">
         <v>-9.567</v>
@@ -32959,7 +32959,7 @@
         <v>2.564</v>
       </c>
       <c r="V26" t="n">
-        <v>-2093.930000000001</v>
+        <v>-2093.93</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -34058,7 +34058,7 @@
         <v>584740.964</v>
       </c>
       <c r="L37" t="n">
-        <v>57219.161</v>
+        <v>57219.16100000001</v>
       </c>
       <c r="M37" t="n">
         <v>1.932</v>
@@ -34370,7 +34370,7 @@
         <v>2.439</v>
       </c>
       <c r="V40" t="n">
-        <v>-6843.676</v>
+        <v>-6843.675999999999</v>
       </c>
       <c r="W40" t="n">
         <v>-9.135999999999999</v>
@@ -34548,7 +34548,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="L42" t="n">
-        <v>2554.764</v>
+        <v>2554.764000000001</v>
       </c>
       <c r="M42" t="n">
         <v>0.946</v>
@@ -35136,7 +35136,7 @@
         <v>3.011</v>
       </c>
       <c r="V49" t="n">
-        <v>1097.083000000001</v>
+        <v>1097.082999999999</v>
       </c>
       <c r="W49" t="n">
         <v>3.244</v>
@@ -36882,7 +36882,7 @@
         <v>53049.641</v>
       </c>
       <c r="L68" t="n">
-        <v>-71627.23299999999</v>
+        <v>-71627.23300000001</v>
       </c>
       <c r="M68" t="n">
         <v>-22.759</v>
@@ -37224,7 +37224,7 @@
         <v>4.335</v>
       </c>
       <c r="V71" t="n">
-        <v>-36336.335</v>
+        <v>-36336.33499999999</v>
       </c>
       <c r="W71" t="n">
         <v>7.502</v>
@@ -37506,7 +37506,7 @@
         <v>3.04</v>
       </c>
       <c r="V74" t="n">
-        <v>1044.137999999998</v>
+        <v>1044.137999999999</v>
       </c>
       <c r="W74" t="n">
         <v>-0.302</v>
@@ -37610,7 +37610,7 @@
         <v>4.485</v>
       </c>
       <c r="V75" t="n">
-        <v>-7342.066000000001</v>
+        <v>-7342.066000000003</v>
       </c>
       <c r="W75" t="n">
         <v>1.12</v>
@@ -38397,7 +38397,7 @@
         <v>3.06</v>
       </c>
       <c r="V83" t="n">
-        <v>44447.07199999999</v>
+        <v>44447.072</v>
       </c>
       <c r="W83" t="n">
         <v>41.067</v>
@@ -39362,7 +39362,7 @@
         <v>6.429</v>
       </c>
       <c r="V95" t="n">
-        <v>-448.7119999999998</v>
+        <v>-448.712</v>
       </c>
       <c r="W95" t="n">
         <v>-8.398</v>
@@ -39644,7 +39644,7 @@
         <v>3.682</v>
       </c>
       <c r="V98" t="n">
-        <v>-8415.234</v>
+        <v>-8415.234000000002</v>
       </c>
       <c r="W98" t="n">
         <v>-5.98</v>
@@ -42027,7 +42027,7 @@
         <v>3.255</v>
       </c>
       <c r="V125" t="n">
-        <v>-95355.82799999999</v>
+        <v>-95355.82799999998</v>
       </c>
       <c r="W125" t="n">
         <v>-8.385</v>
@@ -42131,7 +42131,7 @@
         <v>3.105</v>
       </c>
       <c r="V126" t="n">
-        <v>31803.233</v>
+        <v>31803.23300000001</v>
       </c>
       <c r="W126" t="n">
         <v>4.369</v>
@@ -42235,7 +42235,7 @@
         <v>2.784</v>
       </c>
       <c r="V127" t="n">
-        <v>49624.19499999999</v>
+        <v>49624.19500000001</v>
       </c>
       <c r="W127" t="n">
         <v>9.231999999999999</v>
@@ -42339,7 +42339,7 @@
         <v>2.296</v>
       </c>
       <c r="V128" t="n">
-        <v>47597.06099999999</v>
+        <v>47597.061</v>
       </c>
       <c r="W128" t="n">
         <v>12.611</v>
@@ -44495,7 +44495,7 @@
         <v>3.722</v>
       </c>
       <c r="V154" t="n">
-        <v>18205.905</v>
+        <v>18205.90499999999</v>
       </c>
       <c r="W154" t="n">
         <v>-11.997</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -40188,7 +40188,7 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>2026-09-17T16:19:39+07:00</t>
+          <t>2026-09-17T17:21:29+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2026-08-31T15:15:38+07:00</t>
+          <t>2026-09-17T17:29:41+07:00</t>
         </is>
       </c>
     </row>
@@ -34948,12 +34948,79 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>781937.368</v>
+      </c>
+      <c r="F46" t="n">
+        <v>68407.053</v>
+      </c>
+      <c r="G46" t="n">
+        <v>7763.322</v>
+      </c>
+      <c r="H46" t="n">
+        <v>487862.978</v>
+      </c>
+      <c r="I46" t="n">
+        <v>482446.82</v>
+      </c>
+      <c r="J46" t="n">
+        <v>98.89</v>
+      </c>
+      <c r="K46" t="n">
+        <v>182275.996</v>
+      </c>
+      <c r="L46" t="n">
+        <v>32.341</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3.736</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_HDB_-_BCTC_hop_nhat_Quy_3_nam_2025_1761869961.pdf</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>2026-08-31T15:23:24+07:00</t>
+          <t>2026-09-17T17:31:12+07:00</t>
         </is>
       </c>
     </row>
@@ -38855,12 +38922,103 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>315161.711371066</v>
+      </c>
+      <c r="F88" t="n">
+        <v>32647.855006504</v>
+      </c>
+      <c r="G88" t="n">
+        <v>2424.219290094</v>
+      </c>
+      <c r="H88" t="n">
+        <v>155238.508114289</v>
+      </c>
+      <c r="I88" t="n">
+        <v>192730.756354787</v>
+      </c>
+      <c r="J88" t="n">
+        <v>124.151</v>
+      </c>
+      <c r="K88" t="n">
+        <v>55915.74639558799</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-122022.499097568</v>
+      </c>
+      <c r="M88" t="n">
+        <v>-38.717</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-51.884</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-51.884</v>
+      </c>
+      <c r="P88" t="n">
+        <v>163519.653</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>60858.551</v>
+      </c>
+      <c r="R88" t="n">
+        <v>268.688</v>
+      </c>
+      <c r="S88" t="n">
+        <v>95.196</v>
+      </c>
+      <c r="T88" t="n">
+        <v>105.046</v>
+      </c>
+      <c r="U88" t="n">
+        <v>3.602</v>
+      </c>
+      <c r="V88" t="n">
+        <v>-163515.422343776</v>
+      </c>
+      <c r="W88" t="n">
+        <v>-38.716</v>
+      </c>
+      <c r="X88" t="n">
+        <v>-51.883</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>-51.883</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>141033.646</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>230768.26</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>61.115</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>-1515</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>-62.494</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251028_-_OCB_-_BCTC_hop_nhat_Quy_3_2025_1761822426.pdf</t>
         </is>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>2026-08-31T15:37:44+07:00</t>
+          <t>2026-09-17T17:33:01+07:00</t>
         </is>
       </c>
     </row>
@@ -40314,7 +40472,7 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>2026-08-31T15:42:17+07:00</t>
+          <t>2026-09-17T17:34:13+07:00</t>
         </is>
       </c>
     </row>
@@ -42510,12 +42668,103 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>451893.195</v>
+      </c>
+      <c r="F130" t="n">
+        <v>39993.24</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3237.619</v>
+      </c>
+      <c r="H130" t="n">
+        <v>260245.786</v>
+      </c>
+      <c r="I130" t="n">
+        <v>292020.111</v>
+      </c>
+      <c r="J130" t="n">
+        <v>112.209</v>
+      </c>
+      <c r="K130" t="n">
+        <v>87563.264</v>
+      </c>
+      <c r="L130" t="n">
+        <v>-224607.003</v>
+      </c>
+      <c r="M130" t="n">
+        <v>-49.704</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-53.901</v>
+      </c>
+      <c r="O130" t="n">
+        <v>-36.315</v>
+      </c>
+      <c r="P130" t="n">
+        <v>411899.955</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>208233.938</v>
+      </c>
+      <c r="R130" t="n">
+        <v>197.806</v>
+      </c>
+      <c r="S130" t="n">
+        <v>217.528</v>
+      </c>
+      <c r="T130" t="n">
+        <v>45.971</v>
+      </c>
+      <c r="U130" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="V130" t="n">
+        <v>-263132.046</v>
+      </c>
+      <c r="W130" t="n">
+        <v>-2.247</v>
+      </c>
+      <c r="X130" t="n">
+        <v>-6.445</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>-58.229</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>909690.326</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>608057.379</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>149.606</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>-542</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>-16.741</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>-1.355</v>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_TPB_-_Bao_cao_tai_chinh_hop_nhat_Q3.2025_signed_1761832307.pdf</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>2026-08-31T15:53:04+07:00</t>
+          <t>2026-09-17T17:36:04+07:00</t>
         </is>
       </c>
     </row>
@@ -42924,7 +43173,7 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>2026-08-31T15:57:08+07:00</t>
+          <t>2026-09-17T17:39:50+07:00</t>
         </is>
       </c>
     </row>
@@ -43943,12 +44192,103 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>2378185.628</v>
+      </c>
+      <c r="F148" t="n">
+        <v>222791.545</v>
+      </c>
+      <c r="G148" t="n">
+        <v>14657.24</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1611966.698</v>
+      </c>
+      <c r="I148" t="n">
+        <v>1595933.982</v>
+      </c>
+      <c r="J148" t="n">
+        <v>99.005</v>
+      </c>
+      <c r="K148" t="n">
+        <v>567345.417</v>
+      </c>
+      <c r="L148" t="n">
+        <v>-505610.893</v>
+      </c>
+      <c r="M148" t="n">
+        <v>-21.26</v>
+      </c>
+      <c r="N148" t="n">
+        <v>-15.851</v>
+      </c>
+      <c r="O148" t="n">
+        <v>-15.224</v>
+      </c>
+      <c r="P148" t="n">
+        <v>2136177.852</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>633448.997</v>
+      </c>
+      <c r="R148" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="S148" t="n">
+        <v>37.415</v>
+      </c>
+      <c r="T148" t="n">
+        <v>267.269</v>
+      </c>
+      <c r="U148" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="V148" t="n">
+        <v>-50506.96400000001</v>
+      </c>
+      <c r="W148" t="n">
+        <v>-16.271</v>
+      </c>
+      <c r="X148" t="n">
+        <v>-5.369</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>-2.124</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>523906.365</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>318283.844</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>164.604</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>-656</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>-4.476</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>-0.294</v>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_VCB_-_CBTT_BCTC_Hop_nhat_Q3.2025_1761883208.pdf</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>2026-08-31T16:01:32+07:00</t>
+          <t>2026-09-17T17:41:27+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -32687,7 +32687,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2026-09-17T17:29:41+07:00</t>
+          <t>2026-09-17T18:09:51+07:00</t>
         </is>
       </c>
     </row>
@@ -40472,7 +40472,7 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>2026-09-17T17:34:13+07:00</t>
+          <t>2026-09-17T18:10:56+07:00</t>
         </is>
       </c>
     </row>
@@ -43173,7 +43173,7 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>2026-09-17T17:39:50+07:00</t>
+          <t>2026-09-17T18:14:21+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -30461,7 +30461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH157"/>
+  <dimension ref="A1:AH158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -32704,12 +32704,103 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3330825.72</v>
+      </c>
+      <c r="F23" t="n">
+        <v>173552.902</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19185.173</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2222991.628</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2338009.521</v>
+      </c>
+      <c r="J23" t="n">
+        <v>105.174</v>
+      </c>
+      <c r="K23" t="n">
+        <v>594058.388</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-221635.756</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-6.654</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-8.616</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-8.983000000000001</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3093315.934</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3729403.044</v>
+      </c>
+      <c r="R23" t="n">
+        <v>82.944</v>
+      </c>
+      <c r="S23" t="n">
+        <v>91.02800000000001</v>
+      </c>
+      <c r="T23" t="n">
+        <v>109.857</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-36751.99400000001</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-13.53</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.385</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>-1.103</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3119987.368</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>3088515.12</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>101.019</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>126</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-02/no-name-1775069592.pdf</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2026-08-31T01:08:21+07:00</t>
+          <t>2026-09-17T18:18:58+07:00</t>
         </is>
       </c>
     </row>
@@ -35037,12 +35128,103 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>931103.9449999999</v>
+      </c>
+      <c r="F47" t="n">
+        <v>78285.522</v>
+      </c>
+      <c r="G47" t="n">
+        <v>9755.610000000001</v>
+      </c>
+      <c r="H47" t="n">
+        <v>560714.282</v>
+      </c>
+      <c r="I47" t="n">
+        <v>539071.334</v>
+      </c>
+      <c r="J47" t="n">
+        <v>96.14</v>
+      </c>
+      <c r="K47" t="n">
+        <v>248295.966</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-19416.303</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-2.085</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4.621</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="P47" t="n">
+        <v>151609.858</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>57736.067</v>
+      </c>
+      <c r="R47" t="n">
+        <v>262.591</v>
+      </c>
+      <c r="S47" t="n">
+        <v>78.797</v>
+      </c>
+      <c r="T47" t="n">
+        <v>126.909</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4.428</v>
+      </c>
+      <c r="V47" t="n">
+        <v>68528.505</v>
+      </c>
+      <c r="W47" t="n">
+        <v>7.235</v>
+      </c>
+      <c r="X47" t="n">
+        <v>7.368</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>682745.395</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>370328.376</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>184.362</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>655</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>6.714</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.837</v>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_HDB_-_BCTC_kiem_toan_hop_nhat_nam_2025_giai_trinh_1775008453.pdf</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>2026-08-31T01:18:56+07:00</t>
+          <t>2026-09-17T18:20:09+07:00</t>
         </is>
       </c>
     </row>
@@ -36182,12 +36364,103 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>605584.514</v>
+      </c>
+      <c r="F59" t="n">
+        <v>47192.474</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4781.426</v>
+      </c>
+      <c r="H59" t="n">
+        <v>337583.366</v>
+      </c>
+      <c r="I59" t="n">
+        <v>386867.042</v>
+      </c>
+      <c r="J59" t="n">
+        <v>114.599</v>
+      </c>
+      <c r="K59" t="n">
+        <v>152821.187</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-42953.344</v>
+      </c>
+      <c r="M59" t="n">
+        <v>-7.093</v>
+      </c>
+      <c r="N59" t="n">
+        <v>-15.681</v>
+      </c>
+      <c r="O59" t="n">
+        <v>-15.167</v>
+      </c>
+      <c r="P59" t="n">
+        <v>99775.178</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>178380.419</v>
+      </c>
+      <c r="R59" t="n">
+        <v>55.934</v>
+      </c>
+      <c r="S59" t="n">
+        <v>47.843</v>
+      </c>
+      <c r="T59" t="n">
+        <v>209.019</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4.527</v>
+      </c>
+      <c r="V59" t="n">
+        <v>130259.201</v>
+      </c>
+      <c r="W59" t="n">
+        <v>8.071999999999999</v>
+      </c>
+      <c r="X59" t="n">
+        <v>8.073</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>416206.435</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>239381.648</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>173.867</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>854</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>17.861</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-01/no-name-1774985279.pdf</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>2026-08-31T01:22:06+07:00</t>
+          <t>2026-09-17T18:21:20+07:00</t>
         </is>
       </c>
     </row>
@@ -39030,17 +39303,108 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>322949.479567113</v>
+      </c>
+      <c r="F89" t="n">
+        <v>33924.677884591</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2481.941369042</v>
+      </c>
+      <c r="H89" t="n">
+        <v>150029.644383127</v>
+      </c>
+      <c r="I89" t="n">
+        <v>195190.887725518</v>
+      </c>
+      <c r="J89" t="n">
+        <v>130.102</v>
+      </c>
+      <c r="K89" t="n">
+        <v>57104.9273618</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-8354.105685278017</v>
+      </c>
+      <c r="M89" t="n">
+        <v>-2.587</v>
+      </c>
+      <c r="N89" t="n">
+        <v>17.191</v>
+      </c>
+      <c r="O89" t="n">
+        <v>26.228</v>
+      </c>
+      <c r="P89" t="n">
+        <v>164367.496</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>26356.318</v>
+      </c>
+      <c r="R89" t="n">
+        <v>623.636</v>
+      </c>
+      <c r="S89" t="n">
+        <v>420.106</v>
+      </c>
+      <c r="T89" t="n">
+        <v>23.804</v>
+      </c>
+      <c r="U89" t="n">
+        <v>3.806</v>
+      </c>
+      <c r="V89" t="n">
+        <v>149446.985380176</v>
+      </c>
+      <c r="W89" t="n">
+        <v>25.107</v>
+      </c>
+      <c r="X89" t="n">
+        <v>44.885</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>46.276</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>261998.749</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>127090.628</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>206.151</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>1430</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>57.616</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>4.215</v>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 4 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260130_-_OCB_-_BCTC_hop_nhat_Quy_4_2025_1770023477.pdf</t>
         </is>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>2026-08-31T01:30:30+07:00</t>
+          <t>2026-09-17T18:24:55+07:00</t>
         </is>
       </c>
     </row>
@@ -39052,7 +39416,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -39062,7 +39426,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>2026-09-17T09:46:33+07:00</t>
+          <t>2026-08-31T01:30:30+07:00</t>
         </is>
       </c>
     </row>
@@ -39074,111 +39438,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>351741.185154313</v>
-      </c>
-      <c r="F91" t="n">
-        <v>35821.888904798</v>
-      </c>
-      <c r="G91" t="n">
-        <v>2525.326480196</v>
-      </c>
-      <c r="H91" t="n">
-        <v>159695.164166116</v>
-      </c>
-      <c r="I91" t="n">
-        <v>215783.068010916</v>
-      </c>
-      <c r="J91" t="n">
-        <v>135.122</v>
-      </c>
-      <c r="K91" t="n">
-        <v>63274.816999975</v>
-      </c>
-      <c r="L91" t="n">
-        <v>-44991378216.177</v>
-      </c>
-      <c r="M91" t="n">
-        <v>-12791046.404</v>
-      </c>
-      <c r="N91" t="n">
-        <v>-17044829.992</v>
-      </c>
-      <c r="O91" t="n">
-        <v>-23724367.792</v>
-      </c>
-      <c r="P91" t="n">
-        <v>127669560843.488</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>183410632135.751</v>
-      </c>
-      <c r="R91" t="n">
-        <v>69.60899999999999</v>
-      </c>
-      <c r="S91" t="n">
-        <v>35.701</v>
-      </c>
-      <c r="T91" t="n">
-        <v>280.102</v>
-      </c>
-      <c r="U91" t="n">
-        <v>3.962</v>
-      </c>
-      <c r="V91" t="n">
-        <v>65372669436.32</v>
-      </c>
-      <c r="W91" t="n">
-        <v>4091.598</v>
-      </c>
-      <c r="X91" t="n">
-        <v>17789406.552</v>
-      </c>
-      <c r="Y91" t="n">
-        <v>18585446.401</v>
-      </c>
-      <c r="AC91" t="n">
-        <v>538956902</v>
-      </c>
-      <c r="AD91" t="n">
-        <v>21342068.292</v>
-      </c>
-      <c r="AE91" t="n">
-        <v>1504546.294</v>
-      </c>
-      <c r="AF91" t="inlineStr">
-        <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
-        </is>
-      </c>
-      <c r="AG91" t="inlineStr">
-        <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/OCB_202608142020OCB2020Bao20cao20tai20chinh20hop20nhat20ban20nien202026_20082026094036.pdf?v=1787193638360</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>2026-09-01T09:56:57+07:00</t>
+          <t>2026-09-17T09:46:33+07:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PGB</t>
+          <t>OCB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -39187,75 +39469,90 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>73551.58199999999</v>
+        <v>351741.185154313</v>
       </c>
       <c r="F92" t="n">
-        <v>5242.581</v>
+        <v>35821.888904798</v>
       </c>
       <c r="G92" t="n">
-        <v>458.27</v>
+        <v>2525.326480196</v>
       </c>
       <c r="H92" t="n">
-        <v>46717.488</v>
+        <v>159695.164166116</v>
       </c>
       <c r="I92" t="n">
-        <v>44869.685</v>
+        <v>215783.068010916</v>
       </c>
       <c r="J92" t="n">
-        <v>96.045</v>
+        <v>135.122</v>
       </c>
       <c r="K92" t="n">
-        <v>22839.31</v>
+        <v>63274.816999975</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>-44991378216.177</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>-12791046.404</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>-17044829.992</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>-23724367.792</v>
+      </c>
+      <c r="P92" t="n">
+        <v>127669560843.488</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>183410632135.751</v>
+      </c>
+      <c r="R92" t="n">
+        <v>69.60899999999999</v>
+      </c>
+      <c r="S92" t="n">
+        <v>35.701</v>
+      </c>
+      <c r="T92" t="n">
+        <v>280.102</v>
       </c>
       <c r="U92" t="n">
-        <v>4.889</v>
+        <v>3.962</v>
       </c>
       <c r="V92" t="n">
-        <v>4980.354</v>
+        <v>65372669436.32</v>
       </c>
       <c r="W92" t="n">
-        <v>0.002</v>
+        <v>4091.598</v>
       </c>
       <c r="X92" t="n">
-        <v>0.893</v>
+        <v>17789406.552</v>
       </c>
       <c r="Y92" t="n">
-        <v>6.771</v>
+        <v>18585446.401</v>
       </c>
       <c r="AC92" t="n">
-        <v>35</v>
+        <v>538956902</v>
       </c>
       <c r="AD92" t="n">
-        <v>7.637</v>
+        <v>21342068.292</v>
       </c>
       <c r="AE92" t="n">
-        <v>0.668</v>
+        <v>1504546.294</v>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-18/no-name-1744937049.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/OCB_202608142020OCB2020Bao20cao20tai20chinh20hop20nhat20ban20nien202026_20082026094036.pdf?v=1787193638360</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>2026-08-31T10:25:19+07:00</t>
+          <t>2026-09-01T09:56:57+07:00</t>
         </is>
       </c>
     </row>
@@ -39267,7 +39564,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -39276,90 +39573,75 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>78533.89999999999</v>
+        <v>73551.58199999999</v>
       </c>
       <c r="F93" t="n">
-        <v>6177.553</v>
+        <v>5242.581</v>
       </c>
       <c r="G93" t="n">
-        <v>471.899</v>
+        <v>458.27</v>
       </c>
       <c r="H93" t="n">
-        <v>46726.281</v>
+        <v>46717.488</v>
       </c>
       <c r="I93" t="n">
-        <v>44897.652</v>
+        <v>44869.685</v>
       </c>
       <c r="J93" t="n">
-        <v>96.087</v>
+        <v>96.045</v>
       </c>
       <c r="K93" t="n">
-        <v>24930.12</v>
+        <v>22839.31</v>
       </c>
       <c r="L93" t="n">
-        <v>-3100.088</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>-3.947</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>-10.264</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>-10.259</v>
-      </c>
-      <c r="P93" t="n">
-        <v>27412.477</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>30537.859</v>
-      </c>
-      <c r="R93" t="n">
-        <v>89.76600000000001</v>
-      </c>
-      <c r="S93" t="n">
-        <v>61.336</v>
-      </c>
-      <c r="T93" t="n">
-        <v>163.036</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>5.335</v>
+        <v>4.889</v>
       </c>
       <c r="V93" t="n">
-        <v>1419.186</v>
+        <v>4980.354</v>
       </c>
       <c r="W93" t="n">
         <v>0.002</v>
       </c>
       <c r="X93" t="n">
-        <v>0.003</v>
+        <v>0.893</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.807</v>
+        <v>6.771</v>
       </c>
       <c r="AC93" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="AD93" t="n">
-        <v>0.848</v>
+        <v>7.637</v>
       </c>
       <c r="AE93" t="n">
-        <v>0.065</v>
+        <v>0.668</v>
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất Quý 2 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG93" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-08-19/no-name-1755541972.pdf</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-18/no-name-1744937049.pdf</t>
         </is>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>2026-08-31T12:25:04+07:00</t>
+          <t>2026-08-31T10:25:19+07:00</t>
         </is>
       </c>
     </row>
@@ -39371,7 +39653,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -39380,75 +39662,90 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>79838.139</v>
+        <v>78533.89999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>6361.63</v>
+        <v>6177.553</v>
       </c>
       <c r="G94" t="n">
-        <v>465.866</v>
+        <v>471.899</v>
       </c>
       <c r="H94" t="n">
-        <v>44375.382</v>
+        <v>46726.281</v>
       </c>
       <c r="I94" t="n">
-        <v>43804.438</v>
+        <v>44897.652</v>
       </c>
       <c r="J94" t="n">
-        <v>98.71299999999999</v>
+        <v>96.087</v>
       </c>
       <c r="K94" t="n">
-        <v>26456.808</v>
+        <v>24930.12</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>-3100.088</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>-3.947</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>-10.264</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>-10.259</v>
+      </c>
+      <c r="P94" t="n">
+        <v>27412.477</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>30537.859</v>
+      </c>
+      <c r="R94" t="n">
+        <v>89.76600000000001</v>
+      </c>
+      <c r="S94" t="n">
+        <v>61.336</v>
+      </c>
+      <c r="T94" t="n">
+        <v>163.036</v>
       </c>
       <c r="U94" t="n">
-        <v>5.962</v>
+        <v>5.335</v>
       </c>
       <c r="V94" t="n">
-        <v>1093.899</v>
+        <v>1419.186</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="X94" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.37</v>
+        <v>1.807</v>
       </c>
       <c r="AC94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD94" t="n">
-        <v>0.644</v>
+        <v>0.848</v>
       </c>
       <c r="AE94" t="n">
-        <v>0.047</v>
+        <v>0.065</v>
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất Quý 3 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất Quý 2 năm 2025</t>
         </is>
       </c>
       <c r="AG94" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-10-24/no-name-1761245640.pdf</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-08-19/no-name-1755541972.pdf</t>
         </is>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>2026-08-31T15:38:58+07:00</t>
+          <t>2026-08-31T12:25:04+07:00</t>
         </is>
       </c>
     </row>
@@ -39460,7 +39757,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -39469,90 +39766,75 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>88840.17200000001</v>
+        <v>79838.139</v>
       </c>
       <c r="F95" t="n">
-        <v>6545.253</v>
+        <v>6361.63</v>
       </c>
       <c r="G95" t="n">
-        <v>481.771</v>
+        <v>465.866</v>
       </c>
       <c r="H95" t="n">
-        <v>48460.417</v>
+        <v>44375.382</v>
       </c>
       <c r="I95" t="n">
-        <v>45781.147</v>
+        <v>43804.438</v>
       </c>
       <c r="J95" t="n">
-        <v>94.471</v>
+        <v>98.71299999999999</v>
       </c>
       <c r="K95" t="n">
-        <v>31153.789</v>
+        <v>26456.808</v>
       </c>
       <c r="L95" t="n">
-        <v>-7944.858999999999</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>-8.943</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>-7.796</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>-11.351</v>
-      </c>
-      <c r="P95" t="n">
-        <v>477294.919</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>10940.595</v>
-      </c>
-      <c r="R95" t="n">
-        <v>4362.605</v>
-      </c>
-      <c r="S95" t="n">
-        <v>83.438</v>
-      </c>
-      <c r="T95" t="n">
-        <v>119.849</v>
+        <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>6.429</v>
+        <v>5.962</v>
       </c>
       <c r="V95" t="n">
-        <v>-448.712</v>
+        <v>1093.899</v>
       </c>
       <c r="W95" t="n">
-        <v>-8.398</v>
+        <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>-0.622</v>
+        <v>0.001</v>
       </c>
       <c r="Y95" t="n">
-        <v>-0.505</v>
+        <v>1.37</v>
       </c>
       <c r="AC95" t="n">
-        <v>-20</v>
+        <v>3</v>
       </c>
       <c r="AD95" t="n">
-        <v>-4.151</v>
+        <v>0.644</v>
       </c>
       <c r="AE95" t="n">
-        <v>-0.306</v>
+        <v>0.047</v>
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất Quý 3 năm 2025</t>
         </is>
       </c>
       <c r="AG95" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-02/no-name-1775069400.pdf</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-10-24/no-name-1761245640.pdf</t>
         </is>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>2026-08-31T01:31:51+07:00</t>
+          <t>2026-08-31T15:38:58+07:00</t>
         </is>
       </c>
     </row>
@@ -39564,7 +39846,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -39573,75 +39855,90 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>86711.06299999999</v>
+        <v>88840.17200000001</v>
       </c>
       <c r="F96" t="n">
-        <v>8081.361</v>
+        <v>6545.253</v>
       </c>
       <c r="G96" t="n">
-        <v>457.546</v>
+        <v>481.771</v>
       </c>
       <c r="H96" t="n">
-        <v>47035.359</v>
+        <v>48460.417</v>
       </c>
       <c r="I96" t="n">
-        <v>43825.33</v>
+        <v>45781.147</v>
       </c>
       <c r="J96" t="n">
-        <v>93.175</v>
+        <v>94.471</v>
       </c>
       <c r="K96" t="n">
-        <v>32954.793</v>
+        <v>31153.789</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>-7944.858999999999</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>-8.943</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>-7.796</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>-11.351</v>
+      </c>
+      <c r="P96" t="n">
+        <v>477294.919</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>10940.595</v>
+      </c>
+      <c r="R96" t="n">
+        <v>4362.605</v>
+      </c>
+      <c r="S96" t="n">
+        <v>83.438</v>
+      </c>
+      <c r="T96" t="n">
+        <v>119.849</v>
       </c>
       <c r="U96" t="n">
-        <v>7.006</v>
+        <v>6.429</v>
       </c>
       <c r="V96" t="n">
-        <v>-5400.599999999999</v>
+        <v>-448.712</v>
       </c>
       <c r="W96" t="n">
-        <v>-6.247</v>
+        <v>-8.398</v>
       </c>
       <c r="X96" t="n">
-        <v>-6.235</v>
+        <v>-0.622</v>
       </c>
       <c r="Y96" t="n">
-        <v>-6.228</v>
+        <v>-0.505</v>
       </c>
       <c r="AC96" t="n">
-        <v>-52</v>
+        <v>-20</v>
       </c>
       <c r="AD96" t="n">
-        <v>-11.365</v>
+        <v>-4.151</v>
       </c>
       <c r="AE96" t="n">
-        <v>-0.643</v>
+        <v>-0.306</v>
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
       <c r="AG96" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-30/no-name-1777487970.pdf</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-02/no-name-1775069400.pdf</t>
         </is>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>2026-08-31T23:44:08+07:00</t>
+          <t>2026-08-31T01:31:51+07:00</t>
         </is>
       </c>
     </row>
@@ -39653,7 +39950,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -39662,102 +39959,87 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>89312.48</v>
+        <v>86711.06299999999</v>
       </c>
       <c r="F97" t="n">
-        <v>8212.376</v>
+        <v>8081.361</v>
       </c>
       <c r="G97" t="n">
-        <v>521.519</v>
+        <v>457.546</v>
       </c>
       <c r="H97" t="n">
-        <v>49715.876</v>
+        <v>47035.359</v>
       </c>
       <c r="I97" t="n">
-        <v>47740.104</v>
+        <v>43825.33</v>
       </c>
       <c r="J97" t="n">
-        <v>96.026</v>
+        <v>93.175</v>
       </c>
       <c r="K97" t="n">
-        <v>25908.238</v>
+        <v>32954.793</v>
       </c>
       <c r="L97" t="n">
-        <v>3395.972</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.802</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>-1.896</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>9.872999999999999</v>
-      </c>
-      <c r="P97" t="n">
-        <v>10062.201</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>53185.197</v>
-      </c>
-      <c r="R97" t="n">
-        <v>18.919</v>
-      </c>
-      <c r="S97" t="n">
-        <v>79.861</v>
-      </c>
-      <c r="T97" t="n">
-        <v>125.218</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>5.211</v>
+        <v>7.006</v>
       </c>
       <c r="V97" t="n">
-        <v>1369.378</v>
+        <v>-5400.599999999999</v>
       </c>
       <c r="W97" t="n">
-        <v>3.105</v>
+        <v>-6.247</v>
       </c>
       <c r="X97" t="n">
-        <v>6.176</v>
+        <v>-6.235</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.533</v>
+        <v>-6.228</v>
       </c>
       <c r="AC97" t="n">
-        <v>36</v>
+        <v>-52</v>
       </c>
       <c r="AD97" t="n">
-        <v>6.903</v>
+        <v>-11.365</v>
       </c>
       <c r="AE97" t="n">
-        <v>0.438</v>
+        <v>-0.643</v>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính quý 2 năm 2026 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/PGB_000000016752911_VI_Baocaotaichinh_bannien_nam_2026_18082026140441.pdf?v=1787036682987</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-30/no-name-1777487970.pdf</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>2026-09-01T09:58:24+07:00</t>
+          <t>2026-08-31T23:44:08+07:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SGB</t>
+          <t>PGB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -39766,75 +40048,90 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>33506.33</v>
+        <v>89312.48</v>
       </c>
       <c r="F98" t="n">
-        <v>4172.432</v>
+        <v>8212.376</v>
       </c>
       <c r="G98" t="n">
-        <v>217.861</v>
+        <v>521.519</v>
       </c>
       <c r="H98" t="n">
-        <v>24539.598</v>
+        <v>49715.876</v>
       </c>
       <c r="I98" t="n">
-        <v>20683.652</v>
+        <v>47740.104</v>
       </c>
       <c r="J98" t="n">
-        <v>84.28700000000001</v>
+        <v>96.026</v>
       </c>
       <c r="K98" t="n">
-        <v>9035.235999999999</v>
+        <v>25908.238</v>
       </c>
       <c r="L98" t="n">
-        <v>5121.561</v>
+        <v>3395.972</v>
       </c>
       <c r="M98" t="n">
-        <v>15.285</v>
+        <v>3.802</v>
       </c>
       <c r="N98" t="n">
-        <v>22.732</v>
+        <v>-1.896</v>
       </c>
       <c r="O98" t="n">
-        <v>45.463</v>
+        <v>9.872999999999999</v>
+      </c>
+      <c r="P98" t="n">
+        <v>10062.201</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>53185.197</v>
+      </c>
+      <c r="R98" t="n">
+        <v>18.919</v>
+      </c>
+      <c r="S98" t="n">
+        <v>79.861</v>
+      </c>
+      <c r="T98" t="n">
+        <v>125.218</v>
       </c>
       <c r="U98" t="n">
-        <v>3.682</v>
+        <v>5.211</v>
       </c>
       <c r="V98" t="n">
-        <v>-8415.234000000002</v>
+        <v>1369.378</v>
       </c>
       <c r="W98" t="n">
-        <v>-5.98</v>
+        <v>3.105</v>
       </c>
       <c r="X98" t="n">
-        <v>-26.824</v>
+        <v>6.176</v>
       </c>
       <c r="Y98" t="n">
-        <v>-25.115</v>
+        <v>1.533</v>
       </c>
       <c r="AC98" t="n">
-        <v>-102</v>
+        <v>36</v>
       </c>
       <c r="AD98" t="n">
-        <v>-46.819</v>
+        <v>6.903</v>
       </c>
       <c r="AE98" t="n">
-        <v>-2.445</v>
+        <v>0.438</v>
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+          <t>Báo cáo tài chính quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG98" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014834796_VI_BaoCaotaiChinh_HopNhat_Q1_2025_26042025110134.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/PGB_000000016752911_VI_Baocaotaichinh_bannien_nam_2026_18082026140441.pdf?v=1787036682987</t>
         </is>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>2026-08-31T10:26:54+07:00</t>
+          <t>2026-09-01T09:58:24+07:00</t>
         </is>
       </c>
     </row>
@@ -39846,7 +40143,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -39855,90 +40152,75 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>35140.737</v>
+        <v>33506.33</v>
       </c>
       <c r="F99" t="n">
-        <v>4234.018</v>
+        <v>4172.432</v>
       </c>
       <c r="G99" t="n">
-        <v>233.402</v>
+        <v>217.861</v>
       </c>
       <c r="H99" t="n">
-        <v>25595.19</v>
+        <v>24539.598</v>
       </c>
       <c r="I99" t="n">
-        <v>20050.378</v>
+        <v>20683.652</v>
       </c>
       <c r="J99" t="n">
-        <v>78.337</v>
+        <v>84.28700000000001</v>
       </c>
       <c r="K99" t="n">
-        <v>10508.501</v>
+        <v>9035.235999999999</v>
       </c>
       <c r="L99" t="n">
-        <v>1633.754</v>
+        <v>5121.561</v>
       </c>
       <c r="M99" t="n">
-        <v>4.649</v>
+        <v>15.285</v>
       </c>
       <c r="N99" t="n">
-        <v>17.592</v>
+        <v>22.732</v>
       </c>
       <c r="O99" t="n">
-        <v>46.83</v>
-      </c>
-      <c r="P99" t="n">
-        <v>37088.709</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>36477.346</v>
-      </c>
-      <c r="R99" t="n">
-        <v>101.676</v>
-      </c>
-      <c r="S99" t="n">
-        <v>57.343</v>
-      </c>
-      <c r="T99" t="n">
-        <v>174.388</v>
+        <v>45.463</v>
       </c>
       <c r="U99" t="n">
-        <v>4.106</v>
+        <v>3.682</v>
       </c>
       <c r="V99" t="n">
-        <v>1423.367</v>
+        <v>-8415.234000000002</v>
       </c>
       <c r="W99" t="n">
-        <v>4.526</v>
+        <v>-5.98</v>
       </c>
       <c r="X99" t="n">
-        <v>-0.509</v>
+        <v>-26.824</v>
       </c>
       <c r="Y99" t="n">
-        <v>4.05</v>
+        <v>-25.115</v>
       </c>
       <c r="AC99" t="n">
-        <v>-14</v>
+        <v>-102</v>
       </c>
       <c r="AD99" t="n">
-        <v>-5.998</v>
+        <v>-46.819</v>
       </c>
       <c r="AE99" t="n">
-        <v>-0.331</v>
+        <v>-2.445</v>
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00019753086419753087ngn-hng-tmcp-si-gn-cng-thng14082025-000000bo-co-ti-chnh-bn-nin-2025_1_1022.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014834796_VI_BaoCaotaiChinh_HopNhat_Q1_2025_26042025110134.pdf</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>2026-08-31T12:26:51+07:00</t>
+          <t>2026-08-31T10:26:54+07:00</t>
         </is>
       </c>
     </row>
@@ -39950,7 +40232,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -39959,75 +40241,90 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>34870.159</v>
+        <v>35140.737</v>
       </c>
       <c r="F100" t="n">
-        <v>4286.353</v>
+        <v>4234.018</v>
       </c>
       <c r="G100" t="n">
-        <v>197.656</v>
+        <v>233.402</v>
       </c>
       <c r="H100" t="n">
-        <v>25943.421</v>
+        <v>25595.19</v>
       </c>
       <c r="I100" t="n">
-        <v>20295.602</v>
+        <v>20050.378</v>
       </c>
       <c r="J100" t="n">
-        <v>78.23</v>
+        <v>78.337</v>
       </c>
       <c r="K100" t="n">
-        <v>10327.594</v>
+        <v>10508.501</v>
       </c>
       <c r="L100" t="n">
-        <v>2878.877</v>
+        <v>1633.754</v>
       </c>
       <c r="M100" t="n">
-        <v>8.256</v>
+        <v>4.649</v>
       </c>
       <c r="N100" t="n">
-        <v>11.622</v>
+        <v>17.592</v>
       </c>
       <c r="O100" t="n">
-        <v>11.607</v>
+        <v>46.83</v>
+      </c>
+      <c r="P100" t="n">
+        <v>37088.709</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>36477.346</v>
+      </c>
+      <c r="R100" t="n">
+        <v>101.676</v>
+      </c>
+      <c r="S100" t="n">
+        <v>57.343</v>
+      </c>
+      <c r="T100" t="n">
+        <v>174.388</v>
       </c>
       <c r="U100" t="n">
-        <v>3.981</v>
+        <v>4.106</v>
       </c>
       <c r="V100" t="n">
-        <v>3751.041</v>
+        <v>1423.367</v>
       </c>
       <c r="W100" t="n">
-        <v>3.012</v>
+        <v>4.526</v>
       </c>
       <c r="X100" t="n">
-        <v>2.354</v>
+        <v>-0.509</v>
       </c>
       <c r="Y100" t="n">
-        <v>10.757</v>
+        <v>4.05</v>
       </c>
       <c r="AC100" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="AD100" t="n">
-        <v>1.012</v>
+        <v>-5.998</v>
       </c>
       <c r="AE100" t="n">
-        <v>0.047</v>
+        <v>-0.331</v>
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG100" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_585483_Bao_cao_tai_chinh_quy_32025_1761811756.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00019753086419753087ngn-hng-tmcp-si-gn-cng-thng14082025-000000bo-co-ti-chnh-bn-nin-2025_1_1022.pdf</t>
         </is>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>2026-08-31T15:40:59+07:00</t>
+          <t>2026-08-31T12:26:51+07:00</t>
         </is>
       </c>
     </row>
@@ -40039,7 +40336,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -40048,75 +40345,75 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>35377.029</v>
+        <v>34870.159</v>
       </c>
       <c r="F101" t="n">
-        <v>4194.143</v>
+        <v>4286.353</v>
       </c>
       <c r="G101" t="n">
-        <v>65.943</v>
+        <v>197.656</v>
       </c>
       <c r="H101" t="n">
-        <v>26326.61</v>
+        <v>25943.421</v>
       </c>
       <c r="I101" t="n">
-        <v>21736.612</v>
+        <v>20295.602</v>
       </c>
       <c r="J101" t="n">
-        <v>82.565</v>
+        <v>78.23</v>
       </c>
       <c r="K101" t="n">
-        <v>9373.537</v>
+        <v>10327.594</v>
       </c>
       <c r="L101" t="n">
-        <v>838.0600000000001</v>
+        <v>2878.877</v>
       </c>
       <c r="M101" t="n">
-        <v>2.369</v>
+        <v>8.256</v>
       </c>
       <c r="N101" t="n">
-        <v>-1.011</v>
+        <v>11.622</v>
       </c>
       <c r="O101" t="n">
-        <v>-10.746</v>
+        <v>11.607</v>
       </c>
       <c r="U101" t="n">
-        <v>3.56</v>
+        <v>3.981</v>
       </c>
       <c r="V101" t="n">
-        <v>3391.897</v>
+        <v>3751.041</v>
       </c>
       <c r="W101" t="n">
-        <v>0.061</v>
+        <v>3.012</v>
       </c>
       <c r="X101" t="n">
-        <v>-2.329</v>
+        <v>2.354</v>
       </c>
       <c r="Y101" t="n">
-        <v>9.587999999999999</v>
+        <v>10.757</v>
       </c>
       <c r="AC101" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="AD101" t="n">
-        <v>-10.615</v>
+        <v>1.012</v>
       </c>
       <c r="AE101" t="n">
-        <v>-0.167</v>
+        <v>0.047</v>
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
       <c r="AG101" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604675_Bao_cao_tai_chinh_nam_2025_1776046299.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_585483_Bao_cao_tai_chinh_quy_32025_1761811756.pdf</t>
         </is>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>2026-08-31T01:33:44+07:00</t>
+          <t>2026-08-31T15:40:59+07:00</t>
         </is>
       </c>
     </row>
@@ -40128,7 +40425,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -40137,90 +40434,75 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>35504.997</v>
+        <v>35377.029</v>
       </c>
       <c r="F102" t="n">
-        <v>4267.389</v>
+        <v>4194.143</v>
       </c>
       <c r="G102" t="n">
-        <v>209.921</v>
+        <v>65.943</v>
       </c>
       <c r="H102" t="n">
-        <v>25348.719</v>
+        <v>26326.61</v>
       </c>
       <c r="I102" t="n">
-        <v>21877.614</v>
+        <v>21736.612</v>
       </c>
       <c r="J102" t="n">
-        <v>86.307</v>
+        <v>82.565</v>
       </c>
       <c r="K102" t="n">
-        <v>9440.639000000001</v>
+        <v>9373.537</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>838.0600000000001</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>2.369</v>
       </c>
       <c r="N102" t="n">
-        <v>1.987</v>
+        <v>-1.011</v>
       </c>
       <c r="O102" t="n">
-        <v>1.987</v>
-      </c>
-      <c r="P102" t="n">
-        <v>4376.477</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>17933.317</v>
-      </c>
-      <c r="R102" t="n">
-        <v>24.404</v>
-      </c>
-      <c r="S102" t="n">
-        <v>47.115</v>
-      </c>
-      <c r="T102" t="n">
-        <v>212.245</v>
+        <v>-10.746</v>
       </c>
       <c r="U102" t="n">
-        <v>3.724</v>
+        <v>3.56</v>
       </c>
       <c r="V102" t="n">
-        <v>1778.762000000001</v>
+        <v>3391.897</v>
       </c>
       <c r="W102" t="n">
-        <v>-4.826</v>
+        <v>0.061</v>
       </c>
       <c r="X102" t="n">
-        <v>-7.118</v>
+        <v>-2.329</v>
       </c>
       <c r="Y102" t="n">
-        <v>5.01</v>
+        <v>9.587999999999999</v>
       </c>
       <c r="AC102" t="n">
-        <v>-24</v>
+        <v>-7</v>
       </c>
       <c r="AD102" t="n">
-        <v>-11.433</v>
+        <v>-10.615</v>
       </c>
       <c r="AE102" t="n">
-        <v>-0.5620000000000001</v>
+        <v>-0.167</v>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_611277_Bao_cao_tai_chinh_quy_12026_1777027908.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604675_Bao_cao_tai_chinh_nam_2025_1776046299.pdf</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>2026-08-31T23:45:58+07:00</t>
+          <t>2026-08-31T01:33:44+07:00</t>
         </is>
       </c>
     </row>
@@ -40232,7 +40514,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -40241,112 +40523,194 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>35669.855</v>
+        <v>35504.997</v>
       </c>
       <c r="F103" t="n">
-        <v>4233.066</v>
+        <v>4267.389</v>
       </c>
       <c r="G103" t="n">
-        <v>160.251</v>
+        <v>209.921</v>
       </c>
       <c r="H103" t="n">
-        <v>25205.181</v>
+        <v>25348.719</v>
       </c>
       <c r="I103" t="n">
-        <v>21976.093</v>
+        <v>21877.614</v>
       </c>
       <c r="J103" t="n">
-        <v>87.18899999999999</v>
+        <v>86.307</v>
       </c>
       <c r="K103" t="n">
-        <v>9234.462000000001</v>
+        <v>9440.639000000001</v>
       </c>
       <c r="L103" t="n">
-        <v>-3283.094</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>-9.204000000000001</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>1.624</v>
+        <v>1.987</v>
       </c>
       <c r="O103" t="n">
-        <v>17.973</v>
+        <v>1.987</v>
       </c>
       <c r="P103" t="n">
-        <v>7367.857</v>
+        <v>4376.477</v>
       </c>
       <c r="Q103" t="n">
-        <v>41782.964</v>
+        <v>17933.317</v>
       </c>
       <c r="R103" t="n">
-        <v>17.634</v>
+        <v>24.404</v>
       </c>
       <c r="S103" t="n">
-        <v>23.926</v>
+        <v>47.115</v>
       </c>
       <c r="T103" t="n">
-        <v>417.947</v>
+        <v>212.245</v>
       </c>
       <c r="U103" t="n">
-        <v>3.664</v>
+        <v>3.724</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>1778.762000000001</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>-4.826</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>-7.118</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>-11.433</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
       <c r="AG103" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SGB_000000016770459_VI__Bao_Cao_Tai_Chinh_Hop_Nhat_Ban_Nien_Nam_2026_daky_20082026151909.pdf?v=1787213952177</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_611277_Bao_cao_tai_chinh_quy_12026_1777027908.pdf</t>
         </is>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>2026-09-01T10:00:42+07:00</t>
+          <t>2026-08-31T23:45:58+07:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SHB</t>
+          <t>SGB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>35669.855</v>
+      </c>
+      <c r="F104" t="n">
+        <v>4233.066</v>
+      </c>
+      <c r="G104" t="n">
+        <v>160.251</v>
+      </c>
+      <c r="H104" t="n">
+        <v>25205.181</v>
+      </c>
+      <c r="I104" t="n">
+        <v>21976.093</v>
+      </c>
+      <c r="J104" t="n">
+        <v>87.18899999999999</v>
+      </c>
+      <c r="K104" t="n">
+        <v>9234.462000000001</v>
+      </c>
+      <c r="L104" t="n">
+        <v>-3283.094</v>
+      </c>
+      <c r="M104" t="n">
+        <v>-9.204000000000001</v>
+      </c>
+      <c r="N104" t="n">
+        <v>1.624</v>
+      </c>
+      <c r="O104" t="n">
+        <v>17.973</v>
+      </c>
+      <c r="P104" t="n">
+        <v>7367.857</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>41782.964</v>
+      </c>
+      <c r="R104" t="n">
+        <v>17.634</v>
+      </c>
+      <c r="S104" t="n">
+        <v>23.926</v>
+      </c>
+      <c r="T104" t="n">
+        <v>417.947</v>
+      </c>
+      <c r="U104" t="n">
+        <v>3.664</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SGB_000000016770459_VI__Bao_Cao_Tai_Chinh_Hop_Nhat_Ban_Nien_Nam_2026_daky_20082026151909.pdf?v=1787213952177</t>
         </is>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>2026-09-17T17:21:29+07:00</t>
+          <t>2026-09-01T10:00:42+07:00</t>
         </is>
       </c>
     </row>
@@ -40358,99 +40722,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>825718.9790000001</v>
-      </c>
-      <c r="F105" t="n">
-        <v>63267.914</v>
-      </c>
-      <c r="G105" t="n">
-        <v>9160.064</v>
-      </c>
-      <c r="H105" t="n">
-        <v>561718.311</v>
-      </c>
-      <c r="I105" t="n">
-        <v>584806.6360000001</v>
-      </c>
-      <c r="J105" t="n">
-        <v>104.11</v>
-      </c>
-      <c r="K105" t="n">
-        <v>139362.736</v>
-      </c>
-      <c r="L105" t="n">
-        <v>7001.849</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="N105" t="n">
-        <v>-3.937</v>
-      </c>
-      <c r="O105" t="n">
-        <v>-11.95</v>
-      </c>
-      <c r="P105" t="n">
-        <v>-16796.302</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>320985.483</v>
-      </c>
-      <c r="R105" t="n">
-        <v>-5.233</v>
-      </c>
-      <c r="S105" t="n">
-        <v>66.04300000000001</v>
-      </c>
-      <c r="T105" t="n">
-        <v>151.417</v>
-      </c>
-      <c r="U105" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="V105" t="n">
-        <v>101052.076</v>
-      </c>
-      <c r="W105" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="X105" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>12.238</v>
-      </c>
-      <c r="AC105" t="n">
-        <v>1186</v>
-      </c>
-      <c r="AD105" t="n">
-        <v>12.948</v>
-      </c>
-      <c r="AE105" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
-        </is>
-      </c>
-      <c r="AG105" t="inlineStr">
-        <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250903_-_SHB_-_Bao_Cao_Tai_Chinh_Hop_Nhat_Soat_Xet_Ban_nien_30.6.2025_1756910753.pdf</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>2026-08-31T12:28:17+07:00</t>
+          <t>2026-09-17T17:21:29+07:00</t>
         </is>
       </c>
     </row>
@@ -40462,17 +40744,99 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>825718.9790000001</v>
+      </c>
+      <c r="F106" t="n">
+        <v>63267.914</v>
+      </c>
+      <c r="G106" t="n">
+        <v>9160.064</v>
+      </c>
+      <c r="H106" t="n">
+        <v>561718.311</v>
+      </c>
+      <c r="I106" t="n">
+        <v>584806.6360000001</v>
+      </c>
+      <c r="J106" t="n">
+        <v>104.11</v>
+      </c>
+      <c r="K106" t="n">
+        <v>139362.736</v>
+      </c>
+      <c r="L106" t="n">
+        <v>7001.849</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-3.937</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-11.95</v>
+      </c>
+      <c r="P106" t="n">
+        <v>-16796.302</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>320985.483</v>
+      </c>
+      <c r="R106" t="n">
+        <v>-5.233</v>
+      </c>
+      <c r="S106" t="n">
+        <v>66.04300000000001</v>
+      </c>
+      <c r="T106" t="n">
+        <v>151.417</v>
+      </c>
+      <c r="U106" t="n">
+        <v>2.481</v>
+      </c>
+      <c r="V106" t="n">
+        <v>101052.076</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>12.238</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>1186</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>12.948</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250903_-_SHB_-_Bao_Cao_Tai_Chinh_Hop_Nhat_Soat_Xet_Ban_nien_30.6.2025_1756910753.pdf</t>
         </is>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>2026-09-17T18:10:56+07:00</t>
+          <t>2026-08-31T12:28:17+07:00</t>
         </is>
       </c>
     </row>
@@ -40484,7 +40848,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -40494,7 +40858,7 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>2026-08-31T01:34:56+07:00</t>
+          <t>2026-09-17T18:10:56+07:00</t>
         </is>
       </c>
     </row>
@@ -40506,17 +40870,108 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>892008.709</v>
+      </c>
+      <c r="F108" t="n">
+        <v>68130.93799999999</v>
+      </c>
+      <c r="G108" t="n">
+        <v>187.363</v>
+      </c>
+      <c r="H108" t="n">
+        <v>572149.573</v>
+      </c>
+      <c r="I108" t="n">
+        <v>604363.682</v>
+      </c>
+      <c r="J108" t="n">
+        <v>105.63</v>
+      </c>
+      <c r="K108" t="n">
+        <v>173498.65</v>
+      </c>
+      <c r="L108" t="n">
+        <v>83424.785</v>
+      </c>
+      <c r="M108" t="n">
+        <v>9.352</v>
+      </c>
+      <c r="N108" t="n">
+        <v>9.615</v>
+      </c>
+      <c r="O108" t="n">
+        <v>-1.291</v>
+      </c>
+      <c r="P108" t="n">
+        <v>312589.162</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>201841.576</v>
+      </c>
+      <c r="R108" t="n">
+        <v>154.869</v>
+      </c>
+      <c r="S108" t="n">
+        <v>117.483</v>
+      </c>
+      <c r="T108" t="n">
+        <v>85.119</v>
+      </c>
+      <c r="U108" t="n">
+        <v>3.032</v>
+      </c>
+      <c r="V108" t="n">
+        <v>205456.892</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="X108" t="n">
+        <v>23.013</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>23.033</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>1156478.2</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>836988.189</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>138.171</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>1712</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>913.734</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>2.513</v>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_SHB_-_Bao_cao_tai_chinh_nam_2025_Hop_nhat_1775015883.pdf</t>
         </is>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>2026-09-17T09:48:13+07:00</t>
+          <t>2026-09-17T18:25:58+07:00</t>
         </is>
       </c>
     </row>
@@ -40528,111 +40983,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>962886.7830000001</v>
-      </c>
-      <c r="F109" t="n">
-        <v>75309.442</v>
-      </c>
-      <c r="G109" t="n">
-        <v>6760.976</v>
-      </c>
-      <c r="H109" t="n">
-        <v>624269.133</v>
-      </c>
-      <c r="I109" t="n">
-        <v>648552.733</v>
-      </c>
-      <c r="J109" t="n">
-        <v>103.89</v>
-      </c>
-      <c r="K109" t="n">
-        <v>173099.211</v>
-      </c>
-      <c r="L109" t="n">
-        <v>-40538.58100000001</v>
-      </c>
-      <c r="M109" t="n">
-        <v>-4.21</v>
-      </c>
-      <c r="N109" t="n">
-        <v>-7.459</v>
-      </c>
-      <c r="O109" t="n">
-        <v>-10.033</v>
-      </c>
-      <c r="P109" t="n">
-        <v>740760.497</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>202771.522</v>
-      </c>
-      <c r="R109" t="n">
-        <v>365.318</v>
-      </c>
-      <c r="S109" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="T109" t="n">
-        <v>213.856</v>
-      </c>
-      <c r="U109" t="n">
-        <v>2.773</v>
-      </c>
-      <c r="V109" t="n">
-        <v>118737.975</v>
-      </c>
-      <c r="W109" t="n">
-        <v>4.703</v>
-      </c>
-      <c r="X109" t="n">
-        <v>31.553</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>12.331</v>
-      </c>
-      <c r="AC109" t="n">
-        <v>1431</v>
-      </c>
-      <c r="AD109" t="n">
-        <v>21.166</v>
-      </c>
-      <c r="AE109" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>Báo cáo tài chính hợp nhất đã kiểm toán 6 tháng đầu năm 2026</t>
-        </is>
-      </c>
-      <c r="AG109" t="inlineStr">
-        <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2026-3/2026-09-04/no-name-1788460885.pdf</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>2026-09-04T08:27:55+07:00</t>
+          <t>2026-09-17T09:48:13+07:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SSB</t>
+          <t>SHB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -40641,90 +41014,90 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>333746.268</v>
+        <v>962886.7830000001</v>
       </c>
       <c r="F110" t="n">
-        <v>38599.606</v>
+        <v>75309.442</v>
       </c>
       <c r="G110" t="n">
-        <v>2450.482</v>
+        <v>6760.976</v>
       </c>
       <c r="H110" t="n">
-        <v>160043.132</v>
+        <v>624269.133</v>
       </c>
       <c r="I110" t="n">
-        <v>209845.503</v>
+        <v>648552.733</v>
       </c>
       <c r="J110" t="n">
-        <v>131.118</v>
+        <v>103.89</v>
       </c>
       <c r="K110" t="n">
-        <v>83940.10000000001</v>
+        <v>173099.211</v>
       </c>
       <c r="L110" t="n">
-        <v>24719.945</v>
+        <v>-40538.58100000001</v>
       </c>
       <c r="M110" t="n">
-        <v>7.407</v>
+        <v>-4.21</v>
       </c>
       <c r="N110" t="n">
-        <v>9.519</v>
+        <v>-7.459</v>
       </c>
       <c r="O110" t="n">
-        <v>-2.311</v>
+        <v>-10.033</v>
       </c>
       <c r="P110" t="n">
-        <v>83.80500000000001</v>
+        <v>740760.497</v>
       </c>
       <c r="Q110" t="n">
-        <v>176395.92</v>
+        <v>202771.522</v>
       </c>
       <c r="R110" t="n">
-        <v>0.048</v>
+        <v>365.318</v>
       </c>
       <c r="S110" t="n">
-        <v>114.404</v>
+        <v>46.76</v>
       </c>
       <c r="T110" t="n">
-        <v>87.41</v>
+        <v>213.856</v>
       </c>
       <c r="U110" t="n">
-        <v>5.245</v>
+        <v>2.773</v>
       </c>
       <c r="V110" t="n">
-        <v>0</v>
+        <v>118737.975</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>4.703</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>31.553</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>12.331</v>
       </c>
       <c r="AC110" t="n">
-        <v>0</v>
+        <v>1431</v>
       </c>
       <c r="AD110" t="n">
-        <v>0</v>
+        <v>21.166</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán 6 tháng đầu năm 2026</t>
         </is>
       </c>
       <c r="AG110" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_23052025144847.pdf</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-3/2026-09-04/no-name-1788460885.pdf</t>
         </is>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>2026-08-31T10:31:02+07:00</t>
+          <t>2026-09-04T08:27:55+07:00</t>
         </is>
       </c>
     </row>
@@ -40736,7 +41109,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -40745,40 +41118,55 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>379013.742</v>
+        <v>333746.268</v>
       </c>
       <c r="F111" t="n">
-        <v>39487.97</v>
+        <v>38599.606</v>
       </c>
       <c r="G111" t="n">
-        <v>2464.389</v>
+        <v>2450.482</v>
       </c>
       <c r="H111" t="n">
-        <v>166648.051</v>
+        <v>160043.132</v>
       </c>
       <c r="I111" t="n">
-        <v>217398.122</v>
+        <v>209845.503</v>
       </c>
       <c r="J111" t="n">
-        <v>130.453</v>
+        <v>131.118</v>
       </c>
       <c r="K111" t="n">
-        <v>117396.389</v>
+        <v>83940.10000000001</v>
       </c>
       <c r="L111" t="n">
-        <v>26000.343</v>
+        <v>24719.945</v>
       </c>
       <c r="M111" t="n">
-        <v>6.86</v>
+        <v>7.407</v>
       </c>
       <c r="N111" t="n">
-        <v>1.419</v>
+        <v>9.519</v>
       </c>
       <c r="O111" t="n">
-        <v>-1.845</v>
+        <v>-2.311</v>
+      </c>
+      <c r="P111" t="n">
+        <v>83.80500000000001</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>176395.92</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="S111" t="n">
+        <v>114.404</v>
+      </c>
+      <c r="T111" t="n">
+        <v>87.41</v>
       </c>
       <c r="U111" t="n">
-        <v>7.045</v>
+        <v>5.245</v>
       </c>
       <c r="V111" t="n">
         <v>0</v>
@@ -40803,17 +41191,17 @@
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG111" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250905_-_SSB_-_Bao_cao_tai_chinh_hop_nhat_soat_xet_ban_nien_2025_va_Giai_trinh_bien_dong_LNST_signed_1757323427.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_23052025144847.pdf</t>
         </is>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>2026-08-31T12:30:19+07:00</t>
+          <t>2026-08-31T10:31:02+07:00</t>
         </is>
       </c>
     </row>
@@ -40825,7 +41213,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -40834,90 +41222,75 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>380808.411</v>
+        <v>379013.742</v>
       </c>
       <c r="F112" t="n">
-        <v>40267.975</v>
+        <v>39487.97</v>
       </c>
       <c r="G112" t="n">
-        <v>2337.097</v>
+        <v>2464.389</v>
       </c>
       <c r="H112" t="n">
-        <v>177624.068</v>
+        <v>166648.051</v>
       </c>
       <c r="I112" t="n">
-        <v>230285.992</v>
+        <v>217398.122</v>
       </c>
       <c r="J112" t="n">
-        <v>129.648</v>
+        <v>130.453</v>
       </c>
       <c r="K112" t="n">
-        <v>104995.458</v>
+        <v>117396.389</v>
       </c>
       <c r="L112" t="n">
-        <v>-7619.337</v>
+        <v>26000.343</v>
       </c>
       <c r="M112" t="n">
-        <v>-2.001</v>
+        <v>6.86</v>
       </c>
       <c r="N112" t="n">
-        <v>-14.653</v>
+        <v>1.419</v>
       </c>
       <c r="O112" t="n">
-        <v>-6.377</v>
-      </c>
-      <c r="P112" t="n">
-        <v>105514.171</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>128353.608</v>
-      </c>
-      <c r="R112" t="n">
-        <v>82.206</v>
-      </c>
-      <c r="S112" t="n">
-        <v>49.262</v>
-      </c>
-      <c r="T112" t="n">
-        <v>202.996</v>
+        <v>-1.845</v>
       </c>
       <c r="U112" t="n">
-        <v>5.911</v>
+        <v>7.045</v>
       </c>
       <c r="V112" t="n">
-        <v>-11110.827</v>
+        <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>9.757</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>4.818</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>-2.918</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.241</v>
+        <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_SSB_-_Bao_cao_tai_chinh_Hop_nhat_Quy_III.2025_kem_Giai_trinh_bien_dong_LNST_signed_1761901007.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250905_-_SSB_-_Bao_cao_tai_chinh_hop_nhat_soat_xet_ban_nien_2025_va_Giai_trinh_bien_dong_LNST_signed_1757323427.pdf</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>2026-08-31T15:43:36+07:00</t>
+          <t>2026-08-31T12:30:19+07:00</t>
         </is>
       </c>
     </row>
@@ -40929,7 +41302,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -40938,90 +41311,90 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>396443.131</v>
+        <v>380808.411</v>
       </c>
       <c r="F113" t="n">
-        <v>40372.594</v>
+        <v>40267.975</v>
       </c>
       <c r="G113" t="n">
-        <v>2451.866</v>
+        <v>2337.097</v>
       </c>
       <c r="H113" t="n">
-        <v>191807.215</v>
+        <v>177624.068</v>
       </c>
       <c r="I113" t="n">
-        <v>233780.41</v>
+        <v>230285.992</v>
       </c>
       <c r="J113" t="n">
-        <v>121.883</v>
+        <v>129.648</v>
       </c>
       <c r="K113" t="n">
-        <v>116960.044</v>
+        <v>104995.458</v>
       </c>
       <c r="L113" t="n">
-        <v>1371.248</v>
+        <v>-7619.337</v>
       </c>
       <c r="M113" t="n">
-        <v>0.346</v>
+        <v>-2.001</v>
       </c>
       <c r="N113" t="n">
-        <v>5.467</v>
+        <v>-14.653</v>
       </c>
       <c r="O113" t="n">
-        <v>0.265</v>
+        <v>-6.377</v>
       </c>
       <c r="P113" t="n">
-        <v>1049.962</v>
+        <v>105514.171</v>
       </c>
       <c r="Q113" t="n">
-        <v>8485.277</v>
+        <v>128353.608</v>
       </c>
       <c r="R113" t="n">
-        <v>12.374</v>
+        <v>82.206</v>
       </c>
       <c r="S113" t="n">
-        <v>601.513</v>
+        <v>49.262</v>
       </c>
       <c r="T113" t="n">
-        <v>16.625</v>
+        <v>202.996</v>
       </c>
       <c r="U113" t="n">
-        <v>6.098</v>
+        <v>5.911</v>
       </c>
       <c r="V113" t="n">
-        <v>25542.62000000001</v>
+        <v>-11110.827</v>
       </c>
       <c r="W113" t="n">
-        <v>16.854</v>
+        <v>9.757</v>
       </c>
       <c r="X113" t="n">
-        <v>20.183</v>
+        <v>4.818</v>
       </c>
       <c r="Y113" t="n">
-        <v>6.443</v>
+        <v>-2.918</v>
       </c>
       <c r="AC113" t="n">
-        <v>568</v>
+        <v>29</v>
       </c>
       <c r="AD113" t="n">
-        <v>23.166</v>
+        <v>1.241</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.407</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
       <c r="AG113" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260312_-_SSB_-_BCTC_hop_nhat_kiem_toan_nam_2025_kem_Giai_trinh_bien_dong_LNST_signed_1773310402.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_SSB_-_Bao_cao_tai_chinh_Hop_nhat_Quy_III.2025_kem_Giai_trinh_bien_dong_LNST_signed_1761901007.pdf</t>
         </is>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>2026-08-31T01:36:28+07:00</t>
+          <t>2026-08-31T15:43:36+07:00</t>
         </is>
       </c>
     </row>
@@ -41033,7 +41406,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -41042,90 +41415,90 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>403197.675</v>
+        <v>396443.131</v>
       </c>
       <c r="F114" t="n">
-        <v>41481.767</v>
+        <v>40372.594</v>
       </c>
       <c r="G114" t="n">
-        <v>2413.461</v>
+        <v>2451.866</v>
       </c>
       <c r="H114" t="n">
-        <v>185876.235</v>
+        <v>191807.215</v>
       </c>
       <c r="I114" t="n">
-        <v>235092.973</v>
+        <v>233780.41</v>
       </c>
       <c r="J114" t="n">
-        <v>126.478</v>
+        <v>121.883</v>
       </c>
       <c r="K114" t="n">
-        <v>122548.437</v>
+        <v>116960.044</v>
       </c>
       <c r="L114" t="n">
-        <v>10.278</v>
+        <v>1371.248</v>
       </c>
       <c r="M114" t="n">
-        <v>0.003</v>
+        <v>0.346</v>
       </c>
       <c r="N114" t="n">
-        <v>2.808</v>
+        <v>5.467</v>
       </c>
       <c r="O114" t="n">
-        <v>-5.176</v>
+        <v>0.265</v>
       </c>
       <c r="P114" t="n">
-        <v>90738.379</v>
+        <v>1049.962</v>
       </c>
       <c r="Q114" t="n">
-        <v>187912.121</v>
+        <v>8485.277</v>
       </c>
       <c r="R114" t="n">
-        <v>48.288</v>
+        <v>12.374</v>
       </c>
       <c r="S114" t="n">
-        <v>101.043</v>
+        <v>601.513</v>
       </c>
       <c r="T114" t="n">
-        <v>98.968</v>
+        <v>16.625</v>
       </c>
       <c r="U114" t="n">
-        <v>6.593</v>
+        <v>6.098</v>
       </c>
       <c r="V114" t="n">
-        <v>-40030.429</v>
+        <v>25542.62000000001</v>
       </c>
       <c r="W114" t="n">
-        <v>2.757</v>
+        <v>16.854</v>
       </c>
       <c r="X114" t="n">
-        <v>-0.174</v>
+        <v>20.183</v>
       </c>
       <c r="Y114" t="n">
-        <v>-9.928000000000001</v>
+        <v>6.443</v>
       </c>
       <c r="AC114" t="n">
-        <v>-225</v>
+        <v>568</v>
       </c>
       <c r="AD114" t="n">
-        <v>-9.323</v>
+        <v>23.166</v>
       </c>
       <c r="AE114" t="n">
-        <v>-0.542</v>
+        <v>1.407</v>
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
       <c r="AG114" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_SSB_-_BCTC_Hop_nhat_Quy_I.2026_va_Giai_trinh_bien_dong_LNST_signed_1777467537.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260312_-_SSB_-_BCTC_hop_nhat_kiem_toan_nam_2025_kem_Giai_trinh_bien_dong_LNST_signed_1773310402.pdf</t>
         </is>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>2026-08-31T23:48:58+07:00</t>
+          <t>2026-08-31T01:36:28+07:00</t>
         </is>
       </c>
     </row>
@@ -41137,7 +41510,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -41146,87 +41519,102 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>427107.51</v>
+        <v>403197.675</v>
       </c>
       <c r="F115" t="n">
-        <v>42195.287</v>
+        <v>41481.767</v>
       </c>
       <c r="G115" t="n">
-        <v>2249.952</v>
+        <v>2413.461</v>
       </c>
       <c r="H115" t="n">
-        <v>199777.344</v>
+        <v>185876.235</v>
       </c>
       <c r="I115" t="n">
-        <v>250063.019</v>
+        <v>235092.973</v>
       </c>
       <c r="J115" t="n">
-        <v>125.171</v>
+        <v>126.478</v>
       </c>
       <c r="K115" t="n">
-        <v>128387.671</v>
+        <v>122548.437</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>10.278</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.808</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>-5.176</v>
+      </c>
+      <c r="P115" t="n">
+        <v>90738.379</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>187912.121</v>
+      </c>
+      <c r="R115" t="n">
+        <v>48.288</v>
+      </c>
+      <c r="S115" t="n">
+        <v>101.043</v>
+      </c>
+      <c r="T115" t="n">
+        <v>98.968</v>
       </c>
       <c r="U115" t="n">
-        <v>6.427</v>
+        <v>6.593</v>
       </c>
       <c r="V115" t="n">
-        <v>-15815.236</v>
+        <v>-40030.429</v>
       </c>
       <c r="W115" t="n">
-        <v>0.001</v>
+        <v>2.757</v>
       </c>
       <c r="X115" t="n">
-        <v>0.138</v>
+        <v>-0.174</v>
       </c>
       <c r="Y115" t="n">
-        <v>-3.703</v>
+        <v>-9.928000000000001</v>
       </c>
       <c r="AC115" t="n">
-        <v>-24</v>
+        <v>-225</v>
       </c>
       <c r="AD115" t="n">
-        <v>-1.067</v>
+        <v>-9.323</v>
       </c>
       <c r="AE115" t="n">
-        <v>-0.057</v>
+        <v>-0.542</v>
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
       <c r="AG115" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_202608142020SSB2020Bao20cao20tai20chinh20hop20nhat20soat20xet20ban20nien20202620va20Giai20trinh20bien20dong20LNST_signed_20082026090228.pdf?v=1787191350112</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_SSB_-_BCTC_Hop_nhat_Quy_I.2026_va_Giai_trinh_bien_dong_LNST_signed_1777467537.pdf</t>
         </is>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>2026-09-01T10:03:22+07:00</t>
+          <t>2026-08-31T23:48:58+07:00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>SSB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -41235,75 +41623,75 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>757093.326</v>
+        <v>427107.51</v>
       </c>
       <c r="F116" t="n">
-        <v>57862.377</v>
+        <v>42195.287</v>
       </c>
       <c r="G116" t="n">
-        <v>6863.173</v>
+        <v>2249.952</v>
       </c>
       <c r="H116" t="n">
-        <v>585569.336</v>
+        <v>199777.344</v>
       </c>
       <c r="I116" t="n">
-        <v>553760.8419999999</v>
+        <v>250063.019</v>
       </c>
       <c r="J116" t="n">
-        <v>94.568</v>
+        <v>125.171</v>
       </c>
       <c r="K116" t="n">
-        <v>100730.034</v>
+        <v>128387.671</v>
       </c>
       <c r="L116" t="n">
-        <v>8816.550999999999</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>1.165</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>1.202</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>1.202</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>1.72</v>
+        <v>6.427</v>
       </c>
       <c r="V116" t="n">
-        <v>0</v>
+        <v>-15815.236</v>
       </c>
       <c r="W116" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>-3.703</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>-1.067</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>-0.057</v>
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG116" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-si-gn-thng-tn26042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_202608142020SSB2020Bao20cao20tai20chinh20hop20nhat20soat20xet20ban20nien20202620va20Giai20trinh20bien20dong20LNST_signed_20082026090228.pdf?v=1787191350112</t>
         </is>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>2026-08-31T10:34:12+07:00</t>
+          <t>2026-09-01T10:03:22+07:00</t>
         </is>
       </c>
     </row>
@@ -41315,7 +41703,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -41324,55 +41712,40 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>807339.224</v>
+        <v>757093.326</v>
       </c>
       <c r="F117" t="n">
-        <v>59821.207</v>
+        <v>57862.377</v>
       </c>
       <c r="G117" t="n">
-        <v>6585.077</v>
+        <v>6863.173</v>
       </c>
       <c r="H117" t="n">
-        <v>624314.777</v>
+        <v>585569.336</v>
       </c>
       <c r="I117" t="n">
-        <v>577041.997</v>
+        <v>553760.8419999999</v>
       </c>
       <c r="J117" t="n">
-        <v>92.428</v>
+        <v>94.568</v>
       </c>
       <c r="K117" t="n">
-        <v>125819.938</v>
+        <v>100730.034</v>
       </c>
       <c r="L117" t="n">
-        <v>-70865.32000000001</v>
+        <v>8816.550999999999</v>
       </c>
       <c r="M117" t="n">
-        <v>-8.778</v>
+        <v>1.165</v>
       </c>
       <c r="N117" t="n">
-        <v>-11.204</v>
+        <v>1.202</v>
       </c>
       <c r="O117" t="n">
-        <v>-21.918</v>
-      </c>
-      <c r="P117" t="n">
-        <v>747518.017</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>1027194.659</v>
-      </c>
-      <c r="R117" t="n">
-        <v>72.773</v>
-      </c>
-      <c r="S117" t="n">
-        <v>80.223</v>
-      </c>
-      <c r="T117" t="n">
-        <v>124.652</v>
+        <v>1.202</v>
       </c>
       <c r="U117" t="n">
-        <v>2.015</v>
+        <v>1.72</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
@@ -41397,17 +41770,17 @@
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/STB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025100208.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-si-gn-thng-tn26042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>2026-08-31T12:33:00+07:00</t>
+          <t>2026-08-31T10:34:12+07:00</t>
         </is>
       </c>
     </row>
@@ -41419,7 +41792,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -41428,40 +41801,55 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>848942.045</v>
+        <v>807339.224</v>
       </c>
       <c r="F118" t="n">
-        <v>62704.792</v>
+        <v>59821.207</v>
       </c>
       <c r="G118" t="n">
-        <v>7874.366</v>
+        <v>6585.077</v>
       </c>
       <c r="H118" t="n">
-        <v>641102.057</v>
+        <v>624314.777</v>
       </c>
       <c r="I118" t="n">
-        <v>590505.804</v>
+        <v>577041.997</v>
       </c>
       <c r="J118" t="n">
-        <v>92.108</v>
+        <v>92.428</v>
       </c>
       <c r="K118" t="n">
-        <v>144124.589</v>
+        <v>125819.938</v>
       </c>
       <c r="L118" t="n">
-        <v>4.123</v>
+        <v>-70865.32000000001</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>-8.778</v>
       </c>
       <c r="N118" t="n">
-        <v>2.269</v>
+        <v>-11.204</v>
       </c>
       <c r="O118" t="n">
-        <v>2.976</v>
+        <v>-21.918</v>
+      </c>
+      <c r="P118" t="n">
+        <v>747518.017</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1027194.659</v>
+      </c>
+      <c r="R118" t="n">
+        <v>72.773</v>
+      </c>
+      <c r="S118" t="n">
+        <v>80.223</v>
+      </c>
+      <c r="T118" t="n">
+        <v>124.652</v>
       </c>
       <c r="U118" t="n">
-        <v>2.248</v>
+        <v>2.015</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -41486,17 +41874,17 @@
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG118" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251029_-_STB_-_BCTC_Hop_nhat_Q3.2025_1761804289.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/STB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025100208.pdf</t>
         </is>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>2026-08-31T15:46:18+07:00</t>
+          <t>2026-08-31T12:33:00+07:00</t>
         </is>
       </c>
     </row>
@@ -41508,7 +41896,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -41517,55 +41905,40 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>917119.803</v>
+        <v>848942.045</v>
       </c>
       <c r="F119" t="n">
-        <v>59866.744</v>
+        <v>62704.792</v>
       </c>
       <c r="G119" t="n">
-        <v>5358.002</v>
+        <v>7874.366</v>
       </c>
       <c r="H119" t="n">
-        <v>618341.672</v>
+        <v>641102.057</v>
       </c>
       <c r="I119" t="n">
-        <v>606336.3909999999</v>
+        <v>590505.804</v>
       </c>
       <c r="J119" t="n">
-        <v>98.05800000000001</v>
+        <v>92.108</v>
       </c>
       <c r="K119" t="n">
-        <v>195970.826</v>
+        <v>144124.589</v>
       </c>
       <c r="L119" t="n">
-        <v>-147426.407</v>
+        <v>4.123</v>
       </c>
       <c r="M119" t="n">
-        <v>-16.075</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>-18.767</v>
+        <v>2.269</v>
       </c>
       <c r="O119" t="n">
-        <v>-27.515</v>
-      </c>
-      <c r="P119" t="n">
-        <v>854290.316</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>1114189.719</v>
-      </c>
-      <c r="R119" t="n">
-        <v>76.67400000000001</v>
-      </c>
-      <c r="S119" t="n">
-        <v>82.57899999999999</v>
-      </c>
-      <c r="T119" t="n">
-        <v>121.097</v>
+        <v>2.976</v>
       </c>
       <c r="U119" t="n">
-        <v>3.169</v>
+        <v>2.248</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -41590,17 +41963,17 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
       <c r="AG119" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_STB_-_BCTC_Hop_nhat_nam_2025_da_kiem_toan__1774863040.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251029_-_STB_-_BCTC_Hop_nhat_Q3.2025_1761804289.pdf</t>
         </is>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>2026-08-31T01:38:47+07:00</t>
+          <t>2026-08-31T15:46:18+07:00</t>
         </is>
       </c>
     </row>
@@ -41612,7 +41985,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -41621,94 +41994,90 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>859571.527</v>
+        <v>917119.803</v>
       </c>
       <c r="F120" t="n">
-        <v>61476.611</v>
+        <v>59866.744</v>
       </c>
       <c r="G120" t="n">
-        <v>6042.042</v>
+        <v>5358.002</v>
       </c>
       <c r="H120" t="n">
-        <v>600788.965</v>
+        <v>618341.672</v>
       </c>
       <c r="I120" t="n">
-        <v>604877.709</v>
+        <v>606336.3909999999</v>
       </c>
       <c r="J120" t="n">
-        <v>100.681</v>
+        <v>98.05800000000001</v>
       </c>
       <c r="K120" t="n">
-        <v>136075.405</v>
+        <v>195970.826</v>
       </c>
       <c r="L120" t="n">
-        <v>-53926.931</v>
+        <v>-147426.407</v>
       </c>
       <c r="M120" t="n">
-        <v>-6.274</v>
+        <v>-16.075</v>
       </c>
       <c r="N120" t="n">
-        <v>-10.42</v>
+        <v>-18.767</v>
       </c>
       <c r="O120" t="n">
-        <v>-19.247</v>
+        <v>-27.515</v>
       </c>
       <c r="P120" t="n">
-        <v>776960.677</v>
+        <v>854290.316</v>
       </c>
       <c r="Q120" t="n">
-        <v>281789.178</v>
+        <v>1114189.719</v>
       </c>
       <c r="R120" t="n">
-        <v>275.724</v>
+        <v>76.67400000000001</v>
       </c>
       <c r="S120" t="n">
-        <v>29.317</v>
+        <v>82.57899999999999</v>
       </c>
       <c r="T120" t="n">
-        <v>341.104</v>
+        <v>121.097</v>
       </c>
       <c r="U120" t="n">
-        <v>2.265</v>
+        <v>3.169</v>
       </c>
       <c r="V120" t="n">
-        <v>-38127.26599999999</v>
+        <v>0</v>
       </c>
       <c r="W120" t="n">
-        <v>1.911</v>
+        <v>0</v>
       </c>
       <c r="X120" t="n">
-        <v>27.897</v>
+        <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>-4.436</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>803932.3370000001</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>776334.534</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>103.555</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>659</v>
+        <v>0</v>
       </c>
       <c r="AD120" t="n">
-        <v>10.907</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.072</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy I 2026, OCR khong doc duoc)</t>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_STB_-_BCTC_Hop_nhat_nam_2025_da_kiem_toan__1774863040.pdf</t>
         </is>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>2026-09-17T14:38:33+07:00</t>
+          <t>2026-08-31T01:38:47+07:00</t>
         </is>
       </c>
     </row>
@@ -41720,7 +42089,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -41729,89 +42098,89 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>892048.566</v>
+        <v>859571.527</v>
       </c>
       <c r="F121" t="n">
-        <v>62807.249</v>
+        <v>61476.611</v>
       </c>
       <c r="G121" t="n">
-        <v>6247.243</v>
+        <v>6042.042</v>
       </c>
       <c r="H121" t="n">
-        <v>647939.224</v>
+        <v>600788.965</v>
       </c>
       <c r="I121" t="n">
-        <v>608851.996</v>
+        <v>604877.709</v>
       </c>
       <c r="J121" t="n">
-        <v>93.967</v>
+        <v>100.681</v>
       </c>
       <c r="K121" t="n">
-        <v>154058.217</v>
+        <v>136075.405</v>
       </c>
       <c r="L121" t="n">
-        <v>-32668.77299999999</v>
+        <v>-53926.931</v>
       </c>
       <c r="M121" t="n">
-        <v>-3.662</v>
+        <v>-6.274</v>
       </c>
       <c r="N121" t="n">
-        <v>-5.884</v>
+        <v>-10.42</v>
       </c>
       <c r="O121" t="n">
-        <v>-14.194</v>
+        <v>-19.247</v>
       </c>
       <c r="P121" t="n">
-        <v>776523.792</v>
+        <v>776960.677</v>
       </c>
       <c r="Q121" t="n">
-        <v>280549.491</v>
+        <v>281789.178</v>
       </c>
       <c r="R121" t="n">
-        <v>276.787</v>
+        <v>275.724</v>
       </c>
       <c r="S121" t="n">
-        <v>41.178</v>
+        <v>29.317</v>
       </c>
       <c r="T121" t="n">
-        <v>242.848</v>
+        <v>341.104</v>
       </c>
       <c r="U121" t="n">
-        <v>2.378</v>
+        <v>2.265</v>
       </c>
       <c r="V121" t="n">
-        <v>-7187.399999999994</v>
+        <v>-38127.26599999999</v>
       </c>
       <c r="W121" t="n">
-        <v>2.313</v>
+        <v>1.911</v>
       </c>
       <c r="X121" t="n">
-        <v>29.993</v>
+        <v>27.897</v>
       </c>
       <c r="Y121" t="n">
-        <v>-0.806</v>
+        <v>-4.436</v>
       </c>
       <c r="Z121" t="n">
-        <v>820020.6800000001</v>
+        <v>803932.3370000001</v>
       </c>
       <c r="AA121" t="n">
-        <v>808189.617</v>
+        <v>776334.534</v>
       </c>
       <c r="AB121" t="n">
-        <v>101.464</v>
+        <v>103.555</v>
       </c>
       <c r="AC121" t="n">
-        <v>923</v>
+        <v>659</v>
       </c>
       <c r="AD121" t="n">
-        <v>14.775</v>
+        <v>10.907</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.47</v>
+        <v>1.072</v>
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy II 2026, OCR khong doc duoc)</t>
+          <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy I 2026, OCR khong doc duoc)</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
@@ -41823,12 +42192,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -41837,90 +42206,94 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>989215.993</v>
+        <v>892048.566</v>
       </c>
       <c r="F122" t="n">
-        <v>153952.665</v>
+        <v>62807.249</v>
       </c>
       <c r="G122" t="n">
-        <v>8305.393</v>
+        <v>6247.243</v>
       </c>
       <c r="H122" t="n">
-        <v>531583.052</v>
+        <v>647939.224</v>
       </c>
       <c r="I122" t="n">
-        <v>655007.208</v>
+        <v>608851.996</v>
       </c>
       <c r="J122" t="n">
-        <v>123.218</v>
+        <v>93.967</v>
       </c>
       <c r="K122" t="n">
-        <v>148372.369</v>
+        <v>154058.217</v>
       </c>
       <c r="L122" t="n">
-        <v>-28602.92</v>
+        <v>-32668.77299999999</v>
       </c>
       <c r="M122" t="n">
-        <v>-2.891</v>
+        <v>-3.662</v>
       </c>
       <c r="N122" t="n">
-        <v>-6.045</v>
+        <v>-5.884</v>
       </c>
       <c r="O122" t="n">
-        <v>-3.22</v>
+        <v>-14.194</v>
       </c>
       <c r="P122" t="n">
-        <v>537576.323</v>
+        <v>776523.792</v>
       </c>
       <c r="Q122" t="n">
-        <v>492843.989</v>
+        <v>280549.491</v>
       </c>
       <c r="R122" t="n">
-        <v>109.076</v>
+        <v>276.787</v>
       </c>
       <c r="S122" t="n">
-        <v>91.639</v>
+        <v>41.178</v>
       </c>
       <c r="T122" t="n">
-        <v>109.123</v>
+        <v>242.848</v>
       </c>
       <c r="U122" t="n">
-        <v>2.791</v>
+        <v>2.378</v>
       </c>
       <c r="V122" t="n">
-        <v>12025.473</v>
+        <v>-7187.399999999994</v>
       </c>
       <c r="W122" t="n">
-        <v>4.396</v>
+        <v>2.313</v>
       </c>
       <c r="X122" t="n">
-        <v>-6.833</v>
+        <v>29.993</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.216</v>
+        <v>-0.806</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>820020.6800000001</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>808189.617</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>101.464</v>
       </c>
       <c r="AC122" t="n">
-        <v>-470</v>
+        <v>923</v>
       </c>
       <c r="AD122" t="n">
-        <v>-5.659</v>
+        <v>14.775</v>
       </c>
       <c r="AE122" t="n">
-        <v>-0.305</v>
+        <v>1.47</v>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00001234567901234568ngn-hng-tmcp-k-thng-vit-nam21042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
+          <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy II 2026, OCR khong doc duoc)</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>2026-08-31T10:35:54+07:00</t>
+          <t>2026-09-17T14:38:33+07:00</t>
         </is>
       </c>
     </row>
@@ -41932,7 +42305,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -41941,90 +42314,90 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1037645.395</v>
+        <v>989215.993</v>
       </c>
       <c r="F123" t="n">
-        <v>161827.229</v>
+        <v>153952.665</v>
       </c>
       <c r="G123" t="n">
-        <v>9137.075999999999</v>
+        <v>8305.393</v>
       </c>
       <c r="H123" t="n">
-        <v>545078.843</v>
+        <v>531583.052</v>
       </c>
       <c r="I123" t="n">
-        <v>700801.926</v>
+        <v>655007.208</v>
       </c>
       <c r="J123" t="n">
-        <v>128.569</v>
+        <v>123.218</v>
       </c>
       <c r="K123" t="n">
-        <v>132997.785</v>
+        <v>148372.369</v>
       </c>
       <c r="L123" t="n">
-        <v>-64704.99100000001</v>
+        <v>-28602.92</v>
       </c>
       <c r="M123" t="n">
-        <v>-6.236</v>
+        <v>-2.891</v>
       </c>
       <c r="N123" t="n">
-        <v>-7.932</v>
+        <v>-6.045</v>
       </c>
       <c r="O123" t="n">
-        <v>-2.093</v>
+        <v>-3.22</v>
       </c>
       <c r="P123" t="n">
-        <v>-64704.991</v>
+        <v>537576.323</v>
       </c>
       <c r="Q123" t="n">
-        <v>409618.537</v>
+        <v>492843.989</v>
       </c>
       <c r="R123" t="n">
-        <v>-15.796</v>
+        <v>109.076</v>
       </c>
       <c r="S123" t="n">
-        <v>92.209</v>
+        <v>91.639</v>
       </c>
       <c r="T123" t="n">
-        <v>108.45</v>
+        <v>109.123</v>
       </c>
       <c r="U123" t="n">
-        <v>2.44</v>
+        <v>2.791</v>
       </c>
       <c r="V123" t="n">
-        <v>0</v>
+        <v>12025.473</v>
       </c>
       <c r="W123" t="n">
-        <v>0</v>
+        <v>4.396</v>
       </c>
       <c r="X123" t="n">
-        <v>0</v>
+        <v>-6.833</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.216</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>-470</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>-5.659</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>-0.305</v>
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG123" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025101639.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00001234567901234568ngn-hng-tmcp-k-thng-vit-nam21042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>2026-08-31T12:36:30+07:00</t>
+          <t>2026-08-31T10:35:54+07:00</t>
         </is>
       </c>
     </row>
@@ -42036,7 +42409,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -42045,75 +42418,90 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1129570.458</v>
+        <v>1037645.395</v>
       </c>
       <c r="F124" t="n">
-        <v>179430.593</v>
+        <v>161827.229</v>
       </c>
       <c r="G124" t="n">
-        <v>9924.643</v>
+        <v>9137.075999999999</v>
       </c>
       <c r="H124" t="n">
-        <v>595086.941</v>
+        <v>545078.843</v>
       </c>
       <c r="I124" t="n">
-        <v>756078.003</v>
+        <v>700801.926</v>
       </c>
       <c r="J124" t="n">
-        <v>127.053</v>
+        <v>128.569</v>
       </c>
       <c r="K124" t="n">
-        <v>174631.238</v>
+        <v>132997.785</v>
       </c>
       <c r="L124" t="n">
-        <v>-63749.289</v>
+        <v>-64704.99100000001</v>
       </c>
       <c r="M124" t="n">
-        <v>-5.644</v>
+        <v>-6.236</v>
       </c>
       <c r="N124" t="n">
-        <v>17.559</v>
+        <v>-7.932</v>
       </c>
       <c r="O124" t="n">
-        <v>29.356</v>
+        <v>-2.093</v>
+      </c>
+      <c r="P124" t="n">
+        <v>-64704.991</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>409618.537</v>
+      </c>
+      <c r="R124" t="n">
+        <v>-15.796</v>
+      </c>
+      <c r="S124" t="n">
+        <v>92.209</v>
+      </c>
+      <c r="T124" t="n">
+        <v>108.45</v>
       </c>
       <c r="U124" t="n">
-        <v>2.935</v>
+        <v>2.44</v>
       </c>
       <c r="V124" t="n">
-        <v>77046.068</v>
+        <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>1.404</v>
+        <v>0</v>
       </c>
       <c r="X124" t="n">
-        <v>-0.951</v>
+        <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>6.821</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="AD124" t="n">
-        <v>0.967</v>
+        <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG124" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251021_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-3Q25_1761042656.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025101639.pdf</t>
         </is>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>2026-08-31T15:48:08+07:00</t>
+          <t>2026-08-31T12:36:30+07:00</t>
         </is>
       </c>
     </row>
@@ -42125,7 +42513,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -42134,90 +42522,75 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1192344.137</v>
+        <v>1129570.458</v>
       </c>
       <c r="F125" t="n">
-        <v>179501.442</v>
+        <v>179430.593</v>
       </c>
       <c r="G125" t="n">
-        <v>10787.979</v>
+        <v>9924.643</v>
       </c>
       <c r="H125" t="n">
-        <v>618911.535</v>
+        <v>595086.941</v>
       </c>
       <c r="I125" t="n">
-        <v>757118.751</v>
+        <v>756078.003</v>
       </c>
       <c r="J125" t="n">
-        <v>122.331</v>
+        <v>127.053</v>
       </c>
       <c r="K125" t="n">
-        <v>201481.905</v>
+        <v>174631.238</v>
       </c>
       <c r="L125" t="n">
-        <v>-31183.875</v>
+        <v>-63749.289</v>
       </c>
       <c r="M125" t="n">
-        <v>-2.615</v>
+        <v>-5.644</v>
       </c>
       <c r="N125" t="n">
-        <v>-5.35</v>
+        <v>17.559</v>
       </c>
       <c r="O125" t="n">
-        <v>-3.451</v>
-      </c>
-      <c r="P125" t="n">
-        <v>-121644.354</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>732641.061</v>
-      </c>
-      <c r="R125" t="n">
-        <v>-16.604</v>
-      </c>
-      <c r="S125" t="n">
-        <v>92.86799999999999</v>
-      </c>
-      <c r="T125" t="n">
-        <v>107.68</v>
+        <v>29.356</v>
       </c>
       <c r="U125" t="n">
-        <v>3.255</v>
+        <v>2.935</v>
       </c>
       <c r="V125" t="n">
-        <v>-95355.82799999998</v>
+        <v>77046.068</v>
       </c>
       <c r="W125" t="n">
-        <v>-8.385</v>
+        <v>1.404</v>
       </c>
       <c r="X125" t="n">
-        <v>-11</v>
+        <v>-0.951</v>
       </c>
       <c r="Y125" t="n">
-        <v>-7.997</v>
+        <v>6.821</v>
       </c>
       <c r="AC125" t="n">
-        <v>-1000</v>
+        <v>96</v>
       </c>
       <c r="AD125" t="n">
-        <v>-9.27</v>
+        <v>0.967</v>
       </c>
       <c r="AE125" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.054</v>
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
       <c r="AG125" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260317_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-YE25_1773755161.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251021_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-3Q25_1761042656.pdf</t>
         </is>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>2026-08-31T01:41:25+07:00</t>
+          <t>2026-08-31T15:48:08+07:00</t>
         </is>
       </c>
     </row>
@@ -42229,7 +42602,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -42238,90 +42611,90 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1190453.754</v>
+        <v>1192344.137</v>
       </c>
       <c r="F126" t="n">
-        <v>186682.773</v>
+        <v>179501.442</v>
       </c>
       <c r="G126" t="n">
-        <v>9522.053</v>
+        <v>10787.979</v>
       </c>
       <c r="H126" t="n">
-        <v>599808.238</v>
+        <v>618911.535</v>
       </c>
       <c r="I126" t="n">
-        <v>785612.53</v>
+        <v>757118.751</v>
       </c>
       <c r="J126" t="n">
-        <v>130.977</v>
+        <v>122.331</v>
       </c>
       <c r="K126" t="n">
-        <v>186252.399</v>
+        <v>201481.905</v>
       </c>
       <c r="L126" t="n">
-        <v>-2492.354</v>
+        <v>-31183.875</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.209</v>
+        <v>-2.615</v>
       </c>
       <c r="N126" t="n">
-        <v>-1.301</v>
+        <v>-5.35</v>
       </c>
       <c r="O126" t="n">
-        <v>-6.356</v>
+        <v>-3.451</v>
       </c>
       <c r="P126" t="n">
-        <v>676754.978</v>
+        <v>-121644.354</v>
       </c>
       <c r="Q126" t="n">
-        <v>601221.118</v>
+        <v>732641.061</v>
       </c>
       <c r="R126" t="n">
-        <v>112.563</v>
+        <v>-16.604</v>
       </c>
       <c r="S126" t="n">
-        <v>85.443</v>
+        <v>92.86799999999999</v>
       </c>
       <c r="T126" t="n">
-        <v>117.038</v>
+        <v>107.68</v>
       </c>
       <c r="U126" t="n">
-        <v>3.105</v>
+        <v>3.255</v>
       </c>
       <c r="V126" t="n">
-        <v>31803.23300000001</v>
+        <v>-95355.82799999998</v>
       </c>
       <c r="W126" t="n">
-        <v>4.369</v>
+        <v>-8.385</v>
       </c>
       <c r="X126" t="n">
-        <v>-0.99</v>
+        <v>-11</v>
       </c>
       <c r="Y126" t="n">
-        <v>2.672</v>
+        <v>-7.997</v>
       </c>
       <c r="AC126" t="n">
-        <v>-178</v>
+        <v>-1000</v>
       </c>
       <c r="AD126" t="n">
-        <v>-1.869</v>
+        <v>-9.27</v>
       </c>
       <c r="AE126" t="n">
-        <v>-0.095</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260421_-_TCB_-_bao_cao_tai_chinh_hop_nhat_1Q26_VAS_VN__1776825559.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260317_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-YE25_1773755161.pdf</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>2026-08-31T23:55:42+07:00</t>
+          <t>2026-08-31T01:41:25+07:00</t>
         </is>
       </c>
     </row>
@@ -42333,7 +42706,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -42342,102 +42715,102 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1273076.923</v>
+        <v>1190453.754</v>
       </c>
       <c r="F127" t="n">
-        <v>188997.15</v>
+        <v>186682.773</v>
       </c>
       <c r="G127" t="n">
-        <v>10763.002</v>
+        <v>9522.053</v>
       </c>
       <c r="H127" t="n">
-        <v>662447.73</v>
+        <v>599808.238</v>
       </c>
       <c r="I127" t="n">
-        <v>835813.2830000001</v>
+        <v>785612.53</v>
       </c>
       <c r="J127" t="n">
-        <v>126.17</v>
+        <v>130.977</v>
       </c>
       <c r="K127" t="n">
-        <v>184453.92</v>
+        <v>186252.399</v>
       </c>
       <c r="L127" t="n">
-        <v>-8462.984</v>
+        <v>-2492.354</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.665</v>
+        <v>-0.209</v>
       </c>
       <c r="N127" t="n">
-        <v>-3.883</v>
+        <v>-1.301</v>
       </c>
       <c r="O127" t="n">
-        <v>-4.521</v>
+        <v>-6.356</v>
       </c>
       <c r="P127" t="n">
-        <v>739557.791</v>
+        <v>676754.978</v>
       </c>
       <c r="Q127" t="n">
-        <v>259255.935</v>
+        <v>601221.118</v>
       </c>
       <c r="R127" t="n">
-        <v>285.262</v>
+        <v>112.563</v>
       </c>
       <c r="S127" t="n">
-        <v>72.98699999999999</v>
+        <v>85.443</v>
       </c>
       <c r="T127" t="n">
-        <v>137.01</v>
+        <v>117.038</v>
       </c>
       <c r="U127" t="n">
-        <v>2.784</v>
+        <v>3.105</v>
       </c>
       <c r="V127" t="n">
-        <v>49624.19500000001</v>
+        <v>31803.23300000001</v>
       </c>
       <c r="W127" t="n">
-        <v>9.231999999999999</v>
+        <v>4.369</v>
       </c>
       <c r="X127" t="n">
-        <v>15.674</v>
+        <v>-0.99</v>
       </c>
       <c r="Y127" t="n">
-        <v>3.898</v>
+        <v>2.672</v>
       </c>
       <c r="AC127" t="n">
-        <v>1078</v>
+        <v>-178</v>
       </c>
       <c r="AD127" t="n">
-        <v>10.016</v>
+        <v>-1.869</v>
       </c>
       <c r="AE127" t="n">
-        <v>0.57</v>
+        <v>-0.095</v>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_202608132020TCB2020Bao20cao20tai20chinh20hop20nhat20soat20xet202Q2026_19082026102705.pdf?v=1787110027315</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260421_-_TCB_-_bao_cao_tai_chinh_hop_nhat_1Q26_VAS_VN__1776825559.pdf</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>2026-09-01T10:12:04+07:00</t>
+          <t>2026-08-31T23:55:42+07:00</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TPB</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -42446,99 +42819,90 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>388891.15</v>
+        <v>1273076.923</v>
       </c>
       <c r="F128" t="n">
-        <v>39491.596</v>
+        <v>188997.15</v>
       </c>
       <c r="G128" t="n">
-        <v>3383.618</v>
+        <v>10763.002</v>
       </c>
       <c r="H128" t="n">
-        <v>233114.646</v>
+        <v>662447.73</v>
       </c>
       <c r="I128" t="n">
-        <v>259070.461</v>
+        <v>835813.2830000001</v>
       </c>
       <c r="J128" t="n">
-        <v>111.134</v>
+        <v>126.17</v>
       </c>
       <c r="K128" t="n">
-        <v>53519.87700000001</v>
+        <v>184453.92</v>
       </c>
       <c r="L128" t="n">
-        <v>1173.397999999997</v>
+        <v>-8462.984</v>
       </c>
       <c r="M128" t="n">
-        <v>0.302</v>
+        <v>-0.665</v>
       </c>
       <c r="N128" t="n">
-        <v>0.283</v>
+        <v>-3.883</v>
       </c>
       <c r="O128" t="n">
-        <v>0.323</v>
+        <v>-4.521</v>
       </c>
       <c r="P128" t="n">
-        <v>29361.059</v>
+        <v>739557.791</v>
       </c>
       <c r="Q128" t="n">
-        <v>206.249</v>
+        <v>259255.935</v>
       </c>
       <c r="R128" t="n">
-        <v>14235.734</v>
+        <v>285.262</v>
       </c>
       <c r="S128" t="n">
-        <v>19232.121</v>
+        <v>72.98699999999999</v>
       </c>
       <c r="T128" t="n">
-        <v>0.52</v>
+        <v>137.01</v>
       </c>
       <c r="U128" t="n">
-        <v>2.296</v>
+        <v>2.784</v>
       </c>
       <c r="V128" t="n">
-        <v>47597.061</v>
+        <v>49624.19500000001</v>
       </c>
       <c r="W128" t="n">
-        <v>12.611</v>
+        <v>9.231999999999999</v>
       </c>
       <c r="X128" t="n">
-        <v>12.468</v>
+        <v>15.674</v>
       </c>
       <c r="Y128" t="n">
-        <v>12.239</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>62861.954</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>35233.365</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>178.416</v>
+        <v>3.898</v>
       </c>
       <c r="AC128" t="n">
-        <v>461</v>
+        <v>1078</v>
       </c>
       <c r="AD128" t="n">
-        <v>13.624</v>
+        <v>10.016</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.167</v>
+        <v>0.57</v>
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_Q1_2025_Hopnhat_23052025145349.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_202608132020TCB2020Bao20cao20tai20chinh20hop20nhat20soat20xet202Q2026_19082026102705.pdf?v=1787110027315</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>2026-09-17T15:27:28+07:00</t>
+          <t>2026-09-01T10:12:04+07:00</t>
         </is>
       </c>
     </row>
@@ -42550,7 +42914,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -42559,99 +42923,99 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>428589.979</v>
+        <v>388891.15</v>
       </c>
       <c r="F129" t="n">
-        <v>38229.908</v>
+        <v>39491.596</v>
       </c>
       <c r="G129" t="n">
-        <v>3151.325</v>
+        <v>3383.618</v>
       </c>
       <c r="H129" t="n">
-        <v>246844.312</v>
+        <v>233114.646</v>
       </c>
       <c r="I129" t="n">
-        <v>281188.723</v>
+        <v>259070.461</v>
       </c>
       <c r="J129" t="n">
-        <v>113.913</v>
+        <v>111.134</v>
       </c>
       <c r="K129" t="n">
-        <v>71542.25599999999</v>
+        <v>53519.87700000001</v>
       </c>
       <c r="L129" t="n">
-        <v>-68400.776</v>
+        <v>1173.397999999997</v>
       </c>
       <c r="M129" t="n">
-        <v>-15.959</v>
+        <v>0.302</v>
       </c>
       <c r="N129" t="n">
-        <v>-17.579</v>
+        <v>0.283</v>
       </c>
       <c r="O129" t="n">
-        <v>-17.575</v>
+        <v>0.323</v>
       </c>
       <c r="P129" t="n">
-        <v>322684.431</v>
+        <v>29361.059</v>
       </c>
       <c r="Q129" t="n">
-        <v>164687.777</v>
+        <v>206.249</v>
       </c>
       <c r="R129" t="n">
-        <v>195.937</v>
+        <v>14235.734</v>
       </c>
       <c r="S129" t="n">
-        <v>64.307</v>
+        <v>19232.121</v>
       </c>
       <c r="T129" t="n">
-        <v>155.504</v>
+        <v>0.52</v>
       </c>
       <c r="U129" t="n">
-        <v>2.898</v>
+        <v>2.296</v>
       </c>
       <c r="V129" t="n">
-        <v>-23865.841</v>
+        <v>47597.061</v>
       </c>
       <c r="W129" t="n">
-        <v>0</v>
+        <v>12.611</v>
       </c>
       <c r="X129" t="n">
-        <v>4.669</v>
+        <v>12.468</v>
       </c>
       <c r="Y129" t="n">
-        <v>-5.568</v>
+        <v>12.239</v>
       </c>
       <c r="Z129" t="n">
-        <v>846378.6310000001</v>
+        <v>62861.954</v>
       </c>
       <c r="AA129" t="n">
-        <v>898757.455</v>
+        <v>35233.365</v>
       </c>
       <c r="AB129" t="n">
-        <v>94.172</v>
+        <v>178.416</v>
       </c>
       <c r="AC129" t="n">
-        <v>82</v>
+        <v>461</v>
       </c>
       <c r="AD129" t="n">
-        <v>2.602</v>
+        <v>13.624</v>
       </c>
       <c r="AE129" t="n">
-        <v>0.214</v>
+        <v>1.167</v>
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG129" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025102458.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_Q1_2025_Hopnhat_23052025145349.pdf</t>
         </is>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>2026-09-17T16:32:56+07:00</t>
+          <t>2026-09-17T15:27:28+07:00</t>
         </is>
       </c>
     </row>
@@ -42663,7 +43027,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -42672,99 +43036,99 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>451893.195</v>
+        <v>428589.979</v>
       </c>
       <c r="F130" t="n">
-        <v>39993.24</v>
+        <v>38229.908</v>
       </c>
       <c r="G130" t="n">
-        <v>3237.619</v>
+        <v>3151.325</v>
       </c>
       <c r="H130" t="n">
-        <v>260245.786</v>
+        <v>246844.312</v>
       </c>
       <c r="I130" t="n">
-        <v>292020.111</v>
+        <v>281188.723</v>
       </c>
       <c r="J130" t="n">
-        <v>112.209</v>
+        <v>113.913</v>
       </c>
       <c r="K130" t="n">
-        <v>87563.264</v>
+        <v>71542.25599999999</v>
       </c>
       <c r="L130" t="n">
-        <v>-224607.003</v>
+        <v>-68400.776</v>
       </c>
       <c r="M130" t="n">
-        <v>-49.704</v>
+        <v>-15.959</v>
       </c>
       <c r="N130" t="n">
-        <v>-53.901</v>
+        <v>-17.579</v>
       </c>
       <c r="O130" t="n">
-        <v>-36.315</v>
+        <v>-17.575</v>
       </c>
       <c r="P130" t="n">
-        <v>411899.955</v>
+        <v>322684.431</v>
       </c>
       <c r="Q130" t="n">
-        <v>208233.938</v>
+        <v>164687.777</v>
       </c>
       <c r="R130" t="n">
-        <v>197.806</v>
+        <v>195.937</v>
       </c>
       <c r="S130" t="n">
-        <v>217.528</v>
+        <v>64.307</v>
       </c>
       <c r="T130" t="n">
-        <v>45.971</v>
+        <v>155.504</v>
       </c>
       <c r="U130" t="n">
-        <v>3.365</v>
+        <v>2.898</v>
       </c>
       <c r="V130" t="n">
-        <v>-263132.046</v>
+        <v>-23865.841</v>
       </c>
       <c r="W130" t="n">
-        <v>-2.247</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>-6.445</v>
+        <v>4.669</v>
       </c>
       <c r="Y130" t="n">
-        <v>-58.229</v>
+        <v>-5.568</v>
       </c>
       <c r="Z130" t="n">
-        <v>909690.326</v>
+        <v>846378.6310000001</v>
       </c>
       <c r="AA130" t="n">
-        <v>608057.379</v>
+        <v>898757.455</v>
       </c>
       <c r="AB130" t="n">
-        <v>149.606</v>
+        <v>94.172</v>
       </c>
       <c r="AC130" t="n">
-        <v>-542</v>
+        <v>82</v>
       </c>
       <c r="AD130" t="n">
-        <v>-16.741</v>
+        <v>2.602</v>
       </c>
       <c r="AE130" t="n">
-        <v>-1.355</v>
+        <v>0.214</v>
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG130" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_TPB_-_Bao_cao_tai_chinh_hop_nhat_Q3.2025_signed_1761832307.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025102458.pdf</t>
         </is>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>2026-09-17T17:36:04+07:00</t>
+          <t>2026-09-17T16:32:56+07:00</t>
         </is>
       </c>
     </row>
@@ -42776,7 +43140,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -42785,75 +43149,99 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>505901.57</v>
+        <v>451893.195</v>
       </c>
       <c r="F131" t="n">
-        <v>46048.761</v>
+        <v>39993.24</v>
       </c>
       <c r="G131" t="n">
-        <v>3598.599</v>
+        <v>3237.619</v>
       </c>
       <c r="H131" t="n">
-        <v>279050.251</v>
+        <v>260245.786</v>
       </c>
       <c r="I131" t="n">
-        <v>302186.389</v>
+        <v>292020.111</v>
       </c>
       <c r="J131" t="n">
-        <v>108.291</v>
+        <v>112.209</v>
       </c>
       <c r="K131" t="n">
-        <v>125552.772</v>
+        <v>87563.264</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>-224607.003</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>-49.704</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>-53.901</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>-36.315</v>
+      </c>
+      <c r="P131" t="n">
+        <v>411899.955</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>208233.938</v>
+      </c>
+      <c r="R131" t="n">
+        <v>197.806</v>
+      </c>
+      <c r="S131" t="n">
+        <v>217.528</v>
+      </c>
+      <c r="T131" t="n">
+        <v>45.971</v>
       </c>
       <c r="U131" t="n">
-        <v>4.499</v>
+        <v>3.365</v>
       </c>
       <c r="V131" t="n">
-        <v>1.704</v>
+        <v>-263132.046</v>
       </c>
       <c r="W131" t="n">
-        <v>0</v>
+        <v>-2.247</v>
       </c>
       <c r="X131" t="n">
-        <v>0</v>
+        <v>-6.445</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>-58.229</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>909690.326</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>608057.379</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>149.606</v>
       </c>
       <c r="AC131" t="n">
-        <v>0</v>
+        <v>-542</v>
       </c>
       <c r="AD131" t="n">
-        <v>0</v>
+        <v>-16.741</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>-1.355</v>
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_TPB_-_BCTC_hop_nhat_2025_da_kiem_toan_kem_giai_trinh_chenh_lech_LNST_signed_1774952109.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_TPB_-_Bao_cao_tai_chinh_hop_nhat_Q3.2025_signed_1761832307.pdf</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>2026-08-31T01:43:30+07:00</t>
+          <t>2026-09-17T17:36:04+07:00</t>
         </is>
       </c>
     </row>
@@ -42865,17 +43253,84 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>505901.57</v>
+      </c>
+      <c r="F132" t="n">
+        <v>46048.761</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3598.599</v>
+      </c>
+      <c r="H132" t="n">
+        <v>279050.251</v>
+      </c>
+      <c r="I132" t="n">
+        <v>302186.389</v>
+      </c>
+      <c r="J132" t="n">
+        <v>108.291</v>
+      </c>
+      <c r="K132" t="n">
+        <v>125552.772</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>4.499</v>
+      </c>
+      <c r="V132" t="n">
+        <v>1.704</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_TPB_-_BCTC_hop_nhat_2025_da_kiem_toan_kem_giai_trinh_chenh_lech_LNST_signed_1774952109.pdf</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>2026-09-17T09:59:43+07:00</t>
+          <t>2026-08-31T01:43:30+07:00</t>
         </is>
       </c>
     </row>
@@ -42887,96 +43342,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>547664.403</v>
-      </c>
-      <c r="F133" t="n">
-        <v>49565.884</v>
-      </c>
-      <c r="G133" t="n">
-        <v>3634.174</v>
-      </c>
-      <c r="H133" t="n">
-        <v>288477.683</v>
-      </c>
-      <c r="I133" t="n">
-        <v>333970.52</v>
-      </c>
-      <c r="J133" t="n">
-        <v>115.77</v>
-      </c>
-      <c r="K133" t="n">
-        <v>112974.847</v>
-      </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>3.916</v>
-      </c>
-      <c r="V133" t="n">
-        <v>6224.134000000002</v>
-      </c>
-      <c r="W133" t="n">
-        <v>14.436</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>1.136</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>53</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>1.458</v>
-      </c>
-      <c r="AE133" t="n">
-        <v>0.107</v>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_202608182020TPB2020Bao20cao20tai20chinh20hop20nhat20soat20xet20ban20nien20202620kem20giai20trinh20chenh20lech20LNST_signed_19082026095348.pdf?v=1787108030513</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>2026-09-01T10:14:12+07:00</t>
+          <t>2026-09-17T09:59:43+07:00</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>VAB</t>
+          <t>TPB</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -42985,25 +43373,25 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>129046.444409199</v>
+        <v>547664.403</v>
       </c>
       <c r="F134" t="n">
-        <v>9151.860456363</v>
+        <v>49565.884</v>
       </c>
       <c r="G134" t="n">
-        <v>612.5349521319999</v>
+        <v>3634.174</v>
       </c>
       <c r="H134" t="n">
-        <v>93896.377376687</v>
+        <v>288477.683</v>
       </c>
       <c r="I134" t="n">
-        <v>84104.940067508</v>
+        <v>333970.52</v>
       </c>
       <c r="J134" t="n">
-        <v>89.572</v>
+        <v>115.77</v>
       </c>
       <c r="K134" t="n">
-        <v>19187.7140786</v>
+        <v>112974.847</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -43018,42 +43406,42 @@
         <v>0</v>
       </c>
       <c r="U134" t="n">
-        <v>2.043</v>
+        <v>3.916</v>
       </c>
       <c r="V134" t="n">
-        <v>26350.65</v>
+        <v>6224.134000000002</v>
       </c>
       <c r="W134" t="n">
-        <v>0.614</v>
+        <v>14.436</v>
       </c>
       <c r="X134" t="n">
-        <v>0.614</v>
+        <v>0.541</v>
       </c>
       <c r="Y134" t="n">
-        <v>20.42</v>
+        <v>1.136</v>
       </c>
       <c r="AC134" t="n">
-        <v>167</v>
+        <v>53</v>
       </c>
       <c r="AD134" t="n">
-        <v>27.264</v>
+        <v>1.458</v>
       </c>
       <c r="AE134" t="n">
-        <v>1.825</v>
+        <v>0.107</v>
       </c>
       <c r="AF134" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG134" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014787653_VI_BaoCaoTaiChinh_Q1_2025_18042025134138.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_202608182020TPB2020Bao20cao20tai20chinh20hop20nhat20soat20xet20ban20nien20202620kem20giai20trinh20chenh20lech20LNST_signed_19082026095348.pdf?v=1787108030513</t>
         </is>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>2026-08-31T10:42:19+07:00</t>
+          <t>2026-09-01T10:14:12+07:00</t>
         </is>
       </c>
     </row>
@@ -43065,7 +43453,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -43074,25 +43462,25 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>133951.803544459</v>
+        <v>129046.444409199</v>
       </c>
       <c r="F135" t="n">
-        <v>9420.642668476999</v>
+        <v>9151.860456363</v>
       </c>
       <c r="G135" t="n">
-        <v>542.378510292</v>
+        <v>612.5349521319999</v>
       </c>
       <c r="H135" t="n">
-        <v>95784.767789663</v>
+        <v>93896.377376687</v>
       </c>
       <c r="I135" t="n">
-        <v>86563.862420006</v>
+        <v>84104.940067508</v>
       </c>
       <c r="J135" t="n">
-        <v>90.373</v>
+        <v>89.572</v>
       </c>
       <c r="K135" t="n">
-        <v>19972.595116502</v>
+        <v>19187.7140786</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -43107,51 +43495,42 @@
         <v>0</v>
       </c>
       <c r="U135" t="n">
-        <v>2.085</v>
+        <v>2.043</v>
       </c>
       <c r="V135" t="n">
-        <v>-28908.298</v>
+        <v>26350.65</v>
       </c>
       <c r="W135" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X135" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="Y135" t="n">
-        <v>-21.581</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>28914.298</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
+        <v>20.42</v>
       </c>
       <c r="AC135" t="n">
-        <v>-126</v>
+        <v>167</v>
       </c>
       <c r="AD135" t="n">
-        <v>-23.231</v>
+        <v>27.264</v>
       </c>
       <c r="AE135" t="n">
-        <v>-1.337</v>
+        <v>1.825</v>
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG135" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000007054673721340387ngn-hng-tmcp-vit-24072025-000000bo-co-ti-chnh-hp-nht-qu_1_0914.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014787653_VI_BaoCaoTaiChinh_Q1_2025_18042025134138.pdf</t>
         </is>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>2026-09-17T16:34:18+07:00</t>
+          <t>2026-08-31T10:42:19+07:00</t>
         </is>
       </c>
     </row>
@@ -43163,17 +43542,93 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>133951.803544459</v>
+      </c>
+      <c r="F136" t="n">
+        <v>9420.642668476999</v>
+      </c>
+      <c r="G136" t="n">
+        <v>542.378510292</v>
+      </c>
+      <c r="H136" t="n">
+        <v>95784.767789663</v>
+      </c>
+      <c r="I136" t="n">
+        <v>86563.862420006</v>
+      </c>
+      <c r="J136" t="n">
+        <v>90.373</v>
+      </c>
+      <c r="K136" t="n">
+        <v>19972.595116502</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>2.085</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-28908.298</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-21.581</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>28914.298</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-126</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-23.231</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-1.337</v>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000007054673721340387ngn-hng-tmcp-vit-24072025-000000bo-co-ti-chnh-hp-nht-qu_1_0914.pdf</t>
         </is>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>2026-09-17T18:14:21+07:00</t>
+          <t>2026-09-17T16:34:18+07:00</t>
         </is>
       </c>
     </row>
@@ -43185,99 +43640,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>140485.531667485</v>
-      </c>
-      <c r="F137" t="n">
-        <v>10155.027138318</v>
-      </c>
-      <c r="G137" t="n">
-        <v>1608.289139551</v>
-      </c>
-      <c r="H137" t="n">
-        <v>99079.937892602</v>
-      </c>
-      <c r="I137" t="n">
-        <v>87680.386166857</v>
-      </c>
-      <c r="J137" t="n">
-        <v>88.495</v>
-      </c>
-      <c r="K137" t="n">
-        <v>23789.312582522</v>
-      </c>
-      <c r="L137" t="n">
-        <v>11145.647</v>
-      </c>
-      <c r="M137" t="n">
-        <v>7.934</v>
-      </c>
-      <c r="N137" t="n">
-        <v>-4.005</v>
-      </c>
-      <c r="O137" t="n">
-        <v>-6.105</v>
-      </c>
-      <c r="P137" t="n">
-        <v>57946.823</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>27306.323</v>
-      </c>
-      <c r="R137" t="n">
-        <v>212.21</v>
-      </c>
-      <c r="S137" t="n">
-        <v>63.692</v>
-      </c>
-      <c r="T137" t="n">
-        <v>157.007</v>
-      </c>
-      <c r="U137" t="n">
-        <v>2.401</v>
-      </c>
-      <c r="V137" t="n">
-        <v>9801.561999999998</v>
-      </c>
-      <c r="W137" t="n">
-        <v>-3.436</v>
-      </c>
-      <c r="X137" t="n">
-        <v>10.286</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>6.977</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>114</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>7.088</v>
-      </c>
-      <c r="AE137" t="n">
-        <v>1.123</v>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_VAB_BCTC_hop_nhat_da_kiem_toan_Nam_2025_1775054500.pdf</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>2026-08-31T01:45:19+07:00</t>
+          <t>2026-09-17T18:14:21+07:00</t>
         </is>
       </c>
     </row>
@@ -43289,17 +43662,99 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>140485.531667485</v>
+      </c>
+      <c r="F138" t="n">
+        <v>10155.027138318</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1608.289139551</v>
+      </c>
+      <c r="H138" t="n">
+        <v>99079.937892602</v>
+      </c>
+      <c r="I138" t="n">
+        <v>87680.386166857</v>
+      </c>
+      <c r="J138" t="n">
+        <v>88.495</v>
+      </c>
+      <c r="K138" t="n">
+        <v>23789.312582522</v>
+      </c>
+      <c r="L138" t="n">
+        <v>11145.647</v>
+      </c>
+      <c r="M138" t="n">
+        <v>7.934</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-4.005</v>
+      </c>
+      <c r="O138" t="n">
+        <v>-6.105</v>
+      </c>
+      <c r="P138" t="n">
+        <v>57946.823</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>27306.323</v>
+      </c>
+      <c r="R138" t="n">
+        <v>212.21</v>
+      </c>
+      <c r="S138" t="n">
+        <v>63.692</v>
+      </c>
+      <c r="T138" t="n">
+        <v>157.007</v>
+      </c>
+      <c r="U138" t="n">
+        <v>2.401</v>
+      </c>
+      <c r="V138" t="n">
+        <v>9801.561999999998</v>
+      </c>
+      <c r="W138" t="n">
+        <v>-3.436</v>
+      </c>
+      <c r="X138" t="n">
+        <v>10.286</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>6.977</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>114</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>7.088</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_VAB_BCTC_hop_nhat_da_kiem_toan_Nam_2025_1775054500.pdf</t>
         </is>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>2026-09-17T09:59:50+07:00</t>
+          <t>2026-08-31T01:45:19+07:00</t>
         </is>
       </c>
     </row>
@@ -43311,111 +43766,29 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>reported</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>149129.5947417</v>
-      </c>
-      <c r="F139" t="n">
-        <v>10809.684415361</v>
-      </c>
-      <c r="G139" t="n">
-        <v>576.941677107</v>
-      </c>
-      <c r="H139" t="n">
-        <v>104044.682695361</v>
-      </c>
-      <c r="I139" t="n">
-        <v>95021.138285065</v>
-      </c>
-      <c r="J139" t="n">
-        <v>91.327</v>
-      </c>
-      <c r="K139" t="n">
-        <v>16905.795483056</v>
-      </c>
-      <c r="L139" t="n">
-        <v>22986.852</v>
-      </c>
-      <c r="M139" t="n">
-        <v>15.414</v>
-      </c>
-      <c r="N139" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="O139" t="n">
-        <v>-7.767</v>
-      </c>
-      <c r="P139" t="n">
-        <v>133478.341</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>31680.939</v>
-      </c>
-      <c r="R139" t="n">
-        <v>421.321</v>
-      </c>
-      <c r="S139" t="n">
-        <v>58.872</v>
-      </c>
-      <c r="T139" t="n">
-        <v>169.86</v>
-      </c>
-      <c r="U139" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="V139" t="n">
-        <v>-13314.504</v>
-      </c>
-      <c r="W139" t="n">
-        <v>6.143</v>
-      </c>
-      <c r="X139" t="n">
-        <v>-15.883</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>-8.928000000000001</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>-74</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>-12.826</v>
-      </c>
-      <c r="AE139" t="n">
-        <v>-0.6850000000000001</v>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
-        </is>
-      </c>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VAB_202608212020VAB2020BCTC20HN20SOAT20XET20BAN20NIEN202026_22082026105705.pdf?v=1787371027647</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>2026-09-01T10:15:41+07:00</t>
+          <t>2026-09-17T09:59:50+07:00</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VBB</t>
+          <t>VAB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -43424,75 +43797,90 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>174377.72</v>
+        <v>149129.5947417</v>
       </c>
       <c r="F140" t="n">
-        <v>8897.989</v>
+        <v>10809.684415361</v>
       </c>
       <c r="G140" t="n">
-        <v>702.5119999999999</v>
+        <v>576.941677107</v>
       </c>
       <c r="H140" t="n">
-        <v>103017.174</v>
+        <v>104044.682695361</v>
       </c>
       <c r="I140" t="n">
-        <v>96036.461</v>
+        <v>95021.138285065</v>
       </c>
       <c r="J140" t="n">
-        <v>93.224</v>
+        <v>91.327</v>
       </c>
       <c r="K140" t="n">
-        <v>49825.872</v>
+        <v>16905.795483056</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>22986.852</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>15.414</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>-7.767</v>
+      </c>
+      <c r="P140" t="n">
+        <v>133478.341</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>31680.939</v>
+      </c>
+      <c r="R140" t="n">
+        <v>421.321</v>
+      </c>
+      <c r="S140" t="n">
+        <v>58.872</v>
+      </c>
+      <c r="T140" t="n">
+        <v>169.86</v>
       </c>
       <c r="U140" t="n">
-        <v>4.837</v>
+        <v>1.625</v>
       </c>
       <c r="V140" t="n">
-        <v>14256.841</v>
+        <v>-13314.504</v>
       </c>
       <c r="W140" t="n">
-        <v>0</v>
+        <v>6.143</v>
       </c>
       <c r="X140" t="n">
-        <v>1.511</v>
+        <v>-15.883</v>
       </c>
       <c r="Y140" t="n">
-        <v>8.176</v>
+        <v>-8.928000000000001</v>
       </c>
       <c r="AC140" t="n">
-        <v>51</v>
+        <v>-74</v>
       </c>
       <c r="AD140" t="n">
-        <v>7.26</v>
+        <v>-12.826</v>
       </c>
       <c r="AE140" t="n">
-        <v>0.573</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="AF140" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG140" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/1_vbb_2025_5_7_121b03c_vi_baocaotaichinh_hopnhat_q1_20251_16052025112437.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VAB_202608212020VAB2020BCTC20HN20SOAT20XET20BAN20NIEN202026_22082026105705.pdf?v=1787371027647</t>
         </is>
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>2026-08-31T10:44:04+07:00</t>
+          <t>2026-09-01T10:15:41+07:00</t>
         </is>
       </c>
     </row>
@@ -43504,7 +43892,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -43513,90 +43901,75 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>178670.984</v>
+        <v>174377.72</v>
       </c>
       <c r="F141" t="n">
-        <v>9073.486999999999</v>
+        <v>8897.989</v>
       </c>
       <c r="G141" t="n">
-        <v>687.4059999999999</v>
+        <v>702.5119999999999</v>
       </c>
       <c r="H141" t="n">
-        <v>104208.415</v>
+        <v>103017.174</v>
       </c>
       <c r="I141" t="n">
-        <v>101102.34</v>
+        <v>96036.461</v>
       </c>
       <c r="J141" t="n">
-        <v>97.01900000000001</v>
+        <v>93.224</v>
       </c>
       <c r="K141" t="n">
-        <v>45431.683</v>
+        <v>49825.872</v>
       </c>
       <c r="L141" t="n">
-        <v>-3955.115</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>-2.214</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>-10.987</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>-13.682</v>
-      </c>
-      <c r="P141" t="n">
-        <v>-16499.427</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>44170.618</v>
-      </c>
-      <c r="R141" t="n">
-        <v>-37.354</v>
-      </c>
-      <c r="S141" t="n">
-        <v>41.556</v>
-      </c>
-      <c r="T141" t="n">
-        <v>240.636</v>
+        <v>0</v>
       </c>
       <c r="U141" t="n">
-        <v>4.36</v>
+        <v>4.837</v>
       </c>
       <c r="V141" t="n">
-        <v>16300.747</v>
+        <v>14256.841</v>
       </c>
       <c r="W141" t="n">
-        <v>3.251</v>
+        <v>0</v>
       </c>
       <c r="X141" t="n">
-        <v>9.119999999999999</v>
+        <v>1.511</v>
       </c>
       <c r="Y141" t="n">
-        <v>9.122999999999999</v>
+        <v>8.176</v>
       </c>
       <c r="AC141" t="n">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="AD141" t="n">
-        <v>20.803</v>
+        <v>7.26</v>
       </c>
       <c r="AE141" t="n">
-        <v>1.576</v>
+        <v>0.573</v>
       </c>
       <c r="AF141" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG141" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-vit-nam-thng-tn05082025-000000bo-co-ti-chnh-bn-nin-2025_1_1517.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/1_vbb_2025_5_7_121b03c_vi_baocaotaichinh_hopnhat_q1_20251_16052025112437.pdf</t>
         </is>
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>2026-08-31T12:48:36+07:00</t>
+          <t>2026-08-31T10:44:04+07:00</t>
         </is>
       </c>
     </row>
@@ -43608,7 +43981,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -43617,75 +43990,90 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>188133.411</v>
+        <v>178670.984</v>
       </c>
       <c r="F142" t="n">
-        <v>9353.481</v>
+        <v>9073.486999999999</v>
       </c>
       <c r="G142" t="n">
-        <v>827.9880000000001</v>
+        <v>687.4059999999999</v>
       </c>
       <c r="H142" t="n">
-        <v>100829.796</v>
+        <v>104208.415</v>
       </c>
       <c r="I142" t="n">
-        <v>103779.926</v>
+        <v>101102.34</v>
       </c>
       <c r="J142" t="n">
-        <v>102.926</v>
+        <v>97.01900000000001</v>
       </c>
       <c r="K142" t="n">
-        <v>50691.979</v>
+        <v>45431.683</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>-3955.115</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>-2.214</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>-10.987</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>-13.682</v>
+      </c>
+      <c r="P142" t="n">
+        <v>-16499.427</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>44170.618</v>
+      </c>
+      <c r="R142" t="n">
+        <v>-37.354</v>
+      </c>
+      <c r="S142" t="n">
+        <v>41.556</v>
+      </c>
+      <c r="T142" t="n">
+        <v>240.636</v>
       </c>
       <c r="U142" t="n">
-        <v>5.027</v>
+        <v>4.36</v>
       </c>
       <c r="V142" t="n">
-        <v>35794.599</v>
+        <v>16300.747</v>
       </c>
       <c r="W142" t="n">
-        <v>4.309</v>
+        <v>3.251</v>
       </c>
       <c r="X142" t="n">
-        <v>16.938</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Y142" t="n">
-        <v>19.026</v>
+        <v>9.122999999999999</v>
       </c>
       <c r="AC142" t="n">
-        <v>300</v>
+        <v>143</v>
       </c>
       <c r="AD142" t="n">
-        <v>36.232</v>
+        <v>20.803</v>
       </c>
       <c r="AE142" t="n">
-        <v>3.207</v>
+        <v>1.576</v>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất Quý 3 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-11-05/no-name-1762283224.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-vit-nam-thng-tn05082025-000000bo-co-ti-chnh-bn-nin-2025_1_1517.pdf</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>2026-08-31T15:58:42+07:00</t>
+          <t>2026-08-31T12:48:36+07:00</t>
         </is>
       </c>
     </row>
@@ -43697,7 +44085,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -43706,90 +44094,75 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>196771.033</v>
+        <v>188133.411</v>
       </c>
       <c r="F143" t="n">
-        <v>12431.567</v>
+        <v>9353.481</v>
       </c>
       <c r="G143" t="n">
-        <v>1108.674</v>
+        <v>827.9880000000001</v>
       </c>
       <c r="H143" t="n">
-        <v>101449.573</v>
+        <v>100829.796</v>
       </c>
       <c r="I143" t="n">
-        <v>103772.418</v>
+        <v>103779.926</v>
       </c>
       <c r="J143" t="n">
-        <v>102.29</v>
+        <v>102.926</v>
       </c>
       <c r="K143" t="n">
-        <v>56200.61</v>
+        <v>50691.979</v>
       </c>
       <c r="L143" t="n">
-        <v>-8211.225</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>-4.173</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>-11.339</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>-14.915</v>
-      </c>
-      <c r="P143" t="n">
-        <v>154563.686</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>63929.972</v>
-      </c>
-      <c r="R143" t="n">
-        <v>241.77</v>
-      </c>
-      <c r="S143" t="n">
-        <v>50.182</v>
-      </c>
-      <c r="T143" t="n">
-        <v>199.276</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
-        <v>5.54</v>
+        <v>5.027</v>
       </c>
       <c r="V143" t="n">
-        <v>0</v>
+        <v>35794.599</v>
       </c>
       <c r="W143" t="n">
-        <v>0</v>
+        <v>4.309</v>
       </c>
       <c r="X143" t="n">
-        <v>0</v>
+        <v>16.938</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>19.026</v>
       </c>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>36.232</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>3.207</v>
       </c>
       <c r="AF143" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+          <t>Báo cáo tài chính hợp nhất Quý 3 năm 2025</t>
         </is>
       </c>
       <c r="AG143" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603183_Bao_cao_tai_chinh_nam_2025_1776046427.pdf</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-11-05/no-name-1762283224.pdf</t>
         </is>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>2026-08-31T01:48:14+07:00</t>
+          <t>2026-08-31T15:58:42+07:00</t>
         </is>
       </c>
     </row>
@@ -43801,7 +44174,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -43810,75 +44183,90 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>190211.081</v>
+        <v>196771.033</v>
       </c>
       <c r="F144" t="n">
-        <v>12561.738</v>
+        <v>12431.567</v>
       </c>
       <c r="G144" t="n">
-        <v>768.097</v>
+        <v>1108.674</v>
       </c>
       <c r="H144" t="n">
-        <v>96521.45299999999</v>
+        <v>101449.573</v>
       </c>
       <c r="I144" t="n">
-        <v>108035.481</v>
+        <v>103772.418</v>
       </c>
       <c r="J144" t="n">
-        <v>111.929</v>
+        <v>102.29</v>
       </c>
       <c r="K144" t="n">
-        <v>40917.436</v>
+        <v>56200.61</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>-8211.225</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>-4.173</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>-11.339</v>
       </c>
       <c r="O144" t="n">
-        <v>0</v>
+        <v>-14.915</v>
+      </c>
+      <c r="P144" t="n">
+        <v>154563.686</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>63929.972</v>
+      </c>
+      <c r="R144" t="n">
+        <v>241.77</v>
+      </c>
+      <c r="S144" t="n">
+        <v>50.182</v>
+      </c>
+      <c r="T144" t="n">
+        <v>199.276</v>
       </c>
       <c r="U144" t="n">
-        <v>4.239</v>
+        <v>5.54</v>
       </c>
       <c r="V144" t="n">
-        <v>254171.611</v>
+        <v>0</v>
       </c>
       <c r="W144" t="n">
-        <v>133.626</v>
+        <v>0</v>
       </c>
       <c r="X144" t="n">
-        <v>133.626</v>
+        <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>133.626</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
-        <v>2436</v>
+        <v>0</v>
       </c>
       <c r="AD144" t="n">
-        <v>317.147</v>
+        <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>19.392</v>
+        <v>0</v>
       </c>
       <c r="AF144" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
       <c r="AG144" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VBB_1778222221.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603183_Bao_cao_tai_chinh_nam_2025_1776046427.pdf</t>
         </is>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>2026-09-01T00:03:48+07:00</t>
+          <t>2026-08-31T01:48:14+07:00</t>
         </is>
       </c>
     </row>
@@ -43890,7 +44278,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -43899,102 +44287,87 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>204824.91</v>
+        <v>190211.081</v>
       </c>
       <c r="F145" t="n">
-        <v>13154.026</v>
+        <v>12561.738</v>
       </c>
       <c r="G145" t="n">
-        <v>993.583</v>
+        <v>768.097</v>
       </c>
       <c r="H145" t="n">
-        <v>103892.733</v>
+        <v>96521.45299999999</v>
       </c>
       <c r="I145" t="n">
-        <v>118400.699</v>
+        <v>108035.481</v>
       </c>
       <c r="J145" t="n">
-        <v>113.964</v>
+        <v>111.929</v>
       </c>
       <c r="K145" t="n">
-        <v>50312.896</v>
+        <v>40917.436</v>
       </c>
       <c r="L145" t="n">
-        <v>-3991.597</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>-1.949</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>-5.284</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="P145" t="n">
-        <v>30574.747</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>297062.074</v>
-      </c>
-      <c r="R145" t="n">
-        <v>10.292</v>
-      </c>
-      <c r="S145" t="n">
-        <v>90.03400000000001</v>
-      </c>
-      <c r="T145" t="n">
-        <v>111.07</v>
+        <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>4.843</v>
+        <v>4.239</v>
       </c>
       <c r="V145" t="n">
-        <v>37811.189</v>
+        <v>254171.611</v>
       </c>
       <c r="W145" t="n">
-        <v>-9.045999999999999</v>
+        <v>133.626</v>
       </c>
       <c r="X145" t="n">
-        <v>6.228</v>
+        <v>133.626</v>
       </c>
       <c r="Y145" t="n">
-        <v>18.46</v>
+        <v>133.626</v>
       </c>
       <c r="AC145" t="n">
-        <v>187</v>
+        <v>2436</v>
       </c>
       <c r="AD145" t="n">
-        <v>18.821</v>
+        <v>317.147</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.422</v>
+        <v>19.392</v>
       </c>
       <c r="AF145" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất đã kiểm toán 6 tháng đầu năm 2026</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
       <c r="AG145" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2026-3/2026-08-17/no-name-1786938113.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VBB_1778222221.pdf</t>
         </is>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>2026-09-01T10:19:39+07:00</t>
+          <t>2026-09-01T00:03:48+07:00</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>VCB</t>
+          <t>VBB</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -44003,90 +44376,90 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2109260.616</v>
+        <v>204824.91</v>
       </c>
       <c r="F146" t="n">
-        <v>204941.834</v>
+        <v>13154.026</v>
       </c>
       <c r="G146" t="n">
-        <v>13687.153</v>
+        <v>993.583</v>
       </c>
       <c r="H146" t="n">
-        <v>1509113.389</v>
+        <v>103892.733</v>
       </c>
       <c r="I146" t="n">
-        <v>1433896.493</v>
+        <v>118400.699</v>
       </c>
       <c r="J146" t="n">
-        <v>95.01600000000001</v>
+        <v>113.964</v>
       </c>
       <c r="K146" t="n">
-        <v>452321.798</v>
+        <v>50312.896</v>
       </c>
       <c r="L146" t="n">
-        <v>-461316.069</v>
+        <v>-3991.597</v>
       </c>
       <c r="M146" t="n">
-        <v>-21.871</v>
+        <v>-1.949</v>
       </c>
       <c r="N146" t="n">
-        <v>-14.033</v>
+        <v>-5.284</v>
       </c>
       <c r="O146" t="n">
-        <v>-11.763</v>
+        <v>3.92</v>
       </c>
       <c r="P146" t="n">
-        <v>1888113.608</v>
+        <v>30574.747</v>
       </c>
       <c r="Q146" t="n">
-        <v>502117.121</v>
+        <v>297062.074</v>
       </c>
       <c r="R146" t="n">
-        <v>376.031</v>
+        <v>10.292</v>
       </c>
       <c r="S146" t="n">
-        <v>44.043</v>
+        <v>90.03400000000001</v>
       </c>
       <c r="T146" t="n">
-        <v>227.051</v>
+        <v>111.07</v>
       </c>
       <c r="U146" t="n">
-        <v>2.997</v>
+        <v>4.843</v>
       </c>
       <c r="V146" t="n">
-        <v>-16699.62499999997</v>
+        <v>37811.189</v>
       </c>
       <c r="W146" t="n">
-        <v>-17.035</v>
+        <v>-9.045999999999999</v>
       </c>
       <c r="X146" t="n">
-        <v>-2.394</v>
+        <v>6.228</v>
       </c>
       <c r="Y146" t="n">
-        <v>-0.792</v>
+        <v>18.46</v>
       </c>
       <c r="AC146" t="n">
-        <v>-118</v>
+        <v>187</v>
       </c>
       <c r="AD146" t="n">
-        <v>-0.862</v>
+        <v>18.821</v>
       </c>
       <c r="AE146" t="n">
-        <v>-0.058</v>
+        <v>1.422</v>
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán 6 tháng đầu năm 2026</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_23052025150224.pdf</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-3/2026-08-17/no-name-1786938113.pdf</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>2026-08-31T17:07:33+07:00</t>
+          <t>2026-09-01T10:19:39+07:00</t>
         </is>
       </c>
     </row>
@@ -44098,7 +44471,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -44107,75 +44480,90 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2217636.6</v>
+        <v>2109260.616</v>
       </c>
       <c r="F147" t="n">
-        <v>213749.422</v>
+        <v>204941.834</v>
       </c>
       <c r="G147" t="n">
-        <v>14160.192</v>
+        <v>13687.153</v>
       </c>
       <c r="H147" t="n">
-        <v>1586682.675</v>
+        <v>1509113.389</v>
       </c>
       <c r="I147" t="n">
-        <v>1522462.472</v>
+        <v>1433896.493</v>
       </c>
       <c r="J147" t="n">
-        <v>95.953</v>
+        <v>95.01600000000001</v>
       </c>
       <c r="K147" t="n">
-        <v>485017.633</v>
+        <v>452321.798</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>-461316.069</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>-21.871</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>-14.033</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>-11.763</v>
+      </c>
+      <c r="P147" t="n">
+        <v>1888113.608</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>502117.121</v>
+      </c>
+      <c r="R147" t="n">
+        <v>376.031</v>
+      </c>
+      <c r="S147" t="n">
+        <v>44.043</v>
+      </c>
+      <c r="T147" t="n">
+        <v>227.051</v>
       </c>
       <c r="U147" t="n">
-        <v>3.057</v>
+        <v>2.997</v>
       </c>
       <c r="V147" t="n">
-        <v>-43033.196</v>
+        <v>-16699.62499999997</v>
       </c>
       <c r="W147" t="n">
-        <v>-18.312</v>
+        <v>-17.035</v>
       </c>
       <c r="X147" t="n">
-        <v>-4.16</v>
+        <v>-2.394</v>
       </c>
       <c r="Y147" t="n">
-        <v>-1.94</v>
+        <v>-0.792</v>
       </c>
       <c r="AC147" t="n">
-        <v>-487</v>
+        <v>-118</v>
       </c>
       <c r="AD147" t="n">
-        <v>-3.439</v>
+        <v>-0.862</v>
       </c>
       <c r="AE147" t="n">
-        <v>-0.228</v>
+        <v>-0.058</v>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025111259.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_23052025150224.pdf</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>2026-08-31T12:50:26+07:00</t>
+          <t>2026-08-31T17:07:33+07:00</t>
         </is>
       </c>
     </row>
@@ -44187,7 +44575,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -44196,99 +44584,75 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2378185.628</v>
+        <v>2217636.6</v>
       </c>
       <c r="F148" t="n">
-        <v>222791.545</v>
+        <v>213749.422</v>
       </c>
       <c r="G148" t="n">
-        <v>14657.24</v>
+        <v>14160.192</v>
       </c>
       <c r="H148" t="n">
-        <v>1611966.698</v>
+        <v>1586682.675</v>
       </c>
       <c r="I148" t="n">
-        <v>1595933.982</v>
+        <v>1522462.472</v>
       </c>
       <c r="J148" t="n">
-        <v>99.005</v>
+        <v>95.953</v>
       </c>
       <c r="K148" t="n">
-        <v>567345.417</v>
+        <v>485017.633</v>
       </c>
       <c r="L148" t="n">
-        <v>-505610.893</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>-21.26</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>-15.851</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>-15.224</v>
-      </c>
-      <c r="P148" t="n">
-        <v>2136177.852</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>633448.997</v>
-      </c>
-      <c r="R148" t="n">
-        <v>337.23</v>
-      </c>
-      <c r="S148" t="n">
-        <v>37.415</v>
-      </c>
-      <c r="T148" t="n">
-        <v>267.269</v>
+        <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>3.52</v>
+        <v>3.057</v>
       </c>
       <c r="V148" t="n">
-        <v>-50506.96400000001</v>
+        <v>-43033.196</v>
       </c>
       <c r="W148" t="n">
-        <v>-16.271</v>
+        <v>-18.312</v>
       </c>
       <c r="X148" t="n">
-        <v>-5.369</v>
+        <v>-4.16</v>
       </c>
       <c r="Y148" t="n">
-        <v>-2.124</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>523906.365</v>
-      </c>
-      <c r="AA148" t="n">
-        <v>318283.844</v>
-      </c>
-      <c r="AB148" t="n">
-        <v>164.604</v>
+        <v>-1.94</v>
       </c>
       <c r="AC148" t="n">
-        <v>-656</v>
+        <v>-487</v>
       </c>
       <c r="AD148" t="n">
-        <v>-4.476</v>
+        <v>-3.439</v>
       </c>
       <c r="AE148" t="n">
-        <v>-0.294</v>
+        <v>-0.228</v>
       </c>
       <c r="AF148" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG148" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_VCB_-_CBTT_BCTC_Hop_nhat_Q3.2025_1761883208.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025111259.pdf</t>
         </is>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>2026-09-17T17:41:27+07:00</t>
+          <t>2026-08-31T12:50:26+07:00</t>
         </is>
       </c>
     </row>
@@ -44300,7 +44664,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -44309,75 +44673,99 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2442279.166</v>
+        <v>2378185.628</v>
       </c>
       <c r="F149" t="n">
-        <v>224558.726</v>
+        <v>222791.545</v>
       </c>
       <c r="G149" t="n">
-        <v>16266.825</v>
+        <v>14657.24</v>
       </c>
       <c r="H149" t="n">
-        <v>1672534.846</v>
+        <v>1611966.698</v>
       </c>
       <c r="I149" t="n">
-        <v>1648549.996</v>
+        <v>1595933.982</v>
       </c>
       <c r="J149" t="n">
-        <v>98.566</v>
+        <v>99.005</v>
       </c>
       <c r="K149" t="n">
-        <v>575462.635</v>
+        <v>567345.417</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>-505610.893</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>-21.26</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>-15.851</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>-15.224</v>
+      </c>
+      <c r="P149" t="n">
+        <v>2136177.852</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>633448.997</v>
+      </c>
+      <c r="R149" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="S149" t="n">
+        <v>37.415</v>
+      </c>
+      <c r="T149" t="n">
+        <v>267.269</v>
       </c>
       <c r="U149" t="n">
-        <v>3.441</v>
+        <v>3.52</v>
       </c>
       <c r="V149" t="n">
-        <v>819.975</v>
+        <v>-50506.96400000001</v>
       </c>
       <c r="W149" t="n">
-        <v>0.018</v>
+        <v>-16.271</v>
       </c>
       <c r="X149" t="n">
-        <v>0.02</v>
+        <v>-5.369</v>
       </c>
       <c r="Y149" t="n">
-        <v>0.034</v>
+        <v>-2.124</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>523906.365</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>318283.844</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>164.604</v>
       </c>
       <c r="AC149" t="n">
-        <v>7</v>
+        <v>-656</v>
       </c>
       <c r="AD149" t="n">
-        <v>0.043</v>
+        <v>-4.476</v>
       </c>
       <c r="AE149" t="n">
-        <v>0.003</v>
+        <v>-0.294</v>
       </c>
       <c r="AF149" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
       <c r="AG149" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_VCB_-_BCTC_hop_nhat_kiem_toan_nam_2025_1774870712.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_VCB_-_CBTT_BCTC_Hop_nhat_Q3.2025_1761883208.pdf</t>
         </is>
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>2026-08-31T01:50:20+07:00</t>
+          <t>2026-09-17T17:41:27+07:00</t>
         </is>
       </c>
     </row>
@@ -44389,7 +44777,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -44398,90 +44786,75 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2550963.342</v>
+        <v>2442279.166</v>
       </c>
       <c r="F150" t="n">
-        <v>234031.329</v>
+        <v>224558.726</v>
       </c>
       <c r="G150" t="n">
-        <v>17651.083</v>
+        <v>16266.825</v>
       </c>
       <c r="H150" t="n">
-        <v>1682032.374</v>
+        <v>1672534.846</v>
       </c>
       <c r="I150" t="n">
-        <v>1727390.88</v>
+        <v>1648549.996</v>
       </c>
       <c r="J150" t="n">
-        <v>102.697</v>
+        <v>98.566</v>
       </c>
       <c r="K150" t="n">
-        <v>612410.1</v>
+        <v>575462.635</v>
       </c>
       <c r="L150" t="n">
-        <v>-550103.507</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>-21.565</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>-17.616</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>-16.495</v>
-      </c>
-      <c r="P150" t="n">
-        <v>2230125.265</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>772629.6629999999</v>
-      </c>
-      <c r="R150" t="n">
-        <v>288.641</v>
-      </c>
-      <c r="S150" t="n">
-        <v>41.525</v>
-      </c>
-      <c r="T150" t="n">
-        <v>240.816</v>
+        <v>0</v>
       </c>
       <c r="U150" t="n">
-        <v>3.641</v>
+        <v>3.441</v>
       </c>
       <c r="V150" t="n">
-        <v>-74595.23700000002</v>
+        <v>819.975</v>
       </c>
       <c r="W150" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
       <c r="X150" t="n">
-        <v>0.649</v>
+        <v>0.02</v>
       </c>
       <c r="Y150" t="n">
-        <v>-2.924</v>
+        <v>0.034</v>
       </c>
       <c r="AC150" t="n">
-        <v>-1626</v>
+        <v>7</v>
       </c>
       <c r="AD150" t="n">
-        <v>-9.212</v>
+        <v>0.043</v>
       </c>
       <c r="AE150" t="n">
-        <v>-0.695</v>
+        <v>0.003</v>
       </c>
       <c r="AF150" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
       <c r="AG150" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_VCB_-_BCTC_hop_nhat_Q1.2026_1777452360.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_VCB_-_BCTC_hop_nhat_kiem_toan_nam_2025_1774870712.pdf</t>
         </is>
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>2026-09-01T00:05:30+07:00</t>
+          <t>2026-08-31T01:50:20+07:00</t>
         </is>
       </c>
     </row>
@@ -44493,7 +44866,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-Q2</t>
+          <t>2026-Q1</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -44502,87 +44875,102 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2657440.573</v>
+        <v>2550963.342</v>
       </c>
       <c r="F151" t="n">
-        <v>248490.506</v>
+        <v>234031.329</v>
       </c>
       <c r="G151" t="n">
-        <v>19141.761</v>
+        <v>17651.083</v>
       </c>
       <c r="H151" t="n">
-        <v>1728820.567</v>
+        <v>1682032.374</v>
       </c>
       <c r="I151" t="n">
-        <v>1728183.37</v>
+        <v>1727390.88</v>
       </c>
       <c r="J151" t="n">
-        <v>99.96299999999999</v>
+        <v>102.697</v>
       </c>
       <c r="K151" t="n">
-        <v>708327.0900000001</v>
+        <v>612410.1</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>-550103.507</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>-21.565</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>-17.616</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>-16.495</v>
+      </c>
+      <c r="P151" t="n">
+        <v>2230125.265</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>772629.6629999999</v>
+      </c>
+      <c r="R151" t="n">
+        <v>288.641</v>
+      </c>
+      <c r="S151" t="n">
+        <v>41.525</v>
+      </c>
+      <c r="T151" t="n">
+        <v>240.816</v>
       </c>
       <c r="U151" t="n">
-        <v>4.097</v>
+        <v>3.641</v>
       </c>
       <c r="V151" t="n">
-        <v>527893.2459999999</v>
+        <v>-74595.23700000002</v>
       </c>
       <c r="W151" t="n">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="X151" t="n">
-        <v>0.013</v>
+        <v>0.649</v>
       </c>
       <c r="Y151" t="n">
-        <v>19.865</v>
+        <v>-2.924</v>
       </c>
       <c r="AC151" t="n">
-        <v>2634</v>
+        <v>-1626</v>
       </c>
       <c r="AD151" t="n">
-        <v>13.76</v>
+        <v>-9.212</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.06</v>
+        <v>-0.695</v>
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_202608142020VCB2020BCTC20hop20nhat20soat20xet20ban20nien202026_20082026091404.pdf?v=1787192046593</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_VCB_-_BCTC_hop_nhat_Q1.2026_1777452360.pdf</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>2026-09-01T10:21:39+07:00</t>
+          <t>2026-09-01T00:05:30+07:00</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VIB</t>
+          <t>VCB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2025-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -44591,25 +44979,25 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>495727.377</v>
+        <v>2657440.573</v>
       </c>
       <c r="F152" t="n">
-        <v>43643.267</v>
+        <v>248490.506</v>
       </c>
       <c r="G152" t="n">
-        <v>3737.109</v>
+        <v>19141.761</v>
       </c>
       <c r="H152" t="n">
-        <v>282298.036</v>
+        <v>1728820.567</v>
       </c>
       <c r="I152" t="n">
-        <v>329264.074</v>
+        <v>1728183.37</v>
       </c>
       <c r="J152" t="n">
-        <v>116.637</v>
+        <v>99.96299999999999</v>
       </c>
       <c r="K152" t="n">
-        <v>109632.918</v>
+        <v>708327.0900000001</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -44624,42 +45012,42 @@
         <v>0</v>
       </c>
       <c r="U152" t="n">
-        <v>3.884</v>
+        <v>4.097</v>
       </c>
       <c r="V152" t="n">
-        <v>60162.859</v>
+        <v>527893.2459999999</v>
       </c>
       <c r="W152" t="n">
-        <v>-0.029</v>
+        <v>0.012</v>
       </c>
       <c r="X152" t="n">
-        <v>7.583</v>
+        <v>0.013</v>
       </c>
       <c r="Y152" t="n">
-        <v>12.136</v>
+        <v>19.865</v>
       </c>
       <c r="AC152" t="n">
-        <v>370</v>
+        <v>2634</v>
       </c>
       <c r="AD152" t="n">
-        <v>9.901</v>
+        <v>13.76</v>
       </c>
       <c r="AE152" t="n">
-        <v>0.848</v>
+        <v>1.06</v>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-07-29/no-name-1753727617.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_202608142020VCB2020BCTC20hop20nhat20soat20xet20ban20nien202026_20082026091404.pdf?v=1787192046593</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>2026-08-31T10:48:45+07:00</t>
+          <t>2026-09-01T10:21:39+07:00</t>
         </is>
       </c>
     </row>
@@ -44671,7 +45059,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2025-Q2</t>
+          <t>2025-Q1</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -44680,90 +45068,75 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>530909.024</v>
+        <v>495727.377</v>
       </c>
       <c r="F153" t="n">
-        <v>43627.741</v>
+        <v>43643.267</v>
       </c>
       <c r="G153" t="n">
-        <v>3968.694</v>
+        <v>3737.109</v>
       </c>
       <c r="H153" t="n">
-        <v>304392.951</v>
+        <v>282298.036</v>
       </c>
       <c r="I153" t="n">
-        <v>351360.111</v>
+        <v>329264.074</v>
       </c>
       <c r="J153" t="n">
-        <v>115.43</v>
+        <v>116.637</v>
       </c>
       <c r="K153" t="n">
-        <v>104990.528</v>
+        <v>109632.918</v>
       </c>
       <c r="L153" t="n">
-        <v>-74107.53099999999</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>-13.959</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>-4.908</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>-5.453</v>
-      </c>
-      <c r="P153" t="n">
-        <v>421850.679</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>125888.148</v>
-      </c>
-      <c r="R153" t="n">
-        <v>335.1</v>
-      </c>
-      <c r="S153" t="n">
-        <v>86.631</v>
-      </c>
-      <c r="T153" t="n">
-        <v>115.432</v>
+        <v>0</v>
       </c>
       <c r="U153" t="n">
-        <v>3.449</v>
+        <v>3.884</v>
       </c>
       <c r="V153" t="n">
-        <v>50291.15800000001</v>
+        <v>60162.859</v>
       </c>
       <c r="W153" t="n">
-        <v>-13.959</v>
+        <v>-0.029</v>
       </c>
       <c r="X153" t="n">
-        <v>-4.909</v>
+        <v>7.583</v>
       </c>
       <c r="Y153" t="n">
-        <v>9.473000000000001</v>
+        <v>12.136</v>
       </c>
       <c r="AC153" t="n">
-        <v>-130</v>
+        <v>370</v>
       </c>
       <c r="AD153" t="n">
-        <v>-3.276</v>
+        <v>9.901</v>
       </c>
       <c r="AE153" t="n">
-        <v>-0.298</v>
+        <v>0.848</v>
       </c>
       <c r="AF153" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2025</t>
         </is>
       </c>
       <c r="AG153" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-quc-t-vit-nam06082025-000000bo-co-ti-chnh-hp-nht-bn-nin_1_0929.pdf</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-07-29/no-name-1753727617.pdf</t>
         </is>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>2026-08-31T12:52:16+07:00</t>
+          <t>2026-08-31T10:48:45+07:00</t>
         </is>
       </c>
     </row>
@@ -44775,7 +45148,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2025-Q3</t>
+          <t>2025-Q2</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -44784,90 +45157,90 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>543559.67</v>
+        <v>530909.024</v>
       </c>
       <c r="F154" t="n">
-        <v>45259.765</v>
+        <v>43627.741</v>
       </c>
       <c r="G154" t="n">
-        <v>4172.726</v>
+        <v>3968.694</v>
       </c>
       <c r="H154" t="n">
-        <v>307929.159</v>
+        <v>304392.951</v>
       </c>
       <c r="I154" t="n">
-        <v>367863.425</v>
+        <v>351360.111</v>
       </c>
       <c r="J154" t="n">
-        <v>119.464</v>
+        <v>115.43</v>
       </c>
       <c r="K154" t="n">
-        <v>114615.934</v>
+        <v>104990.528</v>
       </c>
       <c r="L154" t="n">
-        <v>-49593.355</v>
+        <v>-74107.53099999999</v>
       </c>
       <c r="M154" t="n">
-        <v>-9.124000000000001</v>
+        <v>-13.959</v>
       </c>
       <c r="N154" t="n">
-        <v>-7.686</v>
+        <v>-4.908</v>
       </c>
       <c r="O154" t="n">
-        <v>-8.667999999999999</v>
+        <v>-5.453</v>
       </c>
       <c r="P154" t="n">
-        <v>416523.18</v>
+        <v>421850.679</v>
       </c>
       <c r="Q154" t="n">
-        <v>162189.944</v>
+        <v>125888.148</v>
       </c>
       <c r="R154" t="n">
-        <v>256.812</v>
+        <v>335.1</v>
       </c>
       <c r="S154" t="n">
-        <v>77.58</v>
+        <v>86.631</v>
       </c>
       <c r="T154" t="n">
-        <v>128.9</v>
+        <v>115.432</v>
       </c>
       <c r="U154" t="n">
-        <v>3.722</v>
+        <v>3.449</v>
       </c>
       <c r="V154" t="n">
-        <v>18205.90499999999</v>
+        <v>50291.15800000001</v>
       </c>
       <c r="W154" t="n">
-        <v>-11.997</v>
+        <v>-13.959</v>
       </c>
       <c r="X154" t="n">
-        <v>-10.559</v>
+        <v>-4.909</v>
       </c>
       <c r="Y154" t="n">
-        <v>3.349</v>
+        <v>9.473000000000001</v>
       </c>
       <c r="AC154" t="n">
-        <v>-391</v>
+        <v>-130</v>
       </c>
       <c r="AD154" t="n">
-        <v>-9.369999999999999</v>
+        <v>-3.276</v>
       </c>
       <c r="AE154" t="n">
-        <v>-0.864</v>
+        <v>-0.298</v>
       </c>
       <c r="AF154" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 3 năm 2025</t>
+          <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
       <c r="AG154" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-10-30/no-name-1761766923.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-quc-t-vit-nam06082025-000000bo-co-ti-chnh-hp-nht-bn-nin_1_0929.pdf</t>
         </is>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>2026-08-31T16:03:19+07:00</t>
+          <t>2026-08-31T12:52:16+07:00</t>
         </is>
       </c>
     </row>
@@ -44879,7 +45252,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2025-FY</t>
+          <t>2025-Q3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -44888,75 +45261,90 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>556098.441</v>
+        <v>543559.67</v>
       </c>
       <c r="F155" t="n">
-        <v>46904.739</v>
+        <v>45259.765</v>
       </c>
       <c r="G155" t="n">
-        <v>4213.631</v>
+        <v>4172.726</v>
       </c>
       <c r="H155" t="n">
-        <v>294577.661</v>
+        <v>307929.159</v>
       </c>
       <c r="I155" t="n">
-        <v>377113.195</v>
+        <v>367863.425</v>
       </c>
       <c r="J155" t="n">
-        <v>128.018</v>
+        <v>119.464</v>
       </c>
       <c r="K155" t="n">
-        <v>116961.762</v>
+        <v>114615.934</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>-49593.355</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>-9.124000000000001</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>-7.686</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>-8.667999999999999</v>
+      </c>
+      <c r="P155" t="n">
+        <v>416523.18</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>162189.944</v>
+      </c>
+      <c r="R155" t="n">
+        <v>256.812</v>
+      </c>
+      <c r="S155" t="n">
+        <v>77.58</v>
+      </c>
+      <c r="T155" t="n">
+        <v>128.9</v>
       </c>
       <c r="U155" t="n">
-        <v>3.97</v>
+        <v>3.722</v>
       </c>
       <c r="V155" t="n">
-        <v>26608.905</v>
+        <v>18205.90499999999</v>
       </c>
       <c r="W155" t="n">
-        <v>-17.275</v>
+        <v>-11.997</v>
       </c>
       <c r="X155" t="n">
-        <v>-10.284</v>
+        <v>-10.559</v>
       </c>
       <c r="Y155" t="n">
-        <v>4.785</v>
+        <v>3.349</v>
       </c>
       <c r="AC155" t="n">
-        <v>-278</v>
+        <v>-391</v>
       </c>
       <c r="AD155" t="n">
-        <v>-6.598</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AE155" t="n">
-        <v>-0.593</v>
+        <v>-0.864</v>
       </c>
       <c r="AF155" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 3 năm 2025</t>
         </is>
       </c>
       <c r="AG155" t="inlineStr">
         <is>
-          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260302_-_VIB_-_BCTC_hop_nhat_kiem_toan_2025_1772443477.pdf</t>
+          <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-10-30/no-name-1761766923.pdf</t>
         </is>
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>2026-08-31T01:52:28+07:00</t>
+          <t>2026-08-31T16:03:19+07:00</t>
         </is>
       </c>
     </row>
@@ -44968,7 +45356,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2025-FY</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -44977,90 +45365,75 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>564145.938</v>
+        <v>556098.441</v>
       </c>
       <c r="F156" t="n">
-        <v>49144.071</v>
+        <v>46904.739</v>
       </c>
       <c r="G156" t="n">
-        <v>4038.566</v>
+        <v>4213.631</v>
       </c>
       <c r="H156" t="n">
-        <v>316373.838</v>
+        <v>294577.661</v>
       </c>
       <c r="I156" t="n">
-        <v>381361.994</v>
+        <v>377113.195</v>
       </c>
       <c r="J156" t="n">
-        <v>120.542</v>
+        <v>128.018</v>
       </c>
       <c r="K156" t="n">
-        <v>120321.477</v>
+        <v>116961.762</v>
       </c>
       <c r="L156" t="n">
-        <v>-33143.201</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>-5.875</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>6.539</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="P156" t="n">
-        <v>408268.254</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>132763.941</v>
-      </c>
-      <c r="R156" t="n">
-        <v>307.514</v>
-      </c>
-      <c r="S156" t="n">
-        <v>114.651</v>
-      </c>
-      <c r="T156" t="n">
-        <v>87.221</v>
+        <v>0</v>
       </c>
       <c r="U156" t="n">
-        <v>3.803</v>
+        <v>3.97</v>
       </c>
       <c r="V156" t="n">
-        <v>31809.19</v>
+        <v>26608.905</v>
       </c>
       <c r="W156" t="n">
-        <v>-9.518000000000001</v>
+        <v>-17.275</v>
       </c>
       <c r="X156" t="n">
-        <v>2.896</v>
+        <v>-10.284</v>
       </c>
       <c r="Y156" t="n">
-        <v>5.638</v>
+        <v>4.785</v>
       </c>
       <c r="AC156" t="n">
-        <v>54</v>
+        <v>-278</v>
       </c>
       <c r="AD156" t="n">
-        <v>1.337</v>
+        <v>-6.598</v>
       </c>
       <c r="AE156" t="n">
-        <v>0.11</v>
+        <v>-0.593</v>
       </c>
       <c r="AF156" t="inlineStr">
         <is>
-          <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2026</t>
+          <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
       <c r="AG156" t="inlineStr">
         <is>
-          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-30/no-name-1777489917.pdf</t>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260302_-_VIB_-_BCTC_hop_nhat_kiem_toan_2025_1772443477.pdf</t>
         </is>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>2026-09-01T00:07:17+07:00</t>
+          <t>2026-08-31T01:52:28+07:00</t>
         </is>
       </c>
     </row>
@@ -45072,82 +45445,186 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>564145.938</v>
+      </c>
+      <c r="F157" t="n">
+        <v>49144.071</v>
+      </c>
+      <c r="G157" t="n">
+        <v>4038.566</v>
+      </c>
+      <c r="H157" t="n">
+        <v>316373.838</v>
+      </c>
+      <c r="I157" t="n">
+        <v>381361.994</v>
+      </c>
+      <c r="J157" t="n">
+        <v>120.542</v>
+      </c>
+      <c r="K157" t="n">
+        <v>120321.477</v>
+      </c>
+      <c r="L157" t="n">
+        <v>-33143.201</v>
+      </c>
+      <c r="M157" t="n">
+        <v>-5.875</v>
+      </c>
+      <c r="N157" t="n">
+        <v>6.539</v>
+      </c>
+      <c r="O157" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="P157" t="n">
+        <v>408268.254</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>132763.941</v>
+      </c>
+      <c r="R157" t="n">
+        <v>307.514</v>
+      </c>
+      <c r="S157" t="n">
+        <v>114.651</v>
+      </c>
+      <c r="T157" t="n">
+        <v>87.221</v>
+      </c>
+      <c r="U157" t="n">
+        <v>3.803</v>
+      </c>
+      <c r="V157" t="n">
+        <v>31809.19</v>
+      </c>
+      <c r="W157" t="n">
+        <v>-9.518000000000001</v>
+      </c>
+      <c r="X157" t="n">
+        <v>2.896</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>5.638</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>54</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2026</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-30/no-name-1777489917.pdf</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:07:17+07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>VIB</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>2026-Q2</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="E157" t="n">
+      <c r="E158" t="n">
         <v>580998.048</v>
       </c>
-      <c r="F157" t="n">
+      <c r="F158" t="n">
         <v>47837.834</v>
       </c>
-      <c r="G157" t="n">
+      <c r="G158" t="n">
         <v>4367.969</v>
       </c>
-      <c r="H157" t="n">
+      <c r="H158" t="n">
         <v>317451.548</v>
       </c>
-      <c r="I157" t="n">
+      <c r="I158" t="n">
         <v>392020.433</v>
       </c>
-      <c r="J157" t="n">
+      <c r="J158" t="n">
         <v>123.49</v>
       </c>
-      <c r="K157" t="n">
+      <c r="K158" t="n">
         <v>126013.699</v>
       </c>
-      <c r="L157" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0</v>
-      </c>
-      <c r="N157" t="n">
-        <v>0</v>
-      </c>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" t="n">
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="n">
         <v>3.97</v>
       </c>
-      <c r="V157" t="n">
+      <c r="V158" t="n">
         <v>44375.359</v>
       </c>
-      <c r="W157" t="n">
+      <c r="W158" t="n">
         <v>-6.8</v>
       </c>
-      <c r="X157" t="n">
+      <c r="X158" t="n">
         <v>-1.409</v>
       </c>
-      <c r="Y157" t="n">
+      <c r="Y158" t="n">
         <v>7.638</v>
       </c>
-      <c r="AC157" t="n">
+      <c r="AC158" t="n">
         <v>-1</v>
       </c>
-      <c r="AD157" t="n">
+      <c r="AD158" t="n">
         <v>-0.023</v>
       </c>
-      <c r="AE157" t="n">
+      <c r="AE158" t="n">
         <v>-0.002</v>
       </c>
-      <c r="AF157" t="inlineStr">
+      <c r="AF158" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AG157" t="inlineStr">
+      <c r="AG158" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VIB_202608062020VIB2020BCTC20hop20nhat20soat20xet20ban20nien202026_12082026154930.pdf?v=1786524571501</t>
         </is>
       </c>
-      <c r="AH157" t="inlineStr">
+      <c r="AH158" t="inlineStr">
         <is>
           <t>2026-09-01T10:23:21+07:00</t>
         </is>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -36477,12 +36477,94 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>580859.917</v>
+      </c>
+      <c r="F60" t="n">
+        <v>49471.665</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3878.245</v>
+      </c>
+      <c r="H60" t="n">
+        <v>345760.324</v>
+      </c>
+      <c r="I60" t="n">
+        <v>397873.229</v>
+      </c>
+      <c r="J60" t="n">
+        <v>115.072</v>
+      </c>
+      <c r="K60" t="n">
+        <v>109738.331</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-331251.879</v>
+      </c>
+      <c r="M60" t="n">
+        <v>-57.028</v>
+      </c>
+      <c r="N60" t="n">
+        <v>-55.582</v>
+      </c>
+      <c r="O60" t="n">
+        <v>-55.571</v>
+      </c>
+      <c r="P60" t="n">
+        <v>347607.222</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>586084.463</v>
+      </c>
+      <c r="R60" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="S60" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T60" t="n">
+        <v>799.979</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3.174</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-22/no-name-1776797412.pdf</t>
         </is>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>2026-09-17T09:43:14+07:00</t>
+          <t>2026-09-17T19:14:13+07:00</t>
         </is>
       </c>
     </row>
@@ -39443,12 +39525,103 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>344097.628063307</v>
+      </c>
+      <c r="F91" t="n">
+        <v>34900.70310944</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2382.731946497</v>
+      </c>
+      <c r="H91" t="n">
+        <v>158683.19610787</v>
+      </c>
+      <c r="I91" t="n">
+        <v>200503.421569508</v>
+      </c>
+      <c r="J91" t="n">
+        <v>126.355</v>
+      </c>
+      <c r="K91" t="n">
+        <v>70288.959484693</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1187.641439761</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="S91" t="n">
+        <v>37547.712</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="U91" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="V91" t="n">
+        <v>-0.192697418</v>
+      </c>
+      <c r="W91" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>92.95</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>41547.537</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260422_-_OCB_-_BCTC_hop_nhat_Quy_1_2026_1776854955.pdf</t>
         </is>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>2026-09-17T09:46:33+07:00</t>
+          <t>2026-09-17T19:15:32+07:00</t>
         </is>
       </c>
     </row>
@@ -40993,7 +41166,7 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>2026-09-17T09:48:13+07:00</t>
+          <t>2026-09-17T19:16:33+07:00</t>
         </is>
       </c>
     </row>
@@ -43347,12 +43520,103 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>527169.377</v>
+      </c>
+      <c r="F133" t="n">
+        <v>48034.318</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3459.591</v>
+      </c>
+      <c r="H133" t="n">
+        <v>267038.156</v>
+      </c>
+      <c r="I133" t="n">
+        <v>312044.784</v>
+      </c>
+      <c r="J133" t="n">
+        <v>116.854</v>
+      </c>
+      <c r="K133" t="n">
+        <v>121977.888</v>
+      </c>
+      <c r="L133" t="n">
+        <v>861.6610000000001</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="P133" t="n">
+        <v>68366.49800000001</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>24031.185</v>
+      </c>
+      <c r="R133" t="n">
+        <v>284.491</v>
+      </c>
+      <c r="S133" t="n">
+        <v>201.128</v>
+      </c>
+      <c r="T133" t="n">
+        <v>49.719</v>
+      </c>
+      <c r="U133" t="n">
+        <v>4.568</v>
+      </c>
+      <c r="V133" t="n">
+        <v>22216.787</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>-0.915</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>201987.137</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>63845.469</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>316.369</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>159</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>4.596</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_TPB_-_BCTC_hop_nhat_Quy_1_2026_signed_1777457982.pdf</t>
         </is>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>2026-09-17T09:59:43+07:00</t>
+          <t>2026-09-17T19:18:12+07:00</t>
         </is>
       </c>
     </row>
@@ -43776,7 +44040,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>2026-09-17T09:59:50+07:00</t>
+          <t>2026-09-17T19:18:18+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -44040,7 +44040,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>2026-09-17T19:18:18+07:00</t>
+          <t>2026-09-18T08:14:13+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30918,7 +30918,7 @@
         <v>4.068</v>
       </c>
       <c r="V4" t="n">
-        <v>8183.362999999996</v>
+        <v>8183.362999999999</v>
       </c>
       <c r="W4" t="n">
         <v>-7.633</v>
@@ -31007,7 +31007,7 @@
         <v>3.572</v>
       </c>
       <c r="V5" t="n">
-        <v>-2072.081999999995</v>
+        <v>-2072.081999999999</v>
       </c>
       <c r="W5" t="n">
         <v>-6.467</v>
@@ -31111,7 +31111,7 @@
         <v>4.395</v>
       </c>
       <c r="V6" t="n">
-        <v>-5551.592999999999</v>
+        <v>-5551.593000000001</v>
       </c>
       <c r="W6" t="n">
         <v>0.38</v>
@@ -31408,7 +31408,7 @@
         <v>2.424</v>
       </c>
       <c r="V9" t="n">
-        <v>85041.65799999997</v>
+        <v>85041.658</v>
       </c>
       <c r="W9" t="n">
         <v>-9.567</v>
@@ -33050,7 +33050,7 @@
         <v>2.564</v>
       </c>
       <c r="V26" t="n">
-        <v>-2093.93</v>
+        <v>-2093.930000000001</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -34149,7 +34149,7 @@
         <v>584740.964</v>
       </c>
       <c r="L37" t="n">
-        <v>57219.16100000001</v>
+        <v>57219.161</v>
       </c>
       <c r="M37" t="n">
         <v>1.932</v>
@@ -34461,7 +34461,7 @@
         <v>2.439</v>
       </c>
       <c r="V40" t="n">
-        <v>-6843.675999999999</v>
+        <v>-6843.676</v>
       </c>
       <c r="W40" t="n">
         <v>-9.135999999999999</v>
@@ -34639,7 +34639,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="L42" t="n">
-        <v>2554.764000000001</v>
+        <v>2554.764</v>
       </c>
       <c r="M42" t="n">
         <v>0.946</v>
@@ -35385,7 +35385,7 @@
         <v>3.011</v>
       </c>
       <c r="V49" t="n">
-        <v>1097.082999999999</v>
+        <v>1097.083000000001</v>
       </c>
       <c r="W49" t="n">
         <v>3.244</v>
@@ -37304,7 +37304,7 @@
         <v>53049.641</v>
       </c>
       <c r="L68" t="n">
-        <v>-71627.23300000001</v>
+        <v>-71627.23299999999</v>
       </c>
       <c r="M68" t="n">
         <v>-22.759</v>
@@ -37646,7 +37646,7 @@
         <v>4.335</v>
       </c>
       <c r="V71" t="n">
-        <v>-36336.33499999999</v>
+        <v>-36336.335</v>
       </c>
       <c r="W71" t="n">
         <v>7.502</v>
@@ -37928,7 +37928,7 @@
         <v>3.04</v>
       </c>
       <c r="V74" t="n">
-        <v>1044.137999999999</v>
+        <v>1044.137999999998</v>
       </c>
       <c r="W74" t="n">
         <v>-0.302</v>
@@ -38032,7 +38032,7 @@
         <v>4.485</v>
       </c>
       <c r="V75" t="n">
-        <v>-7342.066000000003</v>
+        <v>-7342.066000000001</v>
       </c>
       <c r="W75" t="n">
         <v>1.12</v>
@@ -38819,7 +38819,7 @@
         <v>3.06</v>
       </c>
       <c r="V83" t="n">
-        <v>44447.072</v>
+        <v>44447.07199999999</v>
       </c>
       <c r="W83" t="n">
         <v>41.067</v>
@@ -39415,7 +39415,7 @@
         <v>57104.9273618</v>
       </c>
       <c r="L89" t="n">
-        <v>-8354.105685278017</v>
+        <v>-8354.105685278011</v>
       </c>
       <c r="M89" t="n">
         <v>-2.587</v>
@@ -40079,7 +40079,7 @@
         <v>6.429</v>
       </c>
       <c r="V96" t="n">
-        <v>-448.712</v>
+        <v>-448.7119999999998</v>
       </c>
       <c r="W96" t="n">
         <v>-8.398</v>
@@ -40361,7 +40361,7 @@
         <v>3.682</v>
       </c>
       <c r="V99" t="n">
-        <v>-8415.234000000002</v>
+        <v>-8415.234</v>
       </c>
       <c r="W99" t="n">
         <v>-5.98</v>
@@ -42835,7 +42835,7 @@
         <v>3.255</v>
       </c>
       <c r="V126" t="n">
-        <v>-95355.82799999998</v>
+        <v>-95355.82799999999</v>
       </c>
       <c r="W126" t="n">
         <v>-8.385</v>
@@ -42939,7 +42939,7 @@
         <v>3.105</v>
       </c>
       <c r="V127" t="n">
-        <v>31803.23300000001</v>
+        <v>31803.233</v>
       </c>
       <c r="W127" t="n">
         <v>4.369</v>
@@ -43043,7 +43043,7 @@
         <v>2.784</v>
       </c>
       <c r="V128" t="n">
-        <v>49624.19500000001</v>
+        <v>49624.19499999999</v>
       </c>
       <c r="W128" t="n">
         <v>9.231999999999999</v>
@@ -43147,7 +43147,7 @@
         <v>2.296</v>
       </c>
       <c r="V129" t="n">
-        <v>47597.061</v>
+        <v>47597.06099999999</v>
       </c>
       <c r="W129" t="n">
         <v>12.611</v>
@@ -44035,12 +44035,98 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>142390.241306315</v>
+      </c>
+      <c r="F139" t="n">
+        <v>10569.944213453</v>
+      </c>
+      <c r="G139" t="n">
+        <v>675.525473695</v>
+      </c>
+      <c r="H139" t="n">
+        <v>102351.029371344</v>
+      </c>
+      <c r="I139" t="n">
+        <v>89679.977935756</v>
+      </c>
+      <c r="J139" t="n">
+        <v>87.62</v>
+      </c>
+      <c r="K139" t="n">
+        <v>19802.319642618</v>
+      </c>
+      <c r="L139" t="n">
+        <v>21287.514</v>
+      </c>
+      <c r="M139" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="N139" t="n">
+        <v>9.039</v>
+      </c>
+      <c r="O139" t="n">
+        <v>-8.877000000000001</v>
+      </c>
+      <c r="P139" t="n">
+        <v>127900.126</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>28479.752</v>
+      </c>
+      <c r="R139" t="n">
+        <v>449.091</v>
+      </c>
+      <c r="S139" t="n">
+        <v>50.879</v>
+      </c>
+      <c r="T139" t="n">
+        <v>196.546</v>
+      </c>
+      <c r="U139" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="V139" t="n">
+        <v>3955.387000000001</v>
+      </c>
+      <c r="W139" t="n">
+        <v>-2.566</v>
+      </c>
+      <c r="X139" t="n">
+        <v>7.933</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>2.778</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>131635.815</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>129515.728</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>101.637</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>89</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>Nhap thu cong tu anh chup BCTC that (VAB thuyet minh BCTC Quy 1 2026, cot 'qua han duoi/tren 3 thang' dao nguoc thu tu so voi chuan nen da doi lai khi nhap, don vi da xac nhan la Trieu dong that qua doi chieu Vietcap)</t>
         </is>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>2026-09-18T08:14:13+07:00</t>
+          <t>2026-09-18T08:32:03+07:00</t>
         </is>
       </c>
     </row>
@@ -45576,7 +45662,7 @@
         <v>3.722</v>
       </c>
       <c r="V155" t="n">
-        <v>18205.90499999999</v>
+        <v>18205.905</v>
       </c>
       <c r="W155" t="n">
         <v>-11.997</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30918,7 +30918,7 @@
         <v>4.068</v>
       </c>
       <c r="V4" t="n">
-        <v>8183.362999999999</v>
+        <v>8183.362999999996</v>
       </c>
       <c r="W4" t="n">
         <v>-7.633</v>
@@ -31007,7 +31007,7 @@
         <v>3.572</v>
       </c>
       <c r="V5" t="n">
-        <v>-2072.081999999999</v>
+        <v>-2072.081999999995</v>
       </c>
       <c r="W5" t="n">
         <v>-6.467</v>
@@ -31111,7 +31111,7 @@
         <v>4.395</v>
       </c>
       <c r="V6" t="n">
-        <v>-5551.593000000001</v>
+        <v>-5551.592999999999</v>
       </c>
       <c r="W6" t="n">
         <v>0.38</v>
@@ -31408,7 +31408,7 @@
         <v>2.424</v>
       </c>
       <c r="V9" t="n">
-        <v>85041.658</v>
+        <v>85041.65799999997</v>
       </c>
       <c r="W9" t="n">
         <v>-9.567</v>
@@ -33050,7 +33050,7 @@
         <v>2.564</v>
       </c>
       <c r="V26" t="n">
-        <v>-2093.930000000001</v>
+        <v>-2093.93</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -34149,7 +34149,7 @@
         <v>584740.964</v>
       </c>
       <c r="L37" t="n">
-        <v>57219.161</v>
+        <v>57219.16100000001</v>
       </c>
       <c r="M37" t="n">
         <v>1.932</v>
@@ -34461,7 +34461,7 @@
         <v>2.439</v>
       </c>
       <c r="V40" t="n">
-        <v>-6843.676</v>
+        <v>-6843.675999999999</v>
       </c>
       <c r="W40" t="n">
         <v>-9.135999999999999</v>
@@ -34639,7 +34639,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="L42" t="n">
-        <v>2554.764</v>
+        <v>2554.764000000001</v>
       </c>
       <c r="M42" t="n">
         <v>0.946</v>
@@ -35385,7 +35385,7 @@
         <v>3.011</v>
       </c>
       <c r="V49" t="n">
-        <v>1097.083000000001</v>
+        <v>1097.082999999999</v>
       </c>
       <c r="W49" t="n">
         <v>3.244</v>
@@ -37304,7 +37304,7 @@
         <v>53049.641</v>
       </c>
       <c r="L68" t="n">
-        <v>-71627.23299999999</v>
+        <v>-71627.23300000001</v>
       </c>
       <c r="M68" t="n">
         <v>-22.759</v>
@@ -37646,7 +37646,7 @@
         <v>4.335</v>
       </c>
       <c r="V71" t="n">
-        <v>-36336.335</v>
+        <v>-36336.33499999999</v>
       </c>
       <c r="W71" t="n">
         <v>7.502</v>
@@ -37928,7 +37928,7 @@
         <v>3.04</v>
       </c>
       <c r="V74" t="n">
-        <v>1044.137999999998</v>
+        <v>1044.137999999999</v>
       </c>
       <c r="W74" t="n">
         <v>-0.302</v>
@@ -38032,7 +38032,7 @@
         <v>4.485</v>
       </c>
       <c r="V75" t="n">
-        <v>-7342.066000000001</v>
+        <v>-7342.066000000003</v>
       </c>
       <c r="W75" t="n">
         <v>1.12</v>
@@ -38819,7 +38819,7 @@
         <v>3.06</v>
       </c>
       <c r="V83" t="n">
-        <v>44447.07199999999</v>
+        <v>44447.072</v>
       </c>
       <c r="W83" t="n">
         <v>41.067</v>
@@ -39415,7 +39415,7 @@
         <v>57104.9273618</v>
       </c>
       <c r="L89" t="n">
-        <v>-8354.105685278011</v>
+        <v>-8354.105685278017</v>
       </c>
       <c r="M89" t="n">
         <v>-2.587</v>
@@ -40079,7 +40079,7 @@
         <v>6.429</v>
       </c>
       <c r="V96" t="n">
-        <v>-448.7119999999998</v>
+        <v>-448.712</v>
       </c>
       <c r="W96" t="n">
         <v>-8.398</v>
@@ -40361,7 +40361,7 @@
         <v>3.682</v>
       </c>
       <c r="V99" t="n">
-        <v>-8415.234</v>
+        <v>-8415.234000000002</v>
       </c>
       <c r="W99" t="n">
         <v>-5.98</v>
@@ -42835,7 +42835,7 @@
         <v>3.255</v>
       </c>
       <c r="V126" t="n">
-        <v>-95355.82799999999</v>
+        <v>-95355.82799999998</v>
       </c>
       <c r="W126" t="n">
         <v>-8.385</v>
@@ -42939,7 +42939,7 @@
         <v>3.105</v>
       </c>
       <c r="V127" t="n">
-        <v>31803.233</v>
+        <v>31803.23300000001</v>
       </c>
       <c r="W127" t="n">
         <v>4.369</v>
@@ -43043,7 +43043,7 @@
         <v>2.784</v>
       </c>
       <c r="V128" t="n">
-        <v>49624.19499999999</v>
+        <v>49624.19500000001</v>
       </c>
       <c r="W128" t="n">
         <v>9.231999999999999</v>
@@ -43147,7 +43147,7 @@
         <v>2.296</v>
       </c>
       <c r="V129" t="n">
-        <v>47597.06099999999</v>
+        <v>47597.061</v>
       </c>
       <c r="W129" t="n">
         <v>12.611</v>
@@ -43909,12 +43909,88 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>134613.747271322</v>
+      </c>
+      <c r="F137" t="n">
+        <v>9690.784798859</v>
+      </c>
+      <c r="G137" t="n">
+        <v>638.68127616</v>
+      </c>
+      <c r="H137" t="n">
+        <v>97984.432309576</v>
+      </c>
+      <c r="I137" t="n">
+        <v>85811.150481169</v>
+      </c>
+      <c r="J137" t="n">
+        <v>87.57599999999999</v>
+      </c>
+      <c r="K137" t="n">
+        <v>20755.174731968</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>2.118</v>
+      </c>
+      <c r="V137" t="n">
+        <v>5430.341</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-1.568</v>
+      </c>
+      <c r="X137" t="n">
+        <v>10.425</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>4.034</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>221001.348</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>221087.326</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>99.961</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>93</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>14.561</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251017_-_VAB_-_BCTC_HN_Q3.2025_1761126486.pdf</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>2026-09-17T18:14:21+07:00</t>
+          <t>2026-09-18T08:37:05+07:00</t>
         </is>
       </c>
     </row>
@@ -45662,7 +45738,7 @@
         <v>3.722</v>
       </c>
       <c r="V155" t="n">
-        <v>18205.905</v>
+        <v>18205.90499999999</v>
       </c>
       <c r="W155" t="n">
         <v>-11.997</v>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -32682,12 +32682,97 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3071970.196</v>
+      </c>
+      <c r="F22" t="n">
+        <v>167986.701</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15172.618</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2087181.421</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2197470.752</v>
+      </c>
+      <c r="J22" t="n">
+        <v>105.284</v>
+      </c>
+      <c r="K22" t="n">
+        <v>512310.713</v>
+      </c>
+      <c r="L22" t="n">
+        <v>20511.126</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.237</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>7048.125</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="V22" t="n">
+        <v>459217.92</v>
+      </c>
+      <c r="W22" t="n">
+        <v>7.618</v>
+      </c>
+      <c r="X22" t="n">
+        <v>23.135</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>14.949</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1186171.693</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>441729.583</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>268.529</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4337</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>28.584</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.582</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_BID_-_CBTT_BCTC_HN_giua_nien_do_QIII_1761898492.pdf</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2026-09-17T18:09:51+07:00</t>
+          <t>2026-09-18T08:44:10+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -39571,7 +39571,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>2026-09-17T18:24:55+07:00</t>
+          <t>2026-09-18T08:55:46+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -30461,7 +30461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO158"/>
+  <dimension ref="A1:AS158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30505,6 +30505,10 @@
     <col width="16" customWidth="1" min="39" max="39"/>
     <col width="16" customWidth="1" min="40" max="40"/>
     <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="16" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30665,50 +30669,70 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>Gap lai suat/TTS &lt;=6thang (%)</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>Gap lai suat/TTS &lt;=1nam (%)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Gap lai suat/TTS &lt;=5nam (%)</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>RSA (ty)</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>RSL (ty)</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>RSA/RSL (%)</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Stress NII +100bp (ty)</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Stress NII +100bp/NII (%)</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Stress NII +100bp/VCSH (%)</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Stress NII +200bp (ty)</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Stress NII +200bp/NII (%)</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Nguon (tieu de)</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Nguon (url)</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Cap nhat luc</t>
         </is>
@@ -30782,28 +30806,40 @@
         <v>6.136</v>
       </c>
       <c r="AF2" t="n">
+        <v>2.737</v>
+      </c>
+      <c r="AG2" t="n">
         <v>32.089</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AH2" t="n">
+        <v>13.931</v>
+      </c>
+      <c r="AL2" t="n">
         <v>196</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AM2" t="n">
         <v>23.556</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AN2" t="n">
         <v>1.365</v>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AO2" t="n">
+        <v>392</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>47.112</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-an-bnh29042025-000000bo-co-ti-chnh-qu-1-2025.pdf</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>2026-08-31T09:54:52+07:00</t>
         </is>
@@ -30879,26 +30915,38 @@
       <c r="AF3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00012345679012345679ngn-hng-tmcp-an-bnh04092025-000000bo-co-ti-chnh-bn-nin-2025_1_0945.pdf</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>2026-08-31T11:41:33+07:00</t>
         </is>
@@ -31002,28 +31050,40 @@
         <v>22.918</v>
       </c>
       <c r="AF4" t="n">
+        <v>7.906</v>
+      </c>
+      <c r="AG4" t="n">
         <v>4</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AH4" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AL4" t="n">
         <v>159</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AM4" t="n">
         <v>9.846</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AN4" t="n">
         <v>1.004</v>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AO4" t="n">
+        <v>318</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>19.692</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_586159_Bao_cao_tai_chinh_quy_32025_1762168308.pdf</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>2026-08-31T15:10:19+07:00</t>
         </is>
@@ -31097,28 +31157,40 @@
         <v>25.695</v>
       </c>
       <c r="AF5" t="n">
+        <v>3.451</v>
+      </c>
+      <c r="AG5" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AH5" t="n">
+        <v>-2.785</v>
+      </c>
+      <c r="AL5" t="n">
         <v>124</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AM5" t="n">
         <v>7.256</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AN5" t="n">
         <v>0.738</v>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AO5" t="n">
+        <v>248</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>14.512</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604250_Bao_cao_tai_chinh_nam_2025_1775705238.pdf</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>2026-08-31T01:05:32+07:00</t>
         </is>
@@ -31222,28 +31294,40 @@
         <v>-7.584</v>
       </c>
       <c r="AF6" t="n">
+        <v>-6.439</v>
+      </c>
+      <c r="AG6" t="n">
         <v>-2.22</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AH6" t="n">
+        <v>10.711</v>
+      </c>
+      <c r="AL6" t="n">
         <v>-113</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AM6" t="n">
         <v>-11.553</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AN6" t="n">
         <v>-0.631</v>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AO6" t="n">
+        <v>-226</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-23.106</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-05-09/no-name-1778265007.pdf</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>2026-08-31T23:10:58+07:00</t>
         </is>
@@ -31317,28 +31401,40 @@
         <v>0.17</v>
       </c>
       <c r="AF7" t="n">
+        <v>21.407</v>
+      </c>
+      <c r="AG7" t="n">
         <v>23.454</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AH7" t="n">
+        <v>3.293</v>
+      </c>
+      <c r="AL7" t="n">
         <v>363</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AM7" t="n">
         <v>21.243</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AN7" t="n">
         <v>1.606</v>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AO7" t="n">
+        <v>726</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>42.487</v>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ABB_000000016745964_BCTC_BAN_NIEN_2026_KTSXcompressed_25082026154210.pdf?v=1787647332246</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>2026-09-01T09:31:33+07:00</t>
         </is>
@@ -31444,26 +31540,38 @@
       <c r="AF8" t="n">
         <v>28.296</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AG8" t="n">
+        <v>28.296</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>17.916</v>
+      </c>
+      <c r="AL8" t="n">
         <v>1419</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AM8" t="n">
         <v>22.315</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AN8" t="n">
         <v>1.63</v>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AO8" t="n">
+        <v>2838</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>44.631</v>
+      </c>
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_Baocaotaichinh_Q1_2025_Hopnhat_13052025091456.pdf</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>2026-08-31T09:55:57+07:00</t>
         </is>
@@ -31567,28 +31675,40 @@
         <v>29.286</v>
       </c>
       <c r="AF9" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="AG9" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AH9" t="n">
+        <v>2.199</v>
+      </c>
+      <c r="AL9" t="n">
         <v>1288</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AM9" t="n">
         <v>19.27</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AN9" t="n">
         <v>1.477</v>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AO9" t="n">
+        <v>2576</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>38.541</v>
+      </c>
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_19092025164217.pdf</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>2026-08-31T11:43:25+07:00</t>
         </is>
@@ -31694,26 +31814,38 @@
       <c r="AF10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251022_-_ACB_-_BCTC_hop_nhat_Quy_03_nam_2025_1761122352.pdf</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>2026-08-31T15:12:08+07:00</t>
         </is>
@@ -31817,37 +31949,49 @@
         <v>32.032</v>
       </c>
       <c r="AF11" t="n">
+        <v>15.752</v>
+      </c>
+      <c r="AG11" t="n">
         <v>5.465</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="AI11" t="n">
         <v>971913.916</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AJ11" t="n">
         <v>906469.3540000001</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AK11" t="n">
         <v>107.22</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AL11" t="n">
         <v>1290</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AM11" t="n">
         <v>18.186</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AN11" t="n">
         <v>1.365</v>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AO11" t="n">
+        <v>2580</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>36.372</v>
+      </c>
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-1/2026-03-07/no-name-1772854112.pdf</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>2026-09-17T14:57:20+07:00</t>
         </is>
@@ -31950,26 +32094,38 @@
       <c r="AF12" t="n">
         <v>0</v>
       </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260422_-_ACB_-_BCTC_Hop_nhat_Quy_1_nam_2026_1776932823.pdf</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>2026-09-17T15:01:42+07:00</t>
         </is>
@@ -32073,28 +32229,40 @@
         <v>4.508</v>
       </c>
       <c r="AF13" t="n">
+        <v>4.521</v>
+      </c>
+      <c r="AG13" t="n">
         <v>4.542</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AH13" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AL13" t="n">
         <v>399</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AM13" t="n">
         <v>5.125</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AN13" t="n">
         <v>0.402</v>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AO13" t="n">
+        <v>798</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10.251</v>
+      </c>
+      <c r="AQ13" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AR13" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_202608142020ACB2020BCTC20hop20nhat20ban20nien202026_20082026094407.pdf?v=1787193848805</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
         <is>
           <t>2026-09-01T09:32:55+07:00</t>
         </is>
@@ -32198,28 +32366,40 @@
         <v>26.223</v>
       </c>
       <c r="AF14" t="n">
+        <v>17.562</v>
+      </c>
+      <c r="AG14" t="n">
         <v>11.307</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AH14" t="n">
+        <v>5.281</v>
+      </c>
+      <c r="AL14" t="n">
         <v>274</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AM14" t="n">
         <v>31.351</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AN14" t="n">
         <v>2.269</v>
       </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AO14" t="n">
+        <v>548</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>62.702</v>
+      </c>
+      <c r="AQ14" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AR14" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BAB_25Q1_BCTC_HN_07052025141647.pdf</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>2026-08-31T09:57:27+07:00</t>
         </is>
@@ -32323,28 +32503,40 @@
         <v>28.506</v>
       </c>
       <c r="AF15" t="n">
+        <v>19.807</v>
+      </c>
+      <c r="AG15" t="n">
         <v>9.757999999999999</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AH15" t="n">
+        <v>9.763</v>
+      </c>
+      <c r="AL15" t="n">
         <v>303</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AM15" t="n">
         <v>33.96</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AN15" t="n">
         <v>2.483</v>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AO15" t="n">
+        <v>606</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>67.92</v>
+      </c>
+      <c r="AQ15" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AR15" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-bc-30072025-000000bo-co-ti-chnh-qu-2-2025_3_0910.pdf</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="AS15" t="inlineStr">
         <is>
           <t>2026-08-31T11:44:48+07:00</t>
         </is>
@@ -32418,28 +32610,40 @@
         <v>31.011</v>
       </c>
       <c r="AF16" t="n">
+        <v>22.555</v>
+      </c>
+      <c r="AG16" t="n">
         <v>13.611</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AH16" t="n">
+        <v>6.002</v>
+      </c>
+      <c r="AL16" t="n">
         <v>366</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AM16" t="n">
         <v>52.181</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AN16" t="n">
         <v>2.865</v>
       </c>
-      <c r="AM16" t="inlineStr">
+      <c r="AO16" t="n">
+        <v>732</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>104.363</v>
+      </c>
+      <c r="AQ16" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AR16" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_586650_Bao_cao_tai_chinh_quy_32025_1763615639.pdf</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="AS16" t="inlineStr">
         <is>
           <t>2026-08-31T15:13:52+07:00</t>
         </is>
@@ -32536,26 +32740,38 @@
       <c r="AF17" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AR17" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604687_Bao_cao_tai_chinh_nam_2025_1774883201.pdf</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AS17" t="inlineStr">
         <is>
           <t>2026-08-31T01:08:17+07:00</t>
         </is>
@@ -32629,28 +32845,40 @@
         <v>30.322</v>
       </c>
       <c r="AF18" t="n">
+        <v>23.424</v>
+      </c>
+      <c r="AG18" t="n">
         <v>13.281</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AH18" t="n">
+        <v>4.985</v>
+      </c>
+      <c r="AL18" t="n">
         <v>381</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AM18" t="n">
         <v>37.351</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AN18" t="n">
         <v>2.8</v>
       </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AO18" t="n">
+        <v>762</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>74.703</v>
+      </c>
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AR18" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_612759_Bao_cao_tai_chinh_quy_12026_1777886654.pdf</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>2026-08-31T23:16:58+07:00</t>
         </is>
@@ -32754,28 +32982,40 @@
         <v>26.959</v>
       </c>
       <c r="AF19" t="n">
+        <v>26.959</v>
+      </c>
+      <c r="AG19" t="n">
         <v>15.819</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AH19" t="n">
+        <v>15.349</v>
+      </c>
+      <c r="AL19" t="n">
         <v>419</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AM19" t="n">
         <v>33.837</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AN19" t="n">
         <v>3.05</v>
       </c>
-      <c r="AM19" t="inlineStr">
+      <c r="AO19" t="n">
+        <v>838</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>67.673</v>
+      </c>
+      <c r="AQ19" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AR19" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BAB_000000016757863_VI_BaoCaoTaiChinh_SoatXet_BanNien2026_18082026093732.pdf?v=1787020653929</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
+      <c r="AS19" t="inlineStr">
         <is>
           <t>2026-09-01T09:34:31+07:00</t>
         </is>
@@ -32879,32 +33119,44 @@
         <v>-11.033</v>
       </c>
       <c r="AF20" t="n">
+        <v>7.216</v>
+      </c>
+      <c r="AG20" t="n">
         <v>-5.942</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AH20" t="n">
+        <v>-0.104</v>
+      </c>
+      <c r="AI20" t="n">
         <v>2718135.967</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AJ20" t="n">
         <v>2643816.65</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AK20" t="n">
         <v>102.811</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AL20" t="n">
         <v>-936</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AM20" t="n">
         <v>-6.712</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AN20" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AO20" t="n">
+        <v>-1872</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-13.424</v>
+      </c>
+      <c r="AQ20" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (BID BCTC hop nhat GND Quy I 2025, OCR khong doc duoc)</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr">
+      <c r="AS20" t="inlineStr">
         <is>
           <t>2026-09-17T14:38:33+07:00</t>
         </is>
@@ -32978,37 +33230,49 @@
         <v>-8.513999999999999</v>
       </c>
       <c r="AF21" t="n">
+        <v>-8.061</v>
+      </c>
+      <c r="AG21" t="n">
         <v>-22.633</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AH21" t="n">
+        <v>-24.486</v>
+      </c>
+      <c r="AI21" t="n">
         <v>569385.233</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AJ21" t="n">
         <v>1301394.451</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AK21" t="n">
         <v>43.752</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AL21" t="n">
         <v>-4094</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AM21" t="n">
         <v>-27.308</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AN21" t="n">
         <v>-2.516</v>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AO21" t="n">
+        <v>-8188</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-54.617</v>
+      </c>
+      <c r="AQ21" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AR21" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BID_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025143111.pdf</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AS21" t="inlineStr">
         <is>
           <t>2026-09-17T15:06:22+07:00</t>
         </is>
@@ -33106,37 +33370,49 @@
         <v>23.135</v>
       </c>
       <c r="AF22" t="n">
+        <v>12.293</v>
+      </c>
+      <c r="AG22" t="n">
         <v>14.949</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AH22" t="n">
+        <v>17.421</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1186171.693</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AJ22" t="n">
         <v>441729.583</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AK22" t="n">
         <v>268.529</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AL22" t="n">
         <v>4337</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AM22" t="n">
         <v>28.584</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AN22" t="n">
         <v>2.582</v>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AO22" t="n">
+        <v>8674</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>57.169</v>
+      </c>
+      <c r="AQ22" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AR22" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_BID_-_CBTT_BCTC_HN_giua_nien_do_QIII_1761898492.pdf</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
+      <c r="AS22" t="inlineStr">
         <is>
           <t>2026-09-18T08:44:10+07:00</t>
         </is>
@@ -33240,37 +33516,49 @@
         <v>-1.385</v>
       </c>
       <c r="AF23" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="AG23" t="n">
         <v>-1.103</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AH23" t="n">
+        <v>-1.317</v>
+      </c>
+      <c r="AI23" t="n">
         <v>3119987.368</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AJ23" t="n">
         <v>3088515.12</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AK23" t="n">
         <v>101.019</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AL23" t="n">
         <v>126</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AM23" t="n">
         <v>0.657</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AN23" t="n">
         <v>0.073</v>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AO23" t="n">
+        <v>252</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="AQ23" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AR23" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-02/no-name-1775069592.pdf</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr">
+      <c r="AS23" t="inlineStr">
         <is>
           <t>2026-09-17T18:18:58+07:00</t>
         </is>
@@ -33344,28 +33632,40 @@
         <v>-11.062</v>
       </c>
       <c r="AF24" t="n">
+        <v>-5.198</v>
+      </c>
+      <c r="AG24" t="n">
         <v>13.647</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AH24" t="n">
+        <v>24.709</v>
+      </c>
+      <c r="AL24" t="n">
         <v>-754</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AM24" t="n">
         <v>-4.792</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AN24" t="n">
         <v>-0.396</v>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AO24" t="n">
+        <v>-1508</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>-9.584</v>
+      </c>
+      <c r="AQ24" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AR24" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260424_-_BID_-_CBTT_BCTC_HN_giua_nien_do_Q1_1777032270.pdf</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="AS24" t="inlineStr">
         <is>
           <t>2026-08-31T23:18:24+07:00</t>
         </is>
@@ -33469,28 +33769,40 @@
         <v>0.887</v>
       </c>
       <c r="AF25" t="n">
+        <v>16.708</v>
+      </c>
+      <c r="AG25" t="n">
         <v>2.013</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AH25" t="n">
+        <v>-0.335</v>
+      </c>
+      <c r="AL25" t="n">
         <v>1987</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AM25" t="n">
         <v>11.16</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AN25" t="n">
         <v>1</v>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AO25" t="n">
+        <v>3974</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>22.321</v>
+      </c>
+      <c r="AQ25" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AR25" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BID_202608182020BID2020CBTT20BCTC20HN20ban20nien20da20duoc20soat20xet_20082026090048.pdf?v=1787191250249</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AS25" t="inlineStr">
         <is>
           <t>2026-09-01T09:36:26+07:00</t>
         </is>
@@ -33564,28 +33876,40 @@
         <v>11.222</v>
       </c>
       <c r="AF26" t="n">
+        <v>11.233</v>
+      </c>
+      <c r="AG26" t="n">
         <v>-1.902</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AH26" t="n">
+        <v>-2.508</v>
+      </c>
+      <c r="AL26" t="n">
         <v>67</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AM26" t="n">
         <v>13.273</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AN26" t="n">
         <v>1.077</v>
       </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AO26" t="n">
+        <v>134</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>26.546</v>
+      </c>
+      <c r="AQ26" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AR26" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-29/no-name-1745876078.pdf</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
+      <c r="AS26" t="inlineStr">
         <is>
           <t>2026-08-31T10:02:43+07:00</t>
         </is>
@@ -33659,28 +33983,40 @@
         <v>9.491</v>
       </c>
       <c r="AF27" t="n">
+        <v>-4.129</v>
+      </c>
+      <c r="AG27" t="n">
         <v>-10.133</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AH27" t="n">
+        <v>-9.484</v>
+      </c>
+      <c r="AL27" t="n">
         <v>-28</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AM27" t="n">
         <v>-4.349</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AN27" t="n">
         <v>-0.405</v>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AO27" t="n">
+        <v>-56</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>-8.698</v>
+      </c>
+      <c r="AQ27" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AR27" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-bn-vit15082025-000000bo-co-ti-chnh-bn-nin-2025_5_1133.pdf</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="AS27" t="inlineStr">
         <is>
           <t>2026-08-31T11:53:16+07:00</t>
         </is>
@@ -33784,28 +34120,40 @@
         <v>-6.139</v>
       </c>
       <c r="AF28" t="n">
+        <v>-1.731</v>
+      </c>
+      <c r="AG28" t="n">
         <v>-4.769</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AH28" t="n">
+        <v>4.485</v>
+      </c>
+      <c r="AL28" t="n">
         <v>-20</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AM28" t="n">
         <v>-2.79</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AN28" t="n">
         <v>-0.271</v>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AO28" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>-5.581</v>
+      </c>
+      <c r="AQ28" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AR28" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_585337_Bao_cao_tai_chinh_quy_32025_1761821099.pdf</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="AS28" t="inlineStr">
         <is>
           <t>2026-08-31T15:17:24+07:00</t>
         </is>
@@ -33911,26 +34259,38 @@
       <c r="AF29" t="n">
         <v>0</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
         <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
       </c>
-      <c r="AM29" t="inlineStr">
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AR29" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603502_Bao_cao_tai_chinh_nam_2025_1776046380.pdf</t>
         </is>
       </c>
-      <c r="AO29" t="inlineStr">
+      <c r="AS29" t="inlineStr">
         <is>
           <t>2026-08-31T01:11:30+07:00</t>
         </is>
@@ -34033,26 +34393,38 @@
       <c r="AF30" t="n">
         <v>0</v>
       </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
       </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
+      <c r="AR30" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_612193_Bao_cao_tai_chinh_quy_12026_1777459426.pdf</t>
         </is>
       </c>
-      <c r="AO30" t="inlineStr">
+      <c r="AS30" t="inlineStr">
         <is>
           <t>2026-08-31T23:20:32+07:00</t>
         </is>
@@ -34156,28 +34528,40 @@
         <v>16.428</v>
       </c>
       <c r="AF31" t="n">
+        <v>-0.947</v>
+      </c>
+      <c r="AG31" t="n">
         <v>-7.134</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AH31" t="n">
+        <v>-9.002000000000001</v>
+      </c>
+      <c r="AL31" t="n">
         <v>26</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AM31" t="n">
         <v>2.905</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AN31" t="n">
         <v>0.328</v>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AO31" t="n">
+        <v>52</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>5.809</v>
+      </c>
+      <c r="AQ31" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
+      <c r="AR31" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BVB_202608132020BVB2020Bao20cao20tai20chinh20hop20nhat20ban20nien20202620da20soat20xet20kem20giai20trinh20bien20dong20loi20nhuan_20082026095227.pdf?v=1787194349784</t>
         </is>
       </c>
-      <c r="AO31" t="inlineStr">
+      <c r="AS31" t="inlineStr">
         <is>
           <t>2026-09-01T09:38:24+07:00</t>
         </is>
@@ -34283,26 +34667,38 @@
       <c r="AF32" t="n">
         <v>0</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AR32" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_Baocaotaichinh_Q1_2025_Hopnhat_23052025140616.pdf</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
+      <c r="AS32" t="inlineStr">
         <is>
           <t>2026-08-31T10:05:00+07:00</t>
         </is>
@@ -34406,28 +34802,40 @@
         <v>-7.841</v>
       </c>
       <c r="AF33" t="n">
+        <v>4.389</v>
+      </c>
+      <c r="AG33" t="n">
         <v>-1.232</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AH33" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="AL33" t="n">
         <v>-503</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AM33" t="n">
         <v>-3.175</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AN33" t="n">
         <v>-0.307</v>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AO33" t="n">
+        <v>-1006</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="AQ33" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
+      <c r="AR33" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025145719.pdf</t>
         </is>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AS33" t="inlineStr">
         <is>
           <t>2026-08-31T11:55:46+07:00</t>
         </is>
@@ -34533,26 +34941,38 @@
       <c r="AF34" t="n">
         <v>0</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
+      <c r="AR34" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_CTG_-_BCTC_hop_nhat_Quy_3.2025_va_giai_trinh_bien_dong_loi_nhuan_signed_1761877722.pdf</t>
         </is>
       </c>
-      <c r="AO34" t="inlineStr">
+      <c r="AS34" t="inlineStr">
         <is>
           <t>2026-08-31T15:19:45+07:00</t>
         </is>
@@ -34656,28 +35076,40 @@
         <v>-7.394</v>
       </c>
       <c r="AF35" t="n">
+        <v>4.138</v>
+      </c>
+      <c r="AG35" t="n">
         <v>-1.162</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AH35" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AL35" t="n">
         <v>-503</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AM35" t="n">
         <v>-2.801</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AN35" t="n">
         <v>-0.28</v>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AO35" t="n">
+        <v>-1006</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>-5.601</v>
+      </c>
+      <c r="AQ35" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AR35" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_HK_20260331_-_CTG_-_BCTC_hop_nhat_kiem_toan_nam_2025__18062026104622.pdf</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AS35" t="inlineStr">
         <is>
           <t>2026-08-31T01:14:15+07:00</t>
         </is>
@@ -34781,28 +35213,40 @@
         <v>4.876</v>
       </c>
       <c r="AF36" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="AG36" t="n">
         <v>3.909</v>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AH36" t="n">
+        <v>18.996</v>
+      </c>
+      <c r="AL36" t="n">
         <v>573</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AM36" t="n">
         <v>2.956</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AN36" t="n">
         <v>0.304</v>
       </c>
-      <c r="AM36" t="inlineStr">
+      <c r="AO36" t="n">
+        <v>1146</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>5.912</v>
+      </c>
+      <c r="AQ36" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
+      <c r="AR36" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260428__CTG__BCTC_hop_nhat_Quy_I_13082026151826.2026_va_giai_trinh_bien_dong_loi_nhuan_signed_1777430252?v=1786609107953</t>
         </is>
       </c>
-      <c r="AO36" t="inlineStr">
+      <c r="AS36" t="inlineStr">
         <is>
           <t>2026-08-31T23:22:42+07:00</t>
         </is>
@@ -34876,28 +35320,40 @@
         <v>1.514</v>
       </c>
       <c r="AF37" t="n">
+        <v>16.693</v>
+      </c>
+      <c r="AG37" t="n">
         <v>23.371</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AH37" t="n">
+        <v>17.105</v>
+      </c>
+      <c r="AL37" t="n">
         <v>3710</v>
       </c>
-      <c r="AK37" t="n">
+      <c r="AM37" t="n">
         <v>17.896</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AN37" t="n">
         <v>1.853</v>
       </c>
-      <c r="AM37" t="inlineStr">
+      <c r="AO37" t="n">
+        <v>7420</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>35.793</v>
+      </c>
+      <c r="AQ37" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
+      <c r="AR37" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_202608142020CTG2020BCTC20hop20nhat206T202620da20soat20xet20va20giai20trinh20bien20dong20loi20nhuan_signed_19082026145907.pdf?v=1787126349271</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr">
+      <c r="AS37" t="inlineStr">
         <is>
           <t>2026-09-01T09:40:13+07:00</t>
         </is>
@@ -35001,28 +35457,40 @@
         <v>-4.564</v>
       </c>
       <c r="AF38" t="n">
+        <v>-8.135999999999999</v>
+      </c>
+      <c r="AG38" t="n">
         <v>-9.117000000000001</v>
       </c>
-      <c r="AJ38" t="n">
+      <c r="AH38" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="AL38" t="n">
         <v>-195</v>
       </c>
-      <c r="AK38" t="n">
+      <c r="AM38" t="n">
         <v>-14.398</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AN38" t="n">
         <v>-0.757</v>
       </c>
-      <c r="AM38" t="inlineStr">
+      <c r="AO38" t="n">
+        <v>-390</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>-28.795</v>
+      </c>
+      <c r="AQ38" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
+      <c r="AR38" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_Baocaotaichinh_Q1_2025_Hopnhat_22052025162515.pdf</t>
         </is>
       </c>
-      <c r="AO38" t="inlineStr">
+      <c r="AS38" t="inlineStr">
         <is>
           <t>2026-08-31T10:06:41+07:00</t>
         </is>
@@ -35119,26 +35587,38 @@
       <c r="AF39" t="n">
         <v>0</v>
       </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
       </c>
-      <c r="AM39" t="inlineStr">
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
+      <c r="AR39" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025085527.pdf</t>
         </is>
       </c>
-      <c r="AO39" t="inlineStr">
+      <c r="AS39" t="inlineStr">
         <is>
           <t>2026-08-31T11:57:38+07:00</t>
         </is>
@@ -35212,28 +35692,40 @@
         <v>-3.025</v>
       </c>
       <c r="AF40" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="AG40" t="n">
         <v>-2.676</v>
       </c>
-      <c r="AJ40" t="n">
+      <c r="AH40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AL40" t="n">
         <v>-88</v>
       </c>
-      <c r="AK40" t="n">
+      <c r="AM40" t="n">
         <v>-6.007</v>
       </c>
-      <c r="AL40" t="n">
+      <c r="AN40" t="n">
         <v>-0.332</v>
       </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AO40" t="n">
+        <v>-176</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>-12.014</v>
+      </c>
+      <c r="AQ40" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
+      <c r="AR40" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_EIB_-_BCTC_hop_nhat_Q3.2025_1761868313.pdf</t>
         </is>
       </c>
-      <c r="AO40" t="inlineStr">
+      <c r="AS40" t="inlineStr">
         <is>
           <t>2026-08-31T15:21:25+07:00</t>
         </is>
@@ -35327,26 +35819,38 @@
       <c r="AF41" t="n">
         <v>0</v>
       </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
         <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
       </c>
-      <c r="AM41" t="inlineStr">
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
+      <c r="AR41" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_EIB_-_BCTC_hop_nhat_nam_2025_da_kiem_toan_1774925122.pdf</t>
         </is>
       </c>
-      <c r="AO41" t="inlineStr">
+      <c r="AS41" t="inlineStr">
         <is>
           <t>2026-08-31T01:16:37+07:00</t>
         </is>
@@ -35450,28 +35954,40 @@
         <v>-0.984</v>
       </c>
       <c r="AF42" t="n">
+        <v>-3.548</v>
+      </c>
+      <c r="AG42" t="n">
         <v>-5.742</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AH42" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AL42" t="n">
         <v>-98</v>
       </c>
-      <c r="AK42" t="n">
+      <c r="AM42" t="n">
         <v>-7.102</v>
       </c>
-      <c r="AL42" t="n">
+      <c r="AN42" t="n">
         <v>-0.371</v>
       </c>
-      <c r="AM42" t="inlineStr">
+      <c r="AO42" t="n">
+        <v>-196</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>-14.203</v>
+      </c>
+      <c r="AQ42" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
+      <c r="AR42" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260428_-_EIB_-_BCTC_hop_nhat_Q1.2026_1777374020.pdf</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr">
+      <c r="AS42" t="inlineStr">
         <is>
           <t>2026-08-31T23:24:51+07:00</t>
         </is>
@@ -35565,26 +36081,38 @@
       <c r="AF43" t="n">
         <v>0</v>
       </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" t="n">
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
         <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
       </c>
-      <c r="AM43" t="inlineStr">
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
+      <c r="AR43" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_202608142020EIB2020BCTC20hop20nhat20ban20nien20202620da20soat20xet_20082026091803.pdf?v=1787192285257</t>
         </is>
       </c>
-      <c r="AO43" t="inlineStr">
+      <c r="AS43" t="inlineStr">
         <is>
           <t>2026-09-01T09:42:10+07:00</t>
         </is>
@@ -35688,28 +36216,40 @@
         <v>-4.327</v>
       </c>
       <c r="AF44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG44" t="n">
         <v>14.745</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AH44" t="n">
+        <v>15.444</v>
+      </c>
+      <c r="AL44" t="n">
         <v>155</v>
       </c>
-      <c r="AK44" t="n">
+      <c r="AM44" t="n">
         <v>2.092</v>
       </c>
-      <c r="AL44" t="n">
+      <c r="AN44" t="n">
         <v>0.254</v>
       </c>
-      <c r="AM44" t="inlineStr">
+      <c r="AO44" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>4.185</v>
+      </c>
+      <c r="AQ44" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
+      <c r="AR44" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/HDB_23052025143646.pdf</t>
         </is>
       </c>
-      <c r="AO44" t="inlineStr">
+      <c r="AS44" t="inlineStr">
         <is>
           <t>2026-08-31T16:53:47+07:00</t>
         </is>
@@ -35801,37 +36341,49 @@
         <v>4.299</v>
       </c>
       <c r="AF45" t="n">
+        <v>12.493</v>
+      </c>
+      <c r="AG45" t="n">
         <v>21.936</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AH45" t="n">
+        <v>21.936</v>
+      </c>
+      <c r="AI45" t="n">
         <v>1435902.857</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AJ45" t="n">
         <v>1263818.771</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AK45" t="n">
         <v>113.616</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AL45" t="n">
         <v>871</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AM45" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="AL45" t="n">
+      <c r="AN45" t="n">
         <v>1.348</v>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AO45" t="n">
+        <v>1742</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>17.741</v>
+      </c>
+      <c r="AQ45" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
+      <c r="AR45" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/HDB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025151254.pdf</t>
         </is>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AS45" t="inlineStr">
         <is>
           <t>2026-09-17T16:27:10+07:00</t>
         </is>
@@ -35907,26 +36459,38 @@
       <c r="AF46" t="n">
         <v>0</v>
       </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
         <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
       </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
+      <c r="AR46" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_HDB_-_BCTC_hop_nhat_Quy_3_nam_2025_1761869961.pdf</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr">
+      <c r="AS46" t="inlineStr">
         <is>
           <t>2026-09-17T17:31:12+07:00</t>
         </is>
@@ -36033,34 +36597,46 @@
         <v>7.36</v>
       </c>
       <c r="AG47" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>28.041</v>
+      </c>
+      <c r="AI47" t="n">
         <v>682745.395</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AJ47" t="n">
         <v>370328.376</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AK47" t="n">
         <v>184.362</v>
       </c>
-      <c r="AJ47" t="n">
+      <c r="AL47" t="n">
         <v>655</v>
       </c>
-      <c r="AK47" t="n">
+      <c r="AM47" t="n">
         <v>6.714</v>
       </c>
-      <c r="AL47" t="n">
+      <c r="AN47" t="n">
         <v>0.837</v>
       </c>
-      <c r="AM47" t="inlineStr">
+      <c r="AO47" t="n">
+        <v>1310</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>13.428</v>
+      </c>
+      <c r="AQ47" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
+      <c r="AR47" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_HDB_-_BCTC_kiem_toan_hop_nhat_nam_2025_giai_trinh_1775008453.pdf</t>
         </is>
       </c>
-      <c r="AO47" t="inlineStr">
+      <c r="AS47" t="inlineStr">
         <is>
           <t>2026-09-17T18:20:09+07:00</t>
         </is>
@@ -36164,28 +36740,40 @@
         <v>7.429</v>
       </c>
       <c r="AF48" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AG48" t="n">
         <v>-2.159</v>
       </c>
-      <c r="AJ48" t="n">
+      <c r="AH48" t="n">
+        <v>-0.738</v>
+      </c>
+      <c r="AL48" t="n">
         <v>143</v>
       </c>
-      <c r="AK48" t="n">
+      <c r="AM48" t="n">
         <v>1.686</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AN48" t="n">
         <v>0.172</v>
       </c>
-      <c r="AM48" t="inlineStr">
+      <c r="AO48" t="n">
+        <v>286</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>3.371</v>
+      </c>
+      <c r="AQ48" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
+      <c r="AR48" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_HDB_-_BCTC_hop_nhat_Quy_1.2026_giai_trinh_1777456090.pdf</t>
         </is>
       </c>
-      <c r="AO48" t="inlineStr">
+      <c r="AS48" t="inlineStr">
         <is>
           <t>2026-08-31T23:26:12+07:00</t>
         </is>
@@ -36259,28 +36847,40 @@
         <v>3.236</v>
       </c>
       <c r="AF49" t="n">
+        <v>3.236</v>
+      </c>
+      <c r="AG49" t="n">
         <v>0.105</v>
       </c>
-      <c r="AJ49" t="n">
+      <c r="AH49" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AL49" t="n">
         <v>242</v>
       </c>
-      <c r="AK49" t="n">
+      <c r="AM49" t="n">
         <v>2.485</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AN49" t="n">
         <v>0.268</v>
       </c>
-      <c r="AM49" t="inlineStr">
+      <c r="AO49" t="n">
+        <v>484</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>4.971</v>
+      </c>
+      <c r="AQ49" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
+      <c r="AR49" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/HDB_202607302020HDB2020BCTC20hop20nhat20Quy20220262020giai20trinh_31072026142623.pdf?v=1785482784813</t>
         </is>
       </c>
-      <c r="AO49" t="inlineStr">
+      <c r="AS49" t="inlineStr">
         <is>
           <t>2026-09-01T09:45:14+07:00</t>
         </is>
@@ -36386,26 +36986,38 @@
       <c r="AF50" t="n">
         <v>0</v>
       </c>
-      <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
       </c>
-      <c r="AM50" t="inlineStr">
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
+      <c r="AR50" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014864567_VI_BAO_CAO_TAI_CHINH_QUY_I_06052025105844.2025_HOP_NHAT</t>
         </is>
       </c>
-      <c r="AO50" t="inlineStr">
+      <c r="AS50" t="inlineStr">
         <is>
           <t>2026-08-31T10:10:19+07:00</t>
         </is>
@@ -36511,26 +37123,38 @@
       <c r="AF51" t="n">
         <v>0</v>
       </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
       </c>
-      <c r="AM51" t="inlineStr">
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
+      <c r="AR51" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-kin-long28082025-000000bo-co-ti-chnh-bn-nin-2025_1_0929.pdf</t>
         </is>
       </c>
-      <c r="AO51" t="inlineStr">
+      <c r="AS51" t="inlineStr">
         <is>
           <t>2026-08-31T12:03:05+07:00</t>
         </is>
@@ -36634,28 +37258,40 @@
         <v>-20.648</v>
       </c>
       <c r="AF52" t="n">
+        <v>-26.875</v>
+      </c>
+      <c r="AG52" t="n">
         <v>-23.648</v>
       </c>
-      <c r="AJ52" t="n">
+      <c r="AH52" t="n">
+        <v>-4.788</v>
+      </c>
+      <c r="AL52" t="n">
         <v>-207</v>
       </c>
-      <c r="AK52" t="n">
+      <c r="AM52" t="n">
         <v>-21.169</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AN52" t="n">
         <v>-2.68</v>
       </c>
-      <c r="AM52" t="inlineStr">
+      <c r="AO52" t="n">
+        <v>-414</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>-42.337</v>
+      </c>
+      <c r="AQ52" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
+      <c r="AR52" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_583984_Bao_cao_tai_chinh_quy_32025_1762414456.pdf</t>
         </is>
       </c>
-      <c r="AO52" t="inlineStr">
+      <c r="AS52" t="inlineStr">
         <is>
           <t>2026-08-31T15:24:26+07:00</t>
         </is>
@@ -36761,26 +37397,38 @@
       <c r="AF53" t="n">
         <v>0</v>
       </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
       </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
+      <c r="AR53" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_KLB_-_BCTC_KiemToan_2025_Hop_nhat_1774928715.pdf</t>
         </is>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AS53" t="inlineStr">
         <is>
           <t>2026-08-31T01:20:50+07:00</t>
         </is>
@@ -36886,26 +37534,38 @@
       <c r="AF54" t="n">
         <v>0</v>
       </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
+      <c r="AR54" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260422_-_KLB_-_BCTC_hop_nhat_Quy_1_2026_1776912173.pdf</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AS54" t="inlineStr">
         <is>
           <t>2026-08-31T23:28:02+07:00</t>
         </is>
@@ -37009,28 +37669,40 @@
         <v>0</v>
       </c>
       <c r="AF55" t="n">
+        <v>5.066</v>
+      </c>
+      <c r="AG55" t="n">
         <v>5.037</v>
       </c>
-      <c r="AJ55" t="n">
+      <c r="AH55" t="n">
+        <v>5.997</v>
+      </c>
+      <c r="AL55" t="n">
         <v>37</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AM55" t="n">
         <v>3.675</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AN55" t="n">
         <v>0.398</v>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AO55" t="n">
+        <v>74</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>7.349</v>
+      </c>
+      <c r="AQ55" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AR55" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/KLB_202607222020KLB2020BCTC20hop20nhat20Quy202202026_23072026102613.pdf?v=1784777175496</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AS55" t="inlineStr">
         <is>
           <t>2026-09-01T09:46:18+07:00</t>
         </is>
@@ -37133,26 +37805,38 @@
       <c r="AF56" t="n">
         <v>0</v>
       </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" t="n">
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
         <v>0</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
+      <c r="AR56" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-07-22/no-name-1753123076.pdf</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AS56" t="inlineStr">
         <is>
           <t>2026-08-31T16:55:44+07:00</t>
         </is>
@@ -37256,37 +37940,49 @@
         <v>7.024</v>
       </c>
       <c r="AF57" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="AG57" t="n">
         <v>-5.842</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AH57" t="n">
+        <v>16.055</v>
+      </c>
+      <c r="AI57" t="n">
         <v>495717.531</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AJ57" t="n">
         <v>345939.057</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AK57" t="n">
         <v>143.296</v>
       </c>
-      <c r="AJ57" t="n">
+      <c r="AL57" t="n">
         <v>-59</v>
       </c>
-      <c r="AK57" t="n">
+      <c r="AM57" t="n">
         <v>-1.579</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AN57" t="n">
         <v>-0.145</v>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AO57" t="n">
+        <v>-118</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>-3.159</v>
+      </c>
+      <c r="AQ57" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
+      <c r="AR57" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/LPB_Baocaotaichinh_6T_2025_Soatxet_06102025090900.pdf</t>
         </is>
       </c>
-      <c r="AO57" t="inlineStr">
+      <c r="AS57" t="inlineStr">
         <is>
           <t>2026-09-17T16:28:03+07:00</t>
         </is>
@@ -37360,28 +38056,40 @@
         <v>6.901</v>
       </c>
       <c r="AF58" t="n">
+        <v>4.736</v>
+      </c>
+      <c r="AG58" t="n">
         <v>-2.274</v>
       </c>
-      <c r="AJ58" t="n">
+      <c r="AH58" t="n">
+        <v>-2.274</v>
+      </c>
+      <c r="AL58" t="n">
         <v>89</v>
       </c>
-      <c r="AK58" t="n">
+      <c r="AM58" t="n">
         <v>2.102</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AN58" t="n">
         <v>0.205</v>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AO58" t="n">
+        <v>178</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>4.203</v>
+      </c>
+      <c r="AQ58" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
+      <c r="AR58" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251020_-_LPB_-_VI_BaoCaoTaiChinh_Q3_2025_1761124735.pdf</t>
         </is>
       </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>2026-08-31T15:27:56+07:00</t>
         </is>
@@ -37485,37 +38193,49 @@
         <v>8.073</v>
       </c>
       <c r="AF59" t="n">
+        <v>16.093</v>
+      </c>
+      <c r="AG59" t="n">
         <v>21.51</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AH59" t="n">
+        <v>26.928</v>
+      </c>
+      <c r="AI59" t="n">
         <v>416206.435</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AJ59" t="n">
         <v>239381.648</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AK59" t="n">
         <v>173.867</v>
       </c>
-      <c r="AJ59" t="n">
+      <c r="AL59" t="n">
         <v>854</v>
       </c>
-      <c r="AK59" t="n">
+      <c r="AM59" t="n">
         <v>17.861</v>
       </c>
-      <c r="AL59" t="n">
+      <c r="AN59" t="n">
         <v>1.81</v>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AO59" t="n">
+        <v>1708</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>35.722</v>
+      </c>
+      <c r="AQ59" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
+      <c r="AR59" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-01/no-name-1774985279.pdf</t>
         </is>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AS59" t="inlineStr">
         <is>
           <t>2026-09-17T18:21:20+07:00</t>
         </is>
@@ -37621,26 +38341,38 @@
       <c r="AF60" t="n">
         <v>0</v>
       </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" t="n">
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="n">
         <v>0</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
       </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AM60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ60" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
+      <c r="AR60" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-22/no-name-1776797412.pdf</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
+      <c r="AS60" t="inlineStr">
         <is>
           <t>2026-09-17T19:14:13+07:00</t>
         </is>
@@ -37744,28 +38476,40 @@
         <v>3.461</v>
       </c>
       <c r="AF61" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="AG61" t="n">
         <v>-4.037</v>
       </c>
-      <c r="AJ61" t="n">
+      <c r="AH61" t="n">
+        <v>-1.279</v>
+      </c>
+      <c r="AL61" t="n">
         <v>38</v>
       </c>
-      <c r="AK61" t="n">
+      <c r="AM61" t="n">
         <v>0.977</v>
       </c>
-      <c r="AL61" t="n">
+      <c r="AN61" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AO61" t="n">
+        <v>76</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>1.955</v>
+      </c>
+      <c r="AQ61" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
+      <c r="AR61" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/LPB_202608142020LPB2020Bao20cao20tai20chinh20ban20nien20nam20202620CA_19082026155038.pdf?v=1787129440187</t>
         </is>
       </c>
-      <c r="AO61" t="inlineStr">
+      <c r="AS61" t="inlineStr">
         <is>
           <t>2026-09-01T09:48:15+07:00</t>
         </is>
@@ -37871,26 +38615,38 @@
       <c r="AF62" t="n">
         <v>0.67</v>
       </c>
-      <c r="AJ62" t="n">
+      <c r="AG62" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>-11.068</v>
+      </c>
+      <c r="AL62" t="n">
         <v>65</v>
       </c>
-      <c r="AK62" t="n">
+      <c r="AM62" t="n">
         <v>0.556</v>
       </c>
-      <c r="AL62" t="n">
+      <c r="AN62" t="n">
         <v>0.053</v>
       </c>
-      <c r="AM62" t="inlineStr">
+      <c r="AO62" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="AQ62" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
+      <c r="AR62" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00012345679012345679ngn-hng-tmcp-qun-i24042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
+      <c r="AS62" t="inlineStr">
         <is>
           <t>2026-08-31T10:15:17+07:00</t>
         </is>
@@ -37964,28 +38720,40 @@
         <v>-0.129</v>
       </c>
       <c r="AF63" t="n">
+        <v>2.096</v>
+      </c>
+      <c r="AG63" t="n">
         <v>3.11</v>
       </c>
-      <c r="AJ63" t="n">
+      <c r="AH63" t="n">
+        <v>6.397</v>
+      </c>
+      <c r="AL63" t="n">
         <v>-27</v>
       </c>
-      <c r="AK63" t="n">
+      <c r="AM63" t="n">
         <v>-0.218</v>
       </c>
-      <c r="AL63" t="n">
+      <c r="AN63" t="n">
         <v>-0.021</v>
       </c>
-      <c r="AM63" t="inlineStr">
+      <c r="AO63" t="n">
+        <v>-54</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>-0.436</v>
+      </c>
+      <c r="AQ63" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
+      <c r="AR63" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025091521.pdf</t>
         </is>
       </c>
-      <c r="AO63" t="inlineStr">
+      <c r="AS63" t="inlineStr">
         <is>
           <t>2026-08-31T12:10:05+07:00</t>
         </is>
@@ -38089,28 +38857,40 @@
         <v>3.835</v>
       </c>
       <c r="AF64" t="n">
+        <v>3.836</v>
+      </c>
+      <c r="AG64" t="n">
         <v>5.691</v>
       </c>
-      <c r="AJ64" t="n">
+      <c r="AH64" t="n">
+        <v>11.494</v>
+      </c>
+      <c r="AL64" t="n">
         <v>261</v>
       </c>
-      <c r="AK64" t="n">
+      <c r="AM64" t="n">
         <v>2.009</v>
       </c>
-      <c r="AL64" t="n">
+      <c r="AN64" t="n">
         <v>0.196</v>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AO64" t="n">
+        <v>522</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>4.018</v>
+      </c>
+      <c r="AQ64" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
+      <c r="AR64" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251026_-_MBB_-_BCTC_Hop_nhat_Q3.2025_viet_1761554111.pdf</t>
         </is>
       </c>
-      <c r="AO64" t="inlineStr">
+      <c r="AS64" t="inlineStr">
         <is>
           <t>2026-08-31T15:29:37+07:00</t>
         </is>
@@ -38214,28 +38994,40 @@
         <v>-12.579</v>
       </c>
       <c r="AF65" t="n">
+        <v>-8.715999999999999</v>
+      </c>
+      <c r="AG65" t="n">
         <v>-7.424</v>
       </c>
-      <c r="AJ65" t="n">
+      <c r="AH65" t="n">
+        <v>-5.24</v>
+      </c>
+      <c r="AL65" t="n">
         <v>-1506</v>
       </c>
-      <c r="AK65" t="n">
+      <c r="AM65" t="n">
         <v>-10.347</v>
       </c>
-      <c r="AL65" t="n">
+      <c r="AN65" t="n">
         <v>-1.06</v>
       </c>
-      <c r="AM65" t="inlineStr">
+      <c r="AO65" t="n">
+        <v>-3012</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>-20.694</v>
+      </c>
+      <c r="AQ65" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
+      <c r="AR65" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_Baocaotaichinh_2025_Kiemtoan_Hopnhat_1780022210.pdf</t>
         </is>
       </c>
-      <c r="AO65" t="inlineStr">
+      <c r="AS65" t="inlineStr">
         <is>
           <t>2026-08-31T01:24:23+07:00</t>
         </is>
@@ -38339,28 +39131,40 @@
         <v>6.671</v>
       </c>
       <c r="AF66" t="n">
+        <v>3.449</v>
+      </c>
+      <c r="AG66" t="n">
         <v>3.309</v>
       </c>
-      <c r="AJ66" t="n">
+      <c r="AH66" t="n">
+        <v>7.872</v>
+      </c>
+      <c r="AL66" t="n">
         <v>415</v>
       </c>
-      <c r="AK66" t="n">
+      <c r="AM66" t="n">
         <v>2.783</v>
       </c>
-      <c r="AL66" t="n">
+      <c r="AN66" t="n">
         <v>0.277</v>
       </c>
-      <c r="AM66" t="inlineStr">
+      <c r="AO66" t="n">
+        <v>830</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>5.566</v>
+      </c>
+      <c r="AQ66" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
+      <c r="AR66" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260428_-_MBB_-_BCTC_Hop_nhat_Q1.2026_1777374472.pdf</t>
         </is>
       </c>
-      <c r="AO66" t="inlineStr">
+      <c r="AS66" t="inlineStr">
         <is>
           <t>2026-08-31T23:34:51+07:00</t>
         </is>
@@ -38434,28 +39238,40 @@
         <v>14.055</v>
       </c>
       <c r="AF67" t="n">
+        <v>11.275</v>
+      </c>
+      <c r="AG67" t="n">
         <v>11.756</v>
       </c>
-      <c r="AJ67" t="n">
+      <c r="AH67" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="AL67" t="n">
         <v>1756</v>
       </c>
-      <c r="AK67" t="n">
+      <c r="AM67" t="n">
         <v>10.394</v>
       </c>
-      <c r="AL67" t="n">
+      <c r="AN67" t="n">
         <v>1.12</v>
       </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AO67" t="n">
+        <v>3512</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>20.789</v>
+      </c>
+      <c r="AQ67" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
+      <c r="AR67" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_202608062020MBB2020BCTC20hop20nhat20soat20xet20ban20nien202026_10082026095318.pdf?v=1786330399877</t>
         </is>
       </c>
-      <c r="AO67" t="inlineStr">
+      <c r="AS67" t="inlineStr">
         <is>
           <t>2026-09-01T09:50:15+07:00</t>
         </is>
@@ -38559,28 +39375,40 @@
         <v>-10.814</v>
       </c>
       <c r="AF68" t="n">
+        <v>-6.543</v>
+      </c>
+      <c r="AG68" t="n">
         <v>-5.196</v>
       </c>
-      <c r="AJ68" t="n">
+      <c r="AH68" t="n">
+        <v>-2.116</v>
+      </c>
+      <c r="AL68" t="n">
         <v>-257</v>
       </c>
-      <c r="AK68" t="n">
+      <c r="AM68" t="n">
         <v>-10.264</v>
       </c>
-      <c r="AL68" t="n">
+      <c r="AN68" t="n">
         <v>-0.676</v>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AO68" t="n">
+        <v>-514</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>-20.529</v>
+      </c>
+      <c r="AQ68" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AR68" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-hng-hi-vit-nam28042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AO68" t="inlineStr">
+      <c r="AS68" t="inlineStr">
         <is>
           <t>2026-08-31T10:17:02+07:00</t>
         </is>
@@ -38684,28 +39512,40 @@
         <v>23.289</v>
       </c>
       <c r="AF69" t="n">
+        <v>25.347</v>
+      </c>
+      <c r="AG69" t="n">
         <v>25.892</v>
       </c>
-      <c r="AJ69" t="n">
+      <c r="AH69" t="n">
+        <v>27.205</v>
+      </c>
+      <c r="AL69" t="n">
         <v>774</v>
       </c>
-      <c r="AK69" t="n">
+      <c r="AM69" t="n">
         <v>29.944</v>
       </c>
-      <c r="AL69" t="n">
+      <c r="AN69" t="n">
         <v>1.969</v>
       </c>
-      <c r="AM69" t="inlineStr">
+      <c r="AO69" t="n">
+        <v>1548</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>59.888</v>
+      </c>
+      <c r="AQ69" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
+      <c r="AR69" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025092910.pdf</t>
         </is>
       </c>
-      <c r="AO69" t="inlineStr">
+      <c r="AS69" t="inlineStr">
         <is>
           <t>2026-08-31T12:12:00+07:00</t>
         </is>
@@ -38803,28 +39643,40 @@
         <v>27.346</v>
       </c>
       <c r="AF70" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="AG70" t="n">
         <v>35.285</v>
       </c>
-      <c r="AJ70" t="n">
+      <c r="AH70" t="n">
+        <v>39.079</v>
+      </c>
+      <c r="AL70" t="n">
         <v>1078</v>
       </c>
-      <c r="AK70" t="n">
+      <c r="AM70" t="n">
         <v>38.291</v>
       </c>
-      <c r="AL70" t="n">
+      <c r="AN70" t="n">
         <v>2.658</v>
       </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AO70" t="n">
+        <v>2156</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>76.581</v>
+      </c>
+      <c r="AQ70" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
+      <c r="AR70" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251029_-_MSB_-_CBTT_Bao_cao_tai_chinh_Hop_nhat_Q3.2025_signed_1761876687.pdf</t>
         </is>
       </c>
-      <c r="AO70" t="inlineStr">
+      <c r="AS70" t="inlineStr">
         <is>
           <t>2026-08-31T15:31:21+07:00</t>
         </is>
@@ -38928,28 +39780,40 @@
         <v>-12.367</v>
       </c>
       <c r="AF71" t="n">
+        <v>-11.246</v>
+      </c>
+      <c r="AG71" t="n">
         <v>-8.913</v>
       </c>
-      <c r="AJ71" t="n">
+      <c r="AH71" t="n">
+        <v>-8.912000000000001</v>
+      </c>
+      <c r="AL71" t="n">
         <v>-330</v>
       </c>
-      <c r="AK71" t="n">
+      <c r="AM71" t="n">
         <v>-10.843</v>
       </c>
-      <c r="AL71" t="n">
+      <c r="AN71" t="n">
         <v>-0.777</v>
       </c>
-      <c r="AM71" t="inlineStr">
+      <c r="AO71" t="n">
+        <v>-660</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>-21.685</v>
+      </c>
+      <c r="AQ71" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
+      <c r="AR71" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_HK_20260330_-_MSB_-_BCTC_hop_nhat_kiem_toan_nam_2025__18062026110209.pdf</t>
         </is>
       </c>
-      <c r="AO71" t="inlineStr">
+      <c r="AS71" t="inlineStr">
         <is>
           <t>2026-08-31T01:26:11+07:00</t>
         </is>
@@ -39023,28 +39887,40 @@
         <v>-13.87</v>
       </c>
       <c r="AF72" t="n">
+        <v>-13.306</v>
+      </c>
+      <c r="AG72" t="n">
         <v>-11.829</v>
       </c>
-      <c r="AJ72" t="n">
+      <c r="AH72" t="n">
+        <v>-6.368</v>
+      </c>
+      <c r="AL72" t="n">
         <v>-532</v>
       </c>
-      <c r="AK72" t="n">
+      <c r="AM72" t="n">
         <v>-16.638</v>
       </c>
-      <c r="AL72" t="n">
+      <c r="AN72" t="n">
         <v>-1.21</v>
       </c>
-      <c r="AM72" t="inlineStr">
+      <c r="AO72" t="n">
+        <v>-1064</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>-33.276</v>
+      </c>
+      <c r="AQ72" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
+      <c r="AR72" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260424_-_MSB_-_Bao_cao_tai_chinh_Hop_nhat_Quy_1_2026_signed_1777023593.pdf</t>
         </is>
       </c>
-      <c r="AO72" t="inlineStr">
+      <c r="AS72" t="inlineStr">
         <is>
           <t>2026-08-31T23:36:48+07:00</t>
         </is>
@@ -39120,26 +39996,38 @@
       <c r="AF73" t="n">
         <v>-0.013</v>
       </c>
-      <c r="AJ73" t="n">
+      <c r="AG73" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="AL73" t="n">
         <v>-1</v>
       </c>
-      <c r="AK73" t="n">
+      <c r="AM73" t="n">
         <v>-0.033</v>
       </c>
-      <c r="AL73" t="n">
+      <c r="AN73" t="n">
         <v>-0.002</v>
       </c>
-      <c r="AM73" t="inlineStr">
+      <c r="AO73" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="AQ73" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
+      <c r="AR73" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_202608182020MSB2020BCTC20hop20nhat20ban20nien20soat20xet20202620signed_19082026103646.pdf?v=1787110607275</t>
         </is>
       </c>
-      <c r="AO73" t="inlineStr">
+      <c r="AS73" t="inlineStr">
         <is>
           <t>2026-09-01T09:50:54+07:00</t>
         </is>
@@ -39243,28 +40131,40 @@
         <v>20.497</v>
       </c>
       <c r="AF74" t="n">
+        <v>11.198</v>
+      </c>
+      <c r="AG74" t="n">
         <v>0.398</v>
       </c>
-      <c r="AJ74" t="n">
+      <c r="AH74" t="n">
+        <v>-1.432</v>
+      </c>
+      <c r="AL74" t="n">
         <v>224</v>
       </c>
-      <c r="AK74" t="n">
+      <c r="AM74" t="n">
         <v>10.605</v>
       </c>
-      <c r="AL74" t="n">
+      <c r="AN74" t="n">
         <v>1.108</v>
       </c>
-      <c r="AM74" t="inlineStr">
+      <c r="AO74" t="n">
+        <v>448</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="AQ74" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
+      <c r="AR74" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-nam-28042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AO74" t="inlineStr">
+      <c r="AS74" t="inlineStr">
         <is>
           <t>2026-08-31T10:18:34+07:00</t>
         </is>
@@ -39368,28 +40268,40 @@
         <v>14.227</v>
       </c>
       <c r="AF75" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AG75" t="n">
         <v>-2.332</v>
       </c>
-      <c r="AJ75" t="n">
+      <c r="AH75" t="n">
+        <v>-2.849</v>
+      </c>
+      <c r="AL75" t="n">
         <v>140</v>
       </c>
-      <c r="AK75" t="n">
+      <c r="AM75" t="n">
         <v>6.597</v>
       </c>
-      <c r="AL75" t="n">
+      <c r="AN75" t="n">
         <v>0.659</v>
       </c>
-      <c r="AM75" t="inlineStr">
+      <c r="AO75" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>13.194</v>
+      </c>
+      <c r="AQ75" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
+      <c r="AR75" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025093916.pdf</t>
         </is>
       </c>
-      <c r="AO75" t="inlineStr">
+      <c r="AS75" t="inlineStr">
         <is>
           <t>2026-08-31T12:14:18+07:00</t>
         </is>
@@ -39493,28 +40405,40 @@
         <v>1.709</v>
       </c>
       <c r="AF76" t="n">
+        <v>4.246</v>
+      </c>
+      <c r="AG76" t="n">
         <v>-2.342</v>
       </c>
-      <c r="AJ76" t="n">
+      <c r="AH76" t="n">
+        <v>-1.742</v>
+      </c>
+      <c r="AL76" t="n">
         <v>17</v>
       </c>
-      <c r="AK76" t="n">
+      <c r="AM76" t="n">
         <v>0.827</v>
       </c>
-      <c r="AL76" t="n">
+      <c r="AN76" t="n">
         <v>0.076</v>
       </c>
-      <c r="AM76" t="inlineStr">
+      <c r="AO76" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.655</v>
+      </c>
+      <c r="AQ76" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
+      <c r="AR76" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251029_-_NAB_-_CBTT_BCTC_Q3.2025_HN_1761877543.pdf</t>
         </is>
       </c>
-      <c r="AO76" t="inlineStr">
+      <c r="AS76" t="inlineStr">
         <is>
           <t>2026-08-31T15:32:56+07:00</t>
         </is>
@@ -39618,28 +40542,40 @@
         <v>17.344</v>
       </c>
       <c r="AF77" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="AG77" t="n">
         <v>120.96</v>
       </c>
-      <c r="AJ77" t="n">
+      <c r="AH77" t="n">
+        <v>127.143</v>
+      </c>
+      <c r="AL77" t="n">
         <v>1841</v>
       </c>
-      <c r="AK77" t="n">
+      <c r="AM77" t="n">
         <v>79.096</v>
       </c>
-      <c r="AL77" t="n">
+      <c r="AN77" t="n">
         <v>7.857</v>
       </c>
-      <c r="AM77" t="inlineStr">
+      <c r="AO77" t="n">
+        <v>3682</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>158.192</v>
+      </c>
+      <c r="AQ77" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
+      <c r="AR77" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_Baocaotaichinh_2025_Kiemtoan_Hopnhat_1780023595.pdf</t>
         </is>
       </c>
-      <c r="AO77" t="inlineStr">
+      <c r="AS77" t="inlineStr">
         <is>
           <t>2026-08-31T01:28:37+07:00</t>
         </is>
@@ -39745,26 +40681,38 @@
       <c r="AF78" t="n">
         <v>6.849</v>
       </c>
-      <c r="AJ78" t="n">
+      <c r="AG78" t="n">
+        <v>6.849</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>6.862</v>
+      </c>
+      <c r="AL78" t="n">
         <v>211</v>
       </c>
-      <c r="AK78" t="n">
+      <c r="AM78" t="n">
         <v>10.184</v>
       </c>
-      <c r="AL78" t="n">
+      <c r="AN78" t="n">
         <v>0.855</v>
       </c>
-      <c r="AM78" t="inlineStr">
+      <c r="AO78" t="n">
+        <v>422</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>20.367</v>
+      </c>
+      <c r="AQ78" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
+      <c r="AR78" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-05-05/no-name-1777925637.pdf</t>
         </is>
       </c>
-      <c r="AO78" t="inlineStr">
+      <c r="AS78" t="inlineStr">
         <is>
           <t>2026-08-31T23:37:58+07:00</t>
         </is>
@@ -39838,28 +40786,40 @@
         <v>9.967000000000001</v>
       </c>
       <c r="AF79" t="n">
+        <v>3.449</v>
+      </c>
+      <c r="AG79" t="n">
         <v>46.43</v>
       </c>
-      <c r="AJ79" t="n">
+      <c r="AH79" t="n">
+        <v>140.696</v>
+      </c>
+      <c r="AL79" t="n">
         <v>723</v>
       </c>
-      <c r="AK79" t="n">
+      <c r="AM79" t="n">
         <v>32.459</v>
       </c>
-      <c r="AL79" t="n">
+      <c r="AN79" t="n">
         <v>2.792</v>
       </c>
-      <c r="AM79" t="inlineStr">
+      <c r="AO79" t="n">
+        <v>1446</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>64.91800000000001</v>
+      </c>
+      <c r="AQ79" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
+      <c r="AR79" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_202608082020NAB2020BAN20NIEN20SOAT20XET202026_20HN_12082026154236.pdf?v=1786524157864</t>
         </is>
       </c>
-      <c r="AO79" t="inlineStr">
+      <c r="AS79" t="inlineStr">
         <is>
           <t>2026-09-01T09:53:27+07:00</t>
         </is>
@@ -39963,28 +40923,40 @@
         <v>19.343</v>
       </c>
       <c r="AF80" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="AG80" t="n">
         <v>3.766</v>
       </c>
-      <c r="AJ80" t="n">
+      <c r="AH80" t="n">
+        <v>-6.765</v>
+      </c>
+      <c r="AL80" t="n">
         <v>102</v>
       </c>
-      <c r="AK80" t="n">
+      <c r="AM80" t="n">
         <v>20.204</v>
       </c>
-      <c r="AL80" t="n">
+      <c r="AN80" t="n">
         <v>1.634</v>
       </c>
-      <c r="AM80" t="inlineStr">
+      <c r="AO80" t="n">
+        <v>204</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>40.407</v>
+      </c>
+      <c r="AQ80" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
+      <c r="AR80" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NVB_25Q1_BCTC_HN_09052025064513.pdf</t>
         </is>
       </c>
-      <c r="AO80" t="inlineStr">
+      <c r="AS80" t="inlineStr">
         <is>
           <t>2026-08-31T10:20:53+07:00</t>
         </is>
@@ -40058,28 +41030,40 @@
         <v>-2.96</v>
       </c>
       <c r="AF81" t="n">
+        <v>-29.567</v>
+      </c>
+      <c r="AG81" t="n">
         <v>-40.314</v>
       </c>
-      <c r="AJ81" t="n">
+      <c r="AH81" t="n">
+        <v>-18.45</v>
+      </c>
+      <c r="AL81" t="n">
         <v>-319</v>
       </c>
-      <c r="AK81" t="n">
+      <c r="AM81" t="n">
         <v>-42.102</v>
       </c>
-      <c r="AL81" t="n">
+      <c r="AN81" t="n">
         <v>-4.866</v>
       </c>
-      <c r="AM81" t="inlineStr">
+      <c r="AO81" t="n">
+        <v>-638</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>-84.205</v>
+      </c>
+      <c r="AQ81" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
+      <c r="AR81" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-quc-dn27082025-000000bo-co-ti-chnh-bn-nin-2025_1_0915.pdf</t>
         </is>
       </c>
-      <c r="AO81" t="inlineStr">
+      <c r="AS81" t="inlineStr">
         <is>
           <t>2026-08-31T12:16:11+07:00</t>
         </is>
@@ -40177,28 +41161,40 @@
         <v>2.165</v>
       </c>
       <c r="AF82" t="n">
+        <v>-18.755</v>
+      </c>
+      <c r="AG82" t="n">
         <v>-28.084</v>
       </c>
-      <c r="AJ82" t="n">
+      <c r="AH82" t="n">
+        <v>-25.715</v>
+      </c>
+      <c r="AL82" t="n">
         <v>-215</v>
       </c>
-      <c r="AK82" t="n">
+      <c r="AM82" t="n">
         <v>-31.377</v>
       </c>
-      <c r="AL82" t="n">
+      <c r="AN82" t="n">
         <v>-3.188</v>
       </c>
-      <c r="AM82" t="inlineStr">
+      <c r="AO82" t="n">
+        <v>-430</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>-62.753</v>
+      </c>
+      <c r="AQ82" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
+      <c r="AR82" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_585817_Bao_cao_tai_chinh_quy_32025_1761886641.pdf</t>
         </is>
       </c>
-      <c r="AO82" t="inlineStr">
+      <c r="AS82" t="inlineStr">
         <is>
           <t>2026-08-31T15:34:40+07:00</t>
         </is>
@@ -40272,28 +41268,40 @@
         <v>41.435</v>
       </c>
       <c r="AF83" t="n">
+        <v>56.333</v>
+      </c>
+      <c r="AG83" t="n">
         <v>27.166</v>
       </c>
-      <c r="AJ83" t="n">
+      <c r="AH83" t="n">
+        <v>19.681</v>
+      </c>
+      <c r="AL83" t="n">
         <v>682</v>
       </c>
-      <c r="AK83" t="n">
+      <c r="AM83" t="n">
         <v>160.991</v>
       </c>
-      <c r="AL83" t="n">
+      <c r="AN83" t="n">
         <v>5.017</v>
       </c>
-      <c r="AM83" t="inlineStr">
+      <c r="AO83" t="n">
+        <v>1364</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>321.981</v>
+      </c>
+      <c r="AQ83" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
+      <c r="AR83" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604185_Bao_cao_tai_chinh_nam_2025_1774532924.pdf</t>
         </is>
       </c>
-      <c r="AO83" t="inlineStr">
+      <c r="AS83" t="inlineStr">
         <is>
           <t>2026-08-31T01:30:26+07:00</t>
         </is>
@@ -40393,26 +41401,38 @@
       <c r="AF84" t="n">
         <v>-19.367</v>
       </c>
-      <c r="AJ84" t="n">
+      <c r="AG84" t="n">
+        <v>-19.367</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>-31.501</v>
+      </c>
+      <c r="AL84" t="n">
         <v>-210</v>
       </c>
-      <c r="AK84" t="n">
+      <c r="AM84" t="n">
         <v>-26.514</v>
       </c>
-      <c r="AL84" t="n">
+      <c r="AN84" t="n">
         <v>-1.521</v>
       </c>
-      <c r="AM84" t="inlineStr">
+      <c r="AO84" t="n">
+        <v>-420</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>-53.027</v>
+      </c>
+      <c r="AQ84" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
+      <c r="AR84" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_612736_Bao_cao_tai_chinh_quy_12026_1777882908.pdf</t>
         </is>
       </c>
-      <c r="AO84" t="inlineStr">
+      <c r="AS84" t="inlineStr">
         <is>
           <t>2026-08-31T23:39:44+07:00</t>
         </is>
@@ -40486,28 +41506,40 @@
         <v>44.57</v>
       </c>
       <c r="AF85" t="n">
+        <v>197.765</v>
+      </c>
+      <c r="AG85" t="n">
         <v>205.252</v>
       </c>
-      <c r="AJ85" t="n">
+      <c r="AH85" t="n">
+        <v>216.239</v>
+      </c>
+      <c r="AL85" t="n">
         <v>2736</v>
       </c>
-      <c r="AK85" t="n">
+      <c r="AM85" t="n">
         <v>264.697</v>
       </c>
-      <c r="AL85" t="n">
+      <c r="AN85" t="n">
         <v>19.107</v>
       </c>
-      <c r="AM85" t="inlineStr">
+      <c r="AO85" t="n">
+        <v>5472</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>529.393</v>
+      </c>
+      <c r="AQ85" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
+      <c r="AR85" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NVB_000000016801581_BAO_CAO_TAI_CHINH_HOP_NHAT__TV__SAU_SOAT_XET_BAN_NIEN_2026signed_28082026161720.pdf?v=1787908641915</t>
         </is>
       </c>
-      <c r="AO85" t="inlineStr">
+      <c r="AS85" t="inlineStr">
         <is>
           <t>2026-09-01T09:54:37+07:00</t>
         </is>
@@ -40611,32 +41643,44 @@
         <v>-4.928</v>
       </c>
       <c r="AF86" t="n">
+        <v>2.894</v>
+      </c>
+      <c r="AG86" t="n">
         <v>11.024</v>
       </c>
-      <c r="AG86" t="n">
+      <c r="AH86" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI86" t="n">
         <v>266228.092</v>
       </c>
-      <c r="AH86" t="n">
+      <c r="AJ86" t="n">
         <v>247087.747</v>
       </c>
-      <c r="AI86" t="n">
+      <c r="AK86" t="n">
         <v>107.746</v>
       </c>
-      <c r="AJ86" t="n">
+      <c r="AL86" t="n">
         <v>40</v>
       </c>
-      <c r="AK86" t="n">
+      <c r="AM86" t="n">
         <v>1.849</v>
       </c>
-      <c r="AL86" t="n">
+      <c r="AN86" t="n">
         <v>0.124</v>
       </c>
-      <c r="AM86" t="inlineStr">
+      <c r="AO86" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>3.698</v>
+      </c>
+      <c r="AQ86" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (OCB thuyet minh BCTC hop nhat Quy 1 2025, OCR khong doc duoc - don vi VND thuc, da quy doi ve trieu dong)</t>
         </is>
       </c>
-      <c r="AO86" t="inlineStr">
+      <c r="AS86" t="inlineStr">
         <is>
           <t>2026-09-17T16:12:36+07:00</t>
         </is>
@@ -40740,32 +41784,44 @@
         <v>-4.869</v>
       </c>
       <c r="AF87" t="n">
+        <v>4.763</v>
+      </c>
+      <c r="AG87" t="n">
         <v>11.866</v>
       </c>
-      <c r="AG87" t="n">
+      <c r="AH87" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="AI87" t="n">
         <v>287379.692</v>
       </c>
-      <c r="AH87" t="n">
+      <c r="AJ87" t="n">
         <v>270403.116</v>
       </c>
-      <c r="AI87" t="n">
+      <c r="AK87" t="n">
         <v>106.278</v>
       </c>
-      <c r="AJ87" t="n">
+      <c r="AL87" t="n">
         <v>59</v>
       </c>
-      <c r="AK87" t="n">
+      <c r="AM87" t="n">
         <v>2.708</v>
       </c>
-      <c r="AL87" t="n">
+      <c r="AN87" t="n">
         <v>0.178</v>
       </c>
-      <c r="AM87" t="inlineStr">
+      <c r="AO87" t="n">
+        <v>118</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>5.415</v>
+      </c>
+      <c r="AQ87" t="inlineStr">
         <is>
           <t>Nhap thu cong tu doc truc tiep BCTC that (OCB thuyet minh BCTC hop nhat Quy 2 2025, ban tieng Anh, don vi VND thuc da quy doi ve trieu dong, OCR khong doc duoc do bao cao tieng Anh)</t>
         </is>
       </c>
-      <c r="AO87" t="inlineStr">
+      <c r="AS87" t="inlineStr">
         <is>
           <t>2026-09-17T16:58:29+07:00</t>
         </is>
@@ -40872,34 +41928,46 @@
         <v>-51.883</v>
       </c>
       <c r="AG88" t="n">
+        <v>-51.883</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>-40.596</v>
+      </c>
+      <c r="AI88" t="n">
         <v>141033.646</v>
       </c>
-      <c r="AH88" t="n">
+      <c r="AJ88" t="n">
         <v>230768.26</v>
       </c>
-      <c r="AI88" t="n">
+      <c r="AK88" t="n">
         <v>61.115</v>
       </c>
-      <c r="AJ88" t="n">
+      <c r="AL88" t="n">
         <v>-1515</v>
       </c>
-      <c r="AK88" t="n">
+      <c r="AM88" t="n">
         <v>-62.494</v>
       </c>
-      <c r="AL88" t="n">
+      <c r="AN88" t="n">
         <v>-4.64</v>
       </c>
-      <c r="AM88" t="inlineStr">
+      <c r="AO88" t="n">
+        <v>-3030</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>-124.989</v>
+      </c>
+      <c r="AQ88" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
+      <c r="AR88" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251028_-_OCB_-_BCTC_hop_nhat_Quy_3_2025_1761822426.pdf</t>
         </is>
       </c>
-      <c r="AO88" t="inlineStr">
+      <c r="AS88" t="inlineStr">
         <is>
           <t>2026-09-17T17:33:01+07:00</t>
         </is>
@@ -41003,37 +42071,49 @@
         <v>44.885</v>
       </c>
       <c r="AF89" t="n">
+        <v>53.922</v>
+      </c>
+      <c r="AG89" t="n">
         <v>46.276</v>
       </c>
-      <c r="AG89" t="n">
+      <c r="AH89" t="n">
+        <v>38.303</v>
+      </c>
+      <c r="AI89" t="n">
         <v>261998.749</v>
       </c>
-      <c r="AH89" t="n">
+      <c r="AJ89" t="n">
         <v>127090.628</v>
       </c>
-      <c r="AI89" t="n">
+      <c r="AK89" t="n">
         <v>206.151</v>
       </c>
-      <c r="AJ89" t="n">
+      <c r="AL89" t="n">
         <v>1430</v>
       </c>
-      <c r="AK89" t="n">
+      <c r="AM89" t="n">
         <v>57.616</v>
       </c>
-      <c r="AL89" t="n">
+      <c r="AN89" t="n">
         <v>4.215</v>
       </c>
-      <c r="AM89" t="inlineStr">
+      <c r="AO89" t="n">
+        <v>2860</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>115.232</v>
+      </c>
+      <c r="AQ89" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 4 năm 2025</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
+      <c r="AR89" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260130_-_OCB_-_BCTC_hop_nhat_Quy_4_2025_1770023477.pdf</t>
         </is>
       </c>
-      <c r="AO89" t="inlineStr">
+      <c r="AS89" t="inlineStr">
         <is>
           <t>2026-09-18T08:55:46+07:00</t>
         </is>
@@ -41055,7 +42135,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="AO90" t="inlineStr">
+      <c r="AS90" t="inlineStr">
         <is>
           <t>2026-08-31T01:30:30+07:00</t>
         </is>
@@ -41162,34 +42242,46 @@
         <v>-0</v>
       </c>
       <c r="AG91" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AI91" t="n">
         <v>92.95</v>
       </c>
-      <c r="AH91" t="n">
+      <c r="AJ91" t="n">
         <v>0.224</v>
       </c>
-      <c r="AI91" t="n">
+      <c r="AK91" t="n">
         <v>41547.537</v>
       </c>
-      <c r="AJ91" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK91" t="n">
-        <v>0</v>
-      </c>
       <c r="AL91" t="n">
         <v>0</v>
       </c>
-      <c r="AM91" t="inlineStr">
+      <c r="AM91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ91" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
+      <c r="AR91" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260422_-_OCB_-_BCTC_hop_nhat_Quy_1_2026_1776854955.pdf</t>
         </is>
       </c>
-      <c r="AO91" t="inlineStr">
+      <c r="AS91" t="inlineStr">
         <is>
           <t>2026-09-17T19:15:32+07:00</t>
         </is>
@@ -41295,26 +42387,38 @@
       <c r="AF92" t="n">
         <v>18585446.401</v>
       </c>
-      <c r="AJ92" t="n">
+      <c r="AG92" t="n">
+        <v>18585446.401</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>33039928.708</v>
+      </c>
+      <c r="AL92" t="n">
         <v>538956902</v>
       </c>
-      <c r="AK92" t="n">
+      <c r="AM92" t="n">
         <v>21342068.292</v>
       </c>
-      <c r="AL92" t="n">
+      <c r="AN92" t="n">
         <v>1504546.294</v>
       </c>
-      <c r="AM92" t="inlineStr">
+      <c r="AO92" t="n">
+        <v>1077913804</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>42684136.584</v>
+      </c>
+      <c r="AQ92" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
+      <c r="AR92" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/OCB_202608142020OCB2020Bao20cao20tai20chinh20hop20nhat20ban20nien202026_20082026094036.pdf?v=1787193638360</t>
         </is>
       </c>
-      <c r="AO92" t="inlineStr">
+      <c r="AS92" t="inlineStr">
         <is>
           <t>2026-09-01T09:56:57+07:00</t>
         </is>
@@ -41388,28 +42492,40 @@
         <v>0.893</v>
       </c>
       <c r="AF93" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="AG93" t="n">
         <v>6.771</v>
       </c>
-      <c r="AJ93" t="n">
+      <c r="AH93" t="n">
+        <v>6.013</v>
+      </c>
+      <c r="AL93" t="n">
         <v>35</v>
       </c>
-      <c r="AK93" t="n">
+      <c r="AM93" t="n">
         <v>7.637</v>
       </c>
-      <c r="AL93" t="n">
+      <c r="AN93" t="n">
         <v>0.668</v>
       </c>
-      <c r="AM93" t="inlineStr">
+      <c r="AO93" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>15.275</v>
+      </c>
+      <c r="AQ93" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
+      <c r="AR93" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-18/no-name-1744937049.pdf</t>
         </is>
       </c>
-      <c r="AO93" t="inlineStr">
+      <c r="AS93" t="inlineStr">
         <is>
           <t>2026-08-31T10:25:19+07:00</t>
         </is>
@@ -41513,28 +42629,40 @@
         <v>0.003</v>
       </c>
       <c r="AF94" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="AG94" t="n">
         <v>1.807</v>
       </c>
-      <c r="AJ94" t="n">
+      <c r="AH94" t="n">
+        <v>1.987</v>
+      </c>
+      <c r="AL94" t="n">
         <v>4</v>
       </c>
-      <c r="AK94" t="n">
+      <c r="AM94" t="n">
         <v>0.848</v>
       </c>
-      <c r="AL94" t="n">
+      <c r="AN94" t="n">
         <v>0.065</v>
       </c>
-      <c r="AM94" t="inlineStr">
+      <c r="AO94" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>1.695</v>
+      </c>
+      <c r="AQ94" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 2 năm 2025</t>
         </is>
       </c>
-      <c r="AN94" t="inlineStr">
+      <c r="AR94" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-08-19/no-name-1755541972.pdf</t>
         </is>
       </c>
-      <c r="AO94" t="inlineStr">
+      <c r="AS94" t="inlineStr">
         <is>
           <t>2026-08-31T12:25:04+07:00</t>
         </is>
@@ -41608,28 +42736,40 @@
         <v>0.001</v>
       </c>
       <c r="AF95" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AG95" t="n">
         <v>1.37</v>
       </c>
-      <c r="AJ95" t="n">
+      <c r="AH95" t="n">
+        <v>11.405</v>
+      </c>
+      <c r="AL95" t="n">
         <v>3</v>
       </c>
-      <c r="AK95" t="n">
+      <c r="AM95" t="n">
         <v>0.644</v>
       </c>
-      <c r="AL95" t="n">
+      <c r="AN95" t="n">
         <v>0.047</v>
       </c>
-      <c r="AM95" t="inlineStr">
+      <c r="AO95" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="AQ95" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN95" t="inlineStr">
+      <c r="AR95" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-10-24/no-name-1761245640.pdf</t>
         </is>
       </c>
-      <c r="AO95" t="inlineStr">
+      <c r="AS95" t="inlineStr">
         <is>
           <t>2026-08-31T15:38:58+07:00</t>
         </is>
@@ -41733,28 +42873,40 @@
         <v>-0.622</v>
       </c>
       <c r="AF96" t="n">
+        <v>-2.458</v>
+      </c>
+      <c r="AG96" t="n">
         <v>-0.505</v>
       </c>
-      <c r="AJ96" t="n">
+      <c r="AH96" t="n">
+        <v>-0.8169999999999999</v>
+      </c>
+      <c r="AL96" t="n">
         <v>-20</v>
       </c>
-      <c r="AK96" t="n">
+      <c r="AM96" t="n">
         <v>-4.151</v>
       </c>
-      <c r="AL96" t="n">
+      <c r="AN96" t="n">
         <v>-0.306</v>
       </c>
-      <c r="AM96" t="inlineStr">
+      <c r="AO96" t="n">
+        <v>-40</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>-8.303000000000001</v>
+      </c>
+      <c r="AQ96" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
+      <c r="AR96" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-02/no-name-1775069400.pdf</t>
         </is>
       </c>
-      <c r="AO96" t="inlineStr">
+      <c r="AS96" t="inlineStr">
         <is>
           <t>2026-08-31T01:31:51+07:00</t>
         </is>
@@ -41828,28 +42980,40 @@
         <v>-6.235</v>
       </c>
       <c r="AF97" t="n">
+        <v>-6.233</v>
+      </c>
+      <c r="AG97" t="n">
         <v>-6.228</v>
       </c>
-      <c r="AJ97" t="n">
+      <c r="AH97" t="n">
+        <v>-6.218</v>
+      </c>
+      <c r="AL97" t="n">
         <v>-52</v>
       </c>
-      <c r="AK97" t="n">
+      <c r="AM97" t="n">
         <v>-11.365</v>
       </c>
-      <c r="AL97" t="n">
+      <c r="AN97" t="n">
         <v>-0.643</v>
       </c>
-      <c r="AM97" t="inlineStr">
+      <c r="AO97" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>-22.73</v>
+      </c>
+      <c r="AQ97" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
+      <c r="AR97" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-30/no-name-1777487970.pdf</t>
         </is>
       </c>
-      <c r="AO97" t="inlineStr">
+      <c r="AS97" t="inlineStr">
         <is>
           <t>2026-08-31T23:44:08+07:00</t>
         </is>
@@ -41953,28 +43117,40 @@
         <v>6.176</v>
       </c>
       <c r="AF98" t="n">
+        <v>5.269</v>
+      </c>
+      <c r="AG98" t="n">
         <v>1.533</v>
       </c>
-      <c r="AJ98" t="n">
+      <c r="AH98" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AL98" t="n">
         <v>36</v>
       </c>
-      <c r="AK98" t="n">
+      <c r="AM98" t="n">
         <v>6.903</v>
       </c>
-      <c r="AL98" t="n">
+      <c r="AN98" t="n">
         <v>0.438</v>
       </c>
-      <c r="AM98" t="inlineStr">
+      <c r="AO98" t="n">
+        <v>72</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>13.806</v>
+      </c>
+      <c r="AQ98" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
+      <c r="AR98" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/PGB_000000016752911_VI_Baocaotaichinh_bannien_nam_2026_18082026140441.pdf?v=1787036682987</t>
         </is>
       </c>
-      <c r="AO98" t="inlineStr">
+      <c r="AS98" t="inlineStr">
         <is>
           <t>2026-09-01T09:58:24+07:00</t>
         </is>
@@ -42048,28 +43224,40 @@
         <v>-26.824</v>
       </c>
       <c r="AF99" t="n">
+        <v>-47.667</v>
+      </c>
+      <c r="AG99" t="n">
         <v>-25.115</v>
       </c>
-      <c r="AJ99" t="n">
+      <c r="AH99" t="n">
+        <v>-2.563</v>
+      </c>
+      <c r="AL99" t="n">
         <v>-102</v>
       </c>
-      <c r="AK99" t="n">
+      <c r="AM99" t="n">
         <v>-46.819</v>
       </c>
-      <c r="AL99" t="n">
+      <c r="AN99" t="n">
         <v>-2.445</v>
       </c>
-      <c r="AM99" t="inlineStr">
+      <c r="AO99" t="n">
+        <v>-204</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>-93.63800000000001</v>
+      </c>
+      <c r="AQ99" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
+      <c r="AR99" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014834796_VI_BaoCaotaiChinh_HopNhat_Q1_2025_26042025110134.pdf</t>
         </is>
       </c>
-      <c r="AO99" t="inlineStr">
+      <c r="AS99" t="inlineStr">
         <is>
           <t>2026-08-31T10:26:54+07:00</t>
         </is>
@@ -42173,28 +43361,40 @@
         <v>-0.509</v>
       </c>
       <c r="AF100" t="n">
+        <v>-14.875</v>
+      </c>
+      <c r="AG100" t="n">
         <v>4.05</v>
       </c>
-      <c r="AJ100" t="n">
+      <c r="AH100" t="n">
+        <v>-15.715</v>
+      </c>
+      <c r="AL100" t="n">
         <v>-14</v>
       </c>
-      <c r="AK100" t="n">
+      <c r="AM100" t="n">
         <v>-5.998</v>
       </c>
-      <c r="AL100" t="n">
+      <c r="AN100" t="n">
         <v>-0.331</v>
       </c>
-      <c r="AM100" t="inlineStr">
+      <c r="AO100" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>-11.996</v>
+      </c>
+      <c r="AQ100" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
+      <c r="AR100" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00019753086419753087ngn-hng-tmcp-si-gn-cng-thng14082025-000000bo-co-ti-chnh-bn-nin-2025_1_1022.pdf</t>
         </is>
       </c>
-      <c r="AO100" t="inlineStr">
+      <c r="AS100" t="inlineStr">
         <is>
           <t>2026-08-31T12:26:51+07:00</t>
         </is>
@@ -42268,28 +43468,40 @@
         <v>2.354</v>
       </c>
       <c r="AF101" t="n">
+        <v>-7.816</v>
+      </c>
+      <c r="AG101" t="n">
         <v>10.757</v>
       </c>
-      <c r="AJ101" t="n">
+      <c r="AH101" t="n">
+        <v>-15.113</v>
+      </c>
+      <c r="AL101" t="n">
         <v>2</v>
       </c>
-      <c r="AK101" t="n">
+      <c r="AM101" t="n">
         <v>1.012</v>
       </c>
-      <c r="AL101" t="n">
+      <c r="AN101" t="n">
         <v>0.047</v>
       </c>
-      <c r="AM101" t="inlineStr">
+      <c r="AO101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="AQ101" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
+      <c r="AR101" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_585483_Bao_cao_tai_chinh_quy_32025_1761811756.pdf</t>
         </is>
       </c>
-      <c r="AO101" t="inlineStr">
+      <c r="AS101" t="inlineStr">
         <is>
           <t>2026-08-31T15:40:59+07:00</t>
         </is>
@@ -42363,28 +43575,40 @@
         <v>-2.329</v>
       </c>
       <c r="AF102" t="n">
+        <v>-10.364</v>
+      </c>
+      <c r="AG102" t="n">
         <v>9.587999999999999</v>
       </c>
-      <c r="AJ102" t="n">
+      <c r="AH102" t="n">
+        <v>9.611000000000001</v>
+      </c>
+      <c r="AL102" t="n">
         <v>-7</v>
       </c>
-      <c r="AK102" t="n">
+      <c r="AM102" t="n">
         <v>-10.615</v>
       </c>
-      <c r="AL102" t="n">
+      <c r="AN102" t="n">
         <v>-0.167</v>
       </c>
-      <c r="AM102" t="inlineStr">
+      <c r="AO102" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>-21.23</v>
+      </c>
+      <c r="AQ102" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN102" t="inlineStr">
+      <c r="AR102" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604675_Bao_cao_tai_chinh_nam_2025_1776046299.pdf</t>
         </is>
       </c>
-      <c r="AO102" t="inlineStr">
+      <c r="AS102" t="inlineStr">
         <is>
           <t>2026-08-31T01:33:44+07:00</t>
         </is>
@@ -42485,28 +43709,40 @@
         <v>-7.118</v>
       </c>
       <c r="AF103" t="n">
+        <v>-15.746</v>
+      </c>
+      <c r="AG103" t="n">
         <v>5.01</v>
       </c>
-      <c r="AJ103" t="n">
+      <c r="AH103" t="n">
+        <v>-17.912</v>
+      </c>
+      <c r="AL103" t="n">
         <v>-24</v>
       </c>
-      <c r="AK103" t="n">
+      <c r="AM103" t="n">
         <v>-11.433</v>
       </c>
-      <c r="AL103" t="n">
+      <c r="AN103" t="n">
         <v>-0.5620000000000001</v>
       </c>
-      <c r="AM103" t="inlineStr">
+      <c r="AO103" t="n">
+        <v>-48</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>-22.866</v>
+      </c>
+      <c r="AQ103" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN103" t="inlineStr">
+      <c r="AR103" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_611277_Bao_cao_tai_chinh_quy_12026_1777027908.pdf</t>
         </is>
       </c>
-      <c r="AO103" t="inlineStr">
+      <c r="AS103" t="inlineStr">
         <is>
           <t>2026-08-31T23:45:58+07:00</t>
         </is>
@@ -42612,26 +43848,38 @@
       <c r="AF104" t="n">
         <v>0</v>
       </c>
-      <c r="AJ104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK104" t="n">
+      <c r="AG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="n">
         <v>0</v>
       </c>
       <c r="AL104" t="n">
         <v>0</v>
       </c>
-      <c r="AM104" t="inlineStr">
+      <c r="AM104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ104" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
+      <c r="AR104" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SGB_000000016770459_VI__Bao_Cao_Tai_Chinh_Hop_Nhat_Ban_Nien_Nam_2026_daky_20082026151909.pdf?v=1787213952177</t>
         </is>
       </c>
-      <c r="AO104" t="inlineStr">
+      <c r="AS104" t="inlineStr">
         <is>
           <t>2026-09-01T10:00:42+07:00</t>
         </is>
@@ -42653,7 +43901,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="AO105" t="inlineStr">
+      <c r="AS105" t="inlineStr">
         <is>
           <t>2026-09-17T17:21:29+07:00</t>
         </is>
@@ -42757,28 +44005,40 @@
         <v>0.274</v>
       </c>
       <c r="AF106" t="n">
+        <v>29.917</v>
+      </c>
+      <c r="AG106" t="n">
         <v>12.238</v>
       </c>
-      <c r="AJ106" t="n">
+      <c r="AH106" t="n">
+        <v>-3.633</v>
+      </c>
+      <c r="AL106" t="n">
         <v>1186</v>
       </c>
-      <c r="AK106" t="n">
+      <c r="AM106" t="n">
         <v>12.948</v>
       </c>
-      <c r="AL106" t="n">
+      <c r="AN106" t="n">
         <v>1.875</v>
       </c>
-      <c r="AM106" t="inlineStr">
+      <c r="AO106" t="n">
+        <v>2372</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>25.895</v>
+      </c>
+      <c r="AQ106" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
+      <c r="AR106" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250903_-_SHB_-_Bao_Cao_Tai_Chinh_Hop_Nhat_Soat_Xet_Ban_nien_30.6.2025_1756910753.pdf</t>
         </is>
       </c>
-      <c r="AO106" t="inlineStr">
+      <c r="AS106" t="inlineStr">
         <is>
           <t>2026-08-31T12:28:17+07:00</t>
         </is>
@@ -42800,7 +44060,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="AO107" t="inlineStr">
+      <c r="AS107" t="inlineStr">
         <is>
           <t>2026-09-17T18:10:56+07:00</t>
         </is>
@@ -42904,37 +44164,49 @@
         <v>23.013</v>
       </c>
       <c r="AF108" t="n">
+        <v>23.032</v>
+      </c>
+      <c r="AG108" t="n">
         <v>23.033</v>
       </c>
-      <c r="AG108" t="n">
+      <c r="AH108" t="n">
+        <v>35.007</v>
+      </c>
+      <c r="AI108" t="n">
         <v>1156478.2</v>
       </c>
-      <c r="AH108" t="n">
+      <c r="AJ108" t="n">
         <v>836988.189</v>
       </c>
-      <c r="AI108" t="n">
+      <c r="AK108" t="n">
         <v>138.171</v>
       </c>
-      <c r="AJ108" t="n">
+      <c r="AL108" t="n">
         <v>1712</v>
       </c>
-      <c r="AK108" t="n">
+      <c r="AM108" t="n">
         <v>913.734</v>
       </c>
-      <c r="AL108" t="n">
+      <c r="AN108" t="n">
         <v>2.513</v>
       </c>
-      <c r="AM108" t="inlineStr">
+      <c r="AO108" t="n">
+        <v>3424</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>1827.469</v>
+      </c>
+      <c r="AQ108" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
+      <c r="AR108" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_SHB_-_Bao_cao_tai_chinh_nam_2025_Hop_nhat_1775015883.pdf</t>
         </is>
       </c>
-      <c r="AO108" t="inlineStr">
+      <c r="AS108" t="inlineStr">
         <is>
           <t>2026-09-17T18:25:58+07:00</t>
         </is>
@@ -42956,7 +44228,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="AO109" t="inlineStr">
+      <c r="AS109" t="inlineStr">
         <is>
           <t>2026-09-17T19:16:33+07:00</t>
         </is>
@@ -43060,28 +44332,40 @@
         <v>31.553</v>
       </c>
       <c r="AF110" t="n">
+        <v>12.316</v>
+      </c>
+      <c r="AG110" t="n">
         <v>12.331</v>
       </c>
-      <c r="AJ110" t="n">
+      <c r="AH110" t="n">
+        <v>11.843</v>
+      </c>
+      <c r="AL110" t="n">
         <v>1431</v>
       </c>
-      <c r="AK110" t="n">
+      <c r="AM110" t="n">
         <v>21.166</v>
       </c>
-      <c r="AL110" t="n">
+      <c r="AN110" t="n">
         <v>1.9</v>
       </c>
-      <c r="AM110" t="inlineStr">
+      <c r="AO110" t="n">
+        <v>2862</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>42.331</v>
+      </c>
+      <c r="AQ110" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán 6 tháng đầu năm 2026</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
+      <c r="AR110" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-3/2026-09-04/no-name-1788460885.pdf</t>
         </is>
       </c>
-      <c r="AO110" t="inlineStr">
+      <c r="AS110" t="inlineStr">
         <is>
           <t>2026-09-04T08:27:55+07:00</t>
         </is>
@@ -43181,26 +44465,38 @@
       <c r="AF111" t="n">
         <v>0</v>
       </c>
-      <c r="AJ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK111" t="n">
+      <c r="AG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="n">
         <v>0</v>
       </c>
       <c r="AL111" t="n">
         <v>0</v>
       </c>
-      <c r="AM111" t="inlineStr">
+      <c r="AM111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ111" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
+      <c r="AR111" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_23052025144847.pdf</t>
         </is>
       </c>
-      <c r="AO111" t="inlineStr">
+      <c r="AS111" t="inlineStr">
         <is>
           <t>2026-08-31T10:31:02+07:00</t>
         </is>
@@ -43276,26 +44572,38 @@
       <c r="AF112" t="n">
         <v>0</v>
       </c>
-      <c r="AJ112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK112" t="n">
+      <c r="AG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="n">
         <v>0</v>
       </c>
       <c r="AL112" t="n">
         <v>0</v>
       </c>
-      <c r="AM112" t="inlineStr">
+      <c r="AM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ112" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN112" t="inlineStr">
+      <c r="AR112" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250905_-_SSB_-_Bao_cao_tai_chinh_hop_nhat_soat_xet_ban_nien_2025_va_Giai_trinh_bien_dong_LNST_signed_1757323427.pdf</t>
         </is>
       </c>
-      <c r="AO112" t="inlineStr">
+      <c r="AS112" t="inlineStr">
         <is>
           <t>2026-08-31T12:30:19+07:00</t>
         </is>
@@ -43399,28 +44707,40 @@
         <v>4.818</v>
       </c>
       <c r="AF113" t="n">
+        <v>-1.958</v>
+      </c>
+      <c r="AG113" t="n">
         <v>-2.918</v>
       </c>
-      <c r="AJ113" t="n">
+      <c r="AH113" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="AL113" t="n">
         <v>29</v>
       </c>
-      <c r="AK113" t="n">
+      <c r="AM113" t="n">
         <v>1.241</v>
       </c>
-      <c r="AL113" t="n">
+      <c r="AN113" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="AM113" t="inlineStr">
+      <c r="AO113" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>2.482</v>
+      </c>
+      <c r="AQ113" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN113" t="inlineStr">
+      <c r="AR113" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_SSB_-_Bao_cao_tai_chinh_Hop_nhat_Quy_III.2025_kem_Giai_trinh_bien_dong_LNST_signed_1761901007.pdf</t>
         </is>
       </c>
-      <c r="AO113" t="inlineStr">
+      <c r="AS113" t="inlineStr">
         <is>
           <t>2026-08-31T15:43:36+07:00</t>
         </is>
@@ -43524,28 +44844,40 @@
         <v>20.183</v>
       </c>
       <c r="AF114" t="n">
+        <v>17.103</v>
+      </c>
+      <c r="AG114" t="n">
         <v>6.443</v>
       </c>
-      <c r="AJ114" t="n">
+      <c r="AH114" t="n">
+        <v>4.968</v>
+      </c>
+      <c r="AL114" t="n">
         <v>568</v>
       </c>
-      <c r="AK114" t="n">
+      <c r="AM114" t="n">
         <v>23.166</v>
       </c>
-      <c r="AL114" t="n">
+      <c r="AN114" t="n">
         <v>1.407</v>
       </c>
-      <c r="AM114" t="inlineStr">
+      <c r="AO114" t="n">
+        <v>1136</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>46.332</v>
+      </c>
+      <c r="AQ114" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN114" t="inlineStr">
+      <c r="AR114" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260312_-_SSB_-_BCTC_hop_nhat_kiem_toan_nam_2025_kem_Giai_trinh_bien_dong_LNST_signed_1773310402.pdf</t>
         </is>
       </c>
-      <c r="AO114" t="inlineStr">
+      <c r="AS114" t="inlineStr">
         <is>
           <t>2026-08-31T01:36:28+07:00</t>
         </is>
@@ -43649,28 +44981,40 @@
         <v>-0.174</v>
       </c>
       <c r="AF115" t="n">
+        <v>-9.061</v>
+      </c>
+      <c r="AG115" t="n">
         <v>-9.928000000000001</v>
       </c>
-      <c r="AJ115" t="n">
+      <c r="AH115" t="n">
+        <v>-5.616</v>
+      </c>
+      <c r="AL115" t="n">
         <v>-225</v>
       </c>
-      <c r="AK115" t="n">
+      <c r="AM115" t="n">
         <v>-9.323</v>
       </c>
-      <c r="AL115" t="n">
+      <c r="AN115" t="n">
         <v>-0.542</v>
       </c>
-      <c r="AM115" t="inlineStr">
+      <c r="AO115" t="n">
+        <v>-450</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>-18.645</v>
+      </c>
+      <c r="AQ115" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN115" t="inlineStr">
+      <c r="AR115" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_SSB_-_BCTC_Hop_nhat_Quy_I.2026_va_Giai_trinh_bien_dong_LNST_signed_1777467537.pdf</t>
         </is>
       </c>
-      <c r="AO115" t="inlineStr">
+      <c r="AS115" t="inlineStr">
         <is>
           <t>2026-08-31T23:48:58+07:00</t>
         </is>
@@ -43744,28 +45088,40 @@
         <v>0.138</v>
       </c>
       <c r="AF116" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AG116" t="n">
         <v>-3.703</v>
       </c>
-      <c r="AJ116" t="n">
+      <c r="AH116" t="n">
+        <v>-14.62</v>
+      </c>
+      <c r="AL116" t="n">
         <v>-24</v>
       </c>
-      <c r="AK116" t="n">
+      <c r="AM116" t="n">
         <v>-1.067</v>
       </c>
-      <c r="AL116" t="n">
+      <c r="AN116" t="n">
         <v>-0.057</v>
       </c>
-      <c r="AM116" t="inlineStr">
+      <c r="AO116" t="n">
+        <v>-48</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>-2.133</v>
+      </c>
+      <c r="AQ116" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN116" t="inlineStr">
+      <c r="AR116" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_202608142020SSB2020Bao20cao20tai20chinh20hop20nhat20soat20xet20ban20nien20202620va20Giai20trinh20bien20dong20LNST_signed_20082026090228.pdf?v=1787191350112</t>
         </is>
       </c>
-      <c r="AO116" t="inlineStr">
+      <c r="AS116" t="inlineStr">
         <is>
           <t>2026-09-01T10:03:22+07:00</t>
         </is>
@@ -43841,26 +45197,38 @@
       <c r="AF117" t="n">
         <v>0</v>
       </c>
-      <c r="AJ117" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK117" t="n">
+      <c r="AG117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH117" t="n">
         <v>0</v>
       </c>
       <c r="AL117" t="n">
         <v>0</v>
       </c>
-      <c r="AM117" t="inlineStr">
+      <c r="AM117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ117" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN117" t="inlineStr">
+      <c r="AR117" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-si-gn-thng-tn26042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AO117" t="inlineStr">
+      <c r="AS117" t="inlineStr">
         <is>
           <t>2026-08-31T10:34:12+07:00</t>
         </is>
@@ -43966,26 +45334,38 @@
       <c r="AF118" t="n">
         <v>0</v>
       </c>
-      <c r="AJ118" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK118" t="n">
+      <c r="AG118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="n">
         <v>0</v>
       </c>
       <c r="AL118" t="n">
         <v>0</v>
       </c>
-      <c r="AM118" t="inlineStr">
+      <c r="AM118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ118" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN118" t="inlineStr">
+      <c r="AR118" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/STB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025100208.pdf</t>
         </is>
       </c>
-      <c r="AO118" t="inlineStr">
+      <c r="AS118" t="inlineStr">
         <is>
           <t>2026-08-31T12:33:00+07:00</t>
         </is>
@@ -44061,26 +45441,38 @@
       <c r="AF119" t="n">
         <v>0</v>
       </c>
-      <c r="AJ119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK119" t="n">
+      <c r="AG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="n">
         <v>0</v>
       </c>
       <c r="AL119" t="n">
         <v>0</v>
       </c>
-      <c r="AM119" t="inlineStr">
+      <c r="AM119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ119" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN119" t="inlineStr">
+      <c r="AR119" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251029_-_STB_-_BCTC_Hop_nhat_Q3.2025_1761804289.pdf</t>
         </is>
       </c>
-      <c r="AO119" t="inlineStr">
+      <c r="AS119" t="inlineStr">
         <is>
           <t>2026-08-31T15:46:18+07:00</t>
         </is>
@@ -44186,26 +45578,38 @@
       <c r="AF120" t="n">
         <v>0</v>
       </c>
-      <c r="AJ120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK120" t="n">
+      <c r="AG120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="n">
         <v>0</v>
       </c>
       <c r="AL120" t="n">
         <v>0</v>
       </c>
-      <c r="AM120" t="inlineStr">
+      <c r="AM120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ120" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN120" t="inlineStr">
+      <c r="AR120" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_STB_-_BCTC_Hop_nhat_nam_2025_da_kiem_toan__1774863040.pdf</t>
         </is>
       </c>
-      <c r="AO120" t="inlineStr">
+      <c r="AS120" t="inlineStr">
         <is>
           <t>2026-08-31T01:38:47+07:00</t>
         </is>
@@ -44309,32 +45713,44 @@
         <v>27.897</v>
       </c>
       <c r="AF121" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AG121" t="n">
         <v>-4.436</v>
       </c>
-      <c r="AG121" t="n">
+      <c r="AH121" t="n">
+        <v>-0.856</v>
+      </c>
+      <c r="AI121" t="n">
         <v>803932.3370000001</v>
       </c>
-      <c r="AH121" t="n">
+      <c r="AJ121" t="n">
         <v>776334.534</v>
       </c>
-      <c r="AI121" t="n">
+      <c r="AK121" t="n">
         <v>103.555</v>
       </c>
-      <c r="AJ121" t="n">
+      <c r="AL121" t="n">
         <v>659</v>
       </c>
-      <c r="AK121" t="n">
+      <c r="AM121" t="n">
         <v>10.907</v>
       </c>
-      <c r="AL121" t="n">
+      <c r="AN121" t="n">
         <v>1.072</v>
       </c>
-      <c r="AM121" t="inlineStr">
+      <c r="AO121" t="n">
+        <v>1318</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>21.814</v>
+      </c>
+      <c r="AQ121" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy I 2026, OCR khong doc duoc)</t>
         </is>
       </c>
-      <c r="AO121" t="inlineStr">
+      <c r="AS121" t="inlineStr">
         <is>
           <t>2026-09-17T14:38:33+07:00</t>
         </is>
@@ -44438,32 +45854,44 @@
         <v>29.993</v>
       </c>
       <c r="AF122" t="n">
+        <v>10.697</v>
+      </c>
+      <c r="AG122" t="n">
         <v>-0.806</v>
       </c>
-      <c r="AG122" t="n">
+      <c r="AH122" t="n">
+        <v>-1.092</v>
+      </c>
+      <c r="AI122" t="n">
         <v>820020.6800000001</v>
       </c>
-      <c r="AH122" t="n">
+      <c r="AJ122" t="n">
         <v>808189.617</v>
       </c>
-      <c r="AI122" t="n">
+      <c r="AK122" t="n">
         <v>101.464</v>
       </c>
-      <c r="AJ122" t="n">
+      <c r="AL122" t="n">
         <v>923</v>
       </c>
-      <c r="AK122" t="n">
+      <c r="AM122" t="n">
         <v>14.775</v>
       </c>
-      <c r="AL122" t="n">
+      <c r="AN122" t="n">
         <v>1.47</v>
       </c>
-      <c r="AM122" t="inlineStr">
+      <c r="AO122" t="n">
+        <v>1846</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>29.549</v>
+      </c>
+      <c r="AQ122" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy II 2026, OCR khong doc duoc)</t>
         </is>
       </c>
-      <c r="AO122" t="inlineStr">
+      <c r="AS122" t="inlineStr">
         <is>
           <t>2026-09-17T14:38:33+07:00</t>
         </is>
@@ -44567,28 +45995,40 @@
         <v>-6.833</v>
       </c>
       <c r="AF123" t="n">
+        <v>-11.152</v>
+      </c>
+      <c r="AG123" t="n">
         <v>1.216</v>
       </c>
-      <c r="AJ123" t="n">
+      <c r="AH123" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL123" t="n">
         <v>-470</v>
       </c>
-      <c r="AK123" t="n">
+      <c r="AM123" t="n">
         <v>-5.659</v>
       </c>
-      <c r="AL123" t="n">
+      <c r="AN123" t="n">
         <v>-0.305</v>
       </c>
-      <c r="AM123" t="inlineStr">
+      <c r="AO123" t="n">
+        <v>-940</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>-11.318</v>
+      </c>
+      <c r="AQ123" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN123" t="inlineStr">
+      <c r="AR123" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00001234567901234568ngn-hng-tmcp-k-thng-vit-nam21042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AO123" t="inlineStr">
+      <c r="AS123" t="inlineStr">
         <is>
           <t>2026-08-31T10:35:54+07:00</t>
         </is>
@@ -44691,26 +46131,38 @@
       <c r="AF124" t="n">
         <v>0</v>
       </c>
-      <c r="AJ124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK124" t="n">
+      <c r="AG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="n">
         <v>0</v>
       </c>
       <c r="AL124" t="n">
         <v>0</v>
       </c>
-      <c r="AM124" t="inlineStr">
+      <c r="AM124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ124" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN124" t="inlineStr">
+      <c r="AR124" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025101639.pdf</t>
         </is>
       </c>
-      <c r="AO124" t="inlineStr">
+      <c r="AS124" t="inlineStr">
         <is>
           <t>2026-08-31T12:36:30+07:00</t>
         </is>
@@ -44784,28 +46236,40 @@
         <v>-0.951</v>
       </c>
       <c r="AF125" t="n">
+        <v>-2.226</v>
+      </c>
+      <c r="AG125" t="n">
         <v>6.821</v>
       </c>
-      <c r="AJ125" t="n">
+      <c r="AH125" t="n">
+        <v>4.507</v>
+      </c>
+      <c r="AL125" t="n">
         <v>96</v>
       </c>
-      <c r="AK125" t="n">
+      <c r="AM125" t="n">
         <v>0.967</v>
       </c>
-      <c r="AL125" t="n">
+      <c r="AN125" t="n">
         <v>0.054</v>
       </c>
-      <c r="AM125" t="inlineStr">
+      <c r="AO125" t="n">
+        <v>192</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1.935</v>
+      </c>
+      <c r="AQ125" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN125" t="inlineStr">
+      <c r="AR125" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251021_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-3Q25_1761042656.pdf</t>
         </is>
       </c>
-      <c r="AO125" t="inlineStr">
+      <c r="AS125" t="inlineStr">
         <is>
           <t>2026-08-31T15:48:08+07:00</t>
         </is>
@@ -44909,28 +46373,40 @@
         <v>-11</v>
       </c>
       <c r="AF126" t="n">
+        <v>-8.137</v>
+      </c>
+      <c r="AG126" t="n">
         <v>-7.997</v>
       </c>
-      <c r="AJ126" t="n">
+      <c r="AH126" t="n">
+        <v>76.94799999999999</v>
+      </c>
+      <c r="AL126" t="n">
         <v>-1000</v>
       </c>
-      <c r="AK126" t="n">
+      <c r="AM126" t="n">
         <v>-9.27</v>
       </c>
-      <c r="AL126" t="n">
+      <c r="AN126" t="n">
         <v>-0.5570000000000001</v>
       </c>
-      <c r="AM126" t="inlineStr">
+      <c r="AO126" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-18.539</v>
+      </c>
+      <c r="AQ126" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN126" t="inlineStr">
+      <c r="AR126" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260317_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-YE25_1773755161.pdf</t>
         </is>
       </c>
-      <c r="AO126" t="inlineStr">
+      <c r="AS126" t="inlineStr">
         <is>
           <t>2026-08-31T01:41:25+07:00</t>
         </is>
@@ -45034,28 +46510,40 @@
         <v>-0.99</v>
       </c>
       <c r="AF127" t="n">
+        <v>-6.67</v>
+      </c>
+      <c r="AG127" t="n">
         <v>2.672</v>
       </c>
-      <c r="AJ127" t="n">
+      <c r="AH127" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="AL127" t="n">
         <v>-178</v>
       </c>
-      <c r="AK127" t="n">
+      <c r="AM127" t="n">
         <v>-1.869</v>
       </c>
-      <c r="AL127" t="n">
+      <c r="AN127" t="n">
         <v>-0.095</v>
       </c>
-      <c r="AM127" t="inlineStr">
+      <c r="AO127" t="n">
+        <v>-356</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-3.739</v>
+      </c>
+      <c r="AQ127" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN127" t="inlineStr">
+      <c r="AR127" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260421_-_TCB_-_bao_cao_tai_chinh_hop_nhat_1Q26_VAS_VN__1776825559.pdf</t>
         </is>
       </c>
-      <c r="AO127" t="inlineStr">
+      <c r="AS127" t="inlineStr">
         <is>
           <t>2026-08-31T23:55:42+07:00</t>
         </is>
@@ -45159,28 +46647,40 @@
         <v>15.674</v>
       </c>
       <c r="AF128" t="n">
+        <v>8.188000000000001</v>
+      </c>
+      <c r="AG128" t="n">
         <v>3.898</v>
       </c>
-      <c r="AJ128" t="n">
+      <c r="AH128" t="n">
+        <v>12.742</v>
+      </c>
+      <c r="AL128" t="n">
         <v>1078</v>
       </c>
-      <c r="AK128" t="n">
+      <c r="AM128" t="n">
         <v>10.016</v>
       </c>
-      <c r="AL128" t="n">
+      <c r="AN128" t="n">
         <v>0.57</v>
       </c>
-      <c r="AM128" t="inlineStr">
+      <c r="AO128" t="n">
+        <v>2156</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>20.032</v>
+      </c>
+      <c r="AQ128" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN128" t="inlineStr">
+      <c r="AR128" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_202608132020TCB2020Bao20cao20tai20chinh20hop20nhat20soat20xet202Q2026_19082026102705.pdf?v=1787110027315</t>
         </is>
       </c>
-      <c r="AO128" t="inlineStr">
+      <c r="AS128" t="inlineStr">
         <is>
           <t>2026-09-01T10:12:04+07:00</t>
         </is>
@@ -45284,37 +46784,49 @@
         <v>12.468</v>
       </c>
       <c r="AF129" t="n">
+        <v>12.314</v>
+      </c>
+      <c r="AG129" t="n">
         <v>12.239</v>
       </c>
-      <c r="AG129" t="n">
+      <c r="AH129" t="n">
+        <v>12.654</v>
+      </c>
+      <c r="AI129" t="n">
         <v>62861.954</v>
       </c>
-      <c r="AH129" t="n">
+      <c r="AJ129" t="n">
         <v>35233.365</v>
       </c>
-      <c r="AI129" t="n">
+      <c r="AK129" t="n">
         <v>178.416</v>
       </c>
-      <c r="AJ129" t="n">
+      <c r="AL129" t="n">
         <v>461</v>
       </c>
-      <c r="AK129" t="n">
+      <c r="AM129" t="n">
         <v>13.624</v>
       </c>
-      <c r="AL129" t="n">
+      <c r="AN129" t="n">
         <v>1.167</v>
       </c>
-      <c r="AM129" t="inlineStr">
+      <c r="AO129" t="n">
+        <v>922</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>27.249</v>
+      </c>
+      <c r="AQ129" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN129" t="inlineStr">
+      <c r="AR129" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_Q1_2025_Hopnhat_23052025145349.pdf</t>
         </is>
       </c>
-      <c r="AO129" t="inlineStr">
+      <c r="AS129" t="inlineStr">
         <is>
           <t>2026-09-17T15:27:28+07:00</t>
         </is>
@@ -45418,37 +46930,49 @@
         <v>4.669</v>
       </c>
       <c r="AF130" t="n">
+        <v>6.228</v>
+      </c>
+      <c r="AG130" t="n">
         <v>-5.568</v>
       </c>
-      <c r="AG130" t="n">
+      <c r="AH130" t="n">
+        <v>-5.552</v>
+      </c>
+      <c r="AI130" t="n">
         <v>846378.6310000001</v>
       </c>
-      <c r="AH130" t="n">
+      <c r="AJ130" t="n">
         <v>898757.455</v>
       </c>
-      <c r="AI130" t="n">
+      <c r="AK130" t="n">
         <v>94.172</v>
       </c>
-      <c r="AJ130" t="n">
+      <c r="AL130" t="n">
         <v>82</v>
       </c>
-      <c r="AK130" t="n">
+      <c r="AM130" t="n">
         <v>2.602</v>
       </c>
-      <c r="AL130" t="n">
+      <c r="AN130" t="n">
         <v>0.214</v>
       </c>
-      <c r="AM130" t="inlineStr">
+      <c r="AO130" t="n">
+        <v>164</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>5.204</v>
+      </c>
+      <c r="AQ130" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN130" t="inlineStr">
+      <c r="AR130" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025102458.pdf</t>
         </is>
       </c>
-      <c r="AO130" t="inlineStr">
+      <c r="AS130" t="inlineStr">
         <is>
           <t>2026-09-17T16:32:56+07:00</t>
         </is>
@@ -45552,37 +47076,49 @@
         <v>-6.445</v>
       </c>
       <c r="AF131" t="n">
+        <v>11.141</v>
+      </c>
+      <c r="AG131" t="n">
         <v>-58.229</v>
       </c>
-      <c r="AG131" t="n">
+      <c r="AH131" t="n">
+        <v>-34.166</v>
+      </c>
+      <c r="AI131" t="n">
         <v>909690.326</v>
       </c>
-      <c r="AH131" t="n">
+      <c r="AJ131" t="n">
         <v>608057.379</v>
       </c>
-      <c r="AI131" t="n">
+      <c r="AK131" t="n">
         <v>149.606</v>
       </c>
-      <c r="AJ131" t="n">
+      <c r="AL131" t="n">
         <v>-542</v>
       </c>
-      <c r="AK131" t="n">
+      <c r="AM131" t="n">
         <v>-16.741</v>
       </c>
-      <c r="AL131" t="n">
+      <c r="AN131" t="n">
         <v>-1.355</v>
       </c>
-      <c r="AM131" t="inlineStr">
+      <c r="AO131" t="n">
+        <v>-1084</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>-33.481</v>
+      </c>
+      <c r="AQ131" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN131" t="inlineStr">
+      <c r="AR131" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_TPB_-_Bao_cao_tai_chinh_hop_nhat_Q3.2025_signed_1761832307.pdf</t>
         </is>
       </c>
-      <c r="AO131" t="inlineStr">
+      <c r="AS131" t="inlineStr">
         <is>
           <t>2026-09-17T17:36:04+07:00</t>
         </is>
@@ -45658,26 +47194,38 @@
       <c r="AF132" t="n">
         <v>0</v>
       </c>
-      <c r="AJ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK132" t="n">
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
         <v>0</v>
       </c>
       <c r="AL132" t="n">
         <v>0</v>
       </c>
-      <c r="AM132" t="inlineStr">
+      <c r="AM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ132" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN132" t="inlineStr">
+      <c r="AR132" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_TPB_-_BCTC_hop_nhat_2025_da_kiem_toan_kem_giai_trinh_chenh_lech_LNST_signed_1774952109.pdf</t>
         </is>
       </c>
-      <c r="AO132" t="inlineStr">
+      <c r="AS132" t="inlineStr">
         <is>
           <t>2026-08-31T01:43:30+07:00</t>
         </is>
@@ -45775,37 +47323,49 @@
         <v>-0.915</v>
       </c>
       <c r="AF133" t="n">
+        <v>5.721</v>
+      </c>
+      <c r="AG133" t="n">
         <v>4.214</v>
       </c>
-      <c r="AG133" t="n">
+      <c r="AH133" t="n">
+        <v>22.873</v>
+      </c>
+      <c r="AI133" t="n">
         <v>201987.137</v>
       </c>
-      <c r="AH133" t="n">
+      <c r="AJ133" t="n">
         <v>63845.469</v>
       </c>
-      <c r="AI133" t="n">
+      <c r="AK133" t="n">
         <v>316.369</v>
       </c>
-      <c r="AJ133" t="n">
+      <c r="AL133" t="n">
         <v>159</v>
       </c>
-      <c r="AK133" t="n">
+      <c r="AM133" t="n">
         <v>4.596</v>
       </c>
-      <c r="AL133" t="n">
+      <c r="AN133" t="n">
         <v>0.331</v>
       </c>
-      <c r="AM133" t="inlineStr">
+      <c r="AO133" t="n">
+        <v>318</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>9.192</v>
+      </c>
+      <c r="AQ133" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN133" t="inlineStr">
+      <c r="AR133" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_TPB_-_BCTC_hop_nhat_Quy_1_2026_signed_1777457982.pdf</t>
         </is>
       </c>
-      <c r="AO133" t="inlineStr">
+      <c r="AS133" t="inlineStr">
         <is>
           <t>2026-09-17T19:18:12+07:00</t>
         </is>
@@ -45879,28 +47439,40 @@
         <v>0.541</v>
       </c>
       <c r="AF134" t="n">
+        <v>-3.268</v>
+      </c>
+      <c r="AG134" t="n">
         <v>1.136</v>
       </c>
-      <c r="AJ134" t="n">
+      <c r="AH134" t="n">
+        <v>7.393</v>
+      </c>
+      <c r="AL134" t="n">
         <v>53</v>
       </c>
-      <c r="AK134" t="n">
+      <c r="AM134" t="n">
         <v>1.458</v>
       </c>
-      <c r="AL134" t="n">
+      <c r="AN134" t="n">
         <v>0.107</v>
       </c>
-      <c r="AM134" t="inlineStr">
+      <c r="AO134" t="n">
+        <v>106</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="AQ134" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN134" t="inlineStr">
+      <c r="AR134" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_202608182020TPB2020Bao20cao20tai20chinh20hop20nhat20soat20xet20ban20nien20202620kem20giai20trinh20chenh20lech20LNST_signed_19082026095348.pdf?v=1787108030513</t>
         </is>
       </c>
-      <c r="AO134" t="inlineStr">
+      <c r="AS134" t="inlineStr">
         <is>
           <t>2026-09-01T10:14:12+07:00</t>
         </is>
@@ -45976,26 +47548,38 @@
       <c r="AF135" t="n">
         <v>20.42</v>
       </c>
-      <c r="AJ135" t="n">
+      <c r="AG135" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AL135" t="n">
         <v>167</v>
       </c>
-      <c r="AK135" t="n">
+      <c r="AM135" t="n">
         <v>27.264</v>
       </c>
-      <c r="AL135" t="n">
+      <c r="AN135" t="n">
         <v>1.825</v>
       </c>
-      <c r="AM135" t="inlineStr">
+      <c r="AO135" t="n">
+        <v>334</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>54.528</v>
+      </c>
+      <c r="AQ135" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN135" t="inlineStr">
+      <c r="AR135" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014787653_VI_BaoCaoTaiChinh_Q1_2025_18042025134138.pdf</t>
         </is>
       </c>
-      <c r="AO135" t="inlineStr">
+      <c r="AS135" t="inlineStr">
         <is>
           <t>2026-08-31T10:42:19+07:00</t>
         </is>
@@ -46069,37 +47653,49 @@
         <v>0</v>
       </c>
       <c r="AF136" t="n">
+        <v>-10.791</v>
+      </c>
+      <c r="AG136" t="n">
         <v>-21.581</v>
       </c>
-      <c r="AG136" t="n">
-        <v>0</v>
-      </c>
       <c r="AH136" t="n">
+        <v>-21.581</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" t="n">
         <v>28914.298</v>
       </c>
-      <c r="AI136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ136" t="n">
+      <c r="AK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL136" t="n">
         <v>-126</v>
       </c>
-      <c r="AK136" t="n">
+      <c r="AM136" t="n">
         <v>-23.231</v>
       </c>
-      <c r="AL136" t="n">
+      <c r="AN136" t="n">
         <v>-1.337</v>
       </c>
-      <c r="AM136" t="inlineStr">
+      <c r="AO136" t="n">
+        <v>-252</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-46.462</v>
+      </c>
+      <c r="AQ136" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025</t>
         </is>
       </c>
-      <c r="AN136" t="inlineStr">
+      <c r="AR136" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000007054673721340387ngn-hng-tmcp-vit-24072025-000000bo-co-ti-chnh-hp-nht-qu_1_0914.pdf</t>
         </is>
       </c>
-      <c r="AO136" t="inlineStr">
+      <c r="AS136" t="inlineStr">
         <is>
           <t>2026-09-17T16:34:18+07:00</t>
         </is>
@@ -46173,37 +47769,49 @@
         <v>10.425</v>
       </c>
       <c r="AF137" t="n">
+        <v>10.537</v>
+      </c>
+      <c r="AG137" t="n">
         <v>4.034</v>
       </c>
-      <c r="AG137" t="n">
+      <c r="AH137" t="n">
+        <v>-10.33</v>
+      </c>
+      <c r="AI137" t="n">
         <v>221001.348</v>
       </c>
-      <c r="AH137" t="n">
+      <c r="AJ137" t="n">
         <v>221087.326</v>
       </c>
-      <c r="AI137" t="n">
+      <c r="AK137" t="n">
         <v>99.961</v>
       </c>
-      <c r="AJ137" t="n">
+      <c r="AL137" t="n">
         <v>93</v>
       </c>
-      <c r="AK137" t="n">
+      <c r="AM137" t="n">
         <v>14.561</v>
       </c>
-      <c r="AL137" t="n">
+      <c r="AN137" t="n">
         <v>0.96</v>
       </c>
-      <c r="AM137" t="inlineStr">
+      <c r="AO137" t="n">
+        <v>186</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>29.123</v>
+      </c>
+      <c r="AQ137" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN137" t="inlineStr">
+      <c r="AR137" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251017_-_VAB_-_BCTC_HN_Q3.2025_1761126486.pdf</t>
         </is>
       </c>
-      <c r="AO137" t="inlineStr">
+      <c r="AS137" t="inlineStr">
         <is>
           <t>2026-09-18T08:37:05+07:00</t>
         </is>
@@ -46307,28 +47915,40 @@
         <v>10.286</v>
       </c>
       <c r="AF138" t="n">
+        <v>12.475</v>
+      </c>
+      <c r="AG138" t="n">
         <v>6.977</v>
       </c>
-      <c r="AJ138" t="n">
+      <c r="AH138" t="n">
+        <v>-9.147</v>
+      </c>
+      <c r="AL138" t="n">
         <v>114</v>
       </c>
-      <c r="AK138" t="n">
+      <c r="AM138" t="n">
         <v>7.088</v>
       </c>
-      <c r="AL138" t="n">
+      <c r="AN138" t="n">
         <v>1.123</v>
       </c>
-      <c r="AM138" t="inlineStr">
+      <c r="AO138" t="n">
+        <v>228</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>14.177</v>
+      </c>
+      <c r="AQ138" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN138" t="inlineStr">
+      <c r="AR138" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_VAB_BCTC_hop_nhat_da_kiem_toan_Nam_2025_1775054500.pdf</t>
         </is>
       </c>
-      <c r="AO138" t="inlineStr">
+      <c r="AS138" t="inlineStr">
         <is>
           <t>2026-08-31T01:45:19+07:00</t>
         </is>
@@ -46432,32 +48052,44 @@
         <v>7.933</v>
       </c>
       <c r="AF139" t="n">
+        <v>11.283</v>
+      </c>
+      <c r="AG139" t="n">
         <v>2.778</v>
       </c>
-      <c r="AG139" t="n">
+      <c r="AH139" t="n">
+        <v>-10.068</v>
+      </c>
+      <c r="AI139" t="n">
         <v>131635.815</v>
       </c>
-      <c r="AH139" t="n">
+      <c r="AJ139" t="n">
         <v>129515.728</v>
       </c>
-      <c r="AI139" t="n">
+      <c r="AK139" t="n">
         <v>101.637</v>
       </c>
-      <c r="AJ139" t="n">
+      <c r="AL139" t="n">
         <v>89</v>
       </c>
-      <c r="AK139" t="n">
+      <c r="AM139" t="n">
         <v>13.175</v>
       </c>
-      <c r="AL139" t="n">
+      <c r="AN139" t="n">
         <v>0.842</v>
       </c>
-      <c r="AM139" t="inlineStr">
+      <c r="AO139" t="n">
+        <v>178</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="AQ139" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (VAB thuyet minh BCTC Quy 1 2026, cot 'qua han duoi/tren 3 thang' dao nguoc thu tu so voi chuan nen da doi lai khi nhap, don vi da xac nhan la Trieu dong that qua doi chieu Vietcap)</t>
         </is>
       </c>
-      <c r="AO139" t="inlineStr">
+      <c r="AS139" t="inlineStr">
         <is>
           <t>2026-09-18T08:32:03+07:00</t>
         </is>
@@ -46561,28 +48193,40 @@
         <v>-15.883</v>
       </c>
       <c r="AF140" t="n">
+        <v>-0.419</v>
+      </c>
+      <c r="AG140" t="n">
         <v>-8.928000000000001</v>
       </c>
-      <c r="AJ140" t="n">
+      <c r="AH140" t="n">
+        <v>3.211</v>
+      </c>
+      <c r="AL140" t="n">
         <v>-74</v>
       </c>
-      <c r="AK140" t="n">
+      <c r="AM140" t="n">
         <v>-12.826</v>
       </c>
-      <c r="AL140" t="n">
+      <c r="AN140" t="n">
         <v>-0.6850000000000001</v>
       </c>
-      <c r="AM140" t="inlineStr">
+      <c r="AO140" t="n">
+        <v>-148</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>-25.653</v>
+      </c>
+      <c r="AQ140" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN140" t="inlineStr">
+      <c r="AR140" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VAB_202608212020VAB2020BCTC20HN20SOAT20XET20BAN20NIEN202026_22082026105705.pdf?v=1787371027647</t>
         </is>
       </c>
-      <c r="AO140" t="inlineStr">
+      <c r="AS140" t="inlineStr">
         <is>
           <t>2026-09-01T10:15:41+07:00</t>
         </is>
@@ -46656,28 +48300,40 @@
         <v>1.511</v>
       </c>
       <c r="AF141" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="AG141" t="n">
         <v>8.176</v>
       </c>
-      <c r="AJ141" t="n">
+      <c r="AH141" t="n">
+        <v>8.176</v>
+      </c>
+      <c r="AL141" t="n">
         <v>51</v>
       </c>
-      <c r="AK141" t="n">
+      <c r="AM141" t="n">
         <v>7.26</v>
       </c>
-      <c r="AL141" t="n">
+      <c r="AN141" t="n">
         <v>0.573</v>
       </c>
-      <c r="AM141" t="inlineStr">
+      <c r="AO141" t="n">
+        <v>102</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="AQ141" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN141" t="inlineStr">
+      <c r="AR141" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/1_vbb_2025_5_7_121b03c_vi_baocaotaichinh_hopnhat_q1_20251_16052025112437.pdf</t>
         </is>
       </c>
-      <c r="AO141" t="inlineStr">
+      <c r="AS141" t="inlineStr">
         <is>
           <t>2026-08-31T10:44:04+07:00</t>
         </is>
@@ -46783,26 +48439,38 @@
       <c r="AF142" t="n">
         <v>9.122999999999999</v>
       </c>
-      <c r="AJ142" t="n">
+      <c r="AG142" t="n">
+        <v>9.122999999999999</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>104.045</v>
+      </c>
+      <c r="AL142" t="n">
         <v>143</v>
       </c>
-      <c r="AK142" t="n">
+      <c r="AM142" t="n">
         <v>20.803</v>
       </c>
-      <c r="AL142" t="n">
+      <c r="AN142" t="n">
         <v>1.576</v>
       </c>
-      <c r="AM142" t="inlineStr">
+      <c r="AO142" t="n">
+        <v>286</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>41.606</v>
+      </c>
+      <c r="AQ142" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN142" t="inlineStr">
+      <c r="AR142" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-vit-nam-thng-tn05082025-000000bo-co-ti-chnh-bn-nin-2025_1_1517.pdf</t>
         </is>
       </c>
-      <c r="AO142" t="inlineStr">
+      <c r="AS142" t="inlineStr">
         <is>
           <t>2026-08-31T12:48:36+07:00</t>
         </is>
@@ -46876,28 +48544,40 @@
         <v>16.938</v>
       </c>
       <c r="AF143" t="n">
+        <v>19.023</v>
+      </c>
+      <c r="AG143" t="n">
         <v>19.026</v>
       </c>
-      <c r="AJ143" t="n">
+      <c r="AH143" t="n">
+        <v>24.442</v>
+      </c>
+      <c r="AL143" t="n">
         <v>300</v>
       </c>
-      <c r="AK143" t="n">
+      <c r="AM143" t="n">
         <v>36.232</v>
       </c>
-      <c r="AL143" t="n">
+      <c r="AN143" t="n">
         <v>3.207</v>
       </c>
-      <c r="AM143" t="inlineStr">
+      <c r="AO143" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>72.465</v>
+      </c>
+      <c r="AQ143" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN143" t="inlineStr">
+      <c r="AR143" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-11-05/no-name-1762283224.pdf</t>
         </is>
       </c>
-      <c r="AO143" t="inlineStr">
+      <c r="AS143" t="inlineStr">
         <is>
           <t>2026-08-31T15:58:42+07:00</t>
         </is>
@@ -47003,26 +48683,38 @@
       <c r="AF144" t="n">
         <v>0</v>
       </c>
-      <c r="AJ144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK144" t="n">
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
         <v>0</v>
       </c>
       <c r="AL144" t="n">
         <v>0</v>
       </c>
-      <c r="AM144" t="inlineStr">
+      <c r="AM144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ144" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN144" t="inlineStr">
+      <c r="AR144" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603183_Bao_cao_tai_chinh_nam_2025_1776046427.pdf</t>
         </is>
       </c>
-      <c r="AO144" t="inlineStr">
+      <c r="AS144" t="inlineStr">
         <is>
           <t>2026-08-31T01:48:14+07:00</t>
         </is>
@@ -47098,26 +48790,38 @@
       <c r="AF145" t="n">
         <v>133.626</v>
       </c>
-      <c r="AJ145" t="n">
+      <c r="AG145" t="n">
+        <v>133.626</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>139.206</v>
+      </c>
+      <c r="AL145" t="n">
         <v>2436</v>
       </c>
-      <c r="AK145" t="n">
+      <c r="AM145" t="n">
         <v>317.147</v>
       </c>
-      <c r="AL145" t="n">
+      <c r="AN145" t="n">
         <v>19.392</v>
       </c>
-      <c r="AM145" t="inlineStr">
+      <c r="AO145" t="n">
+        <v>4872</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>634.295</v>
+      </c>
+      <c r="AQ145" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN145" t="inlineStr">
+      <c r="AR145" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VBB_1778222221.pdf</t>
         </is>
       </c>
-      <c r="AO145" t="inlineStr">
+      <c r="AS145" t="inlineStr">
         <is>
           <t>2026-09-01T00:03:48+07:00</t>
         </is>
@@ -47212,28 +48916,40 @@
         <v>6.228</v>
       </c>
       <c r="AF146" t="n">
+        <v>11.536</v>
+      </c>
+      <c r="AG146" t="n">
         <v>18.46</v>
       </c>
-      <c r="AJ146" t="n">
+      <c r="AH146" t="n">
+        <v>22.773</v>
+      </c>
+      <c r="AL146" t="n">
         <v>187</v>
       </c>
-      <c r="AK146" t="n">
+      <c r="AM146" t="n">
         <v>18.821</v>
       </c>
-      <c r="AL146" t="n">
+      <c r="AN146" t="n">
         <v>1.422</v>
       </c>
-      <c r="AM146" t="inlineStr">
+      <c r="AO146" t="n">
+        <v>374</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>37.642</v>
+      </c>
+      <c r="AQ146" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán 6 tháng đầu năm 2026</t>
         </is>
       </c>
-      <c r="AN146" t="inlineStr">
+      <c r="AR146" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-3/2026-08-17/no-name-1786938113.pdf</t>
         </is>
       </c>
-      <c r="AO146" t="inlineStr">
+      <c r="AS146" t="inlineStr">
         <is>
           <t>2026-09-01T10:19:39+07:00</t>
         </is>
@@ -47337,28 +49053,40 @@
         <v>-2.394</v>
       </c>
       <c r="AF147" t="n">
+        <v>6.039</v>
+      </c>
+      <c r="AG147" t="n">
         <v>-0.792</v>
       </c>
-      <c r="AJ147" t="n">
+      <c r="AH147" t="n">
+        <v>7.649</v>
+      </c>
+      <c r="AL147" t="n">
         <v>-118</v>
       </c>
-      <c r="AK147" t="n">
+      <c r="AM147" t="n">
         <v>-0.862</v>
       </c>
-      <c r="AL147" t="n">
+      <c r="AN147" t="n">
         <v>-0.058</v>
       </c>
-      <c r="AM147" t="inlineStr">
+      <c r="AO147" t="n">
+        <v>-236</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>-1.724</v>
+      </c>
+      <c r="AQ147" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN147" t="inlineStr">
+      <c r="AR147" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_23052025150224.pdf</t>
         </is>
       </c>
-      <c r="AO147" t="inlineStr">
+      <c r="AS147" t="inlineStr">
         <is>
           <t>2026-08-31T17:07:33+07:00</t>
         </is>
@@ -47432,28 +49160,40 @@
         <v>-4.16</v>
       </c>
       <c r="AF148" t="n">
+        <v>3.854</v>
+      </c>
+      <c r="AG148" t="n">
         <v>-1.94</v>
       </c>
-      <c r="AJ148" t="n">
+      <c r="AH148" t="n">
+        <v>7.408</v>
+      </c>
+      <c r="AL148" t="n">
         <v>-487</v>
       </c>
-      <c r="AK148" t="n">
+      <c r="AM148" t="n">
         <v>-3.439</v>
       </c>
-      <c r="AL148" t="n">
+      <c r="AN148" t="n">
         <v>-0.228</v>
       </c>
-      <c r="AM148" t="inlineStr">
+      <c r="AO148" t="n">
+        <v>-974</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>-6.878</v>
+      </c>
+      <c r="AQ148" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN148" t="inlineStr">
+      <c r="AR148" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025111259.pdf</t>
         </is>
       </c>
-      <c r="AO148" t="inlineStr">
+      <c r="AS148" t="inlineStr">
         <is>
           <t>2026-08-31T12:50:26+07:00</t>
         </is>
@@ -47557,37 +49297,49 @@
         <v>-5.369</v>
       </c>
       <c r="AF149" t="n">
+        <v>2.471</v>
+      </c>
+      <c r="AG149" t="n">
         <v>-2.124</v>
       </c>
-      <c r="AG149" t="n">
+      <c r="AH149" t="n">
+        <v>7.526</v>
+      </c>
+      <c r="AI149" t="n">
         <v>523906.365</v>
       </c>
-      <c r="AH149" t="n">
+      <c r="AJ149" t="n">
         <v>318283.844</v>
       </c>
-      <c r="AI149" t="n">
+      <c r="AK149" t="n">
         <v>164.604</v>
       </c>
-      <c r="AJ149" t="n">
+      <c r="AL149" t="n">
         <v>-656</v>
       </c>
-      <c r="AK149" t="n">
+      <c r="AM149" t="n">
         <v>-4.476</v>
       </c>
-      <c r="AL149" t="n">
+      <c r="AN149" t="n">
         <v>-0.294</v>
       </c>
-      <c r="AM149" t="inlineStr">
+      <c r="AO149" t="n">
+        <v>-1312</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>-8.951000000000001</v>
+      </c>
+      <c r="AQ149" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN149" t="inlineStr">
+      <c r="AR149" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_VCB_-_CBTT_BCTC_Hop_nhat_Q3.2025_1761883208.pdf</t>
         </is>
       </c>
-      <c r="AO149" t="inlineStr">
+      <c r="AS149" t="inlineStr">
         <is>
           <t>2026-09-17T17:41:27+07:00</t>
         </is>
@@ -47663,26 +49415,38 @@
       <c r="AF150" t="n">
         <v>0.034</v>
       </c>
-      <c r="AJ150" t="n">
+      <c r="AG150" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="AL150" t="n">
         <v>7</v>
       </c>
-      <c r="AK150" t="n">
+      <c r="AM150" t="n">
         <v>0.043</v>
       </c>
-      <c r="AL150" t="n">
+      <c r="AN150" t="n">
         <v>0.003</v>
       </c>
-      <c r="AM150" t="inlineStr">
+      <c r="AO150" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AQ150" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN150" t="inlineStr">
+      <c r="AR150" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_VCB_-_BCTC_hop_nhat_kiem_toan_nam_2025_1774870712.pdf</t>
         </is>
       </c>
-      <c r="AO150" t="inlineStr">
+      <c r="AS150" t="inlineStr">
         <is>
           <t>2026-08-31T01:50:20+07:00</t>
         </is>
@@ -47786,28 +49550,40 @@
         <v>0.649</v>
       </c>
       <c r="AF151" t="n">
+        <v>-15.42</v>
+      </c>
+      <c r="AG151" t="n">
         <v>-2.924</v>
       </c>
-      <c r="AJ151" t="n">
+      <c r="AH151" t="n">
+        <v>3.723</v>
+      </c>
+      <c r="AL151" t="n">
         <v>-1626</v>
       </c>
-      <c r="AK151" t="n">
+      <c r="AM151" t="n">
         <v>-9.212</v>
       </c>
-      <c r="AL151" t="n">
+      <c r="AN151" t="n">
         <v>-0.695</v>
       </c>
-      <c r="AM151" t="inlineStr">
+      <c r="AO151" t="n">
+        <v>-3252</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>-18.424</v>
+      </c>
+      <c r="AQ151" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN151" t="inlineStr">
+      <c r="AR151" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_VCB_-_BCTC_hop_nhat_Q1.2026_1777452360.pdf</t>
         </is>
       </c>
-      <c r="AO151" t="inlineStr">
+      <c r="AS151" t="inlineStr">
         <is>
           <t>2026-09-01T00:05:30+07:00</t>
         </is>
@@ -47881,28 +49657,40 @@
         <v>0.013</v>
       </c>
       <c r="AF152" t="n">
+        <v>13.181</v>
+      </c>
+      <c r="AG152" t="n">
         <v>19.865</v>
       </c>
-      <c r="AJ152" t="n">
+      <c r="AH152" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AL152" t="n">
         <v>2634</v>
       </c>
-      <c r="AK152" t="n">
+      <c r="AM152" t="n">
         <v>13.76</v>
       </c>
-      <c r="AL152" t="n">
+      <c r="AN152" t="n">
         <v>1.06</v>
       </c>
-      <c r="AM152" t="inlineStr">
+      <c r="AO152" t="n">
+        <v>5268</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>27.521</v>
+      </c>
+      <c r="AQ152" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN152" t="inlineStr">
+      <c r="AR152" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_202608142020VCB2020BCTC20hop20nhat20soat20xet20ban20nien202026_20082026091404.pdf?v=1787192046593</t>
         </is>
       </c>
-      <c r="AO152" t="inlineStr">
+      <c r="AS152" t="inlineStr">
         <is>
           <t>2026-09-01T10:21:39+07:00</t>
         </is>
@@ -47976,28 +49764,40 @@
         <v>7.583</v>
       </c>
       <c r="AF153" t="n">
+        <v>7.627</v>
+      </c>
+      <c r="AG153" t="n">
         <v>12.136</v>
       </c>
-      <c r="AJ153" t="n">
+      <c r="AH153" t="n">
+        <v>12.135</v>
+      </c>
+      <c r="AL153" t="n">
         <v>370</v>
       </c>
-      <c r="AK153" t="n">
+      <c r="AM153" t="n">
         <v>9.901</v>
       </c>
-      <c r="AL153" t="n">
+      <c r="AN153" t="n">
         <v>0.848</v>
       </c>
-      <c r="AM153" t="inlineStr">
+      <c r="AO153" t="n">
+        <v>740</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>19.801</v>
+      </c>
+      <c r="AQ153" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AN153" t="inlineStr">
+      <c r="AR153" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-07-29/no-name-1753727617.pdf</t>
         </is>
       </c>
-      <c r="AO153" t="inlineStr">
+      <c r="AS153" t="inlineStr">
         <is>
           <t>2026-08-31T10:48:45+07:00</t>
         </is>
@@ -48101,28 +49901,40 @@
         <v>-4.909</v>
       </c>
       <c r="AF154" t="n">
+        <v>-5.454</v>
+      </c>
+      <c r="AG154" t="n">
         <v>9.473000000000001</v>
       </c>
-      <c r="AJ154" t="n">
+      <c r="AH154" t="n">
+        <v>5.934</v>
+      </c>
+      <c r="AL154" t="n">
         <v>-130</v>
       </c>
-      <c r="AK154" t="n">
+      <c r="AM154" t="n">
         <v>-3.276</v>
       </c>
-      <c r="AL154" t="n">
+      <c r="AN154" t="n">
         <v>-0.298</v>
       </c>
-      <c r="AM154" t="inlineStr">
+      <c r="AO154" t="n">
+        <v>-260</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>-6.551</v>
+      </c>
+      <c r="AQ154" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN154" t="inlineStr">
+      <c r="AR154" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-quc-t-vit-nam06082025-000000bo-co-ti-chnh-hp-nht-bn-nin_1_0929.pdf</t>
         </is>
       </c>
-      <c r="AO154" t="inlineStr">
+      <c r="AS154" t="inlineStr">
         <is>
           <t>2026-08-31T12:52:16+07:00</t>
         </is>
@@ -48226,28 +50038,40 @@
         <v>-10.559</v>
       </c>
       <c r="AF155" t="n">
+        <v>-11.541</v>
+      </c>
+      <c r="AG155" t="n">
         <v>3.349</v>
       </c>
-      <c r="AJ155" t="n">
+      <c r="AH155" t="n">
+        <v>3.475</v>
+      </c>
+      <c r="AL155" t="n">
         <v>-391</v>
       </c>
-      <c r="AK155" t="n">
+      <c r="AM155" t="n">
         <v>-9.369999999999999</v>
       </c>
-      <c r="AL155" t="n">
+      <c r="AN155" t="n">
         <v>-0.864</v>
       </c>
-      <c r="AM155" t="inlineStr">
+      <c r="AO155" t="n">
+        <v>-782</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>-18.741</v>
+      </c>
+      <c r="AQ155" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AN155" t="inlineStr">
+      <c r="AR155" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-10-30/no-name-1761766923.pdf</t>
         </is>
       </c>
-      <c r="AO155" t="inlineStr">
+      <c r="AS155" t="inlineStr">
         <is>
           <t>2026-08-31T16:03:19+07:00</t>
         </is>
@@ -48321,28 +50145,40 @@
         <v>-10.284</v>
       </c>
       <c r="AF156" t="n">
+        <v>-5.045</v>
+      </c>
+      <c r="AG156" t="n">
         <v>4.785</v>
       </c>
-      <c r="AJ156" t="n">
+      <c r="AH156" t="n">
+        <v>3.848</v>
+      </c>
+      <c r="AL156" t="n">
         <v>-278</v>
       </c>
-      <c r="AK156" t="n">
+      <c r="AM156" t="n">
         <v>-6.598</v>
       </c>
-      <c r="AL156" t="n">
+      <c r="AN156" t="n">
         <v>-0.593</v>
       </c>
-      <c r="AM156" t="inlineStr">
+      <c r="AO156" t="n">
+        <v>-556</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>-13.195</v>
+      </c>
+      <c r="AQ156" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AN156" t="inlineStr">
+      <c r="AR156" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260302_-_VIB_-_BCTC_hop_nhat_kiem_toan_2025_1772443477.pdf</t>
         </is>
       </c>
-      <c r="AO156" t="inlineStr">
+      <c r="AS156" t="inlineStr">
         <is>
           <t>2026-08-31T01:52:28+07:00</t>
         </is>
@@ -48446,28 +50282,40 @@
         <v>2.896</v>
       </c>
       <c r="AF157" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="AG157" t="n">
         <v>5.638</v>
       </c>
-      <c r="AJ157" t="n">
+      <c r="AH157" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AL157" t="n">
         <v>54</v>
       </c>
-      <c r="AK157" t="n">
+      <c r="AM157" t="n">
         <v>1.337</v>
       </c>
-      <c r="AL157" t="n">
+      <c r="AN157" t="n">
         <v>0.11</v>
       </c>
-      <c r="AM157" t="inlineStr">
+      <c r="AO157" t="n">
+        <v>108</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>2.674</v>
+      </c>
+      <c r="AQ157" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AN157" t="inlineStr">
+      <c r="AR157" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-30/no-name-1777489917.pdf</t>
         </is>
       </c>
-      <c r="AO157" t="inlineStr">
+      <c r="AS157" t="inlineStr">
         <is>
           <t>2026-09-01T00:07:17+07:00</t>
         </is>
@@ -48541,28 +50389,40 @@
         <v>-1.409</v>
       </c>
       <c r="AF158" t="n">
+        <v>-2.086</v>
+      </c>
+      <c r="AG158" t="n">
         <v>7.638</v>
       </c>
-      <c r="AJ158" t="n">
+      <c r="AH158" t="n">
+        <v>4.335</v>
+      </c>
+      <c r="AL158" t="n">
         <v>-1</v>
       </c>
-      <c r="AK158" t="n">
+      <c r="AM158" t="n">
         <v>-0.023</v>
       </c>
-      <c r="AL158" t="n">
+      <c r="AN158" t="n">
         <v>-0.002</v>
       </c>
-      <c r="AM158" t="inlineStr">
+      <c r="AO158" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="AQ158" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AN158" t="inlineStr">
+      <c r="AR158" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VIB_202608062020VIB2020BCTC20hop20nhat20soat20xet20ban20nien202026_12082026154930.pdf?v=1786524571501</t>
         </is>
       </c>
-      <c r="AO158" t="inlineStr">
+      <c r="AS158" t="inlineStr">
         <is>
           <t>2026-09-01T10:23:21+07:00</t>
         </is>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -30461,7 +30461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS158"/>
+  <dimension ref="A1:BF158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30509,6 +30509,19 @@
     <col width="16" customWidth="1" min="43" max="43"/>
     <col width="16" customWidth="1" min="44" max="44"/>
     <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
+    <col width="16" customWidth="1" min="47" max="47"/>
+    <col width="16" customWidth="1" min="48" max="48"/>
+    <col width="16" customWidth="1" min="49" max="49"/>
+    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="16" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="16" customWidth="1" min="53" max="53"/>
+    <col width="16" customWidth="1" min="54" max="54"/>
+    <col width="16" customWidth="1" min="55" max="55"/>
+    <col width="16" customWidth="1" min="56" max="56"/>
+    <col width="16" customWidth="1" min="57" max="57"/>
+    <col width="16" customWidth="1" min="58" max="58"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30724,15 +30737,80 @@
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
+          <t>FX Assets (ty)</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>FX Liabilities (ty)</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>FX Gap noi bang (ty)</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>FX Trang thai ngoai bang (ty)</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>FX Net Position (ty)</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>FX Positive Position (ty)</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>FX Negative Position (ty)</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>FX Net/FX Assets (%)</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>FX Net/TTS (%)</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>FX Positive/VCSH (%)</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>FX Negative/VCSH (%)</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>FX Dong tien chinh</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>FX Shock +-10% (ty)</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
           <t>Nguon (tieu de)</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Nguon (url)</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Cap nhat luc</t>
         </is>
@@ -30829,17 +30907,17 @@
       <c r="AP2" t="n">
         <v>47.112</v>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-an-bnh29042025-000000bo-co-ti-chnh-qu-1-2025.pdf</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>2026-08-31T09:54:52+07:00</t>
         </is>
@@ -30936,17 +31014,17 @@
       <c r="AP3" t="n">
         <v>0</v>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00012345679012345679ngn-hng-tmcp-an-bnh04092025-000000bo-co-ti-chnh-bn-nin-2025_1_0945.pdf</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2026-08-31T11:41:33+07:00</t>
         </is>
@@ -31073,17 +31151,17 @@
       <c r="AP4" t="n">
         <v>19.692</v>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_586159_Bao_cao_tai_chinh_quy_32025_1762168308.pdf</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>2026-08-31T15:10:19+07:00</t>
         </is>
@@ -31180,17 +31258,17 @@
       <c r="AP5" t="n">
         <v>14.512</v>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604250_Bao_cao_tai_chinh_nam_2025_1775705238.pdf</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>2026-08-31T01:05:32+07:00</t>
         </is>
@@ -31317,17 +31395,17 @@
       <c r="AP6" t="n">
         <v>-23.106</v>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-05-09/no-name-1778265007.pdf</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>2026-08-31T23:10:58+07:00</t>
         </is>
@@ -31424,17 +31502,17 @@
       <c r="AP7" t="n">
         <v>42.487</v>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ABB_000000016745964_BCTC_BAN_NIEN_2026_KTSXcompressed_25082026154210.pdf?v=1787647332246</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>2026-09-01T09:31:33+07:00</t>
         </is>
@@ -31561,17 +31639,17 @@
       <c r="AP8" t="n">
         <v>44.631</v>
       </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_Baocaotaichinh_Q1_2025_Hopnhat_13052025091456.pdf</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>2026-08-31T09:55:57+07:00</t>
         </is>
@@ -31698,17 +31776,17 @@
       <c r="AP9" t="n">
         <v>38.541</v>
       </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_19092025164217.pdf</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>2026-08-31T11:43:25+07:00</t>
         </is>
@@ -31835,17 +31913,17 @@
       <c r="AP10" t="n">
         <v>0</v>
       </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251022_-_ACB_-_BCTC_hop_nhat_Quy_03_nam_2025_1761122352.pdf</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>2026-08-31T15:12:08+07:00</t>
         </is>
@@ -31981,17 +32059,17 @@
       <c r="AP11" t="n">
         <v>36.372</v>
       </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-1/2026-03-07/no-name-1772854112.pdf</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>2026-09-17T14:57:20+07:00</t>
         </is>
@@ -32115,17 +32193,17 @@
       <c r="AP12" t="n">
         <v>0</v>
       </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260422_-_ACB_-_BCTC_Hop_nhat_Quy_1_nam_2026_1776932823.pdf</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>2026-09-17T15:01:42+07:00</t>
         </is>
@@ -32252,17 +32330,17 @@
       <c r="AP13" t="n">
         <v>10.251</v>
       </c>
-      <c r="AQ13" t="inlineStr">
+      <c r="BD13" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
+      <c r="BE13" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/ACB_202608142020ACB2020BCTC20hop20nhat20ban20nien202026_20082026094407.pdf?v=1787193848805</t>
         </is>
       </c>
-      <c r="AS13" t="inlineStr">
+      <c r="BF13" t="inlineStr">
         <is>
           <t>2026-09-01T09:32:55+07:00</t>
         </is>
@@ -32389,17 +32467,17 @@
       <c r="AP14" t="n">
         <v>62.702</v>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="BD14" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="BE14" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BAB_25Q1_BCTC_HN_07052025141647.pdf</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr">
+      <c r="BF14" t="inlineStr">
         <is>
           <t>2026-08-31T09:57:27+07:00</t>
         </is>
@@ -32526,17 +32604,17 @@
       <c r="AP15" t="n">
         <v>67.92</v>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="BD15" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
+      <c r="BE15" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-bc-30072025-000000bo-co-ti-chnh-qu-2-2025_3_0910.pdf</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>2026-08-31T11:44:48+07:00</t>
         </is>
@@ -32633,17 +32711,17 @@
       <c r="AP16" t="n">
         <v>104.363</v>
       </c>
-      <c r="AQ16" t="inlineStr">
+      <c r="BD16" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
+      <c r="BE16" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_586650_Bao_cao_tai_chinh_quy_32025_1763615639.pdf</t>
         </is>
       </c>
-      <c r="AS16" t="inlineStr">
+      <c r="BF16" t="inlineStr">
         <is>
           <t>2026-08-31T15:13:52+07:00</t>
         </is>
@@ -32761,17 +32839,17 @@
       <c r="AP17" t="n">
         <v>0</v>
       </c>
-      <c r="AQ17" t="inlineStr">
+      <c r="BD17" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
+      <c r="BE17" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604687_Bao_cao_tai_chinh_nam_2025_1774883201.pdf</t>
         </is>
       </c>
-      <c r="AS17" t="inlineStr">
+      <c r="BF17" t="inlineStr">
         <is>
           <t>2026-08-31T01:08:17+07:00</t>
         </is>
@@ -32868,17 +32946,17 @@
       <c r="AP18" t="n">
         <v>74.703</v>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="BD18" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
+      <c r="BE18" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_612759_Bao_cao_tai_chinh_quy_12026_1777886654.pdf</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
+      <c r="BF18" t="inlineStr">
         <is>
           <t>2026-08-31T23:16:58+07:00</t>
         </is>
@@ -33005,17 +33083,17 @@
       <c r="AP19" t="n">
         <v>67.673</v>
       </c>
-      <c r="AQ19" t="inlineStr">
+      <c r="BD19" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
+      <c r="BE19" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BAB_000000016757863_VI_BaoCaoTaiChinh_SoatXet_BanNien2026_18082026093732.pdf?v=1787020653929</t>
         </is>
       </c>
-      <c r="AS19" t="inlineStr">
+      <c r="BF19" t="inlineStr">
         <is>
           <t>2026-09-01T09:34:31+07:00</t>
         </is>
@@ -33151,12 +33229,12 @@
       <c r="AP20" t="n">
         <v>-13.424</v>
       </c>
-      <c r="AQ20" t="inlineStr">
+      <c r="BD20" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (BID BCTC hop nhat GND Quy I 2025, OCR khong doc duoc)</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
+      <c r="BF20" t="inlineStr">
         <is>
           <t>2026-09-17T14:38:33+07:00</t>
         </is>
@@ -33262,17 +33340,17 @@
       <c r="AP21" t="n">
         <v>-54.617</v>
       </c>
-      <c r="AQ21" t="inlineStr">
+      <c r="BD21" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
+      <c r="BE21" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BID_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025143111.pdf</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
+      <c r="BF21" t="inlineStr">
         <is>
           <t>2026-09-17T15:06:22+07:00</t>
         </is>
@@ -33402,17 +33480,17 @@
       <c r="AP22" t="n">
         <v>57.169</v>
       </c>
-      <c r="AQ22" t="inlineStr">
+      <c r="BD22" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
+      <c r="BE22" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_BID_-_CBTT_BCTC_HN_giua_nien_do_QIII_1761898492.pdf</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
+      <c r="BF22" t="inlineStr">
         <is>
           <t>2026-09-18T08:44:10+07:00</t>
         </is>
@@ -33548,17 +33626,17 @@
       <c r="AP23" t="n">
         <v>1.314</v>
       </c>
-      <c r="AQ23" t="inlineStr">
+      <c r="BD23" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
+      <c r="BE23" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-02/no-name-1775069592.pdf</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="BF23" t="inlineStr">
         <is>
           <t>2026-09-17T18:18:58+07:00</t>
         </is>
@@ -33655,17 +33733,17 @@
       <c r="AP24" t="n">
         <v>-9.584</v>
       </c>
-      <c r="AQ24" t="inlineStr">
+      <c r="BD24" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
+      <c r="BE24" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260424_-_BID_-_CBTT_BCTC_HN_giua_nien_do_Q1_1777032270.pdf</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="BF24" t="inlineStr">
         <is>
           <t>2026-08-31T23:18:24+07:00</t>
         </is>
@@ -33792,17 +33870,17 @@
       <c r="AP25" t="n">
         <v>22.321</v>
       </c>
-      <c r="AQ25" t="inlineStr">
+      <c r="BD25" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR25" t="inlineStr">
+      <c r="BE25" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BID_202608182020BID2020CBTT20BCTC20HN20ban20nien20da20duoc20soat20xet_20082026090048.pdf?v=1787191250249</t>
         </is>
       </c>
-      <c r="AS25" t="inlineStr">
+      <c r="BF25" t="inlineStr">
         <is>
           <t>2026-09-01T09:36:26+07:00</t>
         </is>
@@ -33899,17 +33977,17 @@
       <c r="AP26" t="n">
         <v>26.546</v>
       </c>
-      <c r="AQ26" t="inlineStr">
+      <c r="BD26" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
+      <c r="BE26" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-29/no-name-1745876078.pdf</t>
         </is>
       </c>
-      <c r="AS26" t="inlineStr">
+      <c r="BF26" t="inlineStr">
         <is>
           <t>2026-08-31T10:02:43+07:00</t>
         </is>
@@ -34006,17 +34084,17 @@
       <c r="AP27" t="n">
         <v>-8.698</v>
       </c>
-      <c r="AQ27" t="inlineStr">
+      <c r="BD27" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
+      <c r="BE27" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-bn-vit15082025-000000bo-co-ti-chnh-bn-nin-2025_5_1133.pdf</t>
         </is>
       </c>
-      <c r="AS27" t="inlineStr">
+      <c r="BF27" t="inlineStr">
         <is>
           <t>2026-08-31T11:53:16+07:00</t>
         </is>
@@ -34143,17 +34221,17 @@
       <c r="AP28" t="n">
         <v>-5.581</v>
       </c>
-      <c r="AQ28" t="inlineStr">
+      <c r="BD28" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR28" t="inlineStr">
+      <c r="BE28" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_585337_Bao_cao_tai_chinh_quy_32025_1761821099.pdf</t>
         </is>
       </c>
-      <c r="AS28" t="inlineStr">
+      <c r="BF28" t="inlineStr">
         <is>
           <t>2026-08-31T15:17:24+07:00</t>
         </is>
@@ -34280,17 +34358,17 @@
       <c r="AP29" t="n">
         <v>0</v>
       </c>
-      <c r="AQ29" t="inlineStr">
+      <c r="BD29" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR29" t="inlineStr">
+      <c r="BE29" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603502_Bao_cao_tai_chinh_nam_2025_1776046380.pdf</t>
         </is>
       </c>
-      <c r="AS29" t="inlineStr">
+      <c r="BF29" t="inlineStr">
         <is>
           <t>2026-08-31T01:11:30+07:00</t>
         </is>
@@ -34414,17 +34492,17 @@
       <c r="AP30" t="n">
         <v>0</v>
       </c>
-      <c r="AQ30" t="inlineStr">
+      <c r="BD30" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR30" t="inlineStr">
+      <c r="BE30" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_612193_Bao_cao_tai_chinh_quy_12026_1777459426.pdf</t>
         </is>
       </c>
-      <c r="AS30" t="inlineStr">
+      <c r="BF30" t="inlineStr">
         <is>
           <t>2026-08-31T23:20:32+07:00</t>
         </is>
@@ -34551,17 +34629,17 @@
       <c r="AP31" t="n">
         <v>5.809</v>
       </c>
-      <c r="AQ31" t="inlineStr">
+      <c r="BD31" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR31" t="inlineStr">
+      <c r="BE31" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/BVB_202608132020BVB2020Bao20cao20tai20chinh20hop20nhat20ban20nien20202620da20soat20xet20kem20giai20trinh20bien20dong20loi20nhuan_20082026095227.pdf?v=1787194349784</t>
         </is>
       </c>
-      <c r="AS31" t="inlineStr">
+      <c r="BF31" t="inlineStr">
         <is>
           <t>2026-09-01T09:38:24+07:00</t>
         </is>
@@ -34688,17 +34766,17 @@
       <c r="AP32" t="n">
         <v>0</v>
       </c>
-      <c r="AQ32" t="inlineStr">
+      <c r="BD32" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR32" t="inlineStr">
+      <c r="BE32" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_Baocaotaichinh_Q1_2025_Hopnhat_23052025140616.pdf</t>
         </is>
       </c>
-      <c r="AS32" t="inlineStr">
+      <c r="BF32" t="inlineStr">
         <is>
           <t>2026-08-31T10:05:00+07:00</t>
         </is>
@@ -34825,17 +34903,17 @@
       <c r="AP33" t="n">
         <v>-6.35</v>
       </c>
-      <c r="AQ33" t="inlineStr">
+      <c r="BD33" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR33" t="inlineStr">
+      <c r="BE33" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025145719.pdf</t>
         </is>
       </c>
-      <c r="AS33" t="inlineStr">
+      <c r="BF33" t="inlineStr">
         <is>
           <t>2026-08-31T11:55:46+07:00</t>
         </is>
@@ -34962,17 +35040,17 @@
       <c r="AP34" t="n">
         <v>0</v>
       </c>
-      <c r="AQ34" t="inlineStr">
+      <c r="BD34" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR34" t="inlineStr">
+      <c r="BE34" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_CTG_-_BCTC_hop_nhat_Quy_3.2025_va_giai_trinh_bien_dong_loi_nhuan_signed_1761877722.pdf</t>
         </is>
       </c>
-      <c r="AS34" t="inlineStr">
+      <c r="BF34" t="inlineStr">
         <is>
           <t>2026-08-31T15:19:45+07:00</t>
         </is>
@@ -35099,17 +35177,17 @@
       <c r="AP35" t="n">
         <v>-5.601</v>
       </c>
-      <c r="AQ35" t="inlineStr">
+      <c r="BD35" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR35" t="inlineStr">
+      <c r="BE35" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_HK_20260331_-_CTG_-_BCTC_hop_nhat_kiem_toan_nam_2025__18062026104622.pdf</t>
         </is>
       </c>
-      <c r="AS35" t="inlineStr">
+      <c r="BF35" t="inlineStr">
         <is>
           <t>2026-08-31T01:14:15+07:00</t>
         </is>
@@ -35236,17 +35314,17 @@
       <c r="AP36" t="n">
         <v>5.912</v>
       </c>
-      <c r="AQ36" t="inlineStr">
+      <c r="BD36" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR36" t="inlineStr">
+      <c r="BE36" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260428__CTG__BCTC_hop_nhat_Quy_I_13082026151826.2026_va_giai_trinh_bien_dong_loi_nhuan_signed_1777430252?v=1786609107953</t>
         </is>
       </c>
-      <c r="AS36" t="inlineStr">
+      <c r="BF36" t="inlineStr">
         <is>
           <t>2026-08-31T23:22:42+07:00</t>
         </is>
@@ -35343,17 +35421,17 @@
       <c r="AP37" t="n">
         <v>35.793</v>
       </c>
-      <c r="AQ37" t="inlineStr">
+      <c r="BD37" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR37" t="inlineStr">
+      <c r="BE37" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/CTG_202608142020CTG2020BCTC20hop20nhat206T202620da20soat20xet20va20giai20trinh20bien20dong20loi20nhuan_signed_19082026145907.pdf?v=1787126349271</t>
         </is>
       </c>
-      <c r="AS37" t="inlineStr">
+      <c r="BF37" t="inlineStr">
         <is>
           <t>2026-09-01T09:40:13+07:00</t>
         </is>
@@ -35480,17 +35558,17 @@
       <c r="AP38" t="n">
         <v>-28.795</v>
       </c>
-      <c r="AQ38" t="inlineStr">
+      <c r="BD38" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR38" t="inlineStr">
+      <c r="BE38" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_Baocaotaichinh_Q1_2025_Hopnhat_22052025162515.pdf</t>
         </is>
       </c>
-      <c r="AS38" t="inlineStr">
+      <c r="BF38" t="inlineStr">
         <is>
           <t>2026-08-31T10:06:41+07:00</t>
         </is>
@@ -35608,17 +35686,17 @@
       <c r="AP39" t="n">
         <v>0</v>
       </c>
-      <c r="AQ39" t="inlineStr">
+      <c r="BD39" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR39" t="inlineStr">
+      <c r="BE39" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025085527.pdf</t>
         </is>
       </c>
-      <c r="AS39" t="inlineStr">
+      <c r="BF39" t="inlineStr">
         <is>
           <t>2026-08-31T11:57:38+07:00</t>
         </is>
@@ -35715,17 +35793,17 @@
       <c r="AP40" t="n">
         <v>-12.014</v>
       </c>
-      <c r="AQ40" t="inlineStr">
+      <c r="BD40" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR40" t="inlineStr">
+      <c r="BE40" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_EIB_-_BCTC_hop_nhat_Q3.2025_1761868313.pdf</t>
         </is>
       </c>
-      <c r="AS40" t="inlineStr">
+      <c r="BF40" t="inlineStr">
         <is>
           <t>2026-08-31T15:21:25+07:00</t>
         </is>
@@ -35840,17 +35918,17 @@
       <c r="AP41" t="n">
         <v>0</v>
       </c>
-      <c r="AQ41" t="inlineStr">
+      <c r="BD41" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR41" t="inlineStr">
+      <c r="BE41" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_EIB_-_BCTC_hop_nhat_nam_2025_da_kiem_toan_1774925122.pdf</t>
         </is>
       </c>
-      <c r="AS41" t="inlineStr">
+      <c r="BF41" t="inlineStr">
         <is>
           <t>2026-08-31T01:16:37+07:00</t>
         </is>
@@ -35977,17 +36055,17 @@
       <c r="AP42" t="n">
         <v>-14.203</v>
       </c>
-      <c r="AQ42" t="inlineStr">
+      <c r="BD42" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR42" t="inlineStr">
+      <c r="BE42" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260428_-_EIB_-_BCTC_hop_nhat_Q1.2026_1777374020.pdf</t>
         </is>
       </c>
-      <c r="AS42" t="inlineStr">
+      <c r="BF42" t="inlineStr">
         <is>
           <t>2026-08-31T23:24:51+07:00</t>
         </is>
@@ -36102,17 +36180,17 @@
       <c r="AP43" t="n">
         <v>0</v>
       </c>
-      <c r="AQ43" t="inlineStr">
+      <c r="BD43" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR43" t="inlineStr">
+      <c r="BE43" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/EIB_202608142020EIB2020BCTC20hop20nhat20ban20nien20202620da20soat20xet_20082026091803.pdf?v=1787192285257</t>
         </is>
       </c>
-      <c r="AS43" t="inlineStr">
+      <c r="BF43" t="inlineStr">
         <is>
           <t>2026-09-01T09:42:10+07:00</t>
         </is>
@@ -36239,17 +36317,17 @@
       <c r="AP44" t="n">
         <v>4.185</v>
       </c>
-      <c r="AQ44" t="inlineStr">
+      <c r="BD44" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR44" t="inlineStr">
+      <c r="BE44" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/HDB_23052025143646.pdf</t>
         </is>
       </c>
-      <c r="AS44" t="inlineStr">
+      <c r="BF44" t="inlineStr">
         <is>
           <t>2026-08-31T16:53:47+07:00</t>
         </is>
@@ -36373,17 +36451,17 @@
       <c r="AP45" t="n">
         <v>17.741</v>
       </c>
-      <c r="AQ45" t="inlineStr">
+      <c r="BD45" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR45" t="inlineStr">
+      <c r="BE45" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/HDB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_03102025151254.pdf</t>
         </is>
       </c>
-      <c r="AS45" t="inlineStr">
+      <c r="BF45" t="inlineStr">
         <is>
           <t>2026-09-17T16:27:10+07:00</t>
         </is>
@@ -36480,17 +36558,17 @@
       <c r="AP46" t="n">
         <v>0</v>
       </c>
-      <c r="AQ46" t="inlineStr">
+      <c r="BD46" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR46" t="inlineStr">
+      <c r="BE46" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_HDB_-_BCTC_hop_nhat_Quy_3_nam_2025_1761869961.pdf</t>
         </is>
       </c>
-      <c r="AS46" t="inlineStr">
+      <c r="BF46" t="inlineStr">
         <is>
           <t>2026-09-17T17:31:12+07:00</t>
         </is>
@@ -36626,17 +36704,17 @@
       <c r="AP47" t="n">
         <v>13.428</v>
       </c>
-      <c r="AQ47" t="inlineStr">
+      <c r="BD47" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR47" t="inlineStr">
+      <c r="BE47" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_HDB_-_BCTC_kiem_toan_hop_nhat_nam_2025_giai_trinh_1775008453.pdf</t>
         </is>
       </c>
-      <c r="AS47" t="inlineStr">
+      <c r="BF47" t="inlineStr">
         <is>
           <t>2026-09-17T18:20:09+07:00</t>
         </is>
@@ -36763,17 +36841,17 @@
       <c r="AP48" t="n">
         <v>3.371</v>
       </c>
-      <c r="AQ48" t="inlineStr">
+      <c r="BD48" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR48" t="inlineStr">
+      <c r="BE48" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_HDB_-_BCTC_hop_nhat_Quy_1.2026_giai_trinh_1777456090.pdf</t>
         </is>
       </c>
-      <c r="AS48" t="inlineStr">
+      <c r="BF48" t="inlineStr">
         <is>
           <t>2026-08-31T23:26:12+07:00</t>
         </is>
@@ -36870,17 +36948,17 @@
       <c r="AP49" t="n">
         <v>4.971</v>
       </c>
-      <c r="AQ49" t="inlineStr">
+      <c r="BD49" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026</t>
         </is>
       </c>
-      <c r="AR49" t="inlineStr">
+      <c r="BE49" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/HDB_202607302020HDB2020BCTC20hop20nhat20Quy20220262020giai20trinh_31072026142623.pdf?v=1785482784813</t>
         </is>
       </c>
-      <c r="AS49" t="inlineStr">
+      <c r="BF49" t="inlineStr">
         <is>
           <t>2026-09-01T09:45:14+07:00</t>
         </is>
@@ -37007,17 +37085,17 @@
       <c r="AP50" t="n">
         <v>0</v>
       </c>
-      <c r="AQ50" t="inlineStr">
+      <c r="BD50" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR50" t="inlineStr">
+      <c r="BE50" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014864567_VI_BAO_CAO_TAI_CHINH_QUY_I_06052025105844.2025_HOP_NHAT</t>
         </is>
       </c>
-      <c r="AS50" t="inlineStr">
+      <c r="BF50" t="inlineStr">
         <is>
           <t>2026-08-31T10:10:19+07:00</t>
         </is>
@@ -37144,17 +37222,17 @@
       <c r="AP51" t="n">
         <v>0</v>
       </c>
-      <c r="AQ51" t="inlineStr">
+      <c r="BD51" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR51" t="inlineStr">
+      <c r="BE51" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-kin-long28082025-000000bo-co-ti-chnh-bn-nin-2025_1_0929.pdf</t>
         </is>
       </c>
-      <c r="AS51" t="inlineStr">
+      <c r="BF51" t="inlineStr">
         <is>
           <t>2026-08-31T12:03:05+07:00</t>
         </is>
@@ -37281,17 +37359,17 @@
       <c r="AP52" t="n">
         <v>-42.337</v>
       </c>
-      <c r="AQ52" t="inlineStr">
+      <c r="BD52" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR52" t="inlineStr">
+      <c r="BE52" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_583984_Bao_cao_tai_chinh_quy_32025_1762414456.pdf</t>
         </is>
       </c>
-      <c r="AS52" t="inlineStr">
+      <c r="BF52" t="inlineStr">
         <is>
           <t>2026-08-31T15:24:26+07:00</t>
         </is>
@@ -37418,17 +37496,17 @@
       <c r="AP53" t="n">
         <v>0</v>
       </c>
-      <c r="AQ53" t="inlineStr">
+      <c r="BD53" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
+      <c r="BE53" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_KLB_-_BCTC_KiemToan_2025_Hop_nhat_1774928715.pdf</t>
         </is>
       </c>
-      <c r="AS53" t="inlineStr">
+      <c r="BF53" t="inlineStr">
         <is>
           <t>2026-08-31T01:20:50+07:00</t>
         </is>
@@ -37555,17 +37633,17 @@
       <c r="AP54" t="n">
         <v>0</v>
       </c>
-      <c r="AQ54" t="inlineStr">
+      <c r="BD54" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
+      <c r="BE54" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260422_-_KLB_-_BCTC_hop_nhat_Quy_1_2026_1776912173.pdf</t>
         </is>
       </c>
-      <c r="AS54" t="inlineStr">
+      <c r="BF54" t="inlineStr">
         <is>
           <t>2026-08-31T23:28:02+07:00</t>
         </is>
@@ -37692,17 +37770,17 @@
       <c r="AP55" t="n">
         <v>7.349</v>
       </c>
-      <c r="AQ55" t="inlineStr">
+      <c r="BD55" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
+      <c r="BE55" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/KLB_202607222020KLB2020BCTC20hop20nhat20Quy202202026_23072026102613.pdf?v=1784777175496</t>
         </is>
       </c>
-      <c r="AS55" t="inlineStr">
+      <c r="BF55" t="inlineStr">
         <is>
           <t>2026-09-01T09:46:18+07:00</t>
         </is>
@@ -37826,17 +37904,17 @@
       <c r="AP56" t="n">
         <v>0</v>
       </c>
-      <c r="AQ56" t="inlineStr">
+      <c r="BD56" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
+      <c r="BE56" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-07-22/no-name-1753123076.pdf</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr">
+      <c r="BF56" t="inlineStr">
         <is>
           <t>2026-08-31T16:55:44+07:00</t>
         </is>
@@ -37972,17 +38050,17 @@
       <c r="AP57" t="n">
         <v>-3.159</v>
       </c>
-      <c r="AQ57" t="inlineStr">
+      <c r="BD57" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
+      <c r="BE57" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/LPB_Baocaotaichinh_6T_2025_Soatxet_06102025090900.pdf</t>
         </is>
       </c>
-      <c r="AS57" t="inlineStr">
+      <c r="BF57" t="inlineStr">
         <is>
           <t>2026-09-17T16:28:03+07:00</t>
         </is>
@@ -38079,17 +38157,17 @@
       <c r="AP58" t="n">
         <v>4.203</v>
       </c>
-      <c r="AQ58" t="inlineStr">
+      <c r="BD58" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR58" t="inlineStr">
+      <c r="BE58" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251020_-_LPB_-_VI_BaoCaoTaiChinh_Q3_2025_1761124735.pdf</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr">
+      <c r="BF58" t="inlineStr">
         <is>
           <t>2026-08-31T15:27:56+07:00</t>
         </is>
@@ -38225,17 +38303,17 @@
       <c r="AP59" t="n">
         <v>35.722</v>
       </c>
-      <c r="AQ59" t="inlineStr">
+      <c r="BD59" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
-      <c r="AR59" t="inlineStr">
+      <c r="BE59" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-01/no-name-1774985279.pdf</t>
         </is>
       </c>
-      <c r="AS59" t="inlineStr">
+      <c r="BF59" t="inlineStr">
         <is>
           <t>2026-09-17T18:21:20+07:00</t>
         </is>
@@ -38362,17 +38440,17 @@
       <c r="AP60" t="n">
         <v>0</v>
       </c>
-      <c r="AQ60" t="inlineStr">
+      <c r="BD60" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
+      <c r="BE60" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-22/no-name-1776797412.pdf</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
+      <c r="BF60" t="inlineStr">
         <is>
           <t>2026-09-17T19:14:13+07:00</t>
         </is>
@@ -38499,17 +38577,17 @@
       <c r="AP61" t="n">
         <v>1.955</v>
       </c>
-      <c r="AQ61" t="inlineStr">
+      <c r="BD61" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
+      <c r="BE61" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/LPB_202608142020LPB2020Bao20cao20tai20chinh20ban20nien20nam20202620CA_19082026155038.pdf?v=1787129440187</t>
         </is>
       </c>
-      <c r="AS61" t="inlineStr">
+      <c r="BF61" t="inlineStr">
         <is>
           <t>2026-09-01T09:48:15+07:00</t>
         </is>
@@ -38636,17 +38714,17 @@
       <c r="AP62" t="n">
         <v>1.112</v>
       </c>
-      <c r="AQ62" t="inlineStr">
+      <c r="BD62" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR62" t="inlineStr">
+      <c r="BE62" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00012345679012345679ngn-hng-tmcp-qun-i24042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AS62" t="inlineStr">
+      <c r="BF62" t="inlineStr">
         <is>
           <t>2026-08-31T10:15:17+07:00</t>
         </is>
@@ -38743,17 +38821,17 @@
       <c r="AP63" t="n">
         <v>-0.436</v>
       </c>
-      <c r="AQ63" t="inlineStr">
+      <c r="BD63" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR63" t="inlineStr">
+      <c r="BE63" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025091521.pdf</t>
         </is>
       </c>
-      <c r="AS63" t="inlineStr">
+      <c r="BF63" t="inlineStr">
         <is>
           <t>2026-08-31T12:10:05+07:00</t>
         </is>
@@ -38880,17 +38958,17 @@
       <c r="AP64" t="n">
         <v>4.018</v>
       </c>
-      <c r="AQ64" t="inlineStr">
+      <c r="BD64" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR64" t="inlineStr">
+      <c r="BE64" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251026_-_MBB_-_BCTC_Hop_nhat_Q3.2025_viet_1761554111.pdf</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr">
+      <c r="BF64" t="inlineStr">
         <is>
           <t>2026-08-31T15:29:37+07:00</t>
         </is>
@@ -39017,17 +39095,17 @@
       <c r="AP65" t="n">
         <v>-20.694</v>
       </c>
-      <c r="AQ65" t="inlineStr">
+      <c r="BD65" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR65" t="inlineStr">
+      <c r="BE65" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_Baocaotaichinh_2025_Kiemtoan_Hopnhat_1780022210.pdf</t>
         </is>
       </c>
-      <c r="AS65" t="inlineStr">
+      <c r="BF65" t="inlineStr">
         <is>
           <t>2026-08-31T01:24:23+07:00</t>
         </is>
@@ -39154,17 +39232,17 @@
       <c r="AP66" t="n">
         <v>5.566</v>
       </c>
-      <c r="AQ66" t="inlineStr">
+      <c r="BD66" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
+      <c r="BE66" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260428_-_MBB_-_BCTC_Hop_nhat_Q1.2026_1777374472.pdf</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr">
+      <c r="BF66" t="inlineStr">
         <is>
           <t>2026-08-31T23:34:51+07:00</t>
         </is>
@@ -39261,17 +39339,17 @@
       <c r="AP67" t="n">
         <v>20.789</v>
       </c>
-      <c r="AQ67" t="inlineStr">
+      <c r="BD67" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
+      <c r="BE67" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MBB_202608062020MBB2020BCTC20hop20nhat20soat20xet20ban20nien202026_10082026095318.pdf?v=1786330399877</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
+      <c r="BF67" t="inlineStr">
         <is>
           <t>2026-09-01T09:50:15+07:00</t>
         </is>
@@ -39398,17 +39476,17 @@
       <c r="AP68" t="n">
         <v>-20.529</v>
       </c>
-      <c r="AQ68" t="inlineStr">
+      <c r="BD68" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR68" t="inlineStr">
+      <c r="BE68" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-hng-hi-vit-nam28042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AS68" t="inlineStr">
+      <c r="BF68" t="inlineStr">
         <is>
           <t>2026-08-31T10:17:02+07:00</t>
         </is>
@@ -39535,17 +39613,17 @@
       <c r="AP69" t="n">
         <v>59.888</v>
       </c>
-      <c r="AQ69" t="inlineStr">
+      <c r="BD69" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
+      <c r="BE69" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025092910.pdf</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
+      <c r="BF69" t="inlineStr">
         <is>
           <t>2026-08-31T12:12:00+07:00</t>
         </is>
@@ -39666,17 +39744,17 @@
       <c r="AP70" t="n">
         <v>76.581</v>
       </c>
-      <c r="AQ70" t="inlineStr">
+      <c r="BD70" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
+      <c r="BE70" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251029_-_MSB_-_CBTT_Bao_cao_tai_chinh_Hop_nhat_Q3.2025_signed_1761876687.pdf</t>
         </is>
       </c>
-      <c r="AS70" t="inlineStr">
+      <c r="BF70" t="inlineStr">
         <is>
           <t>2026-08-31T15:31:21+07:00</t>
         </is>
@@ -39803,17 +39881,17 @@
       <c r="AP71" t="n">
         <v>-21.685</v>
       </c>
-      <c r="AQ71" t="inlineStr">
+      <c r="BD71" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR71" t="inlineStr">
+      <c r="BE71" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_HK_20260330_-_MSB_-_BCTC_hop_nhat_kiem_toan_nam_2025__18062026110209.pdf</t>
         </is>
       </c>
-      <c r="AS71" t="inlineStr">
+      <c r="BF71" t="inlineStr">
         <is>
           <t>2026-08-31T01:26:11+07:00</t>
         </is>
@@ -39910,17 +39988,17 @@
       <c r="AP72" t="n">
         <v>-33.276</v>
       </c>
-      <c r="AQ72" t="inlineStr">
+      <c r="BD72" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR72" t="inlineStr">
+      <c r="BE72" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260424_-_MSB_-_Bao_cao_tai_chinh_Hop_nhat_Quy_1_2026_signed_1777023593.pdf</t>
         </is>
       </c>
-      <c r="AS72" t="inlineStr">
+      <c r="BF72" t="inlineStr">
         <is>
           <t>2026-08-31T23:36:48+07:00</t>
         </is>
@@ -40017,17 +40095,17 @@
       <c r="AP73" t="n">
         <v>-0.067</v>
       </c>
-      <c r="AQ73" t="inlineStr">
+      <c r="BD73" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR73" t="inlineStr">
+      <c r="BE73" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/MSB_202608182020MSB2020BCTC20hop20nhat20ban20nien20soat20xet20202620signed_19082026103646.pdf?v=1787110607275</t>
         </is>
       </c>
-      <c r="AS73" t="inlineStr">
+      <c r="BF73" t="inlineStr">
         <is>
           <t>2026-09-01T09:50:54+07:00</t>
         </is>
@@ -40154,17 +40232,17 @@
       <c r="AP74" t="n">
         <v>21.21</v>
       </c>
-      <c r="AQ74" t="inlineStr">
+      <c r="BD74" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR74" t="inlineStr">
+      <c r="BE74" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-nam-28042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AS74" t="inlineStr">
+      <c r="BF74" t="inlineStr">
         <is>
           <t>2026-08-31T10:18:34+07:00</t>
         </is>
@@ -40291,17 +40369,17 @@
       <c r="AP75" t="n">
         <v>13.194</v>
       </c>
-      <c r="AQ75" t="inlineStr">
+      <c r="BD75" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR75" t="inlineStr">
+      <c r="BE75" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025093916.pdf</t>
         </is>
       </c>
-      <c r="AS75" t="inlineStr">
+      <c r="BF75" t="inlineStr">
         <is>
           <t>2026-08-31T12:14:18+07:00</t>
         </is>
@@ -40428,17 +40506,17 @@
       <c r="AP76" t="n">
         <v>1.655</v>
       </c>
-      <c r="AQ76" t="inlineStr">
+      <c r="BD76" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR76" t="inlineStr">
+      <c r="BE76" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251029_-_NAB_-_CBTT_BCTC_Q3.2025_HN_1761877543.pdf</t>
         </is>
       </c>
-      <c r="AS76" t="inlineStr">
+      <c r="BF76" t="inlineStr">
         <is>
           <t>2026-08-31T15:32:56+07:00</t>
         </is>
@@ -40565,17 +40643,17 @@
       <c r="AP77" t="n">
         <v>158.192</v>
       </c>
-      <c r="AQ77" t="inlineStr">
+      <c r="BD77" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR77" t="inlineStr">
+      <c r="BE77" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_Baocaotaichinh_2025_Kiemtoan_Hopnhat_1780023595.pdf</t>
         </is>
       </c>
-      <c r="AS77" t="inlineStr">
+      <c r="BF77" t="inlineStr">
         <is>
           <t>2026-08-31T01:28:37+07:00</t>
         </is>
@@ -40702,17 +40780,17 @@
       <c r="AP78" t="n">
         <v>20.367</v>
       </c>
-      <c r="AQ78" t="inlineStr">
+      <c r="BD78" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR78" t="inlineStr">
+      <c r="BE78" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-05-05/no-name-1777925637.pdf</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr">
+      <c r="BF78" t="inlineStr">
         <is>
           <t>2026-08-31T23:37:58+07:00</t>
         </is>
@@ -40809,17 +40887,17 @@
       <c r="AP79" t="n">
         <v>64.91800000000001</v>
       </c>
-      <c r="AQ79" t="inlineStr">
+      <c r="BD79" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR79" t="inlineStr">
+      <c r="BE79" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NAB_202608082020NAB2020BAN20NIEN20SOAT20XET202026_20HN_12082026154236.pdf?v=1786524157864</t>
         </is>
       </c>
-      <c r="AS79" t="inlineStr">
+      <c r="BF79" t="inlineStr">
         <is>
           <t>2026-09-01T09:53:27+07:00</t>
         </is>
@@ -40946,17 +41024,17 @@
       <c r="AP80" t="n">
         <v>40.407</v>
       </c>
-      <c r="AQ80" t="inlineStr">
+      <c r="BD80" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR80" t="inlineStr">
+      <c r="BE80" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NVB_25Q1_BCTC_HN_09052025064513.pdf</t>
         </is>
       </c>
-      <c r="AS80" t="inlineStr">
+      <c r="BF80" t="inlineStr">
         <is>
           <t>2026-08-31T10:20:53+07:00</t>
         </is>
@@ -41053,17 +41131,17 @@
       <c r="AP81" t="n">
         <v>-84.205</v>
       </c>
-      <c r="AQ81" t="inlineStr">
+      <c r="BD81" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR81" t="inlineStr">
+      <c r="BE81" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00000617283950617284ngn-hng-tmcp-quc-dn27082025-000000bo-co-ti-chnh-bn-nin-2025_1_0915.pdf</t>
         </is>
       </c>
-      <c r="AS81" t="inlineStr">
+      <c r="BF81" t="inlineStr">
         <is>
           <t>2026-08-31T12:16:11+07:00</t>
         </is>
@@ -41184,17 +41262,17 @@
       <c r="AP82" t="n">
         <v>-62.753</v>
       </c>
-      <c r="AQ82" t="inlineStr">
+      <c r="BD82" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR82" t="inlineStr">
+      <c r="BE82" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_585817_Bao_cao_tai_chinh_quy_32025_1761886641.pdf</t>
         </is>
       </c>
-      <c r="AS82" t="inlineStr">
+      <c r="BF82" t="inlineStr">
         <is>
           <t>2026-08-31T15:34:40+07:00</t>
         </is>
@@ -41291,17 +41369,17 @@
       <c r="AP83" t="n">
         <v>321.981</v>
       </c>
-      <c r="AQ83" t="inlineStr">
+      <c r="BD83" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR83" t="inlineStr">
+      <c r="BE83" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604185_Bao_cao_tai_chinh_nam_2025_1774532924.pdf</t>
         </is>
       </c>
-      <c r="AS83" t="inlineStr">
+      <c r="BF83" t="inlineStr">
         <is>
           <t>2026-08-31T01:30:26+07:00</t>
         </is>
@@ -41422,17 +41500,17 @@
       <c r="AP84" t="n">
         <v>-53.027</v>
       </c>
-      <c r="AQ84" t="inlineStr">
+      <c r="BD84" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR84" t="inlineStr">
+      <c r="BE84" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_612736_Bao_cao_tai_chinh_quy_12026_1777882908.pdf</t>
         </is>
       </c>
-      <c r="AS84" t="inlineStr">
+      <c r="BF84" t="inlineStr">
         <is>
           <t>2026-08-31T23:39:44+07:00</t>
         </is>
@@ -41529,17 +41607,17 @@
       <c r="AP85" t="n">
         <v>529.393</v>
       </c>
-      <c r="AQ85" t="inlineStr">
+      <c r="BD85" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR85" t="inlineStr">
+      <c r="BE85" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/NVB_000000016801581_BAO_CAO_TAI_CHINH_HOP_NHAT__TV__SAU_SOAT_XET_BAN_NIEN_2026signed_28082026161720.pdf?v=1787908641915</t>
         </is>
       </c>
-      <c r="AS85" t="inlineStr">
+      <c r="BF85" t="inlineStr">
         <is>
           <t>2026-09-01T09:54:37+07:00</t>
         </is>
@@ -41675,12 +41753,12 @@
       <c r="AP86" t="n">
         <v>3.698</v>
       </c>
-      <c r="AQ86" t="inlineStr">
+      <c r="BD86" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (OCB thuyet minh BCTC hop nhat Quy 1 2025, OCR khong doc duoc - don vi VND thuc, da quy doi ve trieu dong)</t>
         </is>
       </c>
-      <c r="AS86" t="inlineStr">
+      <c r="BF86" t="inlineStr">
         <is>
           <t>2026-09-17T16:12:36+07:00</t>
         </is>
@@ -41816,12 +41894,12 @@
       <c r="AP87" t="n">
         <v>5.415</v>
       </c>
-      <c r="AQ87" t="inlineStr">
+      <c r="BD87" t="inlineStr">
         <is>
           <t>Nhap thu cong tu doc truc tiep BCTC that (OCB thuyet minh BCTC hop nhat Quy 2 2025, ban tieng Anh, don vi VND thuc da quy doi ve trieu dong, OCR khong doc duoc do bao cao tieng Anh)</t>
         </is>
       </c>
-      <c r="AS87" t="inlineStr">
+      <c r="BF87" t="inlineStr">
         <is>
           <t>2026-09-17T16:58:29+07:00</t>
         </is>
@@ -41957,17 +42035,17 @@
       <c r="AP88" t="n">
         <v>-124.989</v>
       </c>
-      <c r="AQ88" t="inlineStr">
+      <c r="BD88" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR88" t="inlineStr">
+      <c r="BE88" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251028_-_OCB_-_BCTC_hop_nhat_Quy_3_2025_1761822426.pdf</t>
         </is>
       </c>
-      <c r="AS88" t="inlineStr">
+      <c r="BF88" t="inlineStr">
         <is>
           <t>2026-09-17T17:33:01+07:00</t>
         </is>
@@ -42103,17 +42181,17 @@
       <c r="AP89" t="n">
         <v>115.232</v>
       </c>
-      <c r="AQ89" t="inlineStr">
+      <c r="BD89" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 4 năm 2025</t>
         </is>
       </c>
-      <c r="AR89" t="inlineStr">
+      <c r="BE89" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260130_-_OCB_-_BCTC_hop_nhat_Quy_4_2025_1770023477.pdf</t>
         </is>
       </c>
-      <c r="AS89" t="inlineStr">
+      <c r="BF89" t="inlineStr">
         <is>
           <t>2026-09-18T08:55:46+07:00</t>
         </is>
@@ -42135,7 +42213,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="AS90" t="inlineStr">
+      <c r="BF90" t="inlineStr">
         <is>
           <t>2026-08-31T01:30:30+07:00</t>
         </is>
@@ -42271,17 +42349,17 @@
       <c r="AP91" t="n">
         <v>0</v>
       </c>
-      <c r="AQ91" t="inlineStr">
+      <c r="BD91" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR91" t="inlineStr">
+      <c r="BE91" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260422_-_OCB_-_BCTC_hop_nhat_Quy_1_2026_1776854955.pdf</t>
         </is>
       </c>
-      <c r="AS91" t="inlineStr">
+      <c r="BF91" t="inlineStr">
         <is>
           <t>2026-09-17T19:15:32+07:00</t>
         </is>
@@ -42408,17 +42486,17 @@
       <c r="AP92" t="n">
         <v>42684136.584</v>
       </c>
-      <c r="AQ92" t="inlineStr">
+      <c r="BD92" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR92" t="inlineStr">
+      <c r="BE92" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/OCB_202608142020OCB2020Bao20cao20tai20chinh20hop20nhat20ban20nien202026_20082026094036.pdf?v=1787193638360</t>
         </is>
       </c>
-      <c r="AS92" t="inlineStr">
+      <c r="BF92" t="inlineStr">
         <is>
           <t>2026-09-01T09:56:57+07:00</t>
         </is>
@@ -42515,17 +42593,17 @@
       <c r="AP93" t="n">
         <v>15.275</v>
       </c>
-      <c r="AQ93" t="inlineStr">
+      <c r="BD93" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR93" t="inlineStr">
+      <c r="BE93" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-2/2025-04-18/no-name-1744937049.pdf</t>
         </is>
       </c>
-      <c r="AS93" t="inlineStr">
+      <c r="BF93" t="inlineStr">
         <is>
           <t>2026-08-31T10:25:19+07:00</t>
         </is>
@@ -42652,17 +42730,17 @@
       <c r="AP94" t="n">
         <v>1.695</v>
       </c>
-      <c r="AQ94" t="inlineStr">
+      <c r="BD94" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 2 năm 2025</t>
         </is>
       </c>
-      <c r="AR94" t="inlineStr">
+      <c r="BE94" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-08-19/no-name-1755541972.pdf</t>
         </is>
       </c>
-      <c r="AS94" t="inlineStr">
+      <c r="BF94" t="inlineStr">
         <is>
           <t>2026-08-31T12:25:04+07:00</t>
         </is>
@@ -42759,17 +42837,17 @@
       <c r="AP95" t="n">
         <v>1.288</v>
       </c>
-      <c r="AQ95" t="inlineStr">
+      <c r="BD95" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR95" t="inlineStr">
+      <c r="BE95" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-10-24/no-name-1761245640.pdf</t>
         </is>
       </c>
-      <c r="AS95" t="inlineStr">
+      <c r="BF95" t="inlineStr">
         <is>
           <t>2026-08-31T15:38:58+07:00</t>
         </is>
@@ -42896,17 +42974,17 @@
       <c r="AP96" t="n">
         <v>-8.303000000000001</v>
       </c>
-      <c r="AQ96" t="inlineStr">
+      <c r="BD96" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán năm 2025</t>
         </is>
       </c>
-      <c r="AR96" t="inlineStr">
+      <c r="BE96" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-02/no-name-1775069400.pdf</t>
         </is>
       </c>
-      <c r="AS96" t="inlineStr">
+      <c r="BF96" t="inlineStr">
         <is>
           <t>2026-08-31T01:31:51+07:00</t>
         </is>
@@ -43003,17 +43081,17 @@
       <c r="AP97" t="n">
         <v>-22.73</v>
       </c>
-      <c r="AQ97" t="inlineStr">
+      <c r="BD97" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR97" t="inlineStr">
+      <c r="BE97" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-30/no-name-1777487970.pdf</t>
         </is>
       </c>
-      <c r="AS97" t="inlineStr">
+      <c r="BF97" t="inlineStr">
         <is>
           <t>2026-08-31T23:44:08+07:00</t>
         </is>
@@ -43140,17 +43218,17 @@
       <c r="AP98" t="n">
         <v>13.806</v>
       </c>
-      <c r="AQ98" t="inlineStr">
+      <c r="BD98" t="inlineStr">
         <is>
           <t>Báo cáo tài chính quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR98" t="inlineStr">
+      <c r="BE98" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/PGB_000000016752911_VI_Baocaotaichinh_bannien_nam_2026_18082026140441.pdf?v=1787036682987</t>
         </is>
       </c>
-      <c r="AS98" t="inlineStr">
+      <c r="BF98" t="inlineStr">
         <is>
           <t>2026-09-01T09:58:24+07:00</t>
         </is>
@@ -43247,17 +43325,17 @@
       <c r="AP99" t="n">
         <v>-93.63800000000001</v>
       </c>
-      <c r="AQ99" t="inlineStr">
+      <c r="BD99" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR99" t="inlineStr">
+      <c r="BE99" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014834796_VI_BaoCaotaiChinh_HopNhat_Q1_2025_26042025110134.pdf</t>
         </is>
       </c>
-      <c r="AS99" t="inlineStr">
+      <c r="BF99" t="inlineStr">
         <is>
           <t>2026-08-31T10:26:54+07:00</t>
         </is>
@@ -43384,17 +43462,17 @@
       <c r="AP100" t="n">
         <v>-11.996</v>
       </c>
-      <c r="AQ100" t="inlineStr">
+      <c r="BD100" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR100" t="inlineStr">
+      <c r="BE100" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00019753086419753087ngn-hng-tmcp-si-gn-cng-thng14082025-000000bo-co-ti-chnh-bn-nin-2025_1_1022.pdf</t>
         </is>
       </c>
-      <c r="AS100" t="inlineStr">
+      <c r="BF100" t="inlineStr">
         <is>
           <t>2026-08-31T12:26:51+07:00</t>
         </is>
@@ -43491,17 +43569,17 @@
       <c r="AP101" t="n">
         <v>2.024</v>
       </c>
-      <c r="AQ101" t="inlineStr">
+      <c r="BD101" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR101" t="inlineStr">
+      <c r="BE101" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_585483_Bao_cao_tai_chinh_quy_32025_1761811756.pdf</t>
         </is>
       </c>
-      <c r="AS101" t="inlineStr">
+      <c r="BF101" t="inlineStr">
         <is>
           <t>2026-08-31T15:40:59+07:00</t>
         </is>
@@ -43598,17 +43676,17 @@
       <c r="AP102" t="n">
         <v>-21.23</v>
       </c>
-      <c r="AQ102" t="inlineStr">
+      <c r="BD102" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR102" t="inlineStr">
+      <c r="BE102" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_604675_Bao_cao_tai_chinh_nam_2025_1776046299.pdf</t>
         </is>
       </c>
-      <c r="AS102" t="inlineStr">
+      <c r="BF102" t="inlineStr">
         <is>
           <t>2026-08-31T01:33:44+07:00</t>
         </is>
@@ -43732,17 +43810,17 @@
       <c r="AP103" t="n">
         <v>-22.866</v>
       </c>
-      <c r="AQ103" t="inlineStr">
+      <c r="BD103" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR103" t="inlineStr">
+      <c r="BE103" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_611277_Bao_cao_tai_chinh_quy_12026_1777027908.pdf</t>
         </is>
       </c>
-      <c r="AS103" t="inlineStr">
+      <c r="BF103" t="inlineStr">
         <is>
           <t>2026-08-31T23:45:58+07:00</t>
         </is>
@@ -43869,17 +43947,17 @@
       <c r="AP104" t="n">
         <v>0</v>
       </c>
-      <c r="AQ104" t="inlineStr">
+      <c r="BD104" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR104" t="inlineStr">
+      <c r="BE104" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SGB_000000016770459_VI__Bao_Cao_Tai_Chinh_Hop_Nhat_Ban_Nien_Nam_2026_daky_20082026151909.pdf?v=1787213952177</t>
         </is>
       </c>
-      <c r="AS104" t="inlineStr">
+      <c r="BF104" t="inlineStr">
         <is>
           <t>2026-09-01T10:00:42+07:00</t>
         </is>
@@ -43901,7 +43979,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="AS105" t="inlineStr">
+      <c r="BF105" t="inlineStr">
         <is>
           <t>2026-09-17T17:21:29+07:00</t>
         </is>
@@ -44028,17 +44106,17 @@
       <c r="AP106" t="n">
         <v>25.895</v>
       </c>
-      <c r="AQ106" t="inlineStr">
+      <c r="BD106" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR106" t="inlineStr">
+      <c r="BE106" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250903_-_SHB_-_Bao_Cao_Tai_Chinh_Hop_Nhat_Soat_Xet_Ban_nien_30.6.2025_1756910753.pdf</t>
         </is>
       </c>
-      <c r="AS106" t="inlineStr">
+      <c r="BF106" t="inlineStr">
         <is>
           <t>2026-08-31T12:28:17+07:00</t>
         </is>
@@ -44060,7 +44138,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="AS107" t="inlineStr">
+      <c r="BF107" t="inlineStr">
         <is>
           <t>2026-09-17T18:10:56+07:00</t>
         </is>
@@ -44196,17 +44274,17 @@
       <c r="AP108" t="n">
         <v>1827.469</v>
       </c>
-      <c r="AQ108" t="inlineStr">
+      <c r="BD108" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR108" t="inlineStr">
+      <c r="BE108" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_SHB_-_Bao_cao_tai_chinh_nam_2025_Hop_nhat_1775015883.pdf</t>
         </is>
       </c>
-      <c r="AS108" t="inlineStr">
+      <c r="BF108" t="inlineStr">
         <is>
           <t>2026-09-17T18:25:58+07:00</t>
         </is>
@@ -44228,7 +44306,7 @@
           <t>missing</t>
         </is>
       </c>
-      <c r="AS109" t="inlineStr">
+      <c r="BF109" t="inlineStr">
         <is>
           <t>2026-09-17T19:16:33+07:00</t>
         </is>
@@ -44355,17 +44433,17 @@
       <c r="AP110" t="n">
         <v>42.331</v>
       </c>
-      <c r="AQ110" t="inlineStr">
+      <c r="BD110" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán 6 tháng đầu năm 2026</t>
         </is>
       </c>
-      <c r="AR110" t="inlineStr">
+      <c r="BE110" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-3/2026-09-04/no-name-1788460885.pdf</t>
         </is>
       </c>
-      <c r="AS110" t="inlineStr">
+      <c r="BF110" t="inlineStr">
         <is>
           <t>2026-09-04T08:27:55+07:00</t>
         </is>
@@ -44486,17 +44564,17 @@
       <c r="AP111" t="n">
         <v>0</v>
       </c>
-      <c r="AQ111" t="inlineStr">
+      <c r="BD111" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR111" t="inlineStr">
+      <c r="BE111" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_23052025144847.pdf</t>
         </is>
       </c>
-      <c r="AS111" t="inlineStr">
+      <c r="BF111" t="inlineStr">
         <is>
           <t>2026-08-31T10:31:02+07:00</t>
         </is>
@@ -44593,17 +44671,17 @@
       <c r="AP112" t="n">
         <v>0</v>
       </c>
-      <c r="AQ112" t="inlineStr">
+      <c r="BD112" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR112" t="inlineStr">
+      <c r="BE112" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20250905_-_SSB_-_Bao_cao_tai_chinh_hop_nhat_soat_xet_ban_nien_2025_va_Giai_trinh_bien_dong_LNST_signed_1757323427.pdf</t>
         </is>
       </c>
-      <c r="AS112" t="inlineStr">
+      <c r="BF112" t="inlineStr">
         <is>
           <t>2026-08-31T12:30:19+07:00</t>
         </is>
@@ -44730,17 +44808,17 @@
       <c r="AP113" t="n">
         <v>2.482</v>
       </c>
-      <c r="AQ113" t="inlineStr">
+      <c r="BD113" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR113" t="inlineStr">
+      <c r="BE113" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_SSB_-_Bao_cao_tai_chinh_Hop_nhat_Quy_III.2025_kem_Giai_trinh_bien_dong_LNST_signed_1761901007.pdf</t>
         </is>
       </c>
-      <c r="AS113" t="inlineStr">
+      <c r="BF113" t="inlineStr">
         <is>
           <t>2026-08-31T15:43:36+07:00</t>
         </is>
@@ -44867,17 +44945,17 @@
       <c r="AP114" t="n">
         <v>46.332</v>
       </c>
-      <c r="AQ114" t="inlineStr">
+      <c r="BD114" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR114" t="inlineStr">
+      <c r="BE114" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260312_-_SSB_-_BCTC_hop_nhat_kiem_toan_nam_2025_kem_Giai_trinh_bien_dong_LNST_signed_1773310402.pdf</t>
         </is>
       </c>
-      <c r="AS114" t="inlineStr">
+      <c r="BF114" t="inlineStr">
         <is>
           <t>2026-08-31T01:36:28+07:00</t>
         </is>
@@ -45004,17 +45082,17 @@
       <c r="AP115" t="n">
         <v>-18.645</v>
       </c>
-      <c r="AQ115" t="inlineStr">
+      <c r="BD115" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR115" t="inlineStr">
+      <c r="BE115" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_SSB_-_BCTC_Hop_nhat_Quy_I.2026_va_Giai_trinh_bien_dong_LNST_signed_1777467537.pdf</t>
         </is>
       </c>
-      <c r="AS115" t="inlineStr">
+      <c r="BF115" t="inlineStr">
         <is>
           <t>2026-08-31T23:48:58+07:00</t>
         </is>
@@ -45111,17 +45189,17 @@
       <c r="AP116" t="n">
         <v>-2.133</v>
       </c>
-      <c r="AQ116" t="inlineStr">
+      <c r="BD116" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR116" t="inlineStr">
+      <c r="BE116" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/SSB_202608142020SSB2020Bao20cao20tai20chinh20hop20nhat20soat20xet20ban20nien20202620va20Giai20trinh20bien20dong20LNST_signed_20082026090228.pdf?v=1787191350112</t>
         </is>
       </c>
-      <c r="AS116" t="inlineStr">
+      <c r="BF116" t="inlineStr">
         <is>
           <t>2026-09-01T10:03:22+07:00</t>
         </is>
@@ -45218,17 +45296,17 @@
       <c r="AP117" t="n">
         <v>0</v>
       </c>
-      <c r="AQ117" t="inlineStr">
+      <c r="BD117" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR117" t="inlineStr">
+      <c r="BE117" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00032098765432098763ngn-hng-tmcp-si-gn-thng-tn26042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AS117" t="inlineStr">
+      <c r="BF117" t="inlineStr">
         <is>
           <t>2026-08-31T10:34:12+07:00</t>
         </is>
@@ -45355,17 +45433,17 @@
       <c r="AP118" t="n">
         <v>0</v>
       </c>
-      <c r="AQ118" t="inlineStr">
+      <c r="BD118" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR118" t="inlineStr">
+      <c r="BE118" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/STB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025100208.pdf</t>
         </is>
       </c>
-      <c r="AS118" t="inlineStr">
+      <c r="BF118" t="inlineStr">
         <is>
           <t>2026-08-31T12:33:00+07:00</t>
         </is>
@@ -45462,17 +45540,17 @@
       <c r="AP119" t="n">
         <v>0</v>
       </c>
-      <c r="AQ119" t="inlineStr">
+      <c r="BD119" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR119" t="inlineStr">
+      <c r="BE119" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251029_-_STB_-_BCTC_Hop_nhat_Q3.2025_1761804289.pdf</t>
         </is>
       </c>
-      <c r="AS119" t="inlineStr">
+      <c r="BF119" t="inlineStr">
         <is>
           <t>2026-08-31T15:46:18+07:00</t>
         </is>
@@ -45599,17 +45677,17 @@
       <c r="AP120" t="n">
         <v>0</v>
       </c>
-      <c r="AQ120" t="inlineStr">
+      <c r="BD120" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR120" t="inlineStr">
+      <c r="BE120" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_STB_-_BCTC_Hop_nhat_nam_2025_da_kiem_toan__1774863040.pdf</t>
         </is>
       </c>
-      <c r="AS120" t="inlineStr">
+      <c r="BF120" t="inlineStr">
         <is>
           <t>2026-08-31T01:38:47+07:00</t>
         </is>
@@ -45745,12 +45823,12 @@
       <c r="AP121" t="n">
         <v>21.814</v>
       </c>
-      <c r="AQ121" t="inlineStr">
+      <c r="BD121" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy I 2026, OCR khong doc duoc)</t>
         </is>
       </c>
-      <c r="AS121" t="inlineStr">
+      <c r="BF121" t="inlineStr">
         <is>
           <t>2026-09-17T14:38:33+07:00</t>
         </is>
@@ -45886,12 +45964,12 @@
       <c r="AP122" t="n">
         <v>29.549</v>
       </c>
-      <c r="AQ122" t="inlineStr">
+      <c r="BD122" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (STB BCTC hop nhat GND Quy II 2026, OCR khong doc duoc)</t>
         </is>
       </c>
-      <c r="AS122" t="inlineStr">
+      <c r="BF122" t="inlineStr">
         <is>
           <t>2026-09-17T14:38:33+07:00</t>
         </is>
@@ -46018,17 +46096,17 @@
       <c r="AP123" t="n">
         <v>-11.318</v>
       </c>
-      <c r="AQ123" t="inlineStr">
+      <c r="BD123" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR123" t="inlineStr">
+      <c r="BE123" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00001234567901234568ngn-hng-tmcp-k-thng-vit-nam21042025-000000bo-co-ti-chnh-hp-nht-qu.pdf</t>
         </is>
       </c>
-      <c r="AS123" t="inlineStr">
+      <c r="BF123" t="inlineStr">
         <is>
           <t>2026-08-31T10:35:54+07:00</t>
         </is>
@@ -46152,17 +46230,17 @@
       <c r="AP124" t="n">
         <v>0</v>
       </c>
-      <c r="AQ124" t="inlineStr">
+      <c r="BD124" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR124" t="inlineStr">
+      <c r="BE124" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025101639.pdf</t>
         </is>
       </c>
-      <c r="AS124" t="inlineStr">
+      <c r="BF124" t="inlineStr">
         <is>
           <t>2026-08-31T12:36:30+07:00</t>
         </is>
@@ -46259,17 +46337,17 @@
       <c r="AP125" t="n">
         <v>1.935</v>
       </c>
-      <c r="AQ125" t="inlineStr">
+      <c r="BD125" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR125" t="inlineStr">
+      <c r="BE125" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251021_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-3Q25_1761042656.pdf</t>
         </is>
       </c>
-      <c r="AS125" t="inlineStr">
+      <c r="BF125" t="inlineStr">
         <is>
           <t>2026-08-31T15:48:08+07:00</t>
         </is>
@@ -46396,17 +46474,17 @@
       <c r="AP126" t="n">
         <v>-18.539</v>
       </c>
-      <c r="AQ126" t="inlineStr">
+      <c r="BD126" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR126" t="inlineStr">
+      <c r="BE126" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260317_-_TCB_-_Techcombank-VAS-bao_cao_tai_chinh_hop_nhat-YE25_1773755161.pdf</t>
         </is>
       </c>
-      <c r="AS126" t="inlineStr">
+      <c r="BF126" t="inlineStr">
         <is>
           <t>2026-08-31T01:41:25+07:00</t>
         </is>
@@ -46533,17 +46611,58 @@
       <c r="AP127" t="n">
         <v>-3.739</v>
       </c>
-      <c r="AQ127" t="inlineStr">
+      <c r="AQ127" t="n">
+        <v>66784.31600000001</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>66549.84</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>234.476</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>106.659</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>341.135</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>353.03</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>11.895</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="BC127" t="n">
+        <v>34.114</v>
+      </c>
+      <c r="BD127" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR127" t="inlineStr">
+      <c r="BE127" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260421_-_TCB_-_bao_cao_tai_chinh_hop_nhat_1Q26_VAS_VN__1776825559.pdf</t>
         </is>
       </c>
-      <c r="AS127" t="inlineStr">
+      <c r="BF127" t="inlineStr">
         <is>
           <t>2026-08-31T23:55:42+07:00</t>
         </is>
@@ -46670,17 +46789,17 @@
       <c r="AP128" t="n">
         <v>20.032</v>
       </c>
-      <c r="AQ128" t="inlineStr">
+      <c r="BD128" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR128" t="inlineStr">
+      <c r="BE128" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TCB_202608132020TCB2020Bao20cao20tai20chinh20hop20nhat20soat20xet202Q2026_19082026102705.pdf?v=1787110027315</t>
         </is>
       </c>
-      <c r="AS128" t="inlineStr">
+      <c r="BF128" t="inlineStr">
         <is>
           <t>2026-09-01T10:12:04+07:00</t>
         </is>
@@ -46816,17 +46935,17 @@
       <c r="AP129" t="n">
         <v>27.249</v>
       </c>
-      <c r="AQ129" t="inlineStr">
+      <c r="BD129" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR129" t="inlineStr">
+      <c r="BE129" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_Q1_2025_Hopnhat_23052025145349.pdf</t>
         </is>
       </c>
-      <c r="AS129" t="inlineStr">
+      <c r="BF129" t="inlineStr">
         <is>
           <t>2026-09-17T15:27:28+07:00</t>
         </is>
@@ -46962,17 +47081,17 @@
       <c r="AP130" t="n">
         <v>5.204</v>
       </c>
-      <c r="AQ130" t="inlineStr">
+      <c r="BD130" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR130" t="inlineStr">
+      <c r="BE130" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025102458.pdf</t>
         </is>
       </c>
-      <c r="AS130" t="inlineStr">
+      <c r="BF130" t="inlineStr">
         <is>
           <t>2026-09-17T16:32:56+07:00</t>
         </is>
@@ -47108,17 +47227,17 @@
       <c r="AP131" t="n">
         <v>-33.481</v>
       </c>
-      <c r="AQ131" t="inlineStr">
+      <c r="BD131" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR131" t="inlineStr">
+      <c r="BE131" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_TPB_-_Bao_cao_tai_chinh_hop_nhat_Q3.2025_signed_1761832307.pdf</t>
         </is>
       </c>
-      <c r="AS131" t="inlineStr">
+      <c r="BF131" t="inlineStr">
         <is>
           <t>2026-09-17T17:36:04+07:00</t>
         </is>
@@ -47215,17 +47334,17 @@
       <c r="AP132" t="n">
         <v>0</v>
       </c>
-      <c r="AQ132" t="inlineStr">
+      <c r="BD132" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR132" t="inlineStr">
+      <c r="BE132" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260331_-_TPB_-_BCTC_hop_nhat_2025_da_kiem_toan_kem_giai_trinh_chenh_lech_LNST_signed_1774952109.pdf</t>
         </is>
       </c>
-      <c r="AS132" t="inlineStr">
+      <c r="BF132" t="inlineStr">
         <is>
           <t>2026-08-31T01:43:30+07:00</t>
         </is>
@@ -47355,17 +47474,17 @@
       <c r="AP133" t="n">
         <v>9.192</v>
       </c>
-      <c r="AQ133" t="inlineStr">
+      <c r="BD133" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR133" t="inlineStr">
+      <c r="BE133" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_TPB_-_BCTC_hop_nhat_Quy_1_2026_signed_1777457982.pdf</t>
         </is>
       </c>
-      <c r="AS133" t="inlineStr">
+      <c r="BF133" t="inlineStr">
         <is>
           <t>2026-09-17T19:18:12+07:00</t>
         </is>
@@ -47462,17 +47581,17 @@
       <c r="AP134" t="n">
         <v>2.917</v>
       </c>
-      <c r="AQ134" t="inlineStr">
+      <c r="BD134" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR134" t="inlineStr">
+      <c r="BE134" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/TPB_202608182020TPB2020Bao20cao20tai20chinh20hop20nhat20soat20xet20ban20nien20202620kem20giai20trinh20chenh20lech20LNST_signed_19082026095348.pdf?v=1787108030513</t>
         </is>
       </c>
-      <c r="AS134" t="inlineStr">
+      <c r="BF134" t="inlineStr">
         <is>
           <t>2026-09-01T10:14:12+07:00</t>
         </is>
@@ -47569,17 +47688,17 @@
       <c r="AP135" t="n">
         <v>54.528</v>
       </c>
-      <c r="AQ135" t="inlineStr">
+      <c r="BD135" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR135" t="inlineStr">
+      <c r="BE135" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000000014787653_VI_BaoCaoTaiChinh_Q1_2025_18042025134138.pdf</t>
         </is>
       </c>
-      <c r="AS135" t="inlineStr">
+      <c r="BF135" t="inlineStr">
         <is>
           <t>2026-08-31T10:42:19+07:00</t>
         </is>
@@ -47685,17 +47804,17 @@
       <c r="AP136" t="n">
         <v>-46.462</v>
       </c>
-      <c r="AQ136" t="inlineStr">
+      <c r="BD136" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025</t>
         </is>
       </c>
-      <c r="AR136" t="inlineStr">
+      <c r="BE136" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/000007054673721340387ngn-hng-tmcp-vit-24072025-000000bo-co-ti-chnh-hp-nht-qu_1_0914.pdf</t>
         </is>
       </c>
-      <c r="AS136" t="inlineStr">
+      <c r="BF136" t="inlineStr">
         <is>
           <t>2026-09-17T16:34:18+07:00</t>
         </is>
@@ -47801,17 +47920,17 @@
       <c r="AP137" t="n">
         <v>29.123</v>
       </c>
-      <c r="AQ137" t="inlineStr">
+      <c r="BD137" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR137" t="inlineStr">
+      <c r="BE137" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251017_-_VAB_-_BCTC_HN_Q3.2025_1761126486.pdf</t>
         </is>
       </c>
-      <c r="AS137" t="inlineStr">
+      <c r="BF137" t="inlineStr">
         <is>
           <t>2026-09-18T08:37:05+07:00</t>
         </is>
@@ -47938,17 +48057,17 @@
       <c r="AP138" t="n">
         <v>14.177</v>
       </c>
-      <c r="AQ138" t="inlineStr">
+      <c r="BD138" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR138" t="inlineStr">
+      <c r="BE138" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260330_-_VAB_BCTC_hop_nhat_da_kiem_toan_Nam_2025_1775054500.pdf</t>
         </is>
       </c>
-      <c r="AS138" t="inlineStr">
+      <c r="BF138" t="inlineStr">
         <is>
           <t>2026-08-31T01:45:19+07:00</t>
         </is>
@@ -48084,12 +48203,12 @@
       <c r="AP139" t="n">
         <v>26.35</v>
       </c>
-      <c r="AQ139" t="inlineStr">
+      <c r="BD139" t="inlineStr">
         <is>
           <t>Nhap thu cong tu anh chup BCTC that (VAB thuyet minh BCTC Quy 1 2026, cot 'qua han duoi/tren 3 thang' dao nguoc thu tu so voi chuan nen da doi lai khi nhap, don vi da xac nhan la Trieu dong that qua doi chieu Vietcap)</t>
         </is>
       </c>
-      <c r="AS139" t="inlineStr">
+      <c r="BF139" t="inlineStr">
         <is>
           <t>2026-09-18T08:32:03+07:00</t>
         </is>
@@ -48216,17 +48335,17 @@
       <c r="AP140" t="n">
         <v>-25.653</v>
       </c>
-      <c r="AQ140" t="inlineStr">
+      <c r="BD140" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR140" t="inlineStr">
+      <c r="BE140" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VAB_202608212020VAB2020BCTC20HN20SOAT20XET20BAN20NIEN202026_22082026105705.pdf?v=1787371027647</t>
         </is>
       </c>
-      <c r="AS140" t="inlineStr">
+      <c r="BF140" t="inlineStr">
         <is>
           <t>2026-09-01T10:15:41+07:00</t>
         </is>
@@ -48323,17 +48442,17 @@
       <c r="AP141" t="n">
         <v>14.519</v>
       </c>
-      <c r="AQ141" t="inlineStr">
+      <c r="BD141" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR141" t="inlineStr">
+      <c r="BE141" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/1_vbb_2025_5_7_121b03c_vi_baocaotaichinh_hopnhat_q1_20251_16052025112437.pdf</t>
         </is>
       </c>
-      <c r="AS141" t="inlineStr">
+      <c r="BF141" t="inlineStr">
         <is>
           <t>2026-08-31T10:44:04+07:00</t>
         </is>
@@ -48460,17 +48579,17 @@
       <c r="AP142" t="n">
         <v>41.606</v>
       </c>
-      <c r="AQ142" t="inlineStr">
+      <c r="BD142" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR142" t="inlineStr">
+      <c r="BE142" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-vit-nam-thng-tn05082025-000000bo-co-ti-chnh-bn-nin-2025_1_1517.pdf</t>
         </is>
       </c>
-      <c r="AS142" t="inlineStr">
+      <c r="BF142" t="inlineStr">
         <is>
           <t>2026-08-31T12:48:36+07:00</t>
         </is>
@@ -48567,17 +48686,17 @@
       <c r="AP143" t="n">
         <v>72.465</v>
       </c>
-      <c r="AQ143" t="inlineStr">
+      <c r="BD143" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR143" t="inlineStr">
+      <c r="BE143" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-11-05/no-name-1762283224.pdf</t>
         </is>
       </c>
-      <c r="AS143" t="inlineStr">
+      <c r="BF143" t="inlineStr">
         <is>
           <t>2026-08-31T15:58:42+07:00</t>
         </is>
@@ -48704,17 +48823,17 @@
       <c r="AP144" t="n">
         <v>0</v>
       </c>
-      <c r="AQ144" t="inlineStr">
+      <c r="BD144" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR144" t="inlineStr">
+      <c r="BE144" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/_603183_Bao_cao_tai_chinh_nam_2025_1776046427.pdf</t>
         </is>
       </c>
-      <c r="AS144" t="inlineStr">
+      <c r="BF144" t="inlineStr">
         <is>
           <t>2026-08-31T01:48:14+07:00</t>
         </is>
@@ -48811,17 +48930,17 @@
       <c r="AP145" t="n">
         <v>634.295</v>
       </c>
-      <c r="AQ145" t="inlineStr">
+      <c r="BD145" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR145" t="inlineStr">
+      <c r="BE145" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VBB_1778222221.pdf</t>
         </is>
       </c>
-      <c r="AS145" t="inlineStr">
+      <c r="BF145" t="inlineStr">
         <is>
           <t>2026-09-01T00:03:48+07:00</t>
         </is>
@@ -48939,17 +49058,17 @@
       <c r="AP146" t="n">
         <v>37.642</v>
       </c>
-      <c r="AQ146" t="inlineStr">
+      <c r="BD146" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán 6 tháng đầu năm 2026</t>
         </is>
       </c>
-      <c r="AR146" t="inlineStr">
+      <c r="BE146" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-3/2026-08-17/no-name-1786938113.pdf</t>
         </is>
       </c>
-      <c r="AS146" t="inlineStr">
+      <c r="BF146" t="inlineStr">
         <is>
           <t>2026-09-01T10:19:39+07:00</t>
         </is>
@@ -49076,17 +49195,17 @@
       <c r="AP147" t="n">
         <v>-1.724</v>
       </c>
-      <c r="AQ147" t="inlineStr">
+      <c r="BD147" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR147" t="inlineStr">
+      <c r="BE147" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_23052025150224.pdf</t>
         </is>
       </c>
-      <c r="AS147" t="inlineStr">
+      <c r="BF147" t="inlineStr">
         <is>
           <t>2026-08-31T17:07:33+07:00</t>
         </is>
@@ -49183,17 +49302,17 @@
       <c r="AP148" t="n">
         <v>-6.878</v>
       </c>
-      <c r="AQ148" t="inlineStr">
+      <c r="BD148" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR148" t="inlineStr">
+      <c r="BE148" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_Baocaotaichinh_6T_2025_Soatxet_Hopnhat_06102025111259.pdf</t>
         </is>
       </c>
-      <c r="AS148" t="inlineStr">
+      <c r="BF148" t="inlineStr">
         <is>
           <t>2026-08-31T12:50:26+07:00</t>
         </is>
@@ -49329,17 +49448,17 @@
       <c r="AP149" t="n">
         <v>-8.951000000000001</v>
       </c>
-      <c r="AQ149" t="inlineStr">
+      <c r="BD149" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR149" t="inlineStr">
+      <c r="BE149" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20251030_-_VCB_-_CBTT_BCTC_Hop_nhat_Q3.2025_1761883208.pdf</t>
         </is>
       </c>
-      <c r="AS149" t="inlineStr">
+      <c r="BF149" t="inlineStr">
         <is>
           <t>2026-09-17T17:41:27+07:00</t>
         </is>
@@ -49436,17 +49555,17 @@
       <c r="AP150" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="AQ150" t="inlineStr">
+      <c r="BD150" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR150" t="inlineStr">
+      <c r="BE150" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260327_-_VCB_-_BCTC_hop_nhat_kiem_toan_nam_2025_1774870712.pdf</t>
         </is>
       </c>
-      <c r="AS150" t="inlineStr">
+      <c r="BF150" t="inlineStr">
         <is>
           <t>2026-08-31T01:50:20+07:00</t>
         </is>
@@ -49573,17 +49692,17 @@
       <c r="AP151" t="n">
         <v>-18.424</v>
       </c>
-      <c r="AQ151" t="inlineStr">
+      <c r="BD151" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR151" t="inlineStr">
+      <c r="BE151" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260429_-_VCB_-_BCTC_hop_nhat_Q1.2026_1777452360.pdf</t>
         </is>
       </c>
-      <c r="AS151" t="inlineStr">
+      <c r="BF151" t="inlineStr">
         <is>
           <t>2026-09-01T00:05:30+07:00</t>
         </is>
@@ -49680,17 +49799,17 @@
       <c r="AP152" t="n">
         <v>27.521</v>
       </c>
-      <c r="AQ152" t="inlineStr">
+      <c r="BD152" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR152" t="inlineStr">
+      <c r="BE152" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VCB_202608142020VCB2020BCTC20hop20nhat20soat20xet20ban20nien202026_20082026091404.pdf?v=1787192046593</t>
         </is>
       </c>
-      <c r="AS152" t="inlineStr">
+      <c r="BF152" t="inlineStr">
         <is>
           <t>2026-09-01T10:21:39+07:00</t>
         </is>
@@ -49787,17 +49906,17 @@
       <c r="AP153" t="n">
         <v>19.801</v>
       </c>
-      <c r="AQ153" t="inlineStr">
+      <c r="BD153" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2025</t>
         </is>
       </c>
-      <c r="AR153" t="inlineStr">
+      <c r="BE153" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-3/2025-07-29/no-name-1753727617.pdf</t>
         </is>
       </c>
-      <c r="AS153" t="inlineStr">
+      <c r="BF153" t="inlineStr">
         <is>
           <t>2026-08-31T10:48:45+07:00</t>
         </is>
@@ -49924,17 +50043,17 @@
       <c r="AP154" t="n">
         <v>-6.551</v>
       </c>
-      <c r="AQ154" t="inlineStr">
+      <c r="BD154" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2025 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR154" t="inlineStr">
+      <c r="BE154" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/00015520282186948853ngn-hng-tmcp-quc-t-vit-nam06082025-000000bo-co-ti-chnh-hp-nht-bn-nin_1_0929.pdf</t>
         </is>
       </c>
-      <c r="AS154" t="inlineStr">
+      <c r="BF154" t="inlineStr">
         <is>
           <t>2026-08-31T12:52:16+07:00</t>
         </is>
@@ -50061,17 +50180,17 @@
       <c r="AP155" t="n">
         <v>-18.741</v>
       </c>
-      <c r="AQ155" t="inlineStr">
+      <c r="BD155" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 3 năm 2025</t>
         </is>
       </c>
-      <c r="AR155" t="inlineStr">
+      <c r="BE155" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2025-4/2025-10-30/no-name-1761766923.pdf</t>
         </is>
       </c>
-      <c r="AS155" t="inlineStr">
+      <c r="BF155" t="inlineStr">
         <is>
           <t>2026-08-31T16:03:19+07:00</t>
         </is>
@@ -50168,17 +50287,17 @@
       <c r="AP156" t="n">
         <v>-13.195</v>
       </c>
-      <c r="AQ156" t="inlineStr">
+      <c r="BD156" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất năm 2025 (đã kiểm toán)</t>
         </is>
       </c>
-      <c r="AR156" t="inlineStr">
+      <c r="BE156" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/20260302_-_VIB_-_BCTC_hop_nhat_kiem_toan_2025_1772443477.pdf</t>
         </is>
       </c>
-      <c r="AS156" t="inlineStr">
+      <c r="BF156" t="inlineStr">
         <is>
           <t>2026-08-31T01:52:28+07:00</t>
         </is>
@@ -50305,17 +50424,17 @@
       <c r="AP157" t="n">
         <v>2.674</v>
       </c>
-      <c r="AQ157" t="inlineStr">
+      <c r="BD157" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất đã kiểm toán Quý 1 năm 2026</t>
         </is>
       </c>
-      <c r="AR157" t="inlineStr">
+      <c r="BE157" t="inlineStr">
         <is>
           <t>https://cdn.24hmoney.vn/upload/file/2026-2/2026-04-30/no-name-1777489917.pdf</t>
         </is>
       </c>
-      <c r="AS157" t="inlineStr">
+      <c r="BF157" t="inlineStr">
         <is>
           <t>2026-09-01T00:07:17+07:00</t>
         </is>
@@ -50412,17 +50531,17 @@
       <c r="AP158" t="n">
         <v>-0.046</v>
       </c>
-      <c r="AQ158" t="inlineStr">
+      <c r="BD158" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2026 (đã soát xét)</t>
         </is>
       </c>
-      <c r="AR158" t="inlineStr">
+      <c r="BE158" t="inlineStr">
         <is>
           <t>https://cafefnew.mediacdn.vn/Images/Uploaded/DuLieuDownload/BCTC/VIB_202608062020VIB2020BCTC20hop20nhat20soat20xet20ban20nien202026_12082026154930.pdf?v=1786524571501</t>
         </is>
       </c>
-      <c r="AS158" t="inlineStr">
+      <c r="BF158" t="inlineStr">
         <is>
           <t>2026-09-01T10:23:21+07:00</t>
         </is>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ALM_NganHang_RawBuckets" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_RawBuckets" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30930,7 +30930,7 @@
         <v>2.644</v>
       </c>
       <c r="AF2" t="n">
-        <v>5142.781999999998</v>
+        <v>5142.782000000002</v>
       </c>
       <c r="AG2" t="n">
         <v>-6.842</v>
@@ -31076,7 +31076,7 @@
         <v>2.349</v>
       </c>
       <c r="AF3" t="n">
-        <v>6180.511999999999</v>
+        <v>6180.512000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>-6.22</v>
@@ -31436,7 +31436,7 @@
         <v>2.034</v>
       </c>
       <c r="AF6" t="n">
-        <v>8183.362999999996</v>
+        <v>8183.362999999999</v>
       </c>
       <c r="AG6" t="n">
         <v>-7.633</v>
@@ -31543,7 +31543,7 @@
         <v>1.786</v>
       </c>
       <c r="AF7" t="n">
-        <v>-2072.081999999995</v>
+        <v>-2072.081999999999</v>
       </c>
       <c r="AG7" t="n">
         <v>-6.467</v>
@@ -31680,7 +31680,7 @@
         <v>2.198</v>
       </c>
       <c r="AF8" t="n">
-        <v>-5551.592999999999</v>
+        <v>-5551.593000000001</v>
       </c>
       <c r="AG8" t="n">
         <v>0.38</v>
@@ -31924,7 +31924,7 @@
         <v>1.383</v>
       </c>
       <c r="AF10" t="n">
-        <v>72159.24699999994</v>
+        <v>72159.24699999997</v>
       </c>
       <c r="AG10" t="n">
         <v>-11.405</v>
@@ -32070,7 +32070,7 @@
         <v>1.248</v>
       </c>
       <c r="AF11" t="n">
-        <v>75182.47699999997</v>
+        <v>75182.47699999998</v>
       </c>
       <c r="AG11" t="n">
         <v>-9.868</v>
@@ -32353,7 +32353,7 @@
         <v>1.212</v>
       </c>
       <c r="AF13" t="n">
-        <v>85041.65799999997</v>
+        <v>85041.658</v>
       </c>
       <c r="AG13" t="n">
         <v>-9.567</v>
@@ -34256,7 +34256,7 @@
         <v>0.912</v>
       </c>
       <c r="AF27" t="n">
-        <v>482308.4170000001</v>
+        <v>482308.417</v>
       </c>
       <c r="AG27" t="n">
         <v>12.989</v>
@@ -35451,7 +35451,7 @@
         <v>1.282</v>
       </c>
       <c r="AF36" t="n">
-        <v>-2093.93</v>
+        <v>-2093.930000000001</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -37157,7 +37157,7 @@
         <v>584740.964</v>
       </c>
       <c r="L49" t="n">
-        <v>57219.16100000001</v>
+        <v>57219.161</v>
       </c>
       <c r="M49" t="n">
         <v>1.932</v>
@@ -37401,7 +37401,7 @@
         <v>1.207</v>
       </c>
       <c r="AF51" t="n">
-        <v>536.0379999999986</v>
+        <v>536.0379999999996</v>
       </c>
       <c r="AG51" t="n">
         <v>-8.407999999999999</v>
@@ -37782,7 +37782,7 @@
         <v>1.219</v>
       </c>
       <c r="AF54" t="n">
-        <v>-6843.675999999999</v>
+        <v>-6843.676</v>
       </c>
       <c r="AG54" t="n">
         <v>-9.135999999999999</v>
@@ -37993,7 +37993,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="L56" t="n">
-        <v>2554.764000000001</v>
+        <v>2554.764</v>
       </c>
       <c r="M56" t="n">
         <v>0.946</v>
@@ -38255,7 +38255,7 @@
         <v>113076.542</v>
       </c>
       <c r="L58" t="n">
-        <v>89209.49699999999</v>
+        <v>89209.497</v>
       </c>
       <c r="M58" t="n">
         <v>14.805</v>
@@ -39202,7 +39202,7 @@
         <v>1.506</v>
       </c>
       <c r="AF65" t="n">
-        <v>1097.082999999999</v>
+        <v>1097.083000000001</v>
       </c>
       <c r="AG65" t="n">
         <v>3.244</v>
@@ -41653,7 +41653,7 @@
         <v>0.909</v>
       </c>
       <c r="AF83" t="n">
-        <v>20403.411</v>
+        <v>20403.41100000001</v>
       </c>
       <c r="AG83" t="n">
         <v>-10.621</v>
@@ -42648,7 +42648,7 @@
         <v>53049.641</v>
       </c>
       <c r="L92" t="n">
-        <v>-71627.23300000001</v>
+        <v>-71627.23299999999</v>
       </c>
       <c r="M92" t="n">
         <v>-22.759</v>
@@ -43104,7 +43104,7 @@
         <v>2.167</v>
       </c>
       <c r="AF95" t="n">
-        <v>-36336.33499999999</v>
+        <v>-36336.335</v>
       </c>
       <c r="AG95" t="n">
         <v>7.502</v>
@@ -43464,7 +43464,7 @@
         <v>1.218</v>
       </c>
       <c r="AF98" t="n">
-        <v>9206.203000000001</v>
+        <v>9206.203</v>
       </c>
       <c r="AG98" t="n">
         <v>-4.209</v>
@@ -43726,7 +43726,7 @@
         <v>1.52</v>
       </c>
       <c r="AF100" t="n">
-        <v>1044.137999999999</v>
+        <v>1044.137999999998</v>
       </c>
       <c r="AG100" t="n">
         <v>-0.302</v>
@@ -43863,7 +43863,7 @@
         <v>2.243</v>
       </c>
       <c r="AF101" t="n">
-        <v>-7342.066000000003</v>
+        <v>-7342.066000000001</v>
       </c>
       <c r="AG101" t="n">
         <v>1.12</v>
@@ -44489,7 +44489,7 @@
         <v>10333.757</v>
       </c>
       <c r="L107" t="n">
-        <v>4585.812999999998</v>
+        <v>4585.813</v>
       </c>
       <c r="M107" t="n">
         <v>4.439</v>
@@ -45016,7 +45016,7 @@
         <v>1.53</v>
       </c>
       <c r="AF111" t="n">
-        <v>44447.072</v>
+        <v>44447.07199999999</v>
       </c>
       <c r="AG111" t="n">
         <v>41.067</v>
@@ -45340,7 +45340,7 @@
         <v>43767.119108461</v>
       </c>
       <c r="L114" t="n">
-        <v>45040.483647395</v>
+        <v>45040.48364739501</v>
       </c>
       <c r="M114" t="n">
         <v>19.006</v>
@@ -45391,7 +45391,7 @@
         <v>1.727</v>
       </c>
       <c r="AF114" t="n">
-        <v>73880.39491509199</v>
+        <v>73880.39491509201</v>
       </c>
       <c r="AG114" t="n">
         <v>13.551</v>
@@ -46060,7 +46060,7 @@
         <v>57104.9273618</v>
       </c>
       <c r="L119" t="n">
-        <v>-8354.105685278017</v>
+        <v>-8354.105685278011</v>
       </c>
       <c r="M119" t="n">
         <v>-2.587</v>
@@ -47184,7 +47184,7 @@
         <v>3.214</v>
       </c>
       <c r="AF128" t="n">
-        <v>-448.712</v>
+        <v>-448.7119999999998</v>
       </c>
       <c r="AG128" t="n">
         <v>-8.398</v>
@@ -47694,7 +47694,7 @@
         <v>1.841</v>
       </c>
       <c r="AF133" t="n">
-        <v>-8415.234000000002</v>
+        <v>-8415.234</v>
       </c>
       <c r="AG133" t="n">
         <v>-5.98</v>
@@ -48424,7 +48424,7 @@
         <v>110803.352</v>
       </c>
       <c r="L140" t="n">
-        <v>84929.841</v>
+        <v>84929.84099999999</v>
       </c>
       <c r="M140" t="n">
         <v>12.871</v>
@@ -51887,7 +51887,7 @@
         <v>1.628</v>
       </c>
       <c r="AF168" t="n">
-        <v>-95355.82799999998</v>
+        <v>-95355.82799999999</v>
       </c>
       <c r="AG168" t="n">
         <v>-8.385</v>
@@ -52033,7 +52033,7 @@
         <v>1.553</v>
       </c>
       <c r="AF169" t="n">
-        <v>31803.23300000001</v>
+        <v>31803.233</v>
       </c>
       <c r="AG169" t="n">
         <v>4.369</v>
@@ -52211,7 +52211,7 @@
         <v>1.392</v>
       </c>
       <c r="AF170" t="n">
-        <v>49624.19500000001</v>
+        <v>49624.19499999999</v>
       </c>
       <c r="AG170" t="n">
         <v>9.231999999999999</v>
@@ -52655,7 +52655,7 @@
         <v>1.148</v>
       </c>
       <c r="AF173" t="n">
-        <v>47597.061</v>
+        <v>47597.06099999999</v>
       </c>
       <c r="AG173" t="n">
         <v>12.611</v>
@@ -53533,7 +53533,7 @@
         <v>0.951</v>
       </c>
       <c r="AF180" t="n">
-        <v>786.7630000000008</v>
+        <v>786.7630000000004</v>
       </c>
       <c r="AG180" t="n">
         <v>0.008999999999999999</v>
@@ -56409,16 +56409,46 @@
         <v>98235.37700000001</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>-60447.40300000001</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>-14.605</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>-19.961</v>
       </c>
       <c r="O203" t="n">
-        <v>0</v>
+        <v>-10.999</v>
+      </c>
+      <c r="P203" t="n">
+        <v>-12.239</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>315947.782</v>
+      </c>
+      <c r="R203" t="n">
+        <v>148291.407</v>
+      </c>
+      <c r="S203" t="n">
+        <v>213.059</v>
+      </c>
+      <c r="T203" t="n">
+        <v>66.04600000000001</v>
+      </c>
+      <c r="U203" t="n">
+        <v>151.41</v>
+      </c>
+      <c r="V203" t="n">
+        <v>61.087</v>
+      </c>
+      <c r="W203" t="n">
+        <v>62.182</v>
+      </c>
+      <c r="X203" t="n">
+        <v>141.765</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>0.583</v>
       </c>
       <c r="AC203" t="n">
         <v>8.388999999999999</v>
@@ -56927,7 +56957,7 @@
         <v>1.861</v>
       </c>
       <c r="AF207" t="n">
-        <v>18205.90499999999</v>
+        <v>18205.905</v>
       </c>
       <c r="AG207" t="n">
         <v>-11.997</v>
@@ -80528,6 +80558,69 @@
           <t>reported</t>
         </is>
       </c>
+      <c r="D203" t="n">
+        <v>2679.251</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2451.112</v>
+      </c>
+      <c r="F203" t="n">
+        <v>-65577.766</v>
+      </c>
+      <c r="G203" t="n">
+        <v>-22167.444</v>
+      </c>
+      <c r="H203" t="n">
+        <v>37091.246</v>
+      </c>
+      <c r="I203" t="n">
+        <v>3760.642</v>
+      </c>
+      <c r="J203" t="n">
+        <v>85006.45699999999</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>168522.638</v>
+      </c>
+      <c r="N203" t="n">
+        <v>58616.734</v>
+      </c>
+      <c r="O203" t="n">
+        <v>88808.41</v>
+      </c>
+      <c r="P203" t="n">
+        <v>53665.848</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>5858.46</v>
+      </c>
+      <c r="R203" t="n">
+        <v>2679.251</v>
+      </c>
+      <c r="S203" t="n">
+        <v>2451.112</v>
+      </c>
+      <c r="T203" t="n">
+        <v>102944.872</v>
+      </c>
+      <c r="U203" t="n">
+        <v>36449.29</v>
+      </c>
+      <c r="V203" t="n">
+        <v>125899.656</v>
+      </c>
+      <c r="W203" t="n">
+        <v>57426.49</v>
+      </c>
+      <c r="X203" t="n">
+        <v>90864.917</v>
+      </c>
       <c r="Y203" t="n">
         <v>5130.363</v>
       </c>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -53851,16 +53851,46 @@
         <v>20755.174731968</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>25033.844</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>18.597</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>12.414</v>
       </c>
       <c r="O183" t="n">
-        <v>0</v>
+        <v>-6.458</v>
+      </c>
+      <c r="P183" t="n">
+        <v>-7.994</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>118689.709</v>
+      </c>
+      <c r="R183" t="n">
+        <v>25959.603</v>
+      </c>
+      <c r="S183" t="n">
+        <v>457.209</v>
+      </c>
+      <c r="T183" t="n">
+        <v>61.342</v>
+      </c>
+      <c r="U183" t="n">
+        <v>163.021</v>
+      </c>
+      <c r="V183" t="n">
+        <v>159.203</v>
+      </c>
+      <c r="W183" t="n">
+        <v>56.683</v>
+      </c>
+      <c r="X183" t="n">
+        <v>58.137</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>0.535</v>
       </c>
       <c r="AC183" t="n">
         <v>4.236</v>
@@ -53925,7 +53955,7 @@
       </c>
       <c r="BI183" t="inlineStr">
         <is>
-          <t>2026-09-18T08:37:05+07:00</t>
+          <t>2026-09-18T16:27:29+07:00</t>
         </is>
       </c>
     </row>
@@ -78407,6 +78437,69 @@
           <t>reported</t>
         </is>
       </c>
+      <c r="D183" t="n">
+        <v>1272.025</v>
+      </c>
+      <c r="E183" t="n">
+        <v>796.2670000000001</v>
+      </c>
+      <c r="F183" t="n">
+        <v>22965.552</v>
+      </c>
+      <c r="G183" t="n">
+        <v>-8322.723</v>
+      </c>
+      <c r="H183" t="n">
+        <v>-25404.243</v>
+      </c>
+      <c r="I183" t="n">
+        <v>13325.423</v>
+      </c>
+      <c r="J183" t="n">
+        <v>6400.924</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>38791.47</v>
+      </c>
+      <c r="N183" t="n">
+        <v>19213.554</v>
+      </c>
+      <c r="O183" t="n">
+        <v>60684.685</v>
+      </c>
+      <c r="P183" t="n">
+        <v>4933.256</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R183" t="n">
+        <v>1272.025</v>
+      </c>
+      <c r="S183" t="n">
+        <v>796.2670000000001</v>
+      </c>
+      <c r="T183" t="n">
+        <v>61757.022</v>
+      </c>
+      <c r="U183" t="n">
+        <v>10890.831</v>
+      </c>
+      <c r="V183" t="n">
+        <v>35280.442</v>
+      </c>
+      <c r="W183" t="n">
+        <v>18258.679</v>
+      </c>
+      <c r="X183" t="n">
+        <v>7700.924</v>
+      </c>
       <c r="Y183" t="n">
         <v>2068.292</v>
       </c>
@@ -78486,7 +78579,7 @@
       </c>
       <c r="CB183" t="inlineStr">
         <is>
-          <t>2026-09-18T08:37:05+07:00</t>
+          <t>2026-09-18T16:27:29+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_RawBuckets" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ALM_NganHang_RawBuckets" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30963,7 +30963,7 @@
         <v>2.644</v>
       </c>
       <c r="AI2" t="n">
-        <v>5142.782000000002</v>
+        <v>5142.781999999998</v>
       </c>
       <c r="AJ2" t="n">
         <v>-6.842</v>
@@ -31124,7 +31124,7 @@
         <v>2.349</v>
       </c>
       <c r="AI3" t="n">
-        <v>6180.512000000001</v>
+        <v>6180.511999999999</v>
       </c>
       <c r="AJ3" t="n">
         <v>-6.22</v>
@@ -31529,7 +31529,7 @@
         <v>2.034</v>
       </c>
       <c r="AI6" t="n">
-        <v>8183.362999999999</v>
+        <v>8183.362999999996</v>
       </c>
       <c r="AJ6" t="n">
         <v>-7.633</v>
@@ -31651,7 +31651,7 @@
         <v>1.786</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2072.081999999999</v>
+        <v>-2072.081999999995</v>
       </c>
       <c r="AJ7" t="n">
         <v>-6.467</v>
@@ -31803,7 +31803,7 @@
         <v>2.198</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5551.593000000001</v>
+        <v>-5551.592999999999</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.38</v>
@@ -32077,7 +32077,7 @@
         <v>1.383</v>
       </c>
       <c r="AI10" t="n">
-        <v>72159.24699999997</v>
+        <v>72159.24699999994</v>
       </c>
       <c r="AJ10" t="n">
         <v>-11.405</v>
@@ -32238,7 +32238,7 @@
         <v>1.248</v>
       </c>
       <c r="AI11" t="n">
-        <v>75182.47699999998</v>
+        <v>75182.47699999997</v>
       </c>
       <c r="AJ11" t="n">
         <v>-9.868</v>
@@ -32551,7 +32551,7 @@
         <v>1.212</v>
       </c>
       <c r="AI13" t="n">
-        <v>85041.658</v>
+        <v>85041.65799999997</v>
       </c>
       <c r="AJ13" t="n">
         <v>-9.567</v>
@@ -34664,7 +34664,7 @@
         <v>0.912</v>
       </c>
       <c r="AI27" t="n">
-        <v>482308.417</v>
+        <v>482308.4170000001</v>
       </c>
       <c r="AJ27" t="n">
         <v>12.989</v>
@@ -35994,7 +35994,7 @@
         <v>1.282</v>
       </c>
       <c r="AI36" t="n">
-        <v>-2093.930000000001</v>
+        <v>-2093.93</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
@@ -37895,7 +37895,7 @@
         <v>584740.964</v>
       </c>
       <c r="O49" t="n">
-        <v>57219.161</v>
+        <v>57219.16100000001</v>
       </c>
       <c r="P49" t="n">
         <v>1.932</v>
@@ -38169,7 +38169,7 @@
         <v>1.207</v>
       </c>
       <c r="AI51" t="n">
-        <v>536.0379999999996</v>
+        <v>536.0379999999986</v>
       </c>
       <c r="AJ51" t="n">
         <v>-8.407999999999999</v>
@@ -38595,7 +38595,7 @@
         <v>1.219</v>
       </c>
       <c r="AI54" t="n">
-        <v>-6843.676</v>
+        <v>-6843.675999999999</v>
       </c>
       <c r="AJ54" t="n">
         <v>-9.135999999999999</v>
@@ -38836,7 +38836,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="O56" t="n">
-        <v>2554.764</v>
+        <v>2554.764000000001</v>
       </c>
       <c r="P56" t="n">
         <v>0.946</v>
@@ -39128,7 +39128,7 @@
         <v>113076.542</v>
       </c>
       <c r="O58" t="n">
-        <v>89209.497</v>
+        <v>89209.49699999999</v>
       </c>
       <c r="P58" t="n">
         <v>14.805</v>
@@ -40180,7 +40180,7 @@
         <v>1.506</v>
       </c>
       <c r="AI65" t="n">
-        <v>1097.083000000001</v>
+        <v>1097.082999999999</v>
       </c>
       <c r="AJ65" t="n">
         <v>3.244</v>
@@ -42901,7 +42901,7 @@
         <v>0.909</v>
       </c>
       <c r="AI83" t="n">
-        <v>20403.41100000001</v>
+        <v>20403.411</v>
       </c>
       <c r="AJ83" t="n">
         <v>-10.621</v>
@@ -43843,7 +43843,7 @@
       </c>
       <c r="BL90" t="inlineStr">
         <is>
-          <t>2026-09-18T11:56:55+07:00</t>
+          <t>2026-09-18T16:44:46+07:00</t>
         </is>
       </c>
     </row>
@@ -44031,7 +44031,7 @@
         <v>53049.641</v>
       </c>
       <c r="O92" t="n">
-        <v>-71627.23299999999</v>
+        <v>-71627.23300000001</v>
       </c>
       <c r="P92" t="n">
         <v>-22.759</v>
@@ -44532,7 +44532,7 @@
         <v>2.167</v>
       </c>
       <c r="AI95" t="n">
-        <v>-36336.335</v>
+        <v>-36336.33499999999</v>
       </c>
       <c r="AJ95" t="n">
         <v>7.502</v>
@@ -44937,7 +44937,7 @@
         <v>1.218</v>
       </c>
       <c r="AI98" t="n">
-        <v>9206.203</v>
+        <v>9206.203000000001</v>
       </c>
       <c r="AJ98" t="n">
         <v>-4.209</v>
@@ -45229,7 +45229,7 @@
         <v>1.52</v>
       </c>
       <c r="AI100" t="n">
-        <v>1044.137999999998</v>
+        <v>1044.137999999999</v>
       </c>
       <c r="AJ100" t="n">
         <v>-0.302</v>
@@ -45381,7 +45381,7 @@
         <v>2.243</v>
       </c>
       <c r="AI101" t="n">
-        <v>-7342.066000000001</v>
+        <v>-7342.066000000003</v>
       </c>
       <c r="AJ101" t="n">
         <v>1.12</v>
@@ -46040,7 +46040,7 @@
       </c>
       <c r="BL106" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00:15+07:00</t>
+          <t>2026-09-18T16:46:20+07:00</t>
         </is>
       </c>
     </row>
@@ -46097,7 +46097,7 @@
         <v>10333.757</v>
       </c>
       <c r="O107" t="n">
-        <v>4585.813</v>
+        <v>4585.812999999998</v>
       </c>
       <c r="P107" t="n">
         <v>4.439</v>
@@ -46684,7 +46684,7 @@
         <v>1.53</v>
       </c>
       <c r="AI111" t="n">
-        <v>44447.07199999999</v>
+        <v>44447.072</v>
       </c>
       <c r="AJ111" t="n">
         <v>41.067</v>
@@ -47053,7 +47053,7 @@
         <v>43767.119108461</v>
       </c>
       <c r="O114" t="n">
-        <v>45040.48364739501</v>
+        <v>45040.483647395</v>
       </c>
       <c r="P114" t="n">
         <v>19.006</v>
@@ -47104,7 +47104,7 @@
         <v>1.727</v>
       </c>
       <c r="AI114" t="n">
-        <v>73880.39491509201</v>
+        <v>73880.39491509199</v>
       </c>
       <c r="AJ114" t="n">
         <v>13.551</v>
@@ -47848,7 +47848,7 @@
         <v>57104.9273618</v>
       </c>
       <c r="O119" t="n">
-        <v>-8354.105685278011</v>
+        <v>-8354.105685278017</v>
       </c>
       <c r="P119" t="n">
         <v>-2.587</v>
@@ -48433,7 +48433,7 @@
       </c>
       <c r="BL123" t="inlineStr">
         <is>
-          <t>2026-09-18T12:03:53+07:00</t>
+          <t>2026-09-18T16:47:58+07:00</t>
         </is>
       </c>
     </row>
@@ -49107,7 +49107,7 @@
         <v>3.214</v>
       </c>
       <c r="AI128" t="n">
-        <v>-448.7119999999998</v>
+        <v>-448.712</v>
       </c>
       <c r="AJ128" t="n">
         <v>-8.398</v>
@@ -49462,7 +49462,7 @@
       </c>
       <c r="BL131" t="inlineStr">
         <is>
-          <t>2026-09-18T12:05:01+07:00</t>
+          <t>2026-09-18T16:49:11+07:00</t>
         </is>
       </c>
     </row>
@@ -49692,7 +49692,7 @@
         <v>1.841</v>
       </c>
       <c r="AI133" t="n">
-        <v>-8415.234</v>
+        <v>-8415.234000000002</v>
       </c>
       <c r="AJ133" t="n">
         <v>-5.98</v>
@@ -50470,7 +50470,7 @@
       </c>
       <c r="BL139" t="inlineStr">
         <is>
-          <t>2026-09-18T12:05:48+07:00</t>
+          <t>2026-09-18T16:49:58+07:00</t>
         </is>
       </c>
     </row>
@@ -50527,7 +50527,7 @@
         <v>110803.352</v>
       </c>
       <c r="O140" t="n">
-        <v>84929.84099999999</v>
+        <v>84929.841</v>
       </c>
       <c r="P140" t="n">
         <v>12.871</v>
@@ -54410,7 +54410,7 @@
         <v>1.628</v>
       </c>
       <c r="AI168" t="n">
-        <v>-95355.82799999999</v>
+        <v>-95355.82799999998</v>
       </c>
       <c r="AJ168" t="n">
         <v>-8.385</v>
@@ -54571,7 +54571,7 @@
         <v>1.553</v>
       </c>
       <c r="AI169" t="n">
-        <v>31803.233</v>
+        <v>31803.23300000001</v>
       </c>
       <c r="AJ169" t="n">
         <v>4.369</v>
@@ -54764,7 +54764,7 @@
         <v>1.392</v>
       </c>
       <c r="AI170" t="n">
-        <v>49624.19499999999</v>
+        <v>49624.19500000001</v>
       </c>
       <c r="AJ170" t="n">
         <v>9.231999999999999</v>
@@ -55253,7 +55253,7 @@
         <v>1.148</v>
       </c>
       <c r="AI173" t="n">
-        <v>47597.06099999999</v>
+        <v>47597.061</v>
       </c>
       <c r="AJ173" t="n">
         <v>12.611</v>
@@ -56158,7 +56158,7 @@
       </c>
       <c r="BL179" t="inlineStr">
         <is>
-          <t>2026-09-18T12:16:10+07:00</t>
+          <t>2026-09-18T16:52:58+07:00</t>
         </is>
       </c>
     </row>
@@ -56236,7 +56236,7 @@
         <v>0.951</v>
       </c>
       <c r="AI180" t="n">
-        <v>786.7630000000004</v>
+        <v>786.7630000000008</v>
       </c>
       <c r="AJ180" t="n">
         <v>0.008999999999999999</v>
@@ -57294,7 +57294,7 @@
       </c>
       <c r="BL187" t="inlineStr">
         <is>
-          <t>2026-09-18T12:17:37+07:00</t>
+          <t>2026-09-18T16:54:28+07:00</t>
         </is>
       </c>
     </row>
@@ -60095,7 +60095,7 @@
         <v>1.861</v>
       </c>
       <c r="AI207" t="n">
-        <v>18205.905</v>
+        <v>18205.90499999999</v>
       </c>
       <c r="AJ207" t="n">
         <v>-11.997</v>
@@ -72701,7 +72701,7 @@
       </c>
       <c r="CE90" t="inlineStr">
         <is>
-          <t>2026-09-18T11:56:55+07:00</t>
+          <t>2026-09-18T16:44:46+07:00</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74586,7 @@
       </c>
       <c r="CE106" t="inlineStr">
         <is>
-          <t>2026-09-18T12:00:15+07:00</t>
+          <t>2026-09-18T16:46:20+07:00</t>
         </is>
       </c>
     </row>
@@ -76840,7 +76840,7 @@
       </c>
       <c r="CE123" t="inlineStr">
         <is>
-          <t>2026-09-18T12:03:53+07:00</t>
+          <t>2026-09-18T16:47:58+07:00</t>
         </is>
       </c>
     </row>
@@ -77702,7 +77702,7 @@
       </c>
       <c r="CE131" t="inlineStr">
         <is>
-          <t>2026-09-18T12:05:01+07:00</t>
+          <t>2026-09-18T16:49:11+07:00</t>
         </is>
       </c>
     </row>
@@ -78492,7 +78492,7 @@
       </c>
       <c r="CE139" t="inlineStr">
         <is>
-          <t>2026-09-18T12:05:48+07:00</t>
+          <t>2026-09-18T16:49:58+07:00</t>
         </is>
       </c>
     </row>
@@ -84009,7 +84009,7 @@
       </c>
       <c r="CE179" t="inlineStr">
         <is>
-          <t>2026-09-18T12:16:10+07:00</t>
+          <t>2026-09-18T16:52:58+07:00</t>
         </is>
       </c>
     </row>
@@ -85029,7 +85029,7 @@
       </c>
       <c r="CE187" t="inlineStr">
         <is>
-          <t>2026-09-18T12:17:37+07:00</t>
+          <t>2026-09-18T16:54:28+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ALM_NganHang_RawBuckets" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_RawBuckets" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30963,7 +30963,7 @@
         <v>2.644</v>
       </c>
       <c r="AI2" t="n">
-        <v>5142.781999999998</v>
+        <v>5142.782000000002</v>
       </c>
       <c r="AJ2" t="n">
         <v>-6.842</v>
@@ -31124,7 +31124,7 @@
         <v>2.349</v>
       </c>
       <c r="AI3" t="n">
-        <v>6180.511999999999</v>
+        <v>6180.512000000001</v>
       </c>
       <c r="AJ3" t="n">
         <v>-6.22</v>
@@ -31316,7 +31316,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -31529,7 +31529,7 @@
         <v>2.034</v>
       </c>
       <c r="AI6" t="n">
-        <v>8183.362999999996</v>
+        <v>8183.362999999999</v>
       </c>
       <c r="AJ6" t="n">
         <v>-7.633</v>
@@ -31590,7 +31590,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -31651,7 +31651,7 @@
         <v>1.786</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2072.081999999995</v>
+        <v>-2072.081999999999</v>
       </c>
       <c r="AJ7" t="n">
         <v>-6.467</v>
@@ -31803,7 +31803,7 @@
         <v>2.198</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5551.592999999999</v>
+        <v>-5551.593000000001</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.38</v>
@@ -31864,7 +31864,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -32077,7 +32077,7 @@
         <v>1.383</v>
       </c>
       <c r="AI10" t="n">
-        <v>72159.24699999994</v>
+        <v>72159.24699999997</v>
       </c>
       <c r="AJ10" t="n">
         <v>-11.405</v>
@@ -32238,7 +32238,7 @@
         <v>1.248</v>
       </c>
       <c r="AI11" t="n">
-        <v>75182.47699999997</v>
+        <v>75182.47699999998</v>
       </c>
       <c r="AJ11" t="n">
         <v>-9.868</v>
@@ -32551,7 +32551,7 @@
         <v>1.212</v>
       </c>
       <c r="AI13" t="n">
-        <v>85041.65799999997</v>
+        <v>85041.658</v>
       </c>
       <c r="AJ13" t="n">
         <v>-9.567</v>
@@ -32612,7 +32612,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -32925,7 +32925,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -33980,7 +33980,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -34664,7 +34664,7 @@
         <v>0.912</v>
       </c>
       <c r="AI27" t="n">
-        <v>482308.4170000001</v>
+        <v>482308.417</v>
       </c>
       <c r="AJ27" t="n">
         <v>12.989</v>
@@ -34890,7 +34890,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -35337,7 +35337,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -35933,7 +35933,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -35994,7 +35994,7 @@
         <v>1.282</v>
       </c>
       <c r="AI36" t="n">
-        <v>-2093.93</v>
+        <v>-2093.930000000001</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
@@ -36055,7 +36055,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -36329,7 +36329,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -37095,7 +37095,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -37399,7 +37399,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -37895,7 +37895,7 @@
         <v>584740.964</v>
       </c>
       <c r="O49" t="n">
-        <v>57219.16100000001</v>
+        <v>57219.161</v>
       </c>
       <c r="P49" t="n">
         <v>1.932</v>
@@ -38108,7 +38108,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -38169,7 +38169,7 @@
         <v>1.207</v>
       </c>
       <c r="AI51" t="n">
-        <v>536.0379999999986</v>
+        <v>536.0379999999996</v>
       </c>
       <c r="AJ51" t="n">
         <v>-8.407999999999999</v>
@@ -38534,7 +38534,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -38595,7 +38595,7 @@
         <v>1.219</v>
       </c>
       <c r="AI54" t="n">
-        <v>-6843.675999999999</v>
+        <v>-6843.676</v>
       </c>
       <c r="AJ54" t="n">
         <v>-9.135999999999999</v>
@@ -38656,7 +38656,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -38836,7 +38836,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="O56" t="n">
-        <v>2554.764000000001</v>
+        <v>2554.764</v>
       </c>
       <c r="P56" t="n">
         <v>0.946</v>
@@ -38948,7 +38948,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -39128,7 +39128,7 @@
         <v>113076.542</v>
       </c>
       <c r="O58" t="n">
-        <v>89209.49699999999</v>
+        <v>89209.497</v>
       </c>
       <c r="P58" t="n">
         <v>14.805</v>
@@ -39252,7 +39252,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -39684,7 +39684,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -40119,7 +40119,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -40180,7 +40180,7 @@
         <v>1.506</v>
       </c>
       <c r="AI65" t="n">
-        <v>1097.082999999999</v>
+        <v>1097.083000000001</v>
       </c>
       <c r="AJ65" t="n">
         <v>3.244</v>
@@ -40530,7 +40530,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -40682,7 +40682,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -40986,7 +40986,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -41782,7 +41782,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -42092,7 +42092,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -42375,7 +42375,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -42840,7 +42840,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -42901,7 +42901,7 @@
         <v>0.909</v>
       </c>
       <c r="AI83" t="n">
-        <v>20403.411</v>
+        <v>20403.41100000001</v>
       </c>
       <c r="AJ83" t="n">
         <v>-10.621</v>
@@ -43123,7 +43123,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -43701,7 +43701,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -43860,7 +43860,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -44031,7 +44031,7 @@
         <v>53049.641</v>
       </c>
       <c r="O92" t="n">
-        <v>-71627.23300000001</v>
+        <v>-71627.23299999999</v>
       </c>
       <c r="P92" t="n">
         <v>-22.759</v>
@@ -44532,7 +44532,7 @@
         <v>2.167</v>
       </c>
       <c r="AI95" t="n">
-        <v>-36336.33499999999</v>
+        <v>-36336.335</v>
       </c>
       <c r="AJ95" t="n">
         <v>7.502</v>
@@ -44593,7 +44593,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -44937,7 +44937,7 @@
         <v>1.218</v>
       </c>
       <c r="AI98" t="n">
-        <v>9206.203000000001</v>
+        <v>9206.203</v>
       </c>
       <c r="AJ98" t="n">
         <v>-4.209</v>
@@ -45007,7 +45007,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -45229,7 +45229,7 @@
         <v>1.52</v>
       </c>
       <c r="AI100" t="n">
-        <v>1044.137999999999</v>
+        <v>1044.137999999998</v>
       </c>
       <c r="AJ100" t="n">
         <v>-0.302</v>
@@ -45381,7 +45381,7 @@
         <v>2.243</v>
       </c>
       <c r="AI101" t="n">
-        <v>-7342.066000000003</v>
+        <v>-7342.066000000001</v>
       </c>
       <c r="AJ101" t="n">
         <v>1.12</v>
@@ -45898,7 +45898,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -46097,7 +46097,7 @@
         <v>10333.757</v>
       </c>
       <c r="O107" t="n">
-        <v>4585.812999999998</v>
+        <v>4585.813</v>
       </c>
       <c r="P107" t="n">
         <v>4.439</v>
@@ -46355,7 +46355,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -46623,7 +46623,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -46684,7 +46684,7 @@
         <v>1.53</v>
       </c>
       <c r="AI111" t="n">
-        <v>44447.072</v>
+        <v>44447.07199999999</v>
       </c>
       <c r="AJ111" t="n">
         <v>41.067</v>
@@ -47053,7 +47053,7 @@
         <v>43767.119108461</v>
       </c>
       <c r="O114" t="n">
-        <v>45040.483647395</v>
+        <v>45040.48364739501</v>
       </c>
       <c r="P114" t="n">
         <v>19.006</v>
@@ -47104,7 +47104,7 @@
         <v>1.727</v>
       </c>
       <c r="AI114" t="n">
-        <v>73880.39491509199</v>
+        <v>73880.39491509201</v>
       </c>
       <c r="AJ114" t="n">
         <v>13.551</v>
@@ -47848,7 +47848,7 @@
         <v>57104.9273618</v>
       </c>
       <c r="O119" t="n">
-        <v>-8354.105685278017</v>
+        <v>-8354.105685278011</v>
       </c>
       <c r="P119" t="n">
         <v>-2.587</v>
@@ -48319,7 +48319,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -48620,7 +48620,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -48894,7 +48894,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -49107,7 +49107,7 @@
         <v>3.214</v>
       </c>
       <c r="AI128" t="n">
-        <v>-448.712</v>
+        <v>-448.7119999999998</v>
       </c>
       <c r="AJ128" t="n">
         <v>-8.398</v>
@@ -49168,7 +49168,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -49692,7 +49692,7 @@
         <v>1.841</v>
       </c>
       <c r="AI133" t="n">
-        <v>-8415.234000000002</v>
+        <v>-8415.234</v>
       </c>
       <c r="AJ133" t="n">
         <v>-5.98</v>
@@ -50298,7 +50298,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -50527,7 +50527,7 @@
         <v>110803.352</v>
       </c>
       <c r="O140" t="n">
-        <v>84929.841</v>
+        <v>84929.84099999999</v>
       </c>
       <c r="P140" t="n">
         <v>12.871</v>
@@ -51391,7 +51391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -51522,7 +51522,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -51668,7 +51668,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -52246,7 +52246,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -52696,7 +52696,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -52818,7 +52818,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -52970,7 +52970,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -53092,7 +53092,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -54048,7 +54048,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -54410,7 +54410,7 @@
         <v>1.628</v>
       </c>
       <c r="AI168" t="n">
-        <v>-95355.82799999998</v>
+        <v>-95355.82799999999</v>
       </c>
       <c r="AJ168" t="n">
         <v>-8.385</v>
@@ -54571,7 +54571,7 @@
         <v>1.553</v>
       </c>
       <c r="AI169" t="n">
-        <v>31803.23300000001</v>
+        <v>31803.233</v>
       </c>
       <c r="AJ169" t="n">
         <v>4.369</v>
@@ -54764,7 +54764,7 @@
         <v>1.392</v>
       </c>
       <c r="AI170" t="n">
-        <v>49624.19500000001</v>
+        <v>49624.19499999999</v>
       </c>
       <c r="AJ170" t="n">
         <v>9.231999999999999</v>
@@ -55253,7 +55253,7 @@
         <v>1.148</v>
       </c>
       <c r="AI173" t="n">
-        <v>47597.061</v>
+        <v>47597.06099999999</v>
       </c>
       <c r="AJ173" t="n">
         <v>12.611</v>
@@ -55645,7 +55645,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -55922,7 +55922,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -56044,7 +56044,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -56175,7 +56175,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -56236,7 +56236,7 @@
         <v>0.951</v>
       </c>
       <c r="AI180" t="n">
-        <v>786.7630000000008</v>
+        <v>786.7630000000004</v>
       </c>
       <c r="AJ180" t="n">
         <v>0.008999999999999999</v>
@@ -56306,7 +56306,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -56428,7 +56428,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -57180,7 +57180,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -57472,7 +57472,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -57746,7 +57746,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -57868,7 +57868,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -58020,7 +58020,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -58768,7 +58768,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -59051,7 +59051,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -59325,7 +59325,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -59599,7 +59599,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -59730,7 +59730,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -60095,7 +60095,7 @@
         <v>1.861</v>
       </c>
       <c r="AI207" t="n">
-        <v>18205.90499999999</v>
+        <v>18205.905</v>
       </c>
       <c r="AJ207" t="n">
         <v>-11.997</v>
@@ -60156,7 +60156,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -60430,7 +60430,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -61572,7 +61572,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -61767,7 +61767,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -61962,7 +61962,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -62640,7 +62640,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -62922,7 +62922,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -63897,7 +63897,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -64854,7 +64854,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -65322,7 +65322,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -65871,7 +65871,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -65937,7 +65937,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -66132,7 +66132,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -66849,7 +66849,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -67083,7 +67083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -67668,7 +67668,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -68040,7 +68040,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -68106,7 +68106,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -68340,7 +68340,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -68664,7 +68664,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -69084,7 +69084,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -69453,7 +69453,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -69825,7 +69825,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -69930,7 +69930,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -70164,7 +70164,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -70269,7 +70269,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -70983,7 +70983,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -71265,7 +71265,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -71508,7 +71508,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -71919,7 +71919,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -72162,7 +72162,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -72615,7 +72615,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -72718,7 +72718,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -73348,7 +73348,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -73741,7 +73741,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -74500,7 +74500,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -74861,7 +74861,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -75056,7 +75056,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -76743,7 +76743,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -77097,7 +77097,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -77292,7 +77292,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -77487,7 +77487,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -78367,7 +78367,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -79472,7 +79472,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -79586,7 +79586,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -79691,7 +79691,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -80141,7 +80141,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -80603,7 +80603,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -80708,7 +80708,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -80813,7 +80813,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -80876,7 +80876,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -81944,7 +81944,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -83603,7 +83603,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -83846,7 +83846,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -83912,7 +83912,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -84026,7 +84026,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -84140,7 +84140,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -84206,7 +84206,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -84932,7 +84932,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -85223,7 +85223,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -85418,7 +85418,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -85484,7 +85484,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -85589,7 +85589,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -86330,7 +86330,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -86573,7 +86573,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -86768,7 +86768,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -86963,7 +86963,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -87077,7 +87077,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -87401,7 +87401,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -87596,7 +87596,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>reported</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ALM_NganHang_RawBuckets" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Theo quý" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Theo tháng" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Theo năm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Lũy kế (H1-9M-FY)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Theo ngày" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Theo tuần" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ALM_NganHang_Raw" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ALM_NganHang_RawBuckets" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30963,7 +30963,7 @@
         <v>2.644</v>
       </c>
       <c r="AI2" t="n">
-        <v>5142.782000000002</v>
+        <v>5142.781999999998</v>
       </c>
       <c r="AJ2" t="n">
         <v>-6.842</v>
@@ -31124,7 +31124,7 @@
         <v>2.349</v>
       </c>
       <c r="AI3" t="n">
-        <v>6180.512000000001</v>
+        <v>6180.511999999999</v>
       </c>
       <c r="AJ3" t="n">
         <v>-6.22</v>
@@ -31529,7 +31529,7 @@
         <v>2.034</v>
       </c>
       <c r="AI6" t="n">
-        <v>8183.362999999999</v>
+        <v>8183.362999999996</v>
       </c>
       <c r="AJ6" t="n">
         <v>-7.633</v>
@@ -31651,7 +31651,7 @@
         <v>1.786</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2072.081999999999</v>
+        <v>-2072.081999999995</v>
       </c>
       <c r="AJ7" t="n">
         <v>-6.467</v>
@@ -31803,7 +31803,7 @@
         <v>2.198</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5551.593000000001</v>
+        <v>-5551.592999999999</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.38</v>
@@ -32077,7 +32077,7 @@
         <v>1.383</v>
       </c>
       <c r="AI10" t="n">
-        <v>72159.24699999997</v>
+        <v>72159.24699999994</v>
       </c>
       <c r="AJ10" t="n">
         <v>-11.405</v>
@@ -32238,7 +32238,7 @@
         <v>1.248</v>
       </c>
       <c r="AI11" t="n">
-        <v>75182.47699999998</v>
+        <v>75182.47699999997</v>
       </c>
       <c r="AJ11" t="n">
         <v>-9.868</v>
@@ -32551,7 +32551,7 @@
         <v>1.212</v>
       </c>
       <c r="AI13" t="n">
-        <v>85041.658</v>
+        <v>85041.65799999997</v>
       </c>
       <c r="AJ13" t="n">
         <v>-9.567</v>
@@ -34664,7 +34664,7 @@
         <v>0.912</v>
       </c>
       <c r="AI27" t="n">
-        <v>482308.417</v>
+        <v>482308.4170000001</v>
       </c>
       <c r="AJ27" t="n">
         <v>12.989</v>
@@ -35994,7 +35994,7 @@
         <v>1.282</v>
       </c>
       <c r="AI36" t="n">
-        <v>-2093.930000000001</v>
+        <v>-2093.93</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
@@ -37895,7 +37895,7 @@
         <v>584740.964</v>
       </c>
       <c r="O49" t="n">
-        <v>57219.161</v>
+        <v>57219.16100000001</v>
       </c>
       <c r="P49" t="n">
         <v>1.932</v>
@@ -38169,7 +38169,7 @@
         <v>1.207</v>
       </c>
       <c r="AI51" t="n">
-        <v>536.0379999999996</v>
+        <v>536.0379999999986</v>
       </c>
       <c r="AJ51" t="n">
         <v>-8.407999999999999</v>
@@ -38595,7 +38595,7 @@
         <v>1.219</v>
       </c>
       <c r="AI54" t="n">
-        <v>-6843.676</v>
+        <v>-6843.675999999999</v>
       </c>
       <c r="AJ54" t="n">
         <v>-9.135999999999999</v>
@@ -38836,7 +38836,7 @@
         <v>42408.00799999999</v>
       </c>
       <c r="O56" t="n">
-        <v>2554.764</v>
+        <v>2554.764000000001</v>
       </c>
       <c r="P56" t="n">
         <v>0.946</v>
@@ -39128,7 +39128,7 @@
         <v>113076.542</v>
       </c>
       <c r="O58" t="n">
-        <v>89209.497</v>
+        <v>89209.49699999999</v>
       </c>
       <c r="P58" t="n">
         <v>14.805</v>
@@ -40180,7 +40180,7 @@
         <v>1.506</v>
       </c>
       <c r="AI65" t="n">
-        <v>1097.083000000001</v>
+        <v>1097.082999999999</v>
       </c>
       <c r="AJ65" t="n">
         <v>3.244</v>
@@ -42901,7 +42901,7 @@
         <v>0.909</v>
       </c>
       <c r="AI83" t="n">
-        <v>20403.41100000001</v>
+        <v>20403.411</v>
       </c>
       <c r="AJ83" t="n">
         <v>-10.621</v>
@@ -43843,7 +43843,7 @@
       </c>
       <c r="BL90" t="inlineStr">
         <is>
-          <t>2026-09-18T16:44:46+07:00</t>
+          <t>2026-09-18T17:53:32+07:00</t>
         </is>
       </c>
     </row>
@@ -44031,7 +44031,7 @@
         <v>53049.641</v>
       </c>
       <c r="O92" t="n">
-        <v>-71627.23299999999</v>
+        <v>-71627.23300000001</v>
       </c>
       <c r="P92" t="n">
         <v>-22.759</v>
@@ -44532,7 +44532,7 @@
         <v>2.167</v>
       </c>
       <c r="AI95" t="n">
-        <v>-36336.335</v>
+        <v>-36336.33499999999</v>
       </c>
       <c r="AJ95" t="n">
         <v>7.502</v>
@@ -44937,7 +44937,7 @@
         <v>1.218</v>
       </c>
       <c r="AI98" t="n">
-        <v>9206.203</v>
+        <v>9206.203000000001</v>
       </c>
       <c r="AJ98" t="n">
         <v>-4.209</v>
@@ -45229,7 +45229,7 @@
         <v>1.52</v>
       </c>
       <c r="AI100" t="n">
-        <v>1044.137999999998</v>
+        <v>1044.137999999999</v>
       </c>
       <c r="AJ100" t="n">
         <v>-0.302</v>
@@ -45381,7 +45381,7 @@
         <v>2.243</v>
       </c>
       <c r="AI101" t="n">
-        <v>-7342.066000000001</v>
+        <v>-7342.066000000003</v>
       </c>
       <c r="AJ101" t="n">
         <v>1.12</v>
@@ -46040,7 +46040,7 @@
       </c>
       <c r="BL106" t="inlineStr">
         <is>
-          <t>2026-09-18T16:46:20+07:00</t>
+          <t>2026-09-18T17:55:07+07:00</t>
         </is>
       </c>
     </row>
@@ -46097,7 +46097,7 @@
         <v>10333.757</v>
       </c>
       <c r="O107" t="n">
-        <v>4585.813</v>
+        <v>4585.812999999998</v>
       </c>
       <c r="P107" t="n">
         <v>4.439</v>
@@ -46684,7 +46684,7 @@
         <v>1.53</v>
       </c>
       <c r="AI111" t="n">
-        <v>44447.07199999999</v>
+        <v>44447.072</v>
       </c>
       <c r="AJ111" t="n">
         <v>41.067</v>
@@ -47053,7 +47053,7 @@
         <v>43767.119108461</v>
       </c>
       <c r="O114" t="n">
-        <v>45040.48364739501</v>
+        <v>45040.483647395</v>
       </c>
       <c r="P114" t="n">
         <v>19.006</v>
@@ -47104,7 +47104,7 @@
         <v>1.727</v>
       </c>
       <c r="AI114" t="n">
-        <v>73880.39491509201</v>
+        <v>73880.39491509199</v>
       </c>
       <c r="AJ114" t="n">
         <v>13.551</v>
@@ -47848,7 +47848,7 @@
         <v>57104.9273618</v>
       </c>
       <c r="O119" t="n">
-        <v>-8354.105685278011</v>
+        <v>-8354.105685278017</v>
       </c>
       <c r="P119" t="n">
         <v>-2.587</v>
@@ -48334,7 +48334,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -48421,6 +48421,47 @@
       <c r="AV123" t="n">
         <v>-1.589</v>
       </c>
+      <c r="AW123" t="n">
+        <v>2538163</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>2526736</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>11427</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>-28544</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>-2844</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>1035</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>3879</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>-0.112</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>-4.84</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>20.881</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>78.259</v>
+      </c>
+      <c r="BH123" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BI123" t="n">
+        <v>-284.4</v>
+      </c>
       <c r="BJ123" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2024</t>
@@ -48433,7 +48474,7 @@
       </c>
       <c r="BL123" t="inlineStr">
         <is>
-          <t>2026-09-18T16:47:58+07:00</t>
+          <t>2026-09-18T17:56:46+07:00</t>
         </is>
       </c>
     </row>
@@ -49107,7 +49148,7 @@
         <v>3.214</v>
       </c>
       <c r="AI128" t="n">
-        <v>-448.7119999999998</v>
+        <v>-448.712</v>
       </c>
       <c r="AJ128" t="n">
         <v>-8.398</v>
@@ -49462,7 +49503,7 @@
       </c>
       <c r="BL131" t="inlineStr">
         <is>
-          <t>2026-09-18T16:49:11+07:00</t>
+          <t>2026-09-18T17:57:55+07:00</t>
         </is>
       </c>
     </row>
@@ -49692,7 +49733,7 @@
         <v>1.841</v>
       </c>
       <c r="AI133" t="n">
-        <v>-8415.234</v>
+        <v>-8415.234000000002</v>
       </c>
       <c r="AJ133" t="n">
         <v>-5.98</v>
@@ -50470,7 +50511,7 @@
       </c>
       <c r="BL139" t="inlineStr">
         <is>
-          <t>2026-09-18T16:49:58+07:00</t>
+          <t>2026-09-18T17:58:41+07:00</t>
         </is>
       </c>
     </row>
@@ -50527,7 +50568,7 @@
         <v>110803.352</v>
       </c>
       <c r="O140" t="n">
-        <v>84929.84099999999</v>
+        <v>84929.841</v>
       </c>
       <c r="P140" t="n">
         <v>12.871</v>
@@ -54410,7 +54451,7 @@
         <v>1.628</v>
       </c>
       <c r="AI168" t="n">
-        <v>-95355.82799999999</v>
+        <v>-95355.82799999998</v>
       </c>
       <c r="AJ168" t="n">
         <v>-8.385</v>
@@ -54571,7 +54612,7 @@
         <v>1.553</v>
       </c>
       <c r="AI169" t="n">
-        <v>31803.233</v>
+        <v>31803.23300000001</v>
       </c>
       <c r="AJ169" t="n">
         <v>4.369</v>
@@ -54764,7 +54805,7 @@
         <v>1.392</v>
       </c>
       <c r="AI170" t="n">
-        <v>49624.19499999999</v>
+        <v>49624.19500000001</v>
       </c>
       <c r="AJ170" t="n">
         <v>9.231999999999999</v>
@@ -55253,7 +55294,7 @@
         <v>1.148</v>
       </c>
       <c r="AI173" t="n">
-        <v>47597.06099999999</v>
+        <v>47597.061</v>
       </c>
       <c r="AJ173" t="n">
         <v>12.611</v>
@@ -56059,7 +56100,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="H179" t="n">
@@ -56146,6 +56187,47 @@
       <c r="AV179" t="n">
         <v>74.886</v>
       </c>
+      <c r="AW179" t="n">
+        <v>87647.588</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>105619.688</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>866.405</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>866.405</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>1529.09</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>662.6849999999999</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>18.656</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>8.085000000000001</v>
+      </c>
+      <c r="BH179" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
+      <c r="BI179" t="n">
+        <v>86.64</v>
+      </c>
       <c r="BJ179" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2024</t>
@@ -56158,7 +56240,7 @@
       </c>
       <c r="BL179" t="inlineStr">
         <is>
-          <t>2026-09-18T16:52:58+07:00</t>
+          <t>2026-09-18T18:01:54+07:00</t>
         </is>
       </c>
     </row>
@@ -56236,7 +56318,7 @@
         <v>0.951</v>
       </c>
       <c r="AI180" t="n">
-        <v>786.7630000000004</v>
+        <v>786.7630000000008</v>
       </c>
       <c r="AJ180" t="n">
         <v>0.008999999999999999</v>
@@ -57195,7 +57277,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="H187" t="n">
@@ -57282,6 +57364,47 @@
       <c r="AV187" t="n">
         <v>-143.557</v>
       </c>
+      <c r="AW187" t="n">
+        <v>139619.731</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>110975.915</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>28643.816</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>28643.816</v>
+      </c>
+      <c r="BB187" t="n">
+        <v>136890.862</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>108247.046</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>20.516</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>20.628</v>
+      </c>
+      <c r="BF187" t="n">
+        <v>1968.866</v>
+      </c>
+      <c r="BG187" t="n">
+        <v>1556.889</v>
+      </c>
+      <c r="BH187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="BI187" t="n">
+        <v>2864.382</v>
+      </c>
       <c r="BJ187" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2024</t>
@@ -57294,7 +57417,7 @@
       </c>
       <c r="BL187" t="inlineStr">
         <is>
-          <t>2026-09-18T16:54:28+07:00</t>
+          <t>2026-09-18T18:03:26+07:00</t>
         </is>
       </c>
     </row>
@@ -60095,7 +60218,7 @@
         <v>1.861</v>
       </c>
       <c r="AI207" t="n">
-        <v>18205.905</v>
+        <v>18205.90499999999</v>
       </c>
       <c r="AJ207" t="n">
         <v>-11.997</v>
@@ -72701,7 +72824,7 @@
       </c>
       <c r="CE90" t="inlineStr">
         <is>
-          <t>2026-09-18T16:44:46+07:00</t>
+          <t>2026-09-18T17:53:32+07:00</t>
         </is>
       </c>
     </row>
@@ -74586,7 +74709,7 @@
       </c>
       <c r="CE106" t="inlineStr">
         <is>
-          <t>2026-09-18T16:46:20+07:00</t>
+          <t>2026-09-18T17:55:07+07:00</t>
         </is>
       </c>
     </row>
@@ -76758,7 +76881,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="AB123" t="n">
@@ -76833,6 +76956,24 @@
       <c r="AY123" t="n">
         <v>248.2</v>
       </c>
+      <c r="BU123" t="n">
+        <v>12492</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>11457</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>1035</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>2525671</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>2515279</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>-3879</v>
+      </c>
       <c r="CD123" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất Quý 1 năm 2024</t>
@@ -76840,7 +76981,7 @@
       </c>
       <c r="CE123" t="inlineStr">
         <is>
-          <t>2026-09-18T16:47:58+07:00</t>
+          <t>2026-09-18T17:56:46+07:00</t>
         </is>
       </c>
     </row>
@@ -77702,7 +77843,7 @@
       </c>
       <c r="CE131" t="inlineStr">
         <is>
-          <t>2026-09-18T16:49:11+07:00</t>
+          <t>2026-09-18T17:57:55+07:00</t>
         </is>
       </c>
     </row>
@@ -78492,7 +78633,7 @@
       </c>
       <c r="CE139" t="inlineStr">
         <is>
-          <t>2026-09-18T16:49:58+07:00</t>
+          <t>2026-09-18T17:58:41+07:00</t>
         </is>
       </c>
     </row>
@@ -83927,7 +84068,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="AB179" t="n">
@@ -84002,6 +84143,15 @@
       <c r="AY179" t="n">
         <v>21445.743</v>
       </c>
+      <c r="CA179" t="n">
+        <v>-433.029</v>
+      </c>
+      <c r="CB179" t="n">
+        <v>17.845</v>
+      </c>
+      <c r="CC179" t="n">
+        <v>-662.6849999999999</v>
+      </c>
       <c r="CD179" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2024</t>
@@ -84009,7 +84159,7 @@
       </c>
       <c r="CE179" t="inlineStr">
         <is>
-          <t>2026-09-18T16:52:58+07:00</t>
+          <t>2026-09-18T18:01:54+07:00</t>
         </is>
       </c>
     </row>
@@ -84947,7 +85097,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="AB187" t="n">
@@ -85022,6 +85172,33 @@
       <c r="AY187" t="n">
         <v>7837.006</v>
       </c>
+      <c r="BU187" t="n">
+        <v>136890.862</v>
+      </c>
+      <c r="BV187" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW187" t="n">
+        <v>136890.862</v>
+      </c>
+      <c r="BX187" t="n">
+        <v>2722.808</v>
+      </c>
+      <c r="BY187" t="n">
+        <v>3164.379</v>
+      </c>
+      <c r="BZ187" t="n">
+        <v>-441.571</v>
+      </c>
+      <c r="CA187" t="n">
+        <v>6.061</v>
+      </c>
+      <c r="CB187" t="n">
+        <v>107811.536</v>
+      </c>
+      <c r="CC187" t="n">
+        <v>-107805.475</v>
+      </c>
       <c r="CD187" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 1 năm 2024</t>
@@ -85029,7 +85206,7 @@
       </c>
       <c r="CE187" t="inlineStr">
         <is>
-          <t>2026-09-18T16:54:28+07:00</t>
+          <t>2026-09-18T18:03:26+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -38222,7 +38222,7 @@
       </c>
       <c r="BL51" t="inlineStr">
         <is>
-          <t>2026-09-18T14:50:29+07:00</t>
+          <t>2026-09-18T18:42:35+07:00</t>
         </is>
       </c>
     </row>
@@ -39252,7 +39252,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -39262,12 +39262,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -39292,16 +39292,16 @@
         <v>109262.475</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>188322</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>30.158</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>32.425</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>51.972</v>
       </c>
       <c r="AF59" t="n">
         <v>5.653</v>
@@ -39354,6 +39354,47 @@
       <c r="AV59" t="n">
         <v>-9.845000000000001</v>
       </c>
+      <c r="AW59" t="n">
+        <v>704344682</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>855914052</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>50440285</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>1275056</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>51715341</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>51851325</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>135984</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>7.342</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>8281.829</v>
+      </c>
+      <c r="BF59" t="n">
+        <v>98155.47199999999</v>
+      </c>
+      <c r="BG59" t="n">
+        <v>257.42</v>
+      </c>
+      <c r="BH59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="BI59" t="n">
+        <v>5171534.1</v>
+      </c>
       <c r="BJ59" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -39366,7 +39407,7 @@
       </c>
       <c r="BL59" t="inlineStr">
         <is>
-          <t>2026-09-18T14:52:58+07:00</t>
+          <t>2026-09-18T18:44:26+07:00</t>
         </is>
       </c>
     </row>
@@ -42954,7 +42995,7 @@
       </c>
       <c r="BL83" t="inlineStr">
         <is>
-          <t>2026-09-18T14:58:58+07:00</t>
+          <t>2026-09-18T18:47:22+07:00</t>
         </is>
       </c>
     </row>
@@ -43875,7 +43916,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -43962,6 +44003,47 @@
       <c r="AV91" t="n">
         <v>-53.373</v>
       </c>
+      <c r="AW91" t="n">
+        <v>66583.122</v>
+      </c>
+      <c r="AX91" t="n">
+        <v>64169.958</v>
+      </c>
+      <c r="AY91" t="n">
+        <v>5413.161</v>
+      </c>
+      <c r="AZ91" t="n">
+        <v>-348.976</v>
+      </c>
+      <c r="BA91" t="n">
+        <v>5064.188</v>
+      </c>
+      <c r="BB91" t="n">
+        <v>5064.188</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>7.606</v>
+      </c>
+      <c r="BE91" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="BF91" t="n">
+        <v>14.947</v>
+      </c>
+      <c r="BG91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH91" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="BI91" t="n">
+        <v>506.419</v>
+      </c>
       <c r="BJ91" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -43974,7 +44056,7 @@
       </c>
       <c r="BL91" t="inlineStr">
         <is>
-          <t>2026-09-18T15:01:04+07:00</t>
+          <t>2026-09-18T18:49:47+07:00</t>
         </is>
       </c>
     </row>
@@ -45022,7 +45104,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -45109,6 +45191,47 @@
       <c r="AV99" t="n">
         <v>-16.117</v>
       </c>
+      <c r="AW99" t="n">
+        <v>2436.669</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>5757.617</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>-3290.948</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>50.922</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>-3240.026</v>
+      </c>
+      <c r="BB99" t="n">
+        <v>70.176</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>3310.202</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>-132.969</v>
+      </c>
+      <c r="BE99" t="n">
+        <v>-1.415</v>
+      </c>
+      <c r="BF99" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="BG99" t="n">
+        <v>19.537</v>
+      </c>
+      <c r="BH99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="BI99" t="n">
+        <v>-324.003</v>
+      </c>
       <c r="BJ99" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -45121,7 +45244,7 @@
       </c>
       <c r="BL99" t="inlineStr">
         <is>
-          <t>2026-09-18T15:03:23+07:00</t>
+          <t>2026-09-18T18:52:23+07:00</t>
         </is>
       </c>
     </row>
@@ -51447,7 +51570,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="H148" t="n">
@@ -51534,6 +51657,47 @@
       <c r="AV148" t="n">
         <v>10.578</v>
       </c>
+      <c r="AW148" t="n">
+        <v>57.276</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>6159.743</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>-408.755</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>-3773.406</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>-2295.458</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>7.201</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>2302.659</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>-4007.714</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>-0.8179999999999999</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>7.027</v>
+      </c>
+      <c r="BH148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="BI148" t="n">
+        <v>-229.546</v>
+      </c>
       <c r="BJ148" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -51546,7 +51710,7 @@
       </c>
       <c r="BL148" t="inlineStr">
         <is>
-          <t>2026-09-18T15:15:05+07:00</t>
+          <t>2026-09-18T18:55:11+07:00</t>
         </is>
       </c>
     </row>
@@ -56371,7 +56535,7 @@
       </c>
       <c r="BL180" t="inlineStr">
         <is>
-          <t>2026-09-18T15:26:58+07:00</t>
+          <t>2026-09-18T19:02:27+07:00</t>
         </is>
       </c>
     </row>
@@ -59737,7 +59901,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="H204" t="n">
@@ -59824,6 +59988,47 @@
       <c r="AV204" t="n">
         <v>-14.733</v>
       </c>
+      <c r="AW204" t="n">
+        <v>42150.18</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>41735.951</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>-58.814</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>268.788</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>683.0170000000001</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>683.0170000000001</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="BI204" t="n">
+        <v>68.30200000000001</v>
+      </c>
       <c r="BJ204" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -59836,7 +60041,7 @@
       </c>
       <c r="BL204" t="inlineStr">
         <is>
-          <t>2026-09-18T15:32:54+07:00</t>
+          <t>2026-09-18T19:04:54+07:00</t>
         </is>
       </c>
     </row>
@@ -67888,7 +68093,7 @@
       </c>
       <c r="CE51" t="inlineStr">
         <is>
-          <t>2026-09-18T14:50:29+07:00</t>
+          <t>2026-09-18T18:42:35+07:00</t>
         </is>
       </c>
     </row>
@@ -68787,7 +68992,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -68797,13 +69002,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>missing</t>
-        </is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>133137</v>
+      </c>
+      <c r="H59" t="n">
+        <v>37203</v>
+      </c>
+      <c r="I59" t="n">
+        <v>17982</v>
+      </c>
+      <c r="J59" t="n">
+        <v>14154</v>
+      </c>
+      <c r="K59" t="n">
+        <v>122061</v>
+      </c>
+      <c r="L59" t="n">
+        <v>97855</v>
+      </c>
+      <c r="M59" t="n">
+        <v>17645</v>
       </c>
       <c r="AB59" t="n">
         <v>-186493.134</v>
@@ -68877,6 +69103,33 @@
       <c r="AY59" t="n">
         <v>3.858</v>
       </c>
+      <c r="BU59" t="n">
+        <v>658535334</v>
+      </c>
+      <c r="BV59" t="n">
+        <v>806710365</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>51824969</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>44956347</v>
+      </c>
+      <c r="BY59" t="n">
+        <v>46367387</v>
+      </c>
+      <c r="BZ59" t="n">
+        <v>-135984</v>
+      </c>
+      <c r="CA59" t="n">
+        <v>23634</v>
+      </c>
+      <c r="CB59" t="n">
+        <v>2010140</v>
+      </c>
+      <c r="CC59" t="n">
+        <v>23149</v>
+      </c>
       <c r="CD59" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -68884,7 +69137,7 @@
       </c>
       <c r="CE59" t="inlineStr">
         <is>
-          <t>2026-09-18T14:52:58+07:00</t>
+          <t>2026-09-18T18:44:26+07:00</t>
         </is>
       </c>
     </row>
@@ -72139,7 +72392,7 @@
       </c>
       <c r="CE83" t="inlineStr">
         <is>
-          <t>2026-09-18T14:58:58+07:00</t>
+          <t>2026-09-18T18:47:22+07:00</t>
         </is>
       </c>
     </row>
@@ -72856,7 +73109,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="AB91" t="n">
@@ -72931,6 +73184,33 @@
       <c r="AY91" t="n">
         <v>49130.755</v>
       </c>
+      <c r="BU91" t="n">
+        <v>32833.823</v>
+      </c>
+      <c r="BV91" t="n">
+        <v>30589.584</v>
+      </c>
+      <c r="BW91" t="n">
+        <v>881.3200000000001</v>
+      </c>
+      <c r="BX91" t="n">
+        <v>321.626</v>
+      </c>
+      <c r="BY91" t="n">
+        <v>1297.821</v>
+      </c>
+      <c r="BZ91" t="n">
+        <v>144.886</v>
+      </c>
+      <c r="CA91" t="n">
+        <v>136.112</v>
+      </c>
+      <c r="CB91" t="n">
+        <v>197.574</v>
+      </c>
+      <c r="CC91" t="n">
+        <v>5.888</v>
+      </c>
       <c r="CD91" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -72938,7 +73218,7 @@
       </c>
       <c r="CE91" t="inlineStr">
         <is>
-          <t>2026-09-18T15:01:04+07:00</t>
+          <t>2026-09-18T18:49:47+07:00</t>
         </is>
       </c>
     </row>
@@ -73879,7 +74159,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="AB99" t="n">
@@ -73954,6 +74234,33 @@
       <c r="AY99" t="n">
         <v>471.129</v>
       </c>
+      <c r="BU99" t="n">
+        <v>2344.576</v>
+      </c>
+      <c r="BV99" t="n">
+        <v>5703.149</v>
+      </c>
+      <c r="BW99" t="n">
+        <v>-3310.202</v>
+      </c>
+      <c r="BX99" t="n">
+        <v>22.896</v>
+      </c>
+      <c r="BY99" t="n">
+        <v>6.989</v>
+      </c>
+      <c r="BZ99" t="n">
+        <v>15.907</v>
+      </c>
+      <c r="CA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB99" t="n">
+        <v>47.479</v>
+      </c>
+      <c r="CC99" t="n">
+        <v>2.551</v>
+      </c>
       <c r="CD99" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -73961,7 +74268,7 @@
       </c>
       <c r="CE99" t="inlineStr">
         <is>
-          <t>2026-09-18T15:03:23+07:00</t>
+          <t>2026-09-18T18:52:23+07:00</t>
         </is>
       </c>
     </row>
@@ -79628,7 +79935,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="AB148" t="n">
@@ -79703,6 +80010,24 @@
       <c r="AY148" t="n">
         <v>5164.894</v>
       </c>
+      <c r="BU148" t="n">
+        <v>5.609</v>
+      </c>
+      <c r="BV148" t="n">
+        <v>6115.277</v>
+      </c>
+      <c r="BW148" t="n">
+        <v>-2302.659</v>
+      </c>
+      <c r="BX148" t="n">
+        <v>51.667</v>
+      </c>
+      <c r="BY148" t="n">
+        <v>44.466</v>
+      </c>
+      <c r="BZ148" t="n">
+        <v>7.201</v>
+      </c>
       <c r="CD148" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -79710,7 +80035,7 @@
       </c>
       <c r="CE148" t="inlineStr">
         <is>
-          <t>2026-09-18T15:15:05+07:00</t>
+          <t>2026-09-18T18:55:11+07:00</t>
         </is>
       </c>
     </row>
@@ -84273,7 +84598,7 @@
       </c>
       <c r="CE180" t="inlineStr">
         <is>
-          <t>2026-09-18T15:26:58+07:00</t>
+          <t>2026-09-18T19:02:27+07:00</t>
         </is>
       </c>
     </row>
@@ -87155,7 +87480,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="AB204" t="n">
@@ -87230,6 +87555,24 @@
       <c r="AY204" t="n">
         <v>5529.611</v>
       </c>
+      <c r="BU204" t="n">
+        <v>41781.83</v>
+      </c>
+      <c r="BV204" t="n">
+        <v>41304.07</v>
+      </c>
+      <c r="BW204" t="n">
+        <v>678.342</v>
+      </c>
+      <c r="CA204" t="n">
+        <v>368.35</v>
+      </c>
+      <c r="CB204" t="n">
+        <v>431.881</v>
+      </c>
+      <c r="CC204" t="n">
+        <v>4.675</v>
+      </c>
       <c r="CD204" t="inlineStr">
         <is>
           <t>Báo cáo tài chính hợp nhất quý 2 năm 2024 (đã soát xét)</t>
@@ -87237,7 +87580,7 @@
       </c>
       <c r="CE204" t="inlineStr">
         <is>
-          <t>2026-09-18T15:32:54+07:00</t>
+          <t>2026-09-18T19:04:54+07:00</t>
         </is>
       </c>
     </row>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -6187,7 +6187,7 @@
         <v>-0.341</v>
       </c>
       <c r="L57" t="n">
-        <v>382141.116</v>
+        <v>365933.167</v>
       </c>
     </row>
     <row r="58">
@@ -6211,7 +6211,7 @@
         <v>350.3</v>
       </c>
       <c r="L58" t="n">
-        <v>324.1</v>
+        <v>319.7</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
         <v>26044.82</v>
       </c>
       <c r="EA24" t="n">
-        <v>25879.19</v>
+        <v>25964.16</v>
       </c>
     </row>
     <row r="25">
@@ -9529,7 +9529,7 @@
         <v>11.29118768979197</v>
       </c>
       <c r="EA39" t="n">
-        <v>10.87364191092571</v>
+        <v>10.71844462279004</v>
       </c>
     </row>
     <row r="40">
@@ -9550,7 +9550,7 @@
         <v>1.753517800622156</v>
       </c>
       <c r="EA40" t="n">
-        <v>1.688673076051811</v>
+        <v>1.681230884357004</v>
       </c>
     </row>
     <row r="41">
@@ -9571,7 +9571,7 @@
         <v>12.46</v>
       </c>
       <c r="EA41" t="n">
-        <v>12.48</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="42">
@@ -9592,7 +9592,7 @@
         <v>2.06</v>
       </c>
       <c r="EA42" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="43">
@@ -21429,7 +21429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PO47"/>
+  <dimension ref="A1:PV47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21863,6 +21863,13 @@
     <col width="12" customWidth="1" min="429" max="429"/>
     <col width="12" customWidth="1" min="430" max="430"/>
     <col width="12" customWidth="1" min="431" max="431"/>
+    <col width="12" customWidth="1" min="432" max="432"/>
+    <col width="12" customWidth="1" min="433" max="433"/>
+    <col width="12" customWidth="1" min="434" max="434"/>
+    <col width="12" customWidth="1" min="435" max="435"/>
+    <col width="12" customWidth="1" min="436" max="436"/>
+    <col width="12" customWidth="1" min="437" max="437"/>
+    <col width="12" customWidth="1" min="438" max="438"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24021,6 +24028,41 @@
           <t>2026-09-11</t>
         </is>
       </c>
+      <c r="PP1" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="PQ1" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="PR1" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="PS1" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="PT1" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="PU1" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="PV1" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24150,6 +24192,9 @@
       <c r="PM3" t="n">
         <v>109.51</v>
       </c>
+      <c r="PS3" t="n">
+        <v>130.8</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -24222,6 +24267,9 @@
       <c r="PH4" t="n">
         <v>118.07</v>
       </c>
+      <c r="PO4" t="n">
+        <v>118.21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24303,6 +24351,9 @@
       <c r="PN5" t="n">
         <v>367.01</v>
       </c>
+      <c r="PU5" t="n">
+        <v>-358.85</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -24390,6 +24441,9 @@
       <c r="PN6" t="n">
         <v>1.5</v>
       </c>
+      <c r="PU6" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -24477,6 +24531,9 @@
       <c r="PN7" t="n">
         <v>3</v>
       </c>
+      <c r="PU7" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -24564,6 +24621,9 @@
       <c r="PN8" t="n">
         <v>3.8</v>
       </c>
+      <c r="PU8" t="n">
+        <v>5.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -24651,6 +24711,9 @@
       <c r="PN9" t="n">
         <v>5.5</v>
       </c>
+      <c r="PU9" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24738,6 +24801,9 @@
       <c r="PN10" t="n">
         <v>3.7</v>
       </c>
+      <c r="PU10" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24825,6 +24891,9 @@
       <c r="PN11" t="n">
         <v>4.27</v>
       </c>
+      <c r="PU11" t="n">
+        <v>4.29</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24912,6 +24981,9 @@
       <c r="PN12" t="n">
         <v>4.33</v>
       </c>
+      <c r="PU12" t="n">
+        <v>4.34</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -24999,6 +25071,9 @@
       <c r="PN13" t="n">
         <v>4.46</v>
       </c>
+      <c r="PU13" t="n">
+        <v>4.46</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25086,6 +25161,9 @@
       <c r="PN14" t="n">
         <v>4.58</v>
       </c>
+      <c r="PU14" t="n">
+        <v>4.58</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25170,6 +25248,9 @@
       <c r="PN15" t="n">
         <v>-2577.59</v>
       </c>
+      <c r="PU15" t="n">
+        <v>-11853.57</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25326,6 +25407,9 @@
       <c r="PN17" t="n">
         <v>252649.14</v>
       </c>
+      <c r="PU17" t="n">
+        <v>151198.26</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25452,6 +25536,9 @@
       <c r="PO18" t="n">
         <v>2.25</v>
       </c>
+      <c r="PV18" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25578,6 +25665,9 @@
       <c r="PM19" t="n">
         <v>3.73</v>
       </c>
+      <c r="PT19" t="n">
+        <v>3.73</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25662,6 +25752,9 @@
       <c r="DK20" t="n">
         <v>0.48</v>
       </c>
+      <c r="FD20" t="n">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25779,6 +25872,9 @@
       <c r="PM21" t="n">
         <v>4.83</v>
       </c>
+      <c r="PT21" t="n">
+        <v>5.01</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25863,6 +25959,9 @@
       <c r="DK22" t="n">
         <v>2.52</v>
       </c>
+      <c r="FD22" t="n">
+        <v>3.18</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25947,6 +26046,9 @@
       <c r="DK23" t="n">
         <v>1.42</v>
       </c>
+      <c r="FD23" t="n">
+        <v>2.94</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -26031,6 +26133,9 @@
       <c r="DK24" t="n">
         <v>4.52</v>
       </c>
+      <c r="FD24" t="n">
+        <v>4.99</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -26292,6 +26397,9 @@
       <c r="DK27" t="n">
         <v>2.68</v>
       </c>
+      <c r="FD27" t="n">
+        <v>3.35</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -26376,6 +26484,9 @@
       <c r="DK28" t="n">
         <v>2.91</v>
       </c>
+      <c r="FD28" t="n">
+        <v>2.45</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -26721,6 +26832,9 @@
       <c r="DK32" t="n">
         <v>0.58</v>
       </c>
+      <c r="FD32" t="n">
+        <v>1.42</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -26838,6 +26952,9 @@
       <c r="PM33" t="n">
         <v>3.95</v>
       </c>
+      <c r="PT33" t="n">
+        <v>4.14</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26955,6 +27072,9 @@
       <c r="PM34" t="n">
         <v>4.17</v>
       </c>
+      <c r="PT34" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -27072,6 +27192,9 @@
       <c r="PM35" t="n">
         <v>4.43</v>
       </c>
+      <c r="PT35" t="n">
+        <v>4.74</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -27189,6 +27312,9 @@
       <c r="PM36" t="n">
         <v>4.61</v>
       </c>
+      <c r="PT36" t="n">
+        <v>4.86</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -27306,6 +27432,9 @@
       <c r="PM37" t="n">
         <v>5.28</v>
       </c>
+      <c r="PT37" t="n">
+        <v>5.35</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -27843,6 +27972,9 @@
       <c r="PM43" t="n">
         <v>0.4</v>
       </c>
+      <c r="PT43" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -27960,6 +28092,9 @@
       <c r="PM44" t="n">
         <v>0.88</v>
       </c>
+      <c r="PT44" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -28047,6 +28182,9 @@
       <c r="DK45" t="n">
         <v>1.96</v>
       </c>
+      <c r="FD45" t="n">
+        <v>3.23</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -28989,6 +29127,9 @@
       <c r="PN46" t="n">
         <v>0</v>
       </c>
+      <c r="PU46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -29926,6 +30067,9 @@
         <v>0</v>
       </c>
       <c r="PN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="PU47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29940,7 +30084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -29954,6 +30098,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30012,6 +30157,11 @@
           <t>2026-W37</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-W38</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30048,6 +30198,9 @@
       <c r="K2" t="n">
         <v>5.9</v>
       </c>
+      <c r="L2" t="n">
+        <v>5.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30105,6 +30258,9 @@
       <c r="K4" t="n">
         <v>6.2</v>
       </c>
+      <c r="L4" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -30141,6 +30297,9 @@
       <c r="K5" t="n">
         <v>7.15</v>
       </c>
+      <c r="L5" t="n">
+        <v>7.15</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -30177,6 +30336,9 @@
       <c r="K6" t="n">
         <v>6.15</v>
       </c>
+      <c r="L6" t="n">
+        <v>6.15</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -30228,6 +30390,9 @@
       <c r="K8" t="n">
         <v>4.5</v>
       </c>
+      <c r="L8" t="n">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -30264,6 +30429,9 @@
       <c r="K9" t="n">
         <v>6.42</v>
       </c>
+      <c r="L9" t="n">
+        <v>6.89</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -30360,6 +30528,9 @@
       <c r="K14" t="n">
         <v>7.76</v>
       </c>
+      <c r="L14" t="n">
+        <v>7.47</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30396,6 +30567,9 @@
       <c r="K15" t="n">
         <v>8.119999999999999</v>
       </c>
+      <c r="L15" t="n">
+        <v>8.119999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -30449,6 +30623,9 @@
       </c>
       <c r="K17" t="n">
         <v>316</v>
+      </c>
+      <c r="L17" t="n">
+        <v>323</v>
       </c>
     </row>
   </sheetData>

--- a/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
+++ b/Bao cao/VIMO/VIMO_Lich_Su_Chi_So.xlsx
@@ -35558,7 +35558,7 @@
       </c>
       <c r="BL31" t="inlineStr">
         <is>
-          <t>2026-09-18T19:13:58+07:00</t>
+          <t>2026-09-18T20:55:56+07:00</t>
         </is>
       </c>
     </row>
@@ -46313,7 +46313,7 @@
       </c>
       <c r="BL103" t="inlineStr">
         <is>
-          <t>2026-09-18T19:24:17+07:00</t>
+          <t>2026-09-18T20:58:41+07:00</t>
         </is>
       </c>
     </row>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="BL140" t="inlineStr">
         <is>
-          <t>2026-09-18T19:29:28+07:00</t>
+          <t>2026-09-18T21:00:21+07:00</t>
         </is>
       </c>
     </row>
@@ -52827,7 +52827,7 @@
       </c>
       <c r="BL149" t="inlineStr">
         <is>
-          <t>2026-09-18T19:30:51+07:00</t>
+          <t>2026-09-18T21:02:27+07:00</t>
         </is>
       </c>
     </row>
@@ -53881,7 +53881,7 @@
       </c>
       <c r="BL158" t="inlineStr">
         <is>
-          <t>2026-09-18T19:31:22+07:00</t>
+          <t>2026-09-18T21:03:12+07:00</t>
         </is>
       </c>
     </row>
@@ -54968,7 +54968,7 @@
       </c>
       <c r="BL167" t="inlineStr">
         <is>
-          <t>2026-09-18T19:33:04+07:00</t>
+          <t>2026-09-18T21:05:47+07:00</t>
         </is>
       </c>
     </row>
@@ -60504,7 +60504,7 @@
       </c>
       <c r="BL203" t="inlineStr">
         <is>
-          <t>2026-09-18T19:39:32+07:00</t>
+          <t>2026-09-18T21:08:45+07:00</t>
         </is>
       </c>
     </row>
@@ -64416,7 +64416,7 @@
       </c>
       <c r="BL230" t="inlineStr">
         <is>
-          <t>2026-09-18T19:41:51+07:00</t>
+          <t>2026-09-18T21:08:49+07:00</t>
         </is>
       </c>
     </row>
@@ -70113,7 +70113,7 @@
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>2026-09-18T19:13:58+07:00</t>
+          <t>2026-09-18T20:55:56+07:00</t>
         </is>
       </c>
     </row>
@@ -79933,7 +79933,7 @@
       </c>
       <c r="CE103" t="inlineStr">
         <is>
-          <t>2026-09-18T19:24:17+07:00</t>
+          <t>2026-09-18T20:58:41+07:00</t>
         </is>
       </c>
     </row>
@@ -85080,7 +85080,7 @@
       </c>
       <c r="CE140" t="inlineStr">
         <is>
-          <t>2026-09-18T19:29:28+07:00</t>
+          <t>2026-09-18T21:00:21+07:00</t>
         </is>
       </c>
     </row>
@@ -85868,7 +85868,7 @@
       </c>
       <c r="CE149" t="inlineStr">
         <is>
-          <t>2026-09-18T19:30:51+07:00</t>
+          <t>2026-09-18T21:02:27+07:00</t>
         </is>
       </c>
     </row>
@@ -86764,7 +86764,7 @@
       </c>
       <c r="CE158" t="inlineStr">
         <is>
-          <t>2026-09-18T19:31:22+07:00</t>
+          <t>2026-09-18T21:03:12+07:00</t>
         </is>
       </c>
     </row>
@@ -87793,7 +87793,7 @@
       </c>
       <c r="CE167" t="inlineStr">
         <is>
-          <t>2026-09-18T19:33:04+07:00</t>
+          <t>2026-09-18T21:05:47+07:00</t>
         </is>
       </c>
     </row>
@@ -93160,7 +93160,7 @@
       </c>
       <c r="CE203" t="inlineStr">
         <is>
-          <t>2026-09-18T19:39:32+07:00</t>
+          <t>2026-09-18T21:08:45+07:00</t>
         </is>
       </c>
     </row>
@@ -96602,7 +96602,7 @@
       </c>
       <c r="CE230" t="inlineStr">
         <is>
-          <t>2026-09-18T19:41:51+07:00</t>
+          <t>2026-09-18T21:08:49+07:00</t>
         </is>
       </c>
     </row>
